--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -4584,7 +4584,7 @@
         <v>34.39</v>
       </c>
       <c r="H2" t="n">
-        <v>41.1466</v>
+        <v>33.8614</v>
       </c>
       <c r="I2" t="n">
         <v>26.9</v>
@@ -4636,7 +4636,7 @@
         <v>63.41</v>
       </c>
       <c r="H3" t="n">
-        <v>93.9337</v>
+        <v>90.3134</v>
       </c>
       <c r="I3" t="n">
         <v>89.5</v>
@@ -4688,7 +4688,7 @@
         <v>57.32</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5619</v>
+        <v>4.4773</v>
       </c>
       <c r="I4" t="n">
         <v>67.8</v>
@@ -4740,7 +4740,7 @@
         <v>47.63</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1192</v>
+        <v>-0.369</v>
       </c>
       <c r="I5" t="n">
         <v>68.90000000000001</v>
@@ -4792,7 +4792,7 @@
         <v>66.18000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>10.0135</v>
+        <v>10.3596</v>
       </c>
       <c r="I6" t="n">
         <v>119</v>
@@ -4844,7 +4844,7 @@
         <v>66.06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2966</v>
+        <v>2.2045</v>
       </c>
       <c r="I7" t="n">
         <v>105.8</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,61 +476,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>219</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="F2" t="n">
-        <v>332</v>
+        <v>507</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.101</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71.5</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>4.53</v>
       </c>
       <c r="F3" t="n">
-        <v>321</v>
+        <v>487</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.686</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55.9</v>
+        <v>210</v>
       </c>
       <c r="E4" t="n">
-        <v>4.49</v>
+        <v>6.6</v>
       </c>
       <c r="F4" t="n">
-        <v>285</v>
+        <v>428</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.942</v>
+        <v>2.402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>173</v>
+        <v>301</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.9</v>
+        <v>3.26</v>
       </c>
       <c r="F5" t="n">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.945</v>
+        <v>5.474</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.64</v>
+        <v>-5.03</v>
       </c>
       <c r="F6" t="n">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,101 +640,101 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.008</v>
+        <v>2.596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>197</v>
+        <v>19.85</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6</v>
+        <v>-5.48</v>
       </c>
       <c r="F7" t="n">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.902</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57.4</v>
+        <v>36.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1.95</v>
+        <v>-4.47</v>
       </c>
       <c r="F8" t="n">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.758</v>
+        <v>1.245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>53.8</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.42</v>
+        <v>-3.76</v>
       </c>
       <c r="F9" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14.857</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-1.74</v>
       </c>
       <c r="F10" t="n">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.449</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>94.2</v>
+        <v>1975</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>-1</v>
       </c>
       <c r="F11" t="n">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.838</v>
+        <v>72.42400000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="E12" t="n">
-        <v>0.21</v>
+        <v>2.44</v>
       </c>
       <c r="F12" t="n">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.483</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>331.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2.07</v>
+        <v>-1.92</v>
       </c>
       <c r="F13" t="n">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.611</v>
+        <v>9.455</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1995</v>
+        <v>23.95</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.99</v>
+        <v>-0.21</v>
       </c>
       <c r="F14" t="n">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72.789</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>-1.65</v>
       </c>
       <c r="F15" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.644</v>
+        <v>14.617</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>393</v>
+        <v>93</v>
       </c>
       <c r="E16" t="n">
-        <v>1.55</v>
+        <v>-1.27</v>
       </c>
       <c r="F16" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.595</v>
+        <v>1.822</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>1425</v>
       </c>
       <c r="E17" t="n">
-        <v>0.13</v>
+        <v>-0.35</v>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.28</v>
+        <v>18.277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>338</v>
+        <v>38.75</v>
       </c>
       <c r="E18" t="n">
-        <v>4.97</v>
+        <v>1.71</v>
       </c>
       <c r="F18" t="n">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9.699</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>136</v>
+        <v>70.7</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.45</v>
+        <v>-0.98</v>
       </c>
       <c r="F19" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,339 +1082,339 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.025</v>
+        <v>1.184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>387.5</v>
+        <v>212.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.39</v>
+        <v>-2.97</v>
       </c>
       <c r="F20" t="n">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10.029</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>291.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.02</v>
+        <v>-2.26</v>
       </c>
       <c r="F21" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.876</v>
+        <v>1.974</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2770</v>
+        <v>370.5</v>
       </c>
       <c r="E22" t="n">
-        <v>7.57</v>
+        <v>-4.39</v>
       </c>
       <c r="F22" t="n">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9.210000000000001</v>
+        <v>9.679</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>40.55</v>
+        <v>386.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="F23" t="n">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.909</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>481.5</v>
+        <v>40.2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.48</v>
+        <v>-0.86</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.742</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51.6</v>
+        <v>169</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.37</v>
+        <v>-2.31</v>
       </c>
       <c r="F25" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.727</v>
+        <v>5.931</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1430</v>
+        <v>30.3</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.35</v>
+        <v>-1.46</v>
       </c>
       <c r="F26" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.627</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.47</v>
+        <v>-0.74</v>
       </c>
       <c r="F27" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.852</v>
+        <v>4.811</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1945</v>
+        <v>477.5</v>
       </c>
       <c r="E28" t="n">
-        <v>4.01</v>
+        <v>-0.83</v>
       </c>
       <c r="F28" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>22.989</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>204.5</v>
+        <v>291.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.62</v>
+        <v>2.1</v>
       </c>
       <c r="F29" t="n">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.346</v>
+        <v>5.763</v>
       </c>
     </row>
     <row r="30">
@@ -1442,47 +1442,47 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76.7</v>
+        <v>74.8</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.13</v>
+        <v>-2.48</v>
       </c>
       <c r="F30" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>23.338</v>
+        <v>23.009</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1315</v>
+        <v>124.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="F31" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.65</v>
+        <v>24.453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>122.5</v>
+        <v>2645</v>
       </c>
       <c r="E32" t="n">
-        <v>3.81</v>
+        <v>-4.51</v>
       </c>
       <c r="F32" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23.503</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20.75</v>
+        <v>3440</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.35</v>
+        <v>-1.43</v>
       </c>
       <c r="F33" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,101 +1558,101 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.738</v>
+        <v>6.507</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>285.5</v>
+        <v>116</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.19</v>
+        <v>5.45</v>
       </c>
       <c r="F34" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5.49</v>
+        <v>27.193</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30.75</v>
+        <v>1900</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.16</v>
+        <v>-2.31</v>
       </c>
       <c r="F35" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.117</v>
+        <v>22.493</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="E36" t="n">
-        <v>2.19</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.953</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1890</v>
+        <v>20.25</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.82</v>
+        <v>-2.41</v>
       </c>
       <c r="F37" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,203 +1694,203 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>16.58</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>217.5</v>
+        <v>440</v>
       </c>
       <c r="E38" t="n">
-        <v>9.85</v>
+        <v>-3.3</v>
       </c>
       <c r="F38" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.279</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>71.40000000000001</v>
+        <v>1285</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.16</v>
+        <v>-2.28</v>
       </c>
       <c r="F39" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.157</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>65.40000000000001</v>
+        <v>316</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.15</v>
+        <v>-3.36</v>
       </c>
       <c r="F40" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>14.801</v>
+        <v>6.657</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>258</v>
+        <v>129.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F41" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.084</v>
+        <v>5.187</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3490</v>
+        <v>166.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0.29</v>
+        <v>-0.89</v>
       </c>
       <c r="F42" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6.681</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>73.90000000000001</v>
+        <v>285</v>
       </c>
       <c r="E43" t="n">
-        <v>0.82</v>
+        <v>-0.18</v>
       </c>
       <c r="F43" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,177 +1898,177 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.506</v>
+        <v>28.187</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>455</v>
+        <v>253</v>
       </c>
       <c r="E44" t="n">
-        <v>0.55</v>
+        <v>-1.94</v>
       </c>
       <c r="F44" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.56</v>
+        <v>3.821</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>285.5</v>
+        <v>204.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>27.882</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>110</v>
+        <v>44.75</v>
       </c>
       <c r="E46" t="n">
-        <v>1.85</v>
+        <v>-3.24</v>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>25.296</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2530</v>
+        <v>64.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1.81</v>
+        <v>-1.38</v>
       </c>
       <c r="F47" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.558</v>
+        <v>13.495</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>38.1</v>
+        <v>1920</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.26</v>
+        <v>1.59</v>
       </c>
       <c r="F48" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.191</v>
+        <v>15.805</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E49" t="n">
-        <v>0.43</v>
+        <v>-1.69</v>
       </c>
       <c r="F49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,109 +2102,109 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.047</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>46.25</v>
+        <v>218.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.32</v>
+        <v>4.05</v>
       </c>
       <c r="F50" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.935</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>133.5</v>
+        <v>71.7</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.11</v>
+        <v>-2.98</v>
       </c>
       <c r="F51" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5.546</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>210</v>
+        <v>2545</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.33</v>
+        <v>0.59</v>
       </c>
       <c r="F52" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.591</v>
+        <v>4.456</v>
       </c>
     </row>
   </sheetData>
@@ -2280,75 +2280,75 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>57.63</v>
+        <v>64.72</v>
       </c>
       <c r="F2" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.558</v>
+        <v>4.456</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.9</v>
+        <v>58.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1.16</v>
+        <v>0.73</v>
       </c>
       <c r="G3" t="n">
-        <v>9.699</v>
+        <v>27.193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43.23</v>
+        <v>49.32</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>25.296</v>
+        <v>9.455</v>
       </c>
     </row>
     <row r="5">
@@ -2373,432 +2373,432 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39.45</v>
+        <v>44.29</v>
       </c>
       <c r="F5" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.157</v>
+        <v>1.184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.98</v>
+        <v>35.41</v>
       </c>
       <c r="F6" t="n">
-        <v>0.89</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>22.989</v>
+        <v>4.335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30.91</v>
+        <v>29.69</v>
       </c>
       <c r="F7" t="n">
-        <v>1.24</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>10.029</v>
+        <v>22.493</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.55</v>
+        <v>27.32</v>
       </c>
       <c r="F8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="G8" t="n">
-        <v>18.627</v>
+        <v>9.679</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21.7</v>
+        <v>25.55</v>
       </c>
       <c r="F9" t="n">
-        <v>0.97</v>
+        <v>1.23</v>
       </c>
       <c r="G9" t="n">
-        <v>2.727</v>
+        <v>18.277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.13</v>
+        <v>21.15</v>
       </c>
       <c r="F10" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>6.953</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.89</v>
+        <v>19.49</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="G11" t="n">
-        <v>4.279</v>
+        <v>23.009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.46</v>
+        <v>18.35</v>
       </c>
       <c r="F12" t="n">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="G12" t="n">
-        <v>23.338</v>
+        <v>6.657</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.39</v>
+        <v>18.01</v>
       </c>
       <c r="F13" t="n">
-        <v>1.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>72.789</v>
+        <v>24.453</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.609999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>0.74</v>
       </c>
       <c r="G14" t="n">
-        <v>1.942</v>
+        <v>28.187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.720000000000001</v>
+        <v>13.51</v>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="G15" t="n">
-        <v>14.857</v>
+        <v>72.42400000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.41</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>2.01</v>
       </c>
       <c r="G16" t="n">
-        <v>23.503</v>
+        <v>2.402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.359999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.86</v>
+        <v>1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>1.738</v>
+        <v>5.474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.12</v>
+        <v>9.15</v>
       </c>
       <c r="F18" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>5.945</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,339 +2807,339 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.05</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>4.876</v>
+        <v>14.617</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.96</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.83</v>
+        <v>2.15</v>
       </c>
       <c r="G20" t="n">
-        <v>27.882</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.17</v>
+        <v>7.37</v>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>0.96</v>
       </c>
       <c r="G21" t="n">
-        <v>0.758</v>
+        <v>5.763</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.05</v>
+        <v>6.86</v>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>0.85</v>
       </c>
       <c r="G22" t="n">
-        <v>2.008</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.24</v>
+        <v>6.32</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>1.935</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.14</v>
+        <v>6.17</v>
       </c>
       <c r="F24" t="n">
-        <v>1.48</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>1.902</v>
+        <v>6.507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.8</v>
+        <v>5.64</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="G25" t="n">
-        <v>6.681</v>
+        <v>3.821</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.59</v>
+        <v>5.33</v>
       </c>
       <c r="F26" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="G26" t="n">
-        <v>9.210000000000001</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.58</v>
+        <v>5.13</v>
       </c>
       <c r="F27" t="n">
-        <v>0.72</v>
+        <v>1.85</v>
       </c>
       <c r="G27" t="n">
-        <v>4.084</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.56</v>
+        <v>4.97</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="G28" t="n">
-        <v>0.191</v>
+        <v>5.931</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.94</v>
+        <v>3.28</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.65</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3148,695 +3148,695 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.37</v>
+        <v>2.91</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="G30" t="n">
-        <v>0.909</v>
+        <v>1.974</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.23</v>
+        <v>2.57</v>
       </c>
       <c r="F31" t="n">
-        <v>0.96</v>
+        <v>1.72</v>
       </c>
       <c r="G31" t="n">
-        <v>0.611</v>
+        <v>2.596</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.63</v>
+        <v>2.38</v>
       </c>
       <c r="F32" t="n">
-        <v>1.39</v>
+        <v>0.98</v>
       </c>
       <c r="G32" t="n">
-        <v>0.483</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.26</v>
+        <v>1.61</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>1.19</v>
       </c>
       <c r="G33" t="n">
-        <v>1.595</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.21</v>
+        <v>1.12</v>
       </c>
       <c r="F34" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="G34" t="n">
-        <v>1.838</v>
+        <v>4.811</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="F35" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="G35" t="n">
-        <v>5.025</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.26</v>
+        <v>1.01</v>
       </c>
       <c r="F36" t="n">
         <v>1.17</v>
       </c>
       <c r="G36" t="n">
-        <v>0.449</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.28</v>
+        <v>0.79</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="G37" t="n">
-        <v>2.686</v>
+        <v>15.805</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.52</v>
+        <v>0.76</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G38" t="n">
-        <v>1.28</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.73</v>
+        <v>1.46</v>
       </c>
       <c r="G39" t="n">
-        <v>1.047</v>
+        <v>1.822</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-2.39</v>
+        <v>-1.78</v>
       </c>
       <c r="F40" t="n">
-        <v>0.66</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>2.346</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.61</v>
+        <v>-2.11</v>
       </c>
       <c r="F41" t="n">
-        <v>1.11</v>
+        <v>0.55</v>
       </c>
       <c r="G41" t="n">
-        <v>0.644</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3.02</v>
+        <v>-2.63</v>
       </c>
       <c r="F42" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="G42" t="n">
-        <v>0.506</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.54</v>
+        <v>-3.87</v>
       </c>
       <c r="F43" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="G43" t="n">
-        <v>14.801</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.61</v>
+        <v>-4.88</v>
       </c>
       <c r="F44" t="n">
         <v>1.05</v>
       </c>
       <c r="G44" t="n">
-        <v>0.117</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-4.11</v>
+        <v>-5.02</v>
       </c>
       <c r="F45" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="G45" t="n">
-        <v>0.852</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-4.19</v>
+        <v>-5.22</v>
       </c>
       <c r="F46" t="n">
-        <v>0.92</v>
+        <v>1.31</v>
       </c>
       <c r="G46" t="n">
-        <v>5.49</v>
+        <v>1.245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.65</v>
+        <v>-5.41</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="G47" t="n">
-        <v>5.546</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-5.74</v>
+        <v>-5.7</v>
       </c>
       <c r="F48" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="G48" t="n">
-        <v>16.58</v>
+        <v>13.495</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-6.87</v>
+        <v>-10.53</v>
       </c>
       <c r="F49" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="G49" t="n">
-        <v>1.742</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-9.359999999999999</v>
+        <v>-10.79</v>
       </c>
       <c r="F50" t="n">
-        <v>0.92</v>
+        <v>1.57</v>
       </c>
       <c r="G50" t="n">
-        <v>2.56</v>
+        <v>0.835</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-10.43</v>
+        <v>-11.02</v>
       </c>
       <c r="F51" t="n">
-        <v>1.54</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>0.101</v>
+        <v>2.371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-15.32</v>
+        <v>-11.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="G52" t="n">
-        <v>2.591</v>
+        <v>5.187</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.63</v>
+        <v>64.72</v>
       </c>
       <c r="C2" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>4.558</v>
+        <v>4.456</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.23</v>
+        <v>58.25</v>
       </c>
       <c r="C3" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="D3" t="n">
-        <v>25.296</v>
+        <v>27.193</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.98</v>
+        <v>29.69</v>
       </c>
       <c r="C4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="n">
-        <v>22.989</v>
+        <v>22.493</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,39 +3940,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.91</v>
+        <v>28.78</v>
       </c>
       <c r="C5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="D5" t="n">
-        <v>10.029</v>
+        <v>14.352</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.67333333333333</v>
+        <v>27.32</v>
       </c>
       <c r="C6" t="n">
-        <v>1.186666666666667</v>
+        <v>1.26</v>
       </c>
       <c r="D6" t="n">
-        <v>14.589</v>
+        <v>9.679</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.7</v>
+        <v>21.15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="D7" t="n">
-        <v>2.727</v>
+        <v>2.86</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,74 +3997,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.13</v>
+        <v>20.83</v>
       </c>
       <c r="C8" t="n">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>6.953</v>
+        <v>1.81</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.42</v>
+        <v>19.49</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7450000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.801</v>
+        <v>23.009</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16.835</v>
+        <v>18.35</v>
       </c>
       <c r="C10" t="n">
-        <v>1.295</v>
+        <v>0.91</v>
       </c>
       <c r="D10" t="n">
-        <v>24.572</v>
+        <v>6.657</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12.46</v>
+        <v>18.01</v>
       </c>
       <c r="C11" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>23.338</v>
+        <v>24.453</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,36 +4073,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.41</v>
+        <v>15.26</v>
       </c>
       <c r="C12" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="D12" t="n">
-        <v>23.503</v>
+        <v>24.208</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.359999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="C13" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="D13" t="n">
-        <v>1.738</v>
+        <v>28.187</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,17 +4111,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.96</v>
+        <v>9.15</v>
       </c>
       <c r="C14" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="D14" t="n">
-        <v>27.882</v>
+        <v>0.194</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,74 +4130,74 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.425000000000001</v>
+        <v>7.926666666666666</v>
       </c>
       <c r="C15" t="n">
-        <v>1.01</v>
+        <v>2.003333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>87.59</v>
+        <v>3.967</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.2525</v>
+        <v>6.86</v>
       </c>
       <c r="C16" t="n">
-        <v>1.22</v>
+        <v>0.85</v>
       </c>
       <c r="D16" t="n">
-        <v>26.693</v>
+        <v>1.71</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.174</v>
+        <v>5.33</v>
       </c>
       <c r="C17" t="n">
-        <v>1.454</v>
+        <v>0.97</v>
       </c>
       <c r="D17" t="n">
-        <v>7.18</v>
+        <v>1.574</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.695</v>
+        <v>4.105</v>
       </c>
       <c r="C18" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="n">
-        <v>15.891</v>
+        <v>6.417</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -4206,131 +4206,131 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.56</v>
+        <v>3.9575</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.191</v>
+        <v>26.587</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.35</v>
+        <v>3.905</v>
       </c>
       <c r="C20" t="n">
-        <v>1.406666666666667</v>
+        <v>1.06</v>
       </c>
       <c r="D20" t="n">
-        <v>3.109</v>
+        <v>85.91900000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.94</v>
+        <v>3.465</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="D21" t="n">
-        <v>1.65</v>
+        <v>15.307</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="C22" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="D22" t="n">
-        <v>6.77</v>
+        <v>1.542</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.26</v>
+        <v>2.258</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9</v>
+        <v>1.47</v>
       </c>
       <c r="D23" t="n">
-        <v>1.595</v>
+        <v>7.162</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2.315</v>
+        <v>1.746666666666667</v>
       </c>
       <c r="C24" t="n">
-        <v>1.245</v>
+        <v>0.6966666666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>2.132</v>
+        <v>10.693</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-3.02</v>
+        <v>0.79</v>
       </c>
       <c r="C25" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="D25" t="n">
-        <v>0.506</v>
+        <v>15.805</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-3.61</v>
+        <v>-1.78</v>
       </c>
       <c r="C26" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.117</v>
+        <v>0.469</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,36 +4358,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-5.1</v>
+        <v>-4.88</v>
       </c>
       <c r="C27" t="n">
-        <v>0.825</v>
+        <v>1.05</v>
       </c>
       <c r="D27" t="n">
-        <v>3.607</v>
+        <v>1.735</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.65</v>
+        <v>-5.02</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="D28" t="n">
-        <v>5.546</v>
+        <v>0.113</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,74 +4396,74 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-5.74</v>
+        <v>-6.565</v>
       </c>
       <c r="C29" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="D29" t="n">
-        <v>16.58</v>
+        <v>3.328</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-6.87</v>
+        <v>-8.004999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="D30" t="n">
-        <v>1.742</v>
+        <v>2.08</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-7.300000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6766666666666667</v>
+        <v>1.56</v>
       </c>
       <c r="D31" t="n">
-        <v>10.427</v>
+        <v>0.099</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-10.43</v>
+        <v>-11.6</v>
       </c>
       <c r="C32" t="n">
-        <v>1.54</v>
+        <v>0.76</v>
       </c>
       <c r="D32" t="n">
-        <v>0.101</v>
+        <v>5.187</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1890</v>
+        <v>1920</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.82</v>
+        <v>1.59</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.74</v>
+        <v>0.79</v>
       </c>
       <c r="G2" t="n">
-        <v>34.39</v>
+        <v>34.9</v>
       </c>
       <c r="H2" t="n">
-        <v>33.8614</v>
+        <v>28.2067</v>
       </c>
       <c r="I2" t="n">
-        <v>26.9</v>
+        <v>31.6</v>
       </c>
       <c r="J2" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="K2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-15.5</v>
+        <v>-53.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1945</v>
+        <v>1900</v>
       </c>
       <c r="E3" t="n">
-        <v>4.01</v>
+        <v>-2.31</v>
       </c>
       <c r="F3" t="n">
-        <v>30.98</v>
+        <v>29.69</v>
       </c>
       <c r="G3" t="n">
-        <v>63.41</v>
+        <v>59.09</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3134</v>
+        <v>90.3947</v>
       </c>
       <c r="I3" t="n">
-        <v>89.5</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>81.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.82</v>
+        <v>3.98</v>
       </c>
       <c r="L3" t="n">
-        <v>15.8</v>
+        <v>-25.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.16</v>
+        <v>-0.98</v>
       </c>
       <c r="F4" t="n">
-        <v>39.45</v>
+        <v>44.29</v>
       </c>
       <c r="G4" t="n">
-        <v>57.32</v>
+        <v>51.45</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4773</v>
+        <v>4.3148</v>
       </c>
       <c r="I4" t="n">
-        <v>67.8</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
-        <v>68</v>
+        <v>63.4</v>
       </c>
       <c r="K4" t="n">
-        <v>7.47</v>
+        <v>7.54</v>
       </c>
       <c r="L4" t="n">
-        <v>-21</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.82</v>
+        <v>-2.98</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.02</v>
+        <v>-1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>47.63</v>
+        <v>49.19</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.369</v>
+        <v>-0.111</v>
       </c>
       <c r="I5" t="n">
-        <v>68.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>83.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.79</v>
+        <v>5.02</v>
       </c>
       <c r="L5" t="n">
-        <v>-29.6</v>
+        <v>-59.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>217.5</v>
+        <v>239</v>
       </c>
       <c r="E6" t="n">
-        <v>9.85</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>17.89</v>
+        <v>35.41</v>
       </c>
       <c r="G6" t="n">
-        <v>66.18000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3596</v>
+        <v>13.668</v>
       </c>
       <c r="I6" t="n">
-        <v>119</v>
+        <v>123.4</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>6.27</v>
+        <v>6.16</v>
       </c>
       <c r="L6" t="n">
-        <v>-19.4</v>
+        <v>-27.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.42</v>
+        <v>-1.65</v>
       </c>
       <c r="F7" t="n">
-        <v>8.720000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>66.06</v>
+        <v>63.16</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2045</v>
+        <v>2.7887</v>
       </c>
       <c r="I7" t="n">
-        <v>105.8</v>
+        <v>88.7</v>
       </c>
       <c r="J7" t="n">
-        <v>89.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="L7" t="n">
-        <v>92.90000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>4.58</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>507</v>
+        <v>742</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.588</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>4.53</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>487</v>
+        <v>716</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.977</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6</v>
+        <v>8.73</v>
       </c>
       <c r="F4" t="n">
-        <v>428</v>
+        <v>553</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.402</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>301</v>
+        <v>216.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="F5" t="n">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,67 +606,67 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.474</v>
+        <v>2.992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67.90000000000001</v>
+        <v>29.85</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.03</v>
+        <v>-1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.596</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.85</v>
+        <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.48</v>
+        <v>-5.88</v>
       </c>
       <c r="F7" t="n">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,135 +674,135 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.835</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36.3</v>
+        <v>61.9</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.47</v>
+        <v>-8.84</v>
       </c>
       <c r="F8" t="n">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.245</v>
+        <v>2.445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53.8</v>
+        <v>19.25</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.76</v>
+        <v>-3.02</v>
       </c>
       <c r="F9" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.992</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.7</v>
+        <v>35.4</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.74</v>
+        <v>-2.48</v>
       </c>
       <c r="F10" t="n">
         <v>155</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1975</v>
+        <v>229</v>
       </c>
       <c r="E11" t="n">
-        <v>-1</v>
+        <v>-4.18</v>
       </c>
       <c r="F11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>72.42400000000001</v>
+        <v>14.439</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>1340</v>
       </c>
       <c r="E12" t="n">
-        <v>2.44</v>
+        <v>-5.96</v>
       </c>
       <c r="F12" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.5620000000000001</v>
+        <v>16.971</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>331.5</v>
+        <v>164.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.92</v>
+        <v>-1.2</v>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9.455</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23.95</v>
+        <v>38.1</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.21</v>
+        <v>-1.68</v>
       </c>
       <c r="F14" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.48</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>239</v>
+        <v>294.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.65</v>
+        <v>-2.16</v>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14.617</v>
+        <v>5.442</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>1935</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.27</v>
+        <v>-2.03</v>
       </c>
       <c r="F16" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.822</v>
+        <v>72.024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1425</v>
+        <v>68.2</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.35</v>
+        <v>-8.82</v>
       </c>
       <c r="F17" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18.277</v>
+        <v>21.897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38.75</v>
+        <v>53.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.194</v>
+        <v>2.028</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.7</v>
+        <v>359.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.98</v>
+        <v>-2.97</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.184</v>
+        <v>9.566000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>212.5</v>
+        <v>231</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.97</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,135 +1116,135 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.099</v>
+        <v>3.361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77.90000000000001</v>
+        <v>131.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.26</v>
+        <v>-2.59</v>
       </c>
       <c r="F21" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.974</v>
+        <v>4.628</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>370.5</v>
+        <v>1755</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.39</v>
+        <v>-8.59</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9.679</v>
+        <v>14.315</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>386.5</v>
+        <v>42.85</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.65</v>
+        <v>-4.25</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.542</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40.2</v>
+        <v>104.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.86</v>
+        <v>-9.91</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.894</v>
+        <v>25.341</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>169</v>
+        <v>112.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.31</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.931</v>
+        <v>22.835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.3</v>
+        <v>271</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.46</v>
+        <v>-7.03</v>
       </c>
       <c r="F26" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.113</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>135</v>
+        <v>40.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.74</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.811</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>477.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.83</v>
+        <v>-0.39</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.735</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>291.5</v>
+        <v>463</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1</v>
+        <v>-3.04</v>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,169 +1422,169 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.763</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74.8</v>
+        <v>379.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.48</v>
+        <v>-1.81</v>
       </c>
       <c r="F30" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>23.009</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>124.5</v>
+        <v>256.5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.63</v>
+        <v>-10</v>
       </c>
       <c r="F31" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>24.453</v>
+        <v>26.206</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2645</v>
+        <v>165</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.51</v>
+        <v>-2.37</v>
       </c>
       <c r="F32" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8.800000000000001</v>
+        <v>5.582</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3440</v>
+        <v>123</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.43</v>
+        <v>-5.02</v>
       </c>
       <c r="F33" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.507</v>
+        <v>4.863</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>116</v>
+        <v>1815</v>
       </c>
       <c r="E34" t="n">
-        <v>5.45</v>
+        <v>-4.47</v>
       </c>
       <c r="F34" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>27.193</v>
+        <v>21.658</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1900</v>
+        <v>202.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.31</v>
+        <v>-7.32</v>
       </c>
       <c r="F35" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>22.493</v>
+        <v>2.339</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>239</v>
+        <v>3355</v>
       </c>
       <c r="E36" t="n">
-        <v>9.890000000000001</v>
+        <v>-2.47</v>
       </c>
       <c r="F36" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.335</v>
+        <v>6.352</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>20.25</v>
+        <v>251.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.41</v>
+        <v>5.23</v>
       </c>
       <c r="F37" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.71</v>
+        <v>4.553</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>440</v>
+        <v>2490</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.3</v>
+        <v>-5.86</v>
       </c>
       <c r="F38" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.371</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1285</v>
+        <v>433.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.28</v>
+        <v>-1.48</v>
       </c>
       <c r="F39" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.574</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>316</v>
+        <v>24</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.36</v>
+        <v>0.21</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.657</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>129.5</v>
+        <v>192</v>
       </c>
       <c r="E41" t="n">
-        <v>-3</v>
+        <v>-6.11</v>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.187</v>
+        <v>2.281</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>166.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.89</v>
+        <v>-6.79</v>
       </c>
       <c r="F42" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,135 +1864,135 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.626</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>285</v>
+        <v>1235</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.18</v>
+        <v>-3.89</v>
       </c>
       <c r="F43" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.187</v>
+        <v>1.514</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>253</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.94</v>
+        <v>-5.02</v>
       </c>
       <c r="F44" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.821</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>204.5</v>
+        <v>49.95</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-1.48</v>
       </c>
       <c r="F45" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.371</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>44.75</v>
+        <v>114</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.24</v>
+        <v>-1.72</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.685</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>64.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.38</v>
+        <v>0.11</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>13.495</v>
+        <v>1.795</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1920</v>
+        <v>20.05</v>
       </c>
       <c r="E48" t="n">
-        <v>1.59</v>
+        <v>-0.99</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>15.805</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>62.6</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.69</v>
+        <v>-2.95</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.957</v>
+        <v>12.616</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>218.5</v>
+        <v>305</v>
       </c>
       <c r="E50" t="n">
-        <v>4.05</v>
+        <v>-3.48</v>
       </c>
       <c r="F50" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.559</v>
+        <v>6.307</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>71.7</v>
+        <v>2335</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.98</v>
+        <v>-8.25</v>
       </c>
       <c r="F51" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.469</v>
+        <v>3.939</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2545</v>
+        <v>326</v>
       </c>
       <c r="E52" t="n">
-        <v>0.59</v>
+        <v>-1.66</v>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.456</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>64.72</v>
+        <v>56.71</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>4.456</v>
+        <v>3.939</v>
       </c>
     </row>
     <row r="3">
@@ -2311,29 +2311,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58.25</v>
+        <v>42.37</v>
       </c>
       <c r="F3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="G3" t="n">
-        <v>27.193</v>
+        <v>25.341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2342,75 +2342,75 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.32</v>
+        <v>41.69</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="n">
-        <v>9.455</v>
+        <v>4.553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.29</v>
+        <v>39.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.54</v>
+        <v>1.07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.184</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35.41</v>
+        <v>33.4</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>0.62</v>
       </c>
       <c r="G6" t="n">
-        <v>4.335</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="7">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29.69</v>
+        <v>22.22</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="G7" t="n">
-        <v>22.493</v>
+        <v>21.658</v>
       </c>
     </row>
     <row r="8">
@@ -2466,44 +2466,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27.32</v>
+        <v>20.64</v>
       </c>
       <c r="F8" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>9.679</v>
+        <v>9.566000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25.55</v>
+        <v>18.92</v>
       </c>
       <c r="F9" t="n">
-        <v>1.23</v>
+        <v>2.59</v>
       </c>
       <c r="G9" t="n">
-        <v>18.277</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="10">
@@ -2528,401 +2528,401 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21.15</v>
+        <v>14.56</v>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.49</v>
+        <v>13.58</v>
       </c>
       <c r="F11" t="n">
-        <v>1.07</v>
+        <v>2.55</v>
       </c>
       <c r="G11" t="n">
-        <v>23.009</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18.35</v>
+        <v>12.47</v>
       </c>
       <c r="F12" t="n">
-        <v>0.91</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>6.657</v>
+        <v>2.992</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>18.01</v>
+        <v>11.11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="G13" t="n">
-        <v>24.453</v>
+        <v>6.307</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.55</v>
+        <v>9.94</v>
       </c>
       <c r="F14" t="n">
-        <v>0.74</v>
+        <v>1.25</v>
       </c>
       <c r="G14" t="n">
-        <v>28.187</v>
+        <v>72.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.51</v>
+        <v>9.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="G15" t="n">
-        <v>72.42400000000001</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.949999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="F16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.402</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.449999999999999</v>
+        <v>7.66</v>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>0.92</v>
       </c>
       <c r="G17" t="n">
-        <v>5.474</v>
+        <v>22.835</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.15</v>
+        <v>7.63</v>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.194</v>
+        <v>16.971</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.130000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="F19" t="n">
-        <v>1.64</v>
+        <v>1.09</v>
       </c>
       <c r="G19" t="n">
-        <v>14.617</v>
+        <v>21.897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.699999999999999</v>
+        <v>5.53</v>
       </c>
       <c r="F20" t="n">
-        <v>2.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.977</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.37</v>
+        <v>5.31</v>
       </c>
       <c r="F21" t="n">
-        <v>0.96</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>5.763</v>
+        <v>2.028</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.86</v>
+        <v>4.06</v>
       </c>
       <c r="F22" t="n">
-        <v>0.85</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.71</v>
+        <v>5.442</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2931,912 +2931,912 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.32</v>
+        <v>2.65</v>
       </c>
       <c r="F23" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="G23" t="n">
-        <v>1.992</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.17</v>
+        <v>2.46</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>6.507</v>
+        <v>14.439</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.64</v>
+        <v>2.44</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="G25" t="n">
-        <v>3.821</v>
+        <v>6.352</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.33</v>
+        <v>1.64</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="G26" t="n">
-        <v>1.574</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.13</v>
+        <v>1.27</v>
       </c>
       <c r="F27" t="n">
-        <v>1.85</v>
+        <v>1.16</v>
       </c>
       <c r="G27" t="n">
-        <v>0.588</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.97</v>
+        <v>0.41</v>
       </c>
       <c r="F28" t="n">
-        <v>1.33</v>
+        <v>0.9</v>
       </c>
       <c r="G28" t="n">
-        <v>5.931</v>
+        <v>1.514</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.28</v>
+        <v>0.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.67</v>
+        <v>1.24</v>
       </c>
       <c r="G29" t="n">
-        <v>2.371</v>
+        <v>1.795</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.91</v>
+        <v>-1.04</v>
       </c>
       <c r="F30" t="n">
-        <v>1.55</v>
+        <v>0.98</v>
       </c>
       <c r="G30" t="n">
-        <v>1.974</v>
+        <v>1.524</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.57</v>
+        <v>-2.95</v>
       </c>
       <c r="F31" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="G31" t="n">
-        <v>2.596</v>
+        <v>4.628</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.38</v>
+        <v>-3.3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="G32" t="n">
-        <v>1.542</v>
+        <v>8.205</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.61</v>
+        <v>-3.75</v>
       </c>
       <c r="F33" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5620000000000001</v>
+        <v>26.206</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.12</v>
+        <v>-4.36</v>
       </c>
       <c r="F34" t="n">
-        <v>1.35</v>
+        <v>0.96</v>
       </c>
       <c r="G34" t="n">
-        <v>4.811</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.05</v>
+        <v>-5.79</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4</v>
+        <v>0.55</v>
       </c>
       <c r="G35" t="n">
-        <v>0.48</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.01</v>
+        <v>-6.07</v>
       </c>
       <c r="F36" t="n">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="G36" t="n">
-        <v>0.894</v>
+        <v>2.445</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.79</v>
+        <v>-6.28</v>
       </c>
       <c r="F37" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="G37" t="n">
-        <v>15.805</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.76</v>
+        <v>-6.78</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="G38" t="n">
-        <v>8.800000000000001</v>
+        <v>5.582</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-6.8</v>
       </c>
       <c r="F39" t="n">
-        <v>1.46</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
-        <v>1.822</v>
+        <v>2.281</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.78</v>
+        <v>-7.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G40" t="n">
-        <v>0.469</v>
+        <v>12.616</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.11</v>
+        <v>-8.6</v>
       </c>
       <c r="F41" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="G41" t="n">
-        <v>0.957</v>
+        <v>5.556</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.63</v>
+        <v>-9.69</v>
       </c>
       <c r="F42" t="n">
-        <v>0.92</v>
+        <v>1.42</v>
       </c>
       <c r="G42" t="n">
-        <v>0.626</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.87</v>
+        <v>-9.75</v>
       </c>
       <c r="F43" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="G43" t="n">
-        <v>1.685</v>
+        <v>1.715</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-4.88</v>
+        <v>-10.29</v>
       </c>
       <c r="F44" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="G44" t="n">
-        <v>1.735</v>
+        <v>3.361</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-5.02</v>
+        <v>-11.56</v>
       </c>
       <c r="F45" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="G45" t="n">
-        <v>0.113</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.22</v>
+        <v>-12.72</v>
       </c>
       <c r="F46" t="n">
-        <v>1.31</v>
+        <v>0.54</v>
       </c>
       <c r="G46" t="n">
-        <v>1.245</v>
+        <v>2.339</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.41</v>
+        <v>-14.6</v>
       </c>
       <c r="F47" t="n">
-        <v>0.46</v>
+        <v>0.88</v>
       </c>
       <c r="G47" t="n">
-        <v>2.559</v>
+        <v>14.315</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-5.7</v>
+        <v>-14.67</v>
       </c>
       <c r="F48" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G48" t="n">
-        <v>13.495</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-10.53</v>
+        <v>-15.2</v>
       </c>
       <c r="F49" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="G49" t="n">
-        <v>0.099</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-10.79</v>
+        <v>-15.46</v>
       </c>
       <c r="F50" t="n">
-        <v>1.57</v>
+        <v>0.77</v>
       </c>
       <c r="G50" t="n">
-        <v>0.835</v>
+        <v>4.863</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-11.02</v>
+        <v>-15.79</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="G51" t="n">
-        <v>2.371</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-11.6</v>
+        <v>-16.31</v>
       </c>
       <c r="F52" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>5.187</v>
+        <v>1.377</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.72</v>
+        <v>56.71</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.456</v>
+        <v>3.939</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.25</v>
+        <v>42.37</v>
       </c>
       <c r="C3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="D3" t="n">
-        <v>27.193</v>
+        <v>25.341</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,39 +3921,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.69</v>
+        <v>29.95666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>22.493</v>
+        <v>14.274</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.78</v>
+        <v>22.22</v>
       </c>
       <c r="C5" t="n">
-        <v>1.23</v>
+        <v>0.78</v>
       </c>
       <c r="D5" t="n">
-        <v>14.352</v>
+        <v>21.658</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.32</v>
+        <v>20.64</v>
       </c>
       <c r="C6" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="D6" t="n">
-        <v>9.679</v>
+        <v>9.566000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,58 +3978,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.15</v>
+        <v>14.99</v>
       </c>
       <c r="C7" t="n">
-        <v>1.14</v>
+        <v>2.453333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>2.86</v>
+        <v>5.588</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.83</v>
+        <v>14.56</v>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>1.18</v>
       </c>
       <c r="D8" t="n">
-        <v>1.81</v>
+        <v>2.821</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.49</v>
+        <v>14.52</v>
       </c>
       <c r="C9" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="D9" t="n">
-        <v>23.009</v>
+        <v>1.757</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.35</v>
+        <v>11.11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="D10" t="n">
-        <v>6.657</v>
+        <v>6.307</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.01</v>
+        <v>9.17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="D11" t="n">
-        <v>24.453</v>
+        <v>0.195</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,36 +4073,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.26</v>
+        <v>7.66</v>
       </c>
       <c r="C12" t="n">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="D12" t="n">
-        <v>24.208</v>
+        <v>22.835</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.55</v>
+        <v>7.23</v>
       </c>
       <c r="C13" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="D13" t="n">
-        <v>28.187</v>
+        <v>21.897</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,17 +4111,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.15</v>
+        <v>5.53</v>
       </c>
       <c r="C14" t="n">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.194</v>
+        <v>1.718</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,150 +4130,150 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.926666666666666</v>
+        <v>2.196</v>
       </c>
       <c r="C15" t="n">
-        <v>2.003333333333333</v>
+        <v>1.268</v>
       </c>
       <c r="D15" t="n">
-        <v>3.967</v>
+        <v>7.157</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.86</v>
+        <v>1.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1.71</v>
+        <v>84.64</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.33</v>
+        <v>0.4249999999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>0.97</v>
+        <v>1.245</v>
       </c>
       <c r="D17" t="n">
-        <v>1.574</v>
+        <v>22.553</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.105</v>
+        <v>0.41</v>
       </c>
       <c r="C18" t="n">
-        <v>1.25</v>
+        <v>0.9</v>
       </c>
       <c r="D18" t="n">
-        <v>6.417</v>
+        <v>1.514</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.9575</v>
+        <v>-0.4299999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3</v>
+        <v>0.85</v>
       </c>
       <c r="D19" t="n">
-        <v>26.587</v>
+        <v>14.557</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.905</v>
+        <v>-1.04</v>
       </c>
       <c r="C20" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="D20" t="n">
-        <v>85.91900000000001</v>
+        <v>1.524</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.465</v>
+        <v>-3.185</v>
       </c>
       <c r="C21" t="n">
-        <v>0.89</v>
+        <v>1.315</v>
       </c>
       <c r="D21" t="n">
-        <v>15.307</v>
+        <v>25.886</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.38</v>
+        <v>-3.75</v>
       </c>
       <c r="C22" t="n">
-        <v>0.98</v>
+        <v>0.71</v>
       </c>
       <c r="D22" t="n">
-        <v>1.542</v>
+        <v>26.206</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,74 +4282,74 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.258</v>
+        <v>-6.28</v>
       </c>
       <c r="C23" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="D23" t="n">
-        <v>7.162</v>
+        <v>0.119</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.746666666666667</v>
+        <v>-8.18</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6966666666666667</v>
+        <v>1.375</v>
       </c>
       <c r="D24" t="n">
-        <v>10.693</v>
+        <v>5.806</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.79</v>
+        <v>-9.373333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>15.805</v>
+        <v>10.176</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.78</v>
+        <v>-9.75</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.469</v>
+        <v>1.715</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,36 +4358,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-4.88</v>
+        <v>-10.23</v>
       </c>
       <c r="C27" t="n">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="D27" t="n">
-        <v>1.735</v>
+        <v>3.087</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-5.02</v>
+        <v>-11.56</v>
       </c>
       <c r="C28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="D28" t="n">
-        <v>0.113</v>
+        <v>0.372</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-6.565</v>
+        <v>-12.445</v>
       </c>
       <c r="C29" t="n">
-        <v>0.68</v>
+        <v>1.465</v>
       </c>
       <c r="D29" t="n">
-        <v>3.328</v>
+        <v>2.013</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -4415,36 +4415,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-8.004999999999999</v>
+        <v>-14.6</v>
       </c>
       <c r="C30" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="D30" t="n">
-        <v>2.08</v>
+        <v>14.315</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-10.53</v>
+        <v>-15.46</v>
       </c>
       <c r="C31" t="n">
-        <v>1.56</v>
+        <v>0.77</v>
       </c>
       <c r="D31" t="n">
-        <v>0.099</v>
+        <v>4.863</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-11.6</v>
+        <v>-15.79</v>
       </c>
       <c r="C32" t="n">
-        <v>0.76</v>
+        <v>1.64</v>
       </c>
       <c r="D32" t="n">
-        <v>5.187</v>
+        <v>0.098</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1920</v>
+        <v>1755</v>
       </c>
       <c r="E2" t="n">
-        <v>1.59</v>
+        <v>-8.59</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79</v>
+        <v>-14.6</v>
       </c>
       <c r="G2" t="n">
-        <v>34.9</v>
+        <v>27.11</v>
       </c>
       <c r="H2" t="n">
-        <v>28.2067</v>
+        <v>8.5518</v>
       </c>
       <c r="I2" t="n">
-        <v>31.6</v>
+        <v>10.2</v>
       </c>
       <c r="J2" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8.369999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-53.7</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1900</v>
+        <v>1815</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.31</v>
+        <v>-4.47</v>
       </c>
       <c r="F3" t="n">
-        <v>29.69</v>
+        <v>22.22</v>
       </c>
       <c r="G3" t="n">
-        <v>59.09</v>
+        <v>53.79</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3947</v>
+        <v>78.8908</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>56.1</v>
       </c>
       <c r="J3" t="n">
-        <v>81.2</v>
+        <v>45.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.98</v>
+        <v>4.37</v>
       </c>
       <c r="L3" t="n">
-        <v>-25.6</v>
+        <v>-19.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.98</v>
+        <v>-6.79</v>
       </c>
       <c r="F4" t="n">
-        <v>44.29</v>
+        <v>33.4</v>
       </c>
       <c r="G4" t="n">
-        <v>51.45</v>
+        <v>37.79</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3148</v>
+        <v>3.839</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>46.8</v>
       </c>
       <c r="J4" t="n">
-        <v>63.4</v>
+        <v>34.3</v>
       </c>
       <c r="K4" t="n">
-        <v>7.54</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>-25.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.98</v>
+        <v>-5.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.78</v>
+        <v>-11.56</v>
       </c>
       <c r="G5" t="n">
-        <v>49.19</v>
+        <v>49.03</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.111</v>
+        <v>-0.1182</v>
       </c>
       <c r="I5" t="n">
-        <v>60</v>
+        <v>46.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.2</v>
+        <v>55.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5.02</v>
+        <v>5.36</v>
       </c>
       <c r="L5" t="n">
-        <v>-59.5</v>
+        <v>-30.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>239</v>
+        <v>251.5</v>
       </c>
       <c r="E6" t="n">
-        <v>9.890000000000001</v>
+        <v>5.23</v>
       </c>
       <c r="F6" t="n">
-        <v>35.41</v>
+        <v>41.69</v>
       </c>
       <c r="G6" t="n">
-        <v>71.94</v>
+        <v>75.38</v>
       </c>
       <c r="H6" t="n">
-        <v>13.668</v>
+        <v>17.2408</v>
       </c>
       <c r="I6" t="n">
-        <v>123.4</v>
+        <v>116.2</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>6.16</v>
+        <v>6.23</v>
       </c>
       <c r="L6" t="n">
-        <v>-27.5</v>
+        <v>-21.6</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,38 +4832,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.65</v>
+        <v>-4.18</v>
       </c>
       <c r="F7" t="n">
-        <v>9.130000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>63.16</v>
+        <v>56.69</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7887</v>
+        <v>2.2429</v>
       </c>
       <c r="I7" t="n">
-        <v>88.7</v>
+        <v>60.2</v>
       </c>
       <c r="J7" t="n">
-        <v>76.59999999999999</v>
+        <v>45.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>19.2</v>
+        <v>34.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>63.6</v>
       </c>
       <c r="E2" t="n">
-        <v>8.890000000000001</v>
+        <v>-3.64</v>
       </c>
       <c r="F2" t="n">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>2.406</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>81.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>-6.32</v>
       </c>
       <c r="F3" t="n">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.609</v>
+        <v>1.388</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>137</v>
+        <v>209.5</v>
       </c>
       <c r="E4" t="n">
-        <v>8.73</v>
+        <v>-3.23</v>
       </c>
       <c r="F4" t="n">
-        <v>553</v>
+        <v>387</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.751</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>216.5</v>
+        <v>73.2</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1</v>
+        <v>-5.67</v>
       </c>
       <c r="F5" t="n">
-        <v>406</v>
+        <v>212</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.992</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.85</v>
+        <v>50.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.49</v>
+        <v>-5.61</v>
       </c>
       <c r="F6" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,101 +640,101 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.119</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>126.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.88</v>
+        <v>-7.66</v>
       </c>
       <c r="F7" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.098</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61.9</v>
+        <v>89.8</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.84</v>
+        <v>-3.54</v>
       </c>
       <c r="F8" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.445</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.25</v>
+        <v>217</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.02</v>
+        <v>-5.24</v>
       </c>
       <c r="F9" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,135 +742,135 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.837</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35.4</v>
+        <v>1865</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.48</v>
+        <v>-3.62</v>
       </c>
       <c r="F10" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.176</v>
+        <v>73.20099999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>229</v>
+        <v>18.6</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.18</v>
+        <v>-3.38</v>
       </c>
       <c r="F11" t="n">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.439</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1340</v>
+        <v>281</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.96</v>
+        <v>-4.58</v>
       </c>
       <c r="F12" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>16.971</v>
+        <v>5.464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>164.5</v>
+        <v>23.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2</v>
+        <v>-2.29</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,237 +878,237 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.625</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38.1</v>
+        <v>28.55</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.68</v>
+        <v>-4.36</v>
       </c>
       <c r="F14" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.195</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>294.5</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.16</v>
+        <v>-4.94</v>
       </c>
       <c r="F15" t="n">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.442</v>
+        <v>4.535</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1935</v>
+        <v>448.5</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.03</v>
+        <v>3.46</v>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>72.024</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68.2</v>
+        <v>33.85</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.82</v>
+        <v>-4.38</v>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>21.897</v>
+        <v>1.133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>53.5</v>
+        <v>38.9</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-3.71</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.028</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>359.5</v>
+        <v>189.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.97</v>
+        <v>-5.25</v>
       </c>
       <c r="F19" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.566000000000001</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>231</v>
+        <v>1255</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6.34</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.361</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>131.5</v>
+        <v>40.25</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.59</v>
+        <v>-6.07</v>
       </c>
       <c r="F21" t="n">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.628</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1755</v>
+        <v>327.5</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.59</v>
+        <v>-8.9</v>
       </c>
       <c r="F22" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.315</v>
+        <v>8.864000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.85</v>
+        <v>155.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.25</v>
+        <v>-5.76</v>
       </c>
       <c r="F23" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,67 +1218,67 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.377</v>
+        <v>4.919</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>104.5</v>
+        <v>217</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.91</v>
+        <v>-6.06</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25.341</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>112.5</v>
+        <v>1705</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.640000000000001</v>
+        <v>-2.85</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>22.835</v>
+        <v>14.232</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>271</v>
+        <v>445</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.03</v>
+        <v>-3.89</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,101 +1320,101 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.556</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.4</v>
+        <v>158</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>-3.95</v>
       </c>
       <c r="F27" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.895</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>77.59999999999999</v>
+        <v>3120</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.39</v>
+        <v>-7</v>
       </c>
       <c r="F28" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.963</v>
+        <v>5.879</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>463</v>
+        <v>2280</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.04</v>
+        <v>-8.43</v>
       </c>
       <c r="F29" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.715</v>
+        <v>7.474</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>379.5</v>
+        <v>234.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.81</v>
+        <v>-8.58</v>
       </c>
       <c r="F30" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.524</v>
+        <v>23.255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>256.5</v>
+        <v>278</v>
       </c>
       <c r="E31" t="n">
-        <v>-10</v>
+        <v>-8.85</v>
       </c>
       <c r="F31" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>26.206</v>
+        <v>5.617</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>165</v>
+        <v>371</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.37</v>
+        <v>-2.24</v>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.582</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>123</v>
+        <v>1720</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.02</v>
+        <v>-5.23</v>
       </c>
       <c r="F33" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,67 +1558,67 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.863</v>
+        <v>19.585</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1815</v>
+        <v>1165</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.47</v>
+        <v>-5.67</v>
       </c>
       <c r="F34" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.658</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>202.5</v>
+        <v>36.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.32</v>
+        <v>-4.2</v>
       </c>
       <c r="F35" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.339</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3355</v>
+        <v>104</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.47</v>
+        <v>-7.56</v>
       </c>
       <c r="F36" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.352</v>
+        <v>21.792</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>251.5</v>
+        <v>98</v>
       </c>
       <c r="E37" t="n">
-        <v>5.23</v>
+        <v>-6.22</v>
       </c>
       <c r="F37" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.553</v>
+        <v>24.537</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2490</v>
+        <v>108.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-5.86</v>
+        <v>-4.82</v>
       </c>
       <c r="F38" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.205</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>433.5</v>
+        <v>262</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.48</v>
+        <v>-3.32</v>
       </c>
       <c r="F39" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,67 +1762,67 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.182</v>
+        <v>5.171</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.21</v>
+        <v>-4.24</v>
       </c>
       <c r="F40" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.476</v>
+        <v>1.684</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>192</v>
+        <v>46.95</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.11</v>
+        <v>-6.01</v>
       </c>
       <c r="F41" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.281</v>
+        <v>2.635</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>65.90000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="E42" t="n">
-        <v>-6.79</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.132</v>
+        <v>19.332</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1235</v>
+        <v>62</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.89</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.514</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>68.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.02</v>
+        <v>-6.14</v>
       </c>
       <c r="F44" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.372</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>49.95</v>
+        <v>116</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.48</v>
+        <v>-5.69</v>
       </c>
       <c r="F45" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.821</v>
+        <v>4.521</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.72</v>
+        <v>-4.15</v>
       </c>
       <c r="F46" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.905</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>93.09999999999999</v>
+        <v>180</v>
       </c>
       <c r="E47" t="n">
-        <v>0.11</v>
+        <v>-6.25</v>
       </c>
       <c r="F47" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.795</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20.05</v>
+        <v>199</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.99</v>
+        <v>-1.73</v>
       </c>
       <c r="F48" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.718</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62.6</v>
+        <v>293.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.95</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>12.616</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>305</v>
+        <v>2255</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.48</v>
+        <v>-3.43</v>
       </c>
       <c r="F50" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,67 +2136,67 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.307</v>
+        <v>3.717</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2335</v>
+        <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>-8.25</v>
+        <v>-7.44</v>
       </c>
       <c r="F51" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.939</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>326</v>
+        <v>226.5</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.66</v>
+        <v>-9.94</v>
       </c>
       <c r="F52" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>8.970000000000001</v>
+        <v>4.05</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56.71</v>
+        <v>48.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3.939</v>
+        <v>3.717</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42.37</v>
+        <v>41.41</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>25.341</v>
+        <v>24.537</v>
       </c>
     </row>
     <row r="4">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41.69</v>
+        <v>33.24</v>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4.553</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39.02</v>
+        <v>27.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="G5" t="n">
-        <v>8.970000000000001</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="6">
@@ -2404,91 +2404,91 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33.4</v>
+        <v>26.16</v>
       </c>
       <c r="F6" t="n">
         <v>0.62</v>
       </c>
       <c r="G6" t="n">
-        <v>1.132</v>
+        <v>1.059</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.22</v>
+        <v>17.13</v>
       </c>
       <c r="F7" t="n">
-        <v>0.78</v>
+        <v>3.11</v>
       </c>
       <c r="G7" t="n">
-        <v>21.658</v>
+        <v>2.406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20.64</v>
+        <v>10.55</v>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>2.51</v>
       </c>
       <c r="G8" t="n">
-        <v>9.566000000000001</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2497,168 +2497,168 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18.92</v>
+        <v>7.66</v>
       </c>
       <c r="F9" t="n">
-        <v>2.59</v>
+        <v>3.06</v>
       </c>
       <c r="G9" t="n">
-        <v>1.609</v>
+        <v>1.388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14.56</v>
+        <v>6.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>2.821</v>
+        <v>8.864000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.58</v>
+        <v>5.74</v>
       </c>
       <c r="F11" t="n">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.987</v>
+        <v>2.635</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.47</v>
+        <v>5.52</v>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.992</v>
+        <v>19.585</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11.11</v>
+        <v>5.37</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>6.307</v>
+        <v>73.20099999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.94</v>
+        <v>4.96</v>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>72.024</v>
+        <v>19.332</v>
       </c>
     </row>
     <row r="15">
@@ -2683,246 +2683,246 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.17</v>
+        <v>3.69</v>
       </c>
       <c r="F15" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="G15" t="n">
-        <v>0.195</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.16</v>
+        <v>0.97</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="G16" t="n">
-        <v>0.751</v>
+        <v>21.792</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.66</v>
+        <v>0.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.92</v>
+        <v>2.05</v>
       </c>
       <c r="G17" t="n">
-        <v>22.835</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.63</v>
+        <v>0.36</v>
       </c>
       <c r="F18" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="G18" t="n">
-        <v>16.971</v>
+        <v>5.464</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.23</v>
+        <v>0.26</v>
       </c>
       <c r="F19" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="G19" t="n">
-        <v>21.897</v>
+        <v>1.684</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="G20" t="n">
-        <v>1.718</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.31</v>
+        <v>-0.4</v>
       </c>
       <c r="F21" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="G21" t="n">
-        <v>2.028</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.06</v>
+        <v>-1.26</v>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="G22" t="n">
-        <v>5.442</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.65</v>
+        <v>-2.02</v>
       </c>
       <c r="F23" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="G23" t="n">
-        <v>1.963</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="24">
@@ -2962,60 +2962,60 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.46</v>
+        <v>-2.03</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="G24" t="n">
-        <v>14.439</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.44</v>
+        <v>-2.97</v>
       </c>
       <c r="F25" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>6.352</v>
+        <v>5.617</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3024,29 +3024,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.64</v>
+        <v>-3.96</v>
       </c>
       <c r="F26" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.895</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3055,277 +3055,277 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.27</v>
+        <v>-4.44</v>
       </c>
       <c r="F27" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.476</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.41</v>
+        <v>-5.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.514</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.11</v>
+        <v>-7.41</v>
       </c>
       <c r="F29" t="n">
-        <v>1.24</v>
+        <v>0.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.795</v>
+        <v>11.628</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-1.04</v>
+        <v>-8.42</v>
       </c>
       <c r="F30" t="n">
-        <v>0.98</v>
+        <v>1.45</v>
       </c>
       <c r="G30" t="n">
-        <v>1.524</v>
+        <v>4.535</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-2.95</v>
+        <v>-8.67</v>
       </c>
       <c r="F31" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>4.628</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3.3</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.87</v>
+        <v>1.24</v>
       </c>
       <c r="G32" t="n">
-        <v>8.205</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-3.75</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="G33" t="n">
-        <v>26.206</v>
+        <v>5.879</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-4.36</v>
+        <v>-9.59</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96</v>
+        <v>1.42</v>
       </c>
       <c r="G34" t="n">
-        <v>0.625</v>
+        <v>4.919</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-5.79</v>
+        <v>-11.84</v>
       </c>
       <c r="F35" t="n">
-        <v>0.55</v>
+        <v>1.96</v>
       </c>
       <c r="G35" t="n">
-        <v>0.905</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3334,385 +3334,385 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-6.07</v>
+        <v>-11.97</v>
       </c>
       <c r="F36" t="n">
-        <v>1.91</v>
+        <v>0.89</v>
       </c>
       <c r="G36" t="n">
-        <v>2.445</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-6.28</v>
+        <v>-12.15</v>
       </c>
       <c r="F37" t="n">
-        <v>1.23</v>
+        <v>0.61</v>
       </c>
       <c r="G37" t="n">
-        <v>0.119</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-6.78</v>
+        <v>-12.2</v>
       </c>
       <c r="F38" t="n">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="G38" t="n">
-        <v>5.582</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-6.8</v>
+        <v>-12.23</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="G39" t="n">
-        <v>2.281</v>
+        <v>1.674</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-7.4</v>
+        <v>-12.76</v>
       </c>
       <c r="F40" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
       <c r="G40" t="n">
-        <v>12.616</v>
+        <v>1.133</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-8.6</v>
+        <v>-13.63</v>
       </c>
       <c r="F41" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="G41" t="n">
-        <v>5.556</v>
+        <v>23.255</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-9.69</v>
+        <v>-13.7</v>
       </c>
       <c r="F42" t="n">
-        <v>1.42</v>
+        <v>0.95</v>
       </c>
       <c r="G42" t="n">
-        <v>1.176</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-9.75</v>
+        <v>-14.75</v>
       </c>
       <c r="F43" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G43" t="n">
-        <v>1.715</v>
+        <v>14.232</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-10.29</v>
+        <v>-15.06</v>
       </c>
       <c r="F44" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="G44" t="n">
-        <v>3.361</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-11.56</v>
+        <v>-16.15</v>
       </c>
       <c r="F45" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="G45" t="n">
-        <v>0.372</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-12.72</v>
+        <v>-16.33</v>
       </c>
       <c r="F46" t="n">
-        <v>0.54</v>
+        <v>0.95</v>
       </c>
       <c r="G46" t="n">
-        <v>2.339</v>
+        <v>7.474</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-14.6</v>
+        <v>-16.56</v>
       </c>
       <c r="F47" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="G47" t="n">
-        <v>14.315</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-14.67</v>
+        <v>-16.69</v>
       </c>
       <c r="F48" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G48" t="n">
-        <v>2.182</v>
+        <v>5.171</v>
       </c>
     </row>
     <row r="49">
@@ -3737,106 +3737,106 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-15.2</v>
+        <v>-16.78</v>
       </c>
       <c r="F49" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="G49" t="n">
-        <v>0.837</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-15.46</v>
+        <v>-17.44</v>
       </c>
       <c r="F50" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="G50" t="n">
-        <v>4.863</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-15.79</v>
+        <v>-20.82</v>
       </c>
       <c r="F51" t="n">
-        <v>1.64</v>
+        <v>0.67</v>
       </c>
       <c r="G51" t="n">
-        <v>0.098</v>
+        <v>4.521</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-16.31</v>
+        <v>-22.18</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="G52" t="n">
-        <v>1.377</v>
+        <v>0.094</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.71</v>
+        <v>48.36</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="D2" t="n">
-        <v>3.939</v>
+        <v>3.717</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.37</v>
+        <v>41.41</v>
       </c>
       <c r="C3" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="D3" t="n">
-        <v>25.341</v>
+        <v>24.537</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.95666666666667</v>
+        <v>20.45666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.416666666666667</v>
+        <v>1.306666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>14.274</v>
+        <v>12.692</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3940,58 +3940,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.22</v>
+        <v>11.78</v>
       </c>
       <c r="C5" t="n">
-        <v>0.78</v>
+        <v>2.893333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>21.658</v>
+        <v>7.271</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.64</v>
+        <v>8.745000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1.17</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>9.566000000000001</v>
+        <v>1.651</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.99</v>
+        <v>6.5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.453333333333333</v>
+        <v>1.15</v>
       </c>
       <c r="D7" t="n">
-        <v>5.588</v>
+        <v>8.864000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.56</v>
+        <v>5.74</v>
       </c>
       <c r="C8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.821</v>
+        <v>2.635</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,36 +4016,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.52</v>
+        <v>5.52</v>
       </c>
       <c r="C9" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.757</v>
+        <v>19.585</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.11</v>
+        <v>4.96</v>
       </c>
       <c r="C10" t="n">
-        <v>0.78</v>
+        <v>1.04</v>
       </c>
       <c r="D10" t="n">
-        <v>6.307</v>
+        <v>19.332</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.17</v>
+        <v>3.69</v>
       </c>
       <c r="C11" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="D11" t="n">
-        <v>0.195</v>
+        <v>0.191</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.66</v>
+        <v>0.97</v>
       </c>
       <c r="C12" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="D12" t="n">
-        <v>22.835</v>
+        <v>21.792</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,17 +4092,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.23</v>
+        <v>0.26</v>
       </c>
       <c r="C13" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>21.897</v>
+        <v>1.684</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,20 +4111,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.53</v>
+        <v>-1.02</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9950000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.718</v>
+        <v>84.82899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.196</v>
+        <v>-2.336</v>
       </c>
       <c r="C15" t="n">
-        <v>1.268</v>
+        <v>1.36</v>
       </c>
       <c r="D15" t="n">
-        <v>7.157</v>
+        <v>7.238</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -4149,20 +4149,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.27</v>
+        <v>-2.97</v>
       </c>
       <c r="C16" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>84.64</v>
+        <v>5.617</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4249999999999998</v>
+        <v>-4.995</v>
       </c>
       <c r="C17" t="n">
-        <v>1.245</v>
+        <v>1.325</v>
       </c>
       <c r="D17" t="n">
-        <v>22.553</v>
+        <v>20.779</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.41</v>
+        <v>-5.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="D18" t="n">
-        <v>1.514</v>
+        <v>1.415</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,36 +4206,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4299999999999999</v>
+        <v>-6.56</v>
       </c>
       <c r="C19" t="n">
-        <v>0.85</v>
+        <v>1.4775</v>
       </c>
       <c r="D19" t="n">
-        <v>14.557</v>
+        <v>25.58</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.04</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="D20" t="n">
-        <v>1.524</v>
+        <v>0.115</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,36 +4244,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.185</v>
+        <v>-11.905</v>
       </c>
       <c r="C21" t="n">
-        <v>1.315</v>
+        <v>1.425</v>
       </c>
       <c r="D21" t="n">
-        <v>25.886</v>
+        <v>5.368</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-3.75</v>
+        <v>-12.23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="D22" t="n">
-        <v>26.206</v>
+        <v>1.674</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,36 +4282,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-6.28</v>
+        <v>-12.685</v>
       </c>
       <c r="C23" t="n">
-        <v>1.23</v>
+        <v>0.895</v>
       </c>
       <c r="D23" t="n">
-        <v>0.119</v>
+        <v>13.353</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-8.18</v>
+        <v>-13.605</v>
       </c>
       <c r="C24" t="n">
-        <v>1.375</v>
+        <v>0.735</v>
       </c>
       <c r="D24" t="n">
-        <v>5.806</v>
+        <v>3.051</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -4320,36 +4320,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-9.373333333333333</v>
+        <v>-13.63</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="D25" t="n">
-        <v>10.176</v>
+        <v>23.255</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-9.75</v>
+        <v>-13.7</v>
       </c>
       <c r="C26" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="D26" t="n">
-        <v>1.715</v>
+        <v>1.363</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,74 +4358,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-10.23</v>
+        <v>-14.75</v>
       </c>
       <c r="C27" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="D27" t="n">
-        <v>3.087</v>
+        <v>14.232</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-11.56</v>
+        <v>-14.77</v>
       </c>
       <c r="C28" t="n">
-        <v>1.03</v>
+        <v>1.475</v>
       </c>
       <c r="D28" t="n">
-        <v>0.372</v>
+        <v>1.974</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-12.445</v>
+        <v>-15.15</v>
       </c>
       <c r="C29" t="n">
-        <v>1.465</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="D29" t="n">
-        <v>2.013</v>
+        <v>9.528</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-14.6</v>
+        <v>-17.44</v>
       </c>
       <c r="C30" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="D30" t="n">
-        <v>14.315</v>
+        <v>0.315</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-15.46</v>
+        <v>-20.82</v>
       </c>
       <c r="C31" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="D31" t="n">
-        <v>4.863</v>
+        <v>4.521</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-15.79</v>
+        <v>-22.18</v>
       </c>
       <c r="C32" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="D32" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1755</v>
+        <v>1705</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.59</v>
+        <v>-2.85</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.6</v>
+        <v>-14.75</v>
       </c>
       <c r="G2" t="n">
-        <v>27.11</v>
+        <v>31.36</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5518</v>
+        <v>-9.4673</v>
       </c>
       <c r="I2" t="n">
-        <v>10.2</v>
+        <v>8.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>16.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1815</v>
+        <v>1720</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.47</v>
+        <v>-5.23</v>
       </c>
       <c r="F3" t="n">
-        <v>22.22</v>
+        <v>5.52</v>
       </c>
       <c r="G3" t="n">
-        <v>53.79</v>
+        <v>50.98</v>
       </c>
       <c r="H3" t="n">
-        <v>78.8908</v>
+        <v>64.5646</v>
       </c>
       <c r="I3" t="n">
-        <v>56.1</v>
+        <v>16.4</v>
       </c>
       <c r="J3" t="n">
-        <v>45.8</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.37</v>
+        <v>4.71</v>
       </c>
       <c r="L3" t="n">
-        <v>-19.4</v>
+        <v>-3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4676,31 +4676,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.79</v>
+        <v>-7.44</v>
       </c>
       <c r="F4" t="n">
-        <v>33.4</v>
+        <v>26.16</v>
       </c>
       <c r="G4" t="n">
-        <v>37.79</v>
+        <v>36.26</v>
       </c>
       <c r="H4" t="n">
-        <v>3.839</v>
+        <v>2.9612</v>
       </c>
       <c r="I4" t="n">
-        <v>46.8</v>
+        <v>23.7</v>
       </c>
       <c r="J4" t="n">
-        <v>34.3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-25.3</v>
+        <v>-63.2</v>
       </c>
       <c r="M4" t="n">
         <v>0.62</v>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.02</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.56</v>
+        <v>-17.44</v>
       </c>
       <c r="G5" t="n">
-        <v>49.03</v>
+        <v>46.75</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1182</v>
+        <v>-0.6735</v>
       </c>
       <c r="I5" t="n">
-        <v>46.6</v>
+        <v>22.6</v>
       </c>
       <c r="J5" t="n">
-        <v>55.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>5.36</v>
+        <v>6.01</v>
       </c>
       <c r="L5" t="n">
-        <v>-30.7</v>
+        <v>-40.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>251.5</v>
+        <v>226.5</v>
       </c>
       <c r="E6" t="n">
-        <v>5.23</v>
+        <v>-9.94</v>
       </c>
       <c r="F6" t="n">
-        <v>41.69</v>
+        <v>33.24</v>
       </c>
       <c r="G6" t="n">
-        <v>75.38</v>
+        <v>69.66</v>
       </c>
       <c r="H6" t="n">
-        <v>17.2408</v>
+        <v>17.7319</v>
       </c>
       <c r="I6" t="n">
-        <v>116.2</v>
+        <v>86.5</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>71.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.23</v>
+        <v>7.22</v>
       </c>
       <c r="L6" t="n">
-        <v>-21.6</v>
+        <v>-64.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.18</v>
+        <v>-5.24</v>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>-2.03</v>
       </c>
       <c r="G7" t="n">
-        <v>56.69</v>
+        <v>51.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2429</v>
+        <v>0.979</v>
       </c>
       <c r="I7" t="n">
-        <v>60.2</v>
+        <v>28.1</v>
       </c>
       <c r="J7" t="n">
-        <v>45.3</v>
+        <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>34.1</v>
+        <v>74.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63.6</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.64</v>
+        <v>-5.66</v>
       </c>
       <c r="F2" t="n">
-        <v>757</v>
+        <v>316</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.406</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81.5</v>
+        <v>78.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.32</v>
+        <v>-3.44</v>
       </c>
       <c r="F3" t="n">
-        <v>710</v>
+        <v>268</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.388</v>
+        <v>1.519</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>209.5</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.23</v>
+        <v>-1.19</v>
       </c>
       <c r="F4" t="n">
-        <v>387</v>
+        <v>224</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.477</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73.2</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.67</v>
+        <v>-0.72</v>
       </c>
       <c r="F5" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.972</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50.5</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.61</v>
+        <v>1.61</v>
       </c>
       <c r="F6" t="n">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.063</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>126.5</v>
+        <v>470.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.66</v>
+        <v>4.91</v>
       </c>
       <c r="F7" t="n">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.73</v>
+        <v>2.386</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89.8</v>
+        <v>1280</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.54</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,135 +708,135 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.833</v>
+        <v>1.417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>217</v>
+        <v>353.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.24</v>
+        <v>7.94</v>
       </c>
       <c r="F9" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14.6</v>
+        <v>9.885999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1865</v>
+        <v>29.2</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.62</v>
+        <v>2.28</v>
       </c>
       <c r="F10" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.20099999999999</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.6</v>
+        <v>1900</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.38</v>
+        <v>1.88</v>
       </c>
       <c r="F11" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.841</v>
+        <v>76.964</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>281</v>
+        <v>34.05</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.58</v>
+        <v>0.59</v>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.464</v>
+        <v>1.166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.45</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.29</v>
+        <v>0.55</v>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,135 +878,135 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.483</v>
+        <v>2.033</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.55</v>
+        <v>38.35</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.36</v>
+        <v>5.07</v>
       </c>
       <c r="F14" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.115</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>1335</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.94</v>
+        <v>6.37</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.535</v>
+        <v>16.959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>448.5</v>
+        <v>289.5</v>
       </c>
       <c r="E16" t="n">
-        <v>3.46</v>
+        <v>3.02</v>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2.22</v>
+        <v>5.647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33.85</v>
+        <v>128.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.38</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.133</v>
+        <v>4.704</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38.9</v>
+        <v>90.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.71</v>
+        <v>0.78</v>
       </c>
       <c r="F18" t="n">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.887</v>
+        <v>1.871</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>189.5</v>
+        <v>374.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.094</v>
+        <v>1.398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1255</v>
+        <v>456</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.34</v>
+        <v>2.47</v>
       </c>
       <c r="F20" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15.86</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40.25</v>
+        <v>23.4</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.07</v>
+        <v>-0.21</v>
       </c>
       <c r="F21" t="n">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.981</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>327.5</v>
+        <v>295</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.9</v>
+        <v>6.12</v>
       </c>
       <c r="F22" t="n">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8.864000000000001</v>
+        <v>5.824</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>155.5</v>
+        <v>51.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.76</v>
+        <v>1.98</v>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,67 +1218,67 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.919</v>
+        <v>2.122</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>217</v>
+        <v>62.9</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.06</v>
+        <v>8.26</v>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.173</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1705</v>
+        <v>224</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.85</v>
+        <v>3.23</v>
       </c>
       <c r="F25" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14.232</v>
+        <v>15.254</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>445</v>
+        <v>39.3</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.89</v>
+        <v>1.03</v>
       </c>
       <c r="F26" t="n">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.674</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.95</v>
+        <v>7.69</v>
       </c>
       <c r="F27" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.592</v>
+        <v>24.063</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3120</v>
+        <v>161</v>
       </c>
       <c r="E28" t="n">
-        <v>-7</v>
+        <v>3.54</v>
       </c>
       <c r="F28" t="n">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.879</v>
+        <v>5.052</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2280</v>
+        <v>3270</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.43</v>
+        <v>4.81</v>
       </c>
       <c r="F29" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7.474</v>
+        <v>6.119</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>234.5</v>
+        <v>1775</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.58</v>
+        <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>23.255</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>278</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-8.85</v>
+        <v>4.89</v>
       </c>
       <c r="F31" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.617</v>
+        <v>19.941</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>371</v>
+        <v>199.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.24</v>
+        <v>5.28</v>
       </c>
       <c r="F32" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.415</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1720</v>
+        <v>113.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.23</v>
+        <v>4.61</v>
       </c>
       <c r="F33" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>19.585</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1165</v>
+        <v>1800</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.67</v>
+        <v>5.57</v>
       </c>
       <c r="F34" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.363</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36.5</v>
+        <v>285</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.2</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.191</v>
+        <v>5.617</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>104</v>
+        <v>224.5</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.56</v>
+        <v>3.46</v>
       </c>
       <c r="F36" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.792</v>
+        <v>3.219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>98</v>
+        <v>41.9</v>
       </c>
       <c r="E37" t="n">
-        <v>-6.22</v>
+        <v>4.1</v>
       </c>
       <c r="F37" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>24.537</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>108.5</v>
+        <v>2355</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.82</v>
+        <v>3.29</v>
       </c>
       <c r="F38" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.831</v>
+        <v>7.579</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>262</v>
+        <v>47.4</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.32</v>
+        <v>0.96</v>
       </c>
       <c r="F39" t="n">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.171</v>
+        <v>2.523</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19.2</v>
+        <v>159</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.24</v>
+        <v>0.63</v>
       </c>
       <c r="F40" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.684</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>46.95</v>
+        <v>213.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-6.01</v>
+        <v>7.29</v>
       </c>
       <c r="F41" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.635</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>61.4</v>
+        <v>218</v>
       </c>
       <c r="E42" t="n">
-        <v>-9.970000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="F42" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.332</v>
+        <v>3.931</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>19.3</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.960000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="F43" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.315</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>58.1</v>
+        <v>63.3</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.14</v>
+        <v>3.77</v>
       </c>
       <c r="F44" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.195</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>116</v>
+        <v>62.1</v>
       </c>
       <c r="E45" t="n">
-        <v>-5.69</v>
+        <v>3.5</v>
       </c>
       <c r="F45" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4.521</v>
+        <v>11.577</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>119.5</v>
       </c>
       <c r="E46" t="n">
-        <v>-4.15</v>
+        <v>3.02</v>
       </c>
       <c r="F46" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>11.628</v>
+        <v>4.581</v>
       </c>
     </row>
     <row r="47">
@@ -2020,13 +2020,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>180</v>
+        <v>189.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-6.25</v>
+        <v>5.28</v>
       </c>
       <c r="F47" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.166</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>199</v>
+        <v>64.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.73</v>
+        <v>4.03</v>
       </c>
       <c r="F48" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.191</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>293.5</v>
+        <v>107.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-9.970000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="F49" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7.912</v>
+        <v>26.234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2255</v>
+        <v>300</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.43</v>
+        <v>2.21</v>
       </c>
       <c r="F50" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,75 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.717</v>
+        <v>7.746</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>61</v>
+        <v>2425</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.44</v>
+        <v>7.54</v>
       </c>
       <c r="F51" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.059</v>
+        <v>3.863</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>226.5</v>
+        <v>257.5</v>
       </c>
       <c r="E52" t="n">
-        <v>-9.94</v>
+        <v>9.81</v>
       </c>
       <c r="F52" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.05</v>
+        <v>24.377</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48.36</v>
+        <v>48.32</v>
       </c>
       <c r="F2" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.717</v>
+        <v>3.863</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>41.41</v>
+        <v>41.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>24.537</v>
+        <v>26.234</v>
       </c>
     </row>
     <row r="4">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33.24</v>
+        <v>29.76</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>4.05</v>
+        <v>3.931</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>27.33</v>
+        <v>28.21</v>
       </c>
       <c r="F5" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>7.912</v>
+        <v>7.746</v>
       </c>
     </row>
     <row r="6">
@@ -2404,60 +2404,60 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26.16</v>
+        <v>19.21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.059</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.13</v>
+        <v>13.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3.11</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
-        <v>2.406</v>
+        <v>9.885999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2466,29 +2466,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.51</v>
+        <v>3.22</v>
       </c>
       <c r="G8" t="n">
-        <v>3.477</v>
+        <v>2.659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2497,168 +2497,168 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.66</v>
+        <v>10.34</v>
       </c>
       <c r="F9" t="n">
-        <v>3.06</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
-        <v>1.388</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.5</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="G10" t="n">
-        <v>8.864000000000001</v>
+        <v>16.959</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.74</v>
+        <v>8.26</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>2.635</v>
+        <v>76.964</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.52</v>
+        <v>6.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>19.585</v>
+        <v>19.941</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.37</v>
+        <v>5.07</v>
       </c>
       <c r="F13" t="n">
-        <v>1.32</v>
+        <v>3.16</v>
       </c>
       <c r="G13" t="n">
-        <v>73.20099999999999</v>
+        <v>1.519</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.96</v>
+        <v>1.63</v>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>2.19</v>
       </c>
       <c r="G14" t="n">
-        <v>19.332</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="15">
@@ -2683,153 +2683,153 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.69</v>
+        <v>1.19</v>
       </c>
       <c r="F15" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="G15" t="n">
-        <v>0.191</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="F16" t="n">
-        <v>0.83</v>
+        <v>1.59</v>
       </c>
       <c r="G16" t="n">
-        <v>21.792</v>
+        <v>2.122</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="F17" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>0.73</v>
+        <v>5.647</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="F18" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>5.464</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.82</v>
+        <v>1.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1.684</v>
+        <v>15.254</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2838,91 +2838,91 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="F20" t="n">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="G20" t="n">
-        <v>2.063</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-0.4</v>
+        <v>-0.84</v>
       </c>
       <c r="F21" t="n">
-        <v>1.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>15.86</v>
+        <v>5.824</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1.26</v>
+        <v>-0.88</v>
       </c>
       <c r="F22" t="n">
-        <v>1.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.483</v>
+        <v>24.063</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2931,75 +2931,75 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-2.02</v>
+        <v>-1.68</v>
       </c>
       <c r="F23" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="G23" t="n">
-        <v>0.887</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-2.03</v>
+        <v>-1.78</v>
       </c>
       <c r="F24" t="n">
-        <v>1.65</v>
+        <v>0.71</v>
       </c>
       <c r="G24" t="n">
-        <v>14.6</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-2.97</v>
+        <v>-2.87</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="G25" t="n">
-        <v>5.617</v>
+        <v>2.523</v>
       </c>
     </row>
     <row r="26">
@@ -3024,199 +3024,199 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-3.96</v>
+        <v>-2.9</v>
       </c>
       <c r="F26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="G26" t="n">
-        <v>1.833</v>
+        <v>1.871</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-4.44</v>
+        <v>-3.59</v>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="G27" t="n">
-        <v>1.972</v>
+        <v>5.052</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-5.6</v>
+        <v>-4.54</v>
       </c>
       <c r="F28" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="G28" t="n">
-        <v>1.415</v>
+        <v>2.033</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-7.41</v>
+        <v>-4.98</v>
       </c>
       <c r="F29" t="n">
-        <v>0.67</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>11.628</v>
+        <v>2.343</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-8.42</v>
+        <v>-5.43</v>
       </c>
       <c r="F30" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="G30" t="n">
-        <v>4.535</v>
+        <v>1.398</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-8.67</v>
+        <v>-5.86</v>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G31" t="n">
-        <v>0.592</v>
+        <v>4.704</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-8.789999999999999</v>
+        <v>-6.91</v>
       </c>
       <c r="F32" t="n">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="G32" t="n">
-        <v>0.115</v>
+        <v>1.417</v>
       </c>
     </row>
     <row r="33">
@@ -3241,432 +3241,432 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-9.039999999999999</v>
+        <v>-7.1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G33" t="n">
-        <v>5.879</v>
+        <v>6.119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-9.59</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="G34" t="n">
-        <v>4.919</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-11.84</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="G35" t="n">
-        <v>2.195</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-11.97</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="G36" t="n">
-        <v>3.173</v>
+        <v>24.377</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-12.15</v>
+        <v>-9.99</v>
       </c>
       <c r="F37" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="G37" t="n">
-        <v>0.831</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-12.2</v>
+        <v>-10.11</v>
       </c>
       <c r="F38" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="G38" t="n">
-        <v>2.166</v>
+        <v>7.579</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-12.23</v>
+        <v>-10.38</v>
       </c>
       <c r="F39" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1.674</v>
+        <v>2.386</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-12.76</v>
+        <v>-10.39</v>
       </c>
       <c r="F40" t="n">
-        <v>1.49</v>
+        <v>0.62</v>
       </c>
       <c r="G40" t="n">
-        <v>1.133</v>
+        <v>11.577</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-13.63</v>
+        <v>-10.98</v>
       </c>
       <c r="F41" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>23.255</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-13.7</v>
+        <v>-11.56</v>
       </c>
       <c r="F42" t="n">
-        <v>0.95</v>
+        <v>1.52</v>
       </c>
       <c r="G42" t="n">
-        <v>1.363</v>
+        <v>1.166</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-14.75</v>
+        <v>-11.8</v>
       </c>
       <c r="F43" t="n">
         <v>0.97</v>
       </c>
       <c r="G43" t="n">
-        <v>14.232</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-15.06</v>
+        <v>-12.82</v>
       </c>
       <c r="F44" t="n">
         <v>0.86</v>
       </c>
       <c r="G44" t="n">
-        <v>2.22</v>
+        <v>3.219</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-16.15</v>
+        <v>-13.25</v>
       </c>
       <c r="F45" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="G45" t="n">
-        <v>0.981</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-16.33</v>
+        <v>-15.45</v>
       </c>
       <c r="F46" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="G46" t="n">
-        <v>7.474</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3675,106 +3675,106 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-16.56</v>
+        <v>-15.96</v>
       </c>
       <c r="F47" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="G47" t="n">
-        <v>2.191</v>
+        <v>2.258</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-16.69</v>
+        <v>-16</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9</v>
+        <v>1.46</v>
       </c>
       <c r="G48" t="n">
-        <v>5.171</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-16.78</v>
+        <v>-16.34</v>
       </c>
       <c r="F49" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="G49" t="n">
-        <v>0.841</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-17.44</v>
+        <v>-17.51</v>
       </c>
       <c r="F50" t="n">
         <v>0.82</v>
       </c>
       <c r="G50" t="n">
-        <v>0.315</v>
+        <v>5.617</v>
       </c>
     </row>
     <row r="51">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-20.82</v>
+        <v>-17.59</v>
       </c>
       <c r="F51" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G51" t="n">
-        <v>4.521</v>
+        <v>4.581</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-22.18</v>
+        <v>-18.74</v>
       </c>
       <c r="F52" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="G52" t="n">
-        <v>0.094</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.36</v>
+        <v>48.32</v>
       </c>
       <c r="C2" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="D2" t="n">
-        <v>3.717</v>
+        <v>3.863</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.41</v>
+        <v>41.08</v>
       </c>
       <c r="C3" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>24.537</v>
+        <v>26.234</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.45666666666667</v>
+        <v>19.86666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.306666666666667</v>
+        <v>1.236666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>12.692</v>
+        <v>12.468</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3940,55 +3940,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.78</v>
+        <v>13.3</v>
       </c>
       <c r="C5" t="n">
-        <v>2.893333333333333</v>
+        <v>1.14</v>
       </c>
       <c r="D5" t="n">
-        <v>7.271</v>
+        <v>9.885999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.745000000000001</v>
+        <v>8.636666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8300000000000001</v>
+        <v>2.986666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>1.651</v>
+        <v>7.949</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.5</v>
+        <v>6.27</v>
       </c>
       <c r="C7" t="n">
-        <v>1.15</v>
+        <v>0.88</v>
       </c>
       <c r="D7" t="n">
-        <v>8.864000000000001</v>
+        <v>19.941</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,55 +3997,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.74</v>
+        <v>5.165</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2</v>
+        <v>0.845</v>
       </c>
       <c r="D8" t="n">
-        <v>2.635</v>
+        <v>1.674</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.52</v>
+        <v>2.475</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D9" t="n">
-        <v>19.585</v>
+        <v>22.011</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.96</v>
+        <v>1.19</v>
       </c>
       <c r="C10" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="D10" t="n">
-        <v>19.332</v>
+        <v>0.193</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.69</v>
+        <v>0.28</v>
       </c>
       <c r="C11" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="D11" t="n">
-        <v>0.191</v>
+        <v>18.792</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="C12" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>21.792</v>
+        <v>5.824</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,17 +4092,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.26</v>
+        <v>-0.88</v>
       </c>
       <c r="C13" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.684</v>
+        <v>24.063</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.02</v>
+        <v>-1.065</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="D14" t="n">
-        <v>84.82899999999999</v>
+        <v>88.541</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.336</v>
+        <v>-1.754</v>
       </c>
       <c r="C15" t="n">
-        <v>1.36</v>
+        <v>1.308</v>
       </c>
       <c r="D15" t="n">
-        <v>7.238</v>
+        <v>7.391</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -4149,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-2.97</v>
+        <v>-1.78</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="D16" t="n">
-        <v>5.617</v>
+        <v>1.653</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,74 +4168,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-4.995</v>
+        <v>-2.87</v>
       </c>
       <c r="C17" t="n">
-        <v>1.325</v>
+        <v>0.99</v>
       </c>
       <c r="D17" t="n">
-        <v>20.779</v>
+        <v>2.523</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-5.6</v>
+        <v>-3.745</v>
       </c>
       <c r="C18" t="n">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="D18" t="n">
-        <v>1.415</v>
+        <v>26.534</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-6.56</v>
+        <v>-5.43</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4775</v>
+        <v>1.1</v>
       </c>
       <c r="D19" t="n">
-        <v>25.58</v>
+        <v>1.398</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-8.789999999999999</v>
+        <v>-6.91</v>
       </c>
       <c r="C20" t="n">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="D20" t="n">
-        <v>0.115</v>
+        <v>1.417</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-11.905</v>
+        <v>-8.605</v>
       </c>
       <c r="C21" t="n">
-        <v>1.425</v>
+        <v>0.8899999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>5.368</v>
+        <v>13.698</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-12.23</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
       <c r="D22" t="n">
-        <v>1.674</v>
+        <v>0.119</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-12.685</v>
+        <v>-8.9</v>
       </c>
       <c r="C23" t="n">
-        <v>0.895</v>
+        <v>1.29</v>
       </c>
       <c r="D23" t="n">
-        <v>13.353</v>
+        <v>5.561999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4301,55 +4301,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-13.605</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.735</v>
+        <v>0.7</v>
       </c>
       <c r="D24" t="n">
-        <v>3.051</v>
+        <v>24.377</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-13.63</v>
+        <v>-10.68</v>
       </c>
       <c r="C25" t="n">
-        <v>0.76</v>
+        <v>0.845</v>
       </c>
       <c r="D25" t="n">
-        <v>23.255</v>
+        <v>3.192</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-13.7</v>
+        <v>-11.8</v>
       </c>
       <c r="C26" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="D26" t="n">
-        <v>1.363</v>
+        <v>1.732</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-14.75</v>
+        <v>-13.25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="D27" t="n">
-        <v>14.232</v>
+        <v>14.99</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-14.77</v>
+        <v>-13.78</v>
       </c>
       <c r="C28" t="n">
-        <v>1.475</v>
+        <v>1.49</v>
       </c>
       <c r="D28" t="n">
-        <v>1.974</v>
+        <v>2.052</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-15.15</v>
+        <v>-16.30666666666667</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="D29" t="n">
-        <v>9.528</v>
+        <v>10.074</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-17.44</v>
+        <v>-16.34</v>
       </c>
       <c r="C30" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="D30" t="n">
-        <v>0.315</v>
+        <v>0.306</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-20.82</v>
+        <v>-17.59</v>
       </c>
       <c r="C31" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="D31" t="n">
-        <v>4.521</v>
+        <v>4.581</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-22.18</v>
+        <v>-18.74</v>
       </c>
       <c r="C32" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="D32" t="n">
-        <v>0.094</v>
+        <v>0.1</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1705</v>
+        <v>1800</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.85</v>
+        <v>5.57</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.75</v>
+        <v>-13.25</v>
       </c>
       <c r="G2" t="n">
-        <v>31.36</v>
+        <v>41.52</v>
       </c>
       <c r="H2" t="n">
-        <v>-9.4673</v>
+        <v>-15.8986</v>
       </c>
       <c r="I2" t="n">
-        <v>8.5</v>
+        <v>24.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K2" t="n">
-        <v>9.17</v>
+        <v>7.98</v>
       </c>
       <c r="L2" t="n">
-        <v>16.4</v>
+        <v>-36.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1720</v>
+        <v>1775</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.23</v>
+        <v>3.2</v>
       </c>
       <c r="F3" t="n">
-        <v>5.52</v>
+        <v>0.28</v>
       </c>
       <c r="G3" t="n">
-        <v>50.98</v>
+        <v>48.63</v>
       </c>
       <c r="H3" t="n">
-        <v>64.5646</v>
+        <v>56.992</v>
       </c>
       <c r="I3" t="n">
-        <v>16.4</v>
+        <v>38.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>27.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.71</v>
+        <v>4.49</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.2</v>
+        <v>-26.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>63.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.44</v>
+        <v>3.77</v>
       </c>
       <c r="F4" t="n">
-        <v>26.16</v>
+        <v>19.21</v>
       </c>
       <c r="G4" t="n">
-        <v>36.26</v>
+        <v>38.48</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9612</v>
+        <v>2.4232</v>
       </c>
       <c r="I4" t="n">
-        <v>23.7</v>
+        <v>27.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="K4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-63.2</v>
+        <v>-49.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>64.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.960000000000001</v>
+        <v>4.03</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.44</v>
+        <v>-16.34</v>
       </c>
       <c r="G5" t="n">
-        <v>46.75</v>
+        <v>50.87</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6735</v>
+        <v>-0.9016</v>
       </c>
       <c r="I5" t="n">
-        <v>22.6</v>
+        <v>35.5</v>
       </c>
       <c r="J5" t="n">
-        <v>9.199999999999999</v>
+        <v>28.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.01</v>
+        <v>5.77</v>
       </c>
       <c r="L5" t="n">
-        <v>-40.4</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>226.5</v>
+        <v>218</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.94</v>
+        <v>-3.75</v>
       </c>
       <c r="F6" t="n">
-        <v>33.24</v>
+        <v>29.76</v>
       </c>
       <c r="G6" t="n">
-        <v>69.66</v>
+        <v>63.45</v>
       </c>
       <c r="H6" t="n">
-        <v>17.7319</v>
+        <v>17.2365</v>
       </c>
       <c r="I6" t="n">
-        <v>86.5</v>
+        <v>75.7</v>
       </c>
       <c r="J6" t="n">
-        <v>71.3</v>
+        <v>61.5</v>
       </c>
       <c r="K6" t="n">
-        <v>7.22</v>
+        <v>8.16</v>
       </c>
       <c r="L6" t="n">
-        <v>-64.5</v>
+        <v>-45.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,38 +4832,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.24</v>
+        <v>3.23</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.03</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>51.8</v>
+        <v>55.03</v>
       </c>
       <c r="H7" t="n">
-        <v>0.979</v>
+        <v>0.536</v>
       </c>
       <c r="I7" t="n">
-        <v>28.1</v>
+        <v>47.1</v>
       </c>
       <c r="J7" t="n">
-        <v>6.3</v>
+        <v>28.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>74.3</v>
+        <v>-20.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>1285</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.66</v>
+        <v>0.39</v>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>271</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.659</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78.7</v>
+        <v>39.15</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.44</v>
+        <v>2.09</v>
       </c>
       <c r="F3" t="n">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,101 +538,101 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.519</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>287.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.19</v>
+        <v>0.88</v>
       </c>
       <c r="F4" t="n">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.791</v>
+        <v>5.662</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>88.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.72</v>
+        <v>-1.88</v>
       </c>
       <c r="F5" t="n">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.771</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>233</v>
       </c>
       <c r="E6" t="n">
-        <v>1.61</v>
+        <v>-9.51</v>
       </c>
       <c r="F6" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,30 +640,30 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.886</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>470.5</v>
+        <v>60.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4.91</v>
+        <v>1.17</v>
       </c>
       <c r="F7" t="n">
         <v>133</v>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.386</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1280</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>9.869999999999999</v>
+        <v>-0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.417</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>353.5</v>
+        <v>126</v>
       </c>
       <c r="E9" t="n">
-        <v>7.94</v>
+        <v>0.8</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.885999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.2</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,203 +776,203 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.119</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1900</v>
+        <v>29.35</v>
       </c>
       <c r="E11" t="n">
-        <v>1.88</v>
+        <v>0.51</v>
       </c>
       <c r="F11" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>76.964</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34.05</v>
+        <v>210.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.59</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.166</v>
+        <v>3.874</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73.59999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.55</v>
+        <v>5.91</v>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.033</v>
+        <v>2.289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38.35</v>
+        <v>217</v>
       </c>
       <c r="E14" t="n">
-        <v>5.07</v>
+        <v>1.64</v>
       </c>
       <c r="F14" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.193</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1335</v>
+        <v>34.25</v>
       </c>
       <c r="E15" t="n">
-        <v>6.37</v>
+        <v>0.59</v>
       </c>
       <c r="F15" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.959</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>289.5</v>
+        <v>1320</v>
       </c>
       <c r="E16" t="n">
-        <v>3.02</v>
+        <v>-1.12</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.647</v>
+        <v>16.876</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>128.5</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>-0.82</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,67 +1014,67 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4.704</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90.5</v>
+        <v>1890</v>
       </c>
       <c r="E18" t="n">
-        <v>0.78</v>
+        <v>-0.53</v>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.871</v>
+        <v>76.663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>374.5</v>
+        <v>51.4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.19</v>
       </c>
       <c r="F19" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,67 +1082,67 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.398</v>
+        <v>2.102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>456</v>
+        <v>102.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.47</v>
+        <v>-4.65</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.732</v>
+        <v>24.109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>23.4</v>
+        <v>1770</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.21</v>
+        <v>-1.67</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.481</v>
+        <v>14.784</v>
       </c>
     </row>
     <row r="22">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>295</v>
+        <v>284.5</v>
       </c>
       <c r="E22" t="n">
-        <v>6.12</v>
+        <v>-3.56</v>
       </c>
       <c r="F22" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,101 +1184,101 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.824</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>51.5</v>
+        <v>289</v>
       </c>
       <c r="E23" t="n">
-        <v>1.98</v>
+        <v>-0.17</v>
       </c>
       <c r="F23" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.122</v>
+        <v>5.663</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.9</v>
+        <v>39.3</v>
       </c>
       <c r="E24" t="n">
-        <v>8.26</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.343</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>224</v>
+        <v>375</v>
       </c>
       <c r="E25" t="n">
-        <v>3.23</v>
+        <v>0.13</v>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,67 +1286,67 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>15.254</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39.3</v>
+        <v>3310</v>
       </c>
       <c r="E26" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.884</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>112</v>
+        <v>2385</v>
       </c>
       <c r="E27" t="n">
-        <v>7.69</v>
+        <v>1.27</v>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24.063</v>
+        <v>7.461</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>161</v>
+        <v>130.5</v>
       </c>
       <c r="E28" t="n">
-        <v>3.54</v>
+        <v>1.56</v>
       </c>
       <c r="F28" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.052</v>
+        <v>4.662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3270</v>
+        <v>106.5</v>
       </c>
       <c r="E29" t="n">
-        <v>4.81</v>
+        <v>-4.91</v>
       </c>
       <c r="F29" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.119</v>
+        <v>22.045</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1775</v>
+        <v>467</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>-0.74</v>
       </c>
       <c r="F30" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>18.792</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>64.40000000000001</v>
+        <v>200.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.89</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>19.941</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>199.5</v>
+        <v>23.4</v>
       </c>
       <c r="E32" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.1</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>113.5</v>
+        <v>223</v>
       </c>
       <c r="E33" t="n">
-        <v>4.61</v>
+        <v>-0.45</v>
       </c>
       <c r="F33" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.806</v>
+        <v>15.193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1800</v>
+        <v>159</v>
       </c>
       <c r="E34" t="n">
-        <v>5.57</v>
+        <v>-1.24</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14.99</v>
+        <v>4.939</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>285</v>
+        <v>61.9</v>
       </c>
       <c r="E35" t="n">
-        <v>8.779999999999999</v>
+        <v>-1.59</v>
       </c>
       <c r="F35" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.617</v>
+        <v>2.224</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>224.5</v>
+        <v>463</v>
       </c>
       <c r="E36" t="n">
-        <v>3.46</v>
+        <v>1.54</v>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.219</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>41.9</v>
+        <v>64.3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.1</v>
+        <v>-0.16</v>
       </c>
       <c r="F37" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.929</v>
+        <v>19.522</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2355</v>
+        <v>225</v>
       </c>
       <c r="E38" t="n">
-        <v>3.29</v>
+        <v>0.22</v>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.579</v>
+        <v>2.996</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>47.4</v>
+        <v>342</v>
       </c>
       <c r="E39" t="n">
-        <v>0.96</v>
+        <v>-3.25</v>
       </c>
       <c r="F39" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.523</v>
+        <v>9.581</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>159</v>
+        <v>61.7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.63</v>
+        <v>-2.53</v>
       </c>
       <c r="F40" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.591</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>213.5</v>
+        <v>1765</v>
       </c>
       <c r="E41" t="n">
-        <v>7.29</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.199</v>
+        <v>18.043</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>218</v>
+        <v>41.8</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.75</v>
+        <v>-0.24</v>
       </c>
       <c r="F42" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.931</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>19.3</v>
+        <v>186</v>
       </c>
       <c r="E43" t="n">
-        <v>0.52</v>
+        <v>-1.85</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.653</v>
+        <v>1.967</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>63.3</v>
+        <v>19.9</v>
       </c>
       <c r="E44" t="n">
-        <v>3.77</v>
+        <v>3.11</v>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.083</v>
+        <v>1.684</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>62.1</v>
+        <v>158.5</v>
       </c>
       <c r="E45" t="n">
-        <v>3.5</v>
+        <v>-0.31</v>
       </c>
       <c r="F45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>11.577</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>119.5</v>
+        <v>115</v>
       </c>
       <c r="E46" t="n">
-        <v>3.02</v>
+        <v>1.32</v>
       </c>
       <c r="F46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.581</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>189.5</v>
+        <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>5.28</v>
+        <v>-0.16</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.258</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>64.5</v>
+        <v>118.5</v>
       </c>
       <c r="E48" t="n">
-        <v>4.03</v>
+        <v>-0.84</v>
       </c>
       <c r="F48" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.306</v>
+        <v>4.361</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>107.5</v>
+        <v>217</v>
       </c>
       <c r="E49" t="n">
-        <v>9.69</v>
+        <v>-0.46</v>
       </c>
       <c r="F49" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>26.234</v>
+        <v>3.825</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>300</v>
+        <v>2390</v>
       </c>
       <c r="E50" t="n">
-        <v>2.21</v>
+        <v>-1.44</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,75 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>7.746</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2425</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>7.54</v>
+        <v>-0.62</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.863</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>257.5</v>
+        <v>298.5</v>
       </c>
       <c r="E52" t="n">
-        <v>9.81</v>
+        <v>-0.5</v>
       </c>
       <c r="F52" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>24.377</v>
+        <v>7.313</v>
       </c>
     </row>
   </sheetData>
@@ -2261,63 +2261,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48.32</v>
+        <v>34.51</v>
       </c>
       <c r="F2" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>3.863</v>
+        <v>24.109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>41.08</v>
+        <v>33.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="G3" t="n">
-        <v>26.234</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="4">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29.76</v>
+        <v>26.53</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="G4" t="n">
-        <v>3.931</v>
+        <v>3.825</v>
       </c>
     </row>
     <row r="5">
@@ -2373,168 +2373,168 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28.21</v>
+        <v>23.86</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>0.59</v>
       </c>
       <c r="G5" t="n">
-        <v>7.746</v>
+        <v>7.313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19.21</v>
+        <v>12.62</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>3.17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.083</v>
+        <v>2.848</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.3</v>
+        <v>12.57</v>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="G7" t="n">
-        <v>9.885999999999999</v>
+        <v>3.874</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.5</v>
+        <v>11.58</v>
       </c>
       <c r="F8" t="n">
-        <v>3.22</v>
+        <v>0.96</v>
       </c>
       <c r="G8" t="n">
-        <v>2.659</v>
+        <v>9.581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.34</v>
+        <v>8.07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>0.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3.771</v>
+        <v>19.522</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8.539999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.21</v>
+        <v>3.16</v>
       </c>
       <c r="G10" t="n">
-        <v>16.959</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="11">
@@ -2559,463 +2559,463 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.26</v>
+        <v>6.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G11" t="n">
-        <v>76.964</v>
+        <v>76.663</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.27</v>
+        <v>5.65</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="G12" t="n">
-        <v>19.941</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.07</v>
+        <v>5.6</v>
       </c>
       <c r="F13" t="n">
-        <v>3.16</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.519</v>
+        <v>16.876</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.63</v>
+        <v>4.4</v>
       </c>
       <c r="F14" t="n">
-        <v>2.19</v>
+        <v>1.37</v>
       </c>
       <c r="G14" t="n">
-        <v>0.791</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.19</v>
+        <v>2.84</v>
       </c>
       <c r="F15" t="n">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="G15" t="n">
-        <v>0.193</v>
+        <v>1.684</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.98</v>
+        <v>1.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="G16" t="n">
-        <v>2.122</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.87</v>
+        <v>1.18</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="G17" t="n">
-        <v>5.647</v>
+        <v>2.102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.28</v>
+        <v>0.52</v>
       </c>
       <c r="F18" t="n">
-        <v>0.96</v>
+        <v>1.32</v>
       </c>
       <c r="G18" t="n">
-        <v>18.792</v>
+        <v>5.663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="F19" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="G19" t="n">
-        <v>15.254</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.63</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="G20" t="n">
-        <v>0.884</v>
+        <v>18.043</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-0.84</v>
+        <v>-1.11</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="G21" t="n">
-        <v>5.824</v>
+        <v>15.193</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-0.88</v>
+        <v>-1.27</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>24.063</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-1.68</v>
+        <v>-1.57</v>
       </c>
       <c r="F23" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>0.481</v>
+        <v>2.289</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-1.78</v>
+        <v>-2.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.71</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>1.653</v>
+        <v>4.662</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-2.87</v>
+        <v>-3.5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="G25" t="n">
-        <v>2.523</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3024,571 +3024,571 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-2.9</v>
+        <v>-3.82</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="G26" t="n">
-        <v>1.871</v>
+        <v>1.992</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-3.59</v>
+        <v>-3.9</v>
       </c>
       <c r="F27" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="G27" t="n">
-        <v>5.052</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-4.54</v>
+        <v>-5.06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.47</v>
+        <v>0.91</v>
       </c>
       <c r="G28" t="n">
-        <v>2.033</v>
+        <v>1.369</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-4.98</v>
+        <v>-5.17</v>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>0.79</v>
       </c>
       <c r="G29" t="n">
-        <v>2.343</v>
+        <v>5.403</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-5.43</v>
+        <v>-6.19</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1</v>
+        <v>0.89</v>
       </c>
       <c r="G30" t="n">
-        <v>1.398</v>
+        <v>4.939</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-5.86</v>
+        <v>-6.97</v>
       </c>
       <c r="F31" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="G31" t="n">
-        <v>4.704</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-6.91</v>
+        <v>-7.06</v>
       </c>
       <c r="F32" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="G32" t="n">
-        <v>1.417</v>
+        <v>2.224</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-7.1</v>
+        <v>-7.63</v>
       </c>
       <c r="F33" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="G33" t="n">
-        <v>6.119</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-8.880000000000001</v>
+        <v>-7.74</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>0.591</v>
+        <v>7.461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.79</v>
       </c>
       <c r="F35" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="G35" t="n">
-        <v>0.119</v>
+        <v>22.045</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-9.970000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="G36" t="n">
-        <v>24.377</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-9.99</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="G37" t="n">
-        <v>0.929</v>
+        <v>1.473</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-10.11</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="G38" t="n">
-        <v>7.579</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-10.38</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="G39" t="n">
-        <v>2.386</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-10.39</v>
+        <v>-10.57</v>
       </c>
       <c r="F40" t="n">
-        <v>0.62</v>
+        <v>1.38</v>
       </c>
       <c r="G40" t="n">
-        <v>11.577</v>
+        <v>1.174</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-10.98</v>
+        <v>-11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G41" t="n">
-        <v>0.806</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-11.56</v>
+        <v>-12.64</v>
       </c>
       <c r="F42" t="n">
-        <v>1.52</v>
+        <v>0.83</v>
       </c>
       <c r="G42" t="n">
-        <v>1.166</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-11.8</v>
+        <v>-14.61</v>
       </c>
       <c r="F43" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="G43" t="n">
-        <v>1.732</v>
+        <v>2.996</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-12.82</v>
+        <v>-15.88</v>
       </c>
       <c r="F44" t="n">
         <v>0.86</v>
       </c>
       <c r="G44" t="n">
-        <v>3.219</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="45">
@@ -3613,137 +3613,137 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-13.25</v>
+        <v>-16.51</v>
       </c>
       <c r="F45" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="G45" t="n">
-        <v>14.99</v>
+        <v>14.784</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-15.45</v>
+        <v>-17.47</v>
       </c>
       <c r="F46" t="n">
-        <v>0.59</v>
+        <v>1.44</v>
       </c>
       <c r="G46" t="n">
-        <v>2.199</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-15.96</v>
+        <v>-17.82</v>
       </c>
       <c r="F47" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>2.258</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-16</v>
+        <v>-18.64</v>
       </c>
       <c r="F48" t="n">
-        <v>1.46</v>
+        <v>0.55</v>
       </c>
       <c r="G48" t="n">
-        <v>0.886</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-16.34</v>
+        <v>-18.83</v>
       </c>
       <c r="F49" t="n">
-        <v>0.67</v>
+        <v>1.09</v>
       </c>
       <c r="G49" t="n">
-        <v>0.306</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="50">
@@ -3768,75 +3768,75 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-17.51</v>
+        <v>-19.24</v>
       </c>
       <c r="F50" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="G50" t="n">
-        <v>5.617</v>
+        <v>5.662</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-17.59</v>
+        <v>-25</v>
       </c>
       <c r="F51" t="n">
         <v>0.57</v>
       </c>
       <c r="G51" t="n">
-        <v>4.581</v>
+        <v>1.967</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-18.74</v>
+        <v>-25.71</v>
       </c>
       <c r="F52" t="n">
-        <v>1.55</v>
+        <v>0.55</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1</v>
+        <v>4.361</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.32</v>
+        <v>34.51</v>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="D2" t="n">
-        <v>3.863</v>
+        <v>24.109</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.08</v>
+        <v>33.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="D3" t="n">
-        <v>26.234</v>
+        <v>3.665</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.86666666666667</v>
+        <v>17.19666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>1.236666666666667</v>
+        <v>1.08</v>
       </c>
       <c r="D4" t="n">
-        <v>12.468</v>
+        <v>11.952</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.3</v>
+        <v>11.58</v>
       </c>
       <c r="C5" t="n">
-        <v>1.14</v>
+        <v>0.96</v>
       </c>
       <c r="D5" t="n">
-        <v>9.885999999999999</v>
+        <v>9.581</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.636666666666667</v>
+        <v>10.47</v>
       </c>
       <c r="C6" t="n">
-        <v>2.986666666666667</v>
+        <v>2.926666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>7.949</v>
+        <v>8.302</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.27</v>
+        <v>8.07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="D7" t="n">
-        <v>19.941</v>
+        <v>19.522</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,58 +3997,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.165</v>
+        <v>4.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.845</v>
+        <v>1.37</v>
       </c>
       <c r="D8" t="n">
-        <v>1.674</v>
+        <v>0.191</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.475</v>
+        <v>2.84</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="D9" t="n">
-        <v>22.011</v>
+        <v>1.684</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.19</v>
+        <v>-0.2950000000000004</v>
       </c>
       <c r="C10" t="n">
-        <v>0.98</v>
+        <v>0.9950000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.193</v>
+        <v>21.815</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>18.792</v>
+        <v>18.043</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.84</v>
+        <v>-1.57</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="D12" t="n">
-        <v>5.824</v>
+        <v>2.289</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,36 +4092,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.88</v>
+        <v>-1.638</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.108</v>
       </c>
       <c r="D13" t="n">
-        <v>24.063</v>
+        <v>7.327</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.065</v>
+        <v>-2.774999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.97</v>
+        <v>0.735</v>
       </c>
       <c r="D14" t="n">
-        <v>88.541</v>
+        <v>1.564</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4130,36 +4130,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.754</v>
+        <v>-2.9225</v>
       </c>
       <c r="C15" t="n">
-        <v>1.308</v>
+        <v>1.095</v>
       </c>
       <c r="D15" t="n">
-        <v>7.391</v>
+        <v>26.382</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.78</v>
+        <v>-5.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="D16" t="n">
-        <v>1.653</v>
+        <v>1.369</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-2.87</v>
+        <v>-5.17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="D17" t="n">
-        <v>2.523</v>
+        <v>5.403</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,55 +4187,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-3.745</v>
+        <v>-5.62</v>
       </c>
       <c r="C18" t="n">
-        <v>1.23</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>26.534</v>
+        <v>13.361</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-5.43</v>
+        <v>-6.23</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1</v>
+        <v>0.865</v>
       </c>
       <c r="D19" t="n">
-        <v>1.398</v>
+        <v>86.84299999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-6.91</v>
+        <v>-6.97</v>
       </c>
       <c r="C20" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="D20" t="n">
-        <v>1.417</v>
+        <v>0.119</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,131 +4244,131 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-8.605</v>
+        <v>-7.79</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="D21" t="n">
-        <v>13.698</v>
+        <v>22.045</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1.25</v>
+        <v>0.835</v>
       </c>
       <c r="D22" t="n">
-        <v>0.119</v>
+        <v>3.089</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-8.9</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="D23" t="n">
-        <v>5.561999999999999</v>
+        <v>1.473</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-9.970000000000001</v>
+        <v>-10.835</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7</v>
+        <v>1.025</v>
       </c>
       <c r="D24" t="n">
-        <v>24.377</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-10.68</v>
+        <v>-12.64</v>
       </c>
       <c r="C25" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="D25" t="n">
-        <v>3.192</v>
+        <v>1.721</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-11.8</v>
+        <v>-14.02</v>
       </c>
       <c r="C26" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
       <c r="D26" t="n">
-        <v>1.732</v>
+        <v>2.053</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-13.25</v>
+        <v>-15.88</v>
       </c>
       <c r="C27" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="D27" t="n">
-        <v>14.99</v>
+        <v>23.022</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,74 +4377,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-13.78</v>
+        <v>-16.51</v>
       </c>
       <c r="C28" t="n">
-        <v>1.49</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="n">
-        <v>2.052</v>
+        <v>14.784</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-16.30666666666667</v>
+        <v>-17.82</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>10.074</v>
+        <v>0.274</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-16.34</v>
+        <v>-18.06666666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>0.67</v>
+        <v>0.7433333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>0.306</v>
+        <v>9.809000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-17.59</v>
+        <v>-18.83</v>
       </c>
       <c r="C31" t="n">
-        <v>0.57</v>
+        <v>1.09</v>
       </c>
       <c r="D31" t="n">
-        <v>4.581</v>
+        <v>0.098</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-18.74</v>
+        <v>-25.71</v>
       </c>
       <c r="C32" t="n">
-        <v>1.55</v>
+        <v>0.55</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1</v>
+        <v>4.361</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>1770</v>
       </c>
       <c r="E2" t="n">
-        <v>5.57</v>
+        <v>-1.67</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.25</v>
+        <v>-16.51</v>
       </c>
       <c r="G2" t="n">
-        <v>41.52</v>
+        <v>36.87</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.8986</v>
+        <v>-37.5009</v>
       </c>
       <c r="I2" t="n">
-        <v>24.3</v>
+        <v>23.1</v>
       </c>
       <c r="J2" t="n">
-        <v>26</v>
+        <v>17.8</v>
       </c>
       <c r="K2" t="n">
-        <v>7.98</v>
+        <v>8.07</v>
       </c>
       <c r="L2" t="n">
-        <v>-36.7</v>
+        <v>-27.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1775</v>
+        <v>1765</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>48.63</v>
+        <v>47.62</v>
       </c>
       <c r="H3" t="n">
-        <v>56.992</v>
+        <v>53.0835</v>
       </c>
       <c r="I3" t="n">
-        <v>38.7</v>
+        <v>34.9</v>
       </c>
       <c r="J3" t="n">
-        <v>27.7</v>
+        <v>23.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="L3" t="n">
-        <v>-26.1</v>
+        <v>-56.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63.3</v>
+        <v>61.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3.77</v>
+        <v>-2.53</v>
       </c>
       <c r="F4" t="n">
-        <v>19.21</v>
+        <v>5.65</v>
       </c>
       <c r="G4" t="n">
-        <v>38.48</v>
+        <v>40.41</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4232</v>
+        <v>1.8545</v>
       </c>
       <c r="I4" t="n">
-        <v>27.8</v>
+        <v>17.7</v>
       </c>
       <c r="J4" t="n">
-        <v>16.1</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="L4" t="n">
-        <v>-49.9</v>
+        <v>-56</v>
       </c>
       <c r="M4" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>4.03</v>
+        <v>-0.62</v>
       </c>
       <c r="F5" t="n">
-        <v>-16.34</v>
+        <v>-17.82</v>
       </c>
       <c r="G5" t="n">
-        <v>50.87</v>
+        <v>48.82</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9016</v>
+        <v>-0.7541</v>
       </c>
       <c r="I5" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J5" t="n">
-        <v>28.2</v>
+        <v>25.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.77</v>
+        <v>5.79</v>
       </c>
       <c r="L5" t="n">
-        <v>-65.90000000000001</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.75</v>
+        <v>-0.46</v>
       </c>
       <c r="F6" t="n">
-        <v>29.76</v>
+        <v>26.53</v>
       </c>
       <c r="G6" t="n">
-        <v>63.45</v>
+        <v>60.92</v>
       </c>
       <c r="H6" t="n">
-        <v>17.2365</v>
+        <v>16.4923</v>
       </c>
       <c r="I6" t="n">
-        <v>75.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>61.5</v>
+        <v>60.3</v>
       </c>
       <c r="K6" t="n">
         <v>8.16</v>
       </c>
       <c r="L6" t="n">
-        <v>-45.2</v>
+        <v>-77</v>
       </c>
       <c r="M6" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
-        <v>3.23</v>
+        <v>-0.45</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>55.03</v>
+        <v>52.74</v>
       </c>
       <c r="H7" t="n">
-        <v>0.536</v>
+        <v>0.4776</v>
       </c>
       <c r="I7" t="n">
-        <v>47.1</v>
+        <v>44.7</v>
       </c>
       <c r="J7" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="L7" t="n">
-        <v>-20.1</v>
+        <v>-46.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1285</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.39</v>
+        <v>3.18</v>
       </c>
       <c r="F2" t="n">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,135 +504,135 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.473</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39.15</v>
+        <v>47.35</v>
       </c>
       <c r="E3" t="n">
-        <v>2.09</v>
+        <v>-5.68</v>
       </c>
       <c r="F3" t="n">
-        <v>241</v>
+        <v>312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.191</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>287.5</v>
+        <v>61.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>1.48</v>
       </c>
       <c r="F4" t="n">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.662</v>
+        <v>3.353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88.8</v>
+        <v>210.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.893</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>233</v>
+        <v>304</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.51</v>
+        <v>5.74</v>
       </c>
       <c r="F6" t="n">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,135 +640,135 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>23.022</v>
+        <v>6.311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60.7</v>
+        <v>32.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.17</v>
+        <v>-5.11</v>
       </c>
       <c r="F7" t="n">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.848</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.13</v>
+        <v>-1.8</v>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.58</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>126</v>
+        <v>1810</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>-4.23</v>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8139999999999999</v>
+        <v>77.68600000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.9</v>
+        <v>27.75</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-5.45</v>
       </c>
       <c r="F10" t="n">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.879</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29.35</v>
+        <v>1220</v>
       </c>
       <c r="E11" t="n">
-        <v>0.51</v>
+        <v>-7.58</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,203 +810,203 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.119</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>210.5</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2</v>
+        <v>-0.78</v>
       </c>
       <c r="F12" t="n">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.874</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50.2</v>
+        <v>1220</v>
       </c>
       <c r="E13" t="n">
-        <v>5.91</v>
+        <v>-5.06</v>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.289</v>
+        <v>1.446</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>217</v>
+        <v>484</v>
       </c>
       <c r="E14" t="n">
-        <v>1.64</v>
+        <v>4.54</v>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34.25</v>
+        <v>37.15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.59</v>
+        <v>-5.11</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.174</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1320</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.12</v>
+        <v>-4.11</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16.876</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>272</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.82</v>
+        <v>-4.39</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,67 +1014,67 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.992</v>
+        <v>5.249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1890</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.53</v>
+        <v>-1.71</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>76.663</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.4</v>
+        <v>18.25</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.19</v>
+        <v>-3.44</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,67 +1082,67 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.102</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>102.5</v>
+        <v>210.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.65</v>
+        <v>-5.61</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24.109</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1770</v>
+        <v>39.2</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.67</v>
+        <v>-0.25</v>
       </c>
       <c r="F21" t="n">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,101 +1150,101 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14.784</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>284.5</v>
+        <v>379</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.56</v>
+        <v>1.07</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.403</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>289</v>
+        <v>144</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.17</v>
+        <v>-9.15</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.663</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>39.3</v>
+        <v>1605</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-9.32</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.863</v>
+        <v>13.607</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>375</v>
+        <v>127.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.13</v>
+        <v>-2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.369</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="26">
@@ -1306,81 +1306,81 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3310</v>
+        <v>2995</v>
       </c>
       <c r="E26" t="n">
-        <v>1.22</v>
+        <v>-9.52</v>
       </c>
       <c r="F26" t="n">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.9</v>
+        <v>5.373</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2385</v>
+        <v>126</v>
       </c>
       <c r="E27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>7.461</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>130.5</v>
+        <v>1665</v>
       </c>
       <c r="E28" t="n">
-        <v>1.56</v>
+        <v>-5.67</v>
       </c>
       <c r="F28" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.662</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106.5</v>
+        <v>105.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.91</v>
+        <v>-8.26</v>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22.045</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>467</v>
+        <v>320</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.74</v>
+        <v>-6.43</v>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.326</v>
+        <v>9.125</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>200.5</v>
+        <v>282</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>-2.42</v>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.098</v>
+        <v>5.569</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>23.4</v>
+        <v>40.05</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-4.19</v>
       </c>
       <c r="F32" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.477</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.45</v>
+        <v>-4.74</v>
       </c>
       <c r="F33" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>15.193</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>159</v>
+        <v>101</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.24</v>
+        <v>-5.16</v>
       </c>
       <c r="F34" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.939</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>61.9</v>
+        <v>202.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.59</v>
+        <v>-10</v>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.224</v>
+        <v>2.365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>463</v>
+        <v>59.7</v>
       </c>
       <c r="E36" t="n">
-        <v>1.54</v>
+        <v>-3.71</v>
       </c>
       <c r="F36" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.721</v>
+        <v>8.567</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>64.3</v>
+        <v>19.15</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.16</v>
+        <v>-3.77</v>
       </c>
       <c r="F37" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19.522</v>
+        <v>1.633</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>225</v>
+        <v>428.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.22</v>
+        <v>-8.24</v>
       </c>
       <c r="F38" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,41 +1728,41 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.996</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>342</v>
+        <v>149</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.25</v>
+        <v>-6.29</v>
       </c>
       <c r="F39" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9.581</v>
+        <v>4.579</v>
       </c>
     </row>
     <row r="40">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>61.7</v>
+        <v>64.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.53</v>
+        <v>4.54</v>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.023</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1765</v>
+        <v>110</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-7.17</v>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>18.043</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>41.8</v>
+        <v>212.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.24</v>
+        <v>-2.07</v>
       </c>
       <c r="F42" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.864</v>
+        <v>2.021</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>186</v>
+        <v>2190</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.85</v>
+        <v>-8.18</v>
       </c>
       <c r="F43" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.967</v>
+        <v>6.748</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19.9</v>
+        <v>182</v>
       </c>
       <c r="E44" t="n">
-        <v>3.11</v>
+        <v>-2.15</v>
       </c>
       <c r="F44" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.684</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>158.5</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.31</v>
+        <v>-7.96</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.541</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>115</v>
+        <v>59.4</v>
       </c>
       <c r="E46" t="n">
-        <v>1.32</v>
+        <v>-7.62</v>
       </c>
       <c r="F46" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.763</v>
+        <v>17.366</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>62</v>
+        <v>2190</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.16</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>10.18</v>
+        <v>2.944</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>118.5</v>
+        <v>58.4</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.84</v>
+        <v>-5.65</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4.361</v>
+        <v>2.027</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.46</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.825</v>
+        <v>19.737</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2390</v>
+        <v>195.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.44</v>
+        <v>-9.91</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.665</v>
+        <v>3.235</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>64.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.62</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.274</v>
+        <v>20.901</v>
       </c>
     </row>
     <row r="52">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>298.5</v>
+        <v>269</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7.313</v>
+        <v>6.15</v>
       </c>
     </row>
   </sheetData>
@@ -2261,141 +2261,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34.51</v>
+        <v>12.68</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="G2" t="n">
-        <v>24.109</v>
+        <v>3.235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33.15</v>
+        <v>12.41</v>
       </c>
       <c r="F3" t="n">
-        <v>0.38</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.665</v>
+        <v>3.353</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26.53</v>
+        <v>11.17</v>
       </c>
       <c r="F4" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="G4" t="n">
-        <v>3.825</v>
+        <v>2.944</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23.86</v>
+        <v>10.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="G5" t="n">
-        <v>7.313</v>
+        <v>20.901</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2404,29 +2404,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12.62</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>3.17</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.848</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2435,137 +2435,137 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12.57</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="G7" t="n">
-        <v>3.874</v>
+        <v>1.903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>11.58</v>
+        <v>4.26</v>
       </c>
       <c r="F8" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="G8" t="n">
-        <v>9.581</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8.07</v>
+        <v>2.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>19.522</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.22</v>
+        <v>1.91</v>
       </c>
       <c r="F10" t="n">
-        <v>3.16</v>
+        <v>0.97</v>
       </c>
       <c r="G10" t="n">
-        <v>1.58</v>
+        <v>9.125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.18</v>
+        <v>0.68</v>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>76.663</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="12">
@@ -2590,277 +2590,277 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.65</v>
+        <v>0.47</v>
       </c>
       <c r="F12" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.023</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>-0.39</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
-        <v>16.876</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.4</v>
+        <v>-0.51</v>
       </c>
       <c r="F14" t="n">
-        <v>1.37</v>
+        <v>0.99</v>
       </c>
       <c r="G14" t="n">
-        <v>0.191</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.84</v>
+        <v>-0.55</v>
       </c>
       <c r="F15" t="n">
-        <v>0.61</v>
+        <v>1.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1.684</v>
+        <v>77.68600000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.2</v>
+        <v>-1.74</v>
       </c>
       <c r="F16" t="n">
-        <v>2.11</v>
+        <v>1.05</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8139999999999999</v>
+        <v>5.569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.18</v>
+        <v>-2.3</v>
       </c>
       <c r="F17" t="n">
-        <v>1.26</v>
+        <v>0.62</v>
       </c>
       <c r="G17" t="n">
-        <v>2.102</v>
+        <v>1.633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.52</v>
+        <v>-2.95</v>
       </c>
       <c r="F18" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>5.663</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.38</v>
+        <v>-3.56</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.863</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.69</v>
       </c>
       <c r="F20" t="n">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="G20" t="n">
-        <v>18.043</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2869,29 +2869,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-1.11</v>
+        <v>-5.2</v>
       </c>
       <c r="F21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="G21" t="n">
-        <v>15.193</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2900,60 +2900,60 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1.27</v>
+        <v>-5.73</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="G22" t="n">
-        <v>0.477</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-1.57</v>
+        <v>-6.46</v>
       </c>
       <c r="F23" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="G23" t="n">
-        <v>2.289</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2962,447 +2962,447 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-2.97</v>
+        <v>-6.65</v>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="G24" t="n">
-        <v>4.662</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-3.5</v>
+        <v>-7.65</v>
       </c>
       <c r="F25" t="n">
-        <v>0.84</v>
+        <v>1.23</v>
       </c>
       <c r="G25" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-3.82</v>
+        <v>-7.7</v>
       </c>
       <c r="F26" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="G26" t="n">
-        <v>1.992</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-3.9</v>
+        <v>-7.81</v>
       </c>
       <c r="F27" t="n">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
       <c r="G27" t="n">
-        <v>1.893</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-5.06</v>
+        <v>-9.17</v>
       </c>
       <c r="F28" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="G28" t="n">
-        <v>1.369</v>
+        <v>17.366</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-5.17</v>
+        <v>-10.98</v>
       </c>
       <c r="F29" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="G29" t="n">
-        <v>5.403</v>
+        <v>2.027</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-6.19</v>
+        <v>-11.13</v>
       </c>
       <c r="F30" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="n">
-        <v>4.939</v>
+        <v>5.373</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-6.97</v>
+        <v>-11.27</v>
       </c>
       <c r="F31" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.119</v>
+        <v>1.446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-7.06</v>
+        <v>-11.48</v>
       </c>
       <c r="F32" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="G32" t="n">
-        <v>2.224</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-7.63</v>
+        <v>-12.54</v>
       </c>
       <c r="F33" t="n">
-        <v>0.68</v>
+        <v>0.93</v>
       </c>
       <c r="G33" t="n">
-        <v>0.763</v>
+        <v>5.249</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-7.74</v>
+        <v>-13.12</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="G34" t="n">
-        <v>7.461</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-7.79</v>
+        <v>-13.62</v>
       </c>
       <c r="F35" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="G35" t="n">
-        <v>22.045</v>
+        <v>4.579</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-8.130000000000001</v>
+        <v>-14.57</v>
       </c>
       <c r="F36" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
-        <v>0.864</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-8.210000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="F37" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.473</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-8.609999999999999</v>
+        <v>-15.12</v>
       </c>
       <c r="F38" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="G38" t="n">
-        <v>2.326</v>
+        <v>6.748</v>
       </c>
     </row>
     <row r="39">
@@ -3427,230 +3427,230 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-9.960000000000001</v>
+        <v>-15.17</v>
       </c>
       <c r="F39" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="G39" t="n">
-        <v>2.18</v>
+        <v>2.021</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-10.57</v>
+        <v>-15.82</v>
       </c>
       <c r="F40" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="G40" t="n">
-        <v>1.174</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-11.2</v>
+        <v>-17.62</v>
       </c>
       <c r="F41" t="n">
-        <v>0.84</v>
+        <v>1.24</v>
       </c>
       <c r="G41" t="n">
-        <v>0.541</v>
+        <v>6.311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-12.64</v>
+        <v>-18.64</v>
       </c>
       <c r="F42" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="G42" t="n">
-        <v>1.721</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-14.61</v>
+        <v>-18.89</v>
       </c>
       <c r="F43" t="n">
-        <v>0.84</v>
+        <v>1.32</v>
       </c>
       <c r="G43" t="n">
-        <v>2.996</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-15.88</v>
+        <v>-20.47</v>
       </c>
       <c r="F44" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>23.022</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-16.51</v>
+        <v>-21.34</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="G45" t="n">
-        <v>14.784</v>
+        <v>8.567</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-17.47</v>
+        <v>-21.72</v>
       </c>
       <c r="F46" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="G46" t="n">
-        <v>0.879</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="47">
@@ -3675,137 +3675,137 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-17.82</v>
+        <v>-21.75</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="G47" t="n">
-        <v>0.274</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-18.64</v>
+        <v>-22.56</v>
       </c>
       <c r="F48" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="G48" t="n">
-        <v>10.18</v>
+        <v>2.365</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-18.83</v>
+        <v>-29.04</v>
       </c>
       <c r="F49" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="G49" t="n">
-        <v>0.098</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-19.24</v>
+        <v>-29.29</v>
       </c>
       <c r="F50" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="G50" t="n">
-        <v>5.662</v>
+        <v>19.737</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-25</v>
+        <v>-29.76</v>
       </c>
       <c r="F51" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>1.967</v>
+        <v>13.607</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-25.71</v>
+        <v>-32.52</v>
       </c>
       <c r="F52" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G52" t="n">
-        <v>4.361</v>
+        <v>3.83</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.51</v>
+        <v>11.17</v>
       </c>
       <c r="C2" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="D2" t="n">
-        <v>24.109</v>
+        <v>2.944</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.15</v>
+        <v>10.14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.38</v>
+        <v>0.64</v>
       </c>
       <c r="D3" t="n">
-        <v>3.665</v>
+        <v>20.901</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.19666666666667</v>
+        <v>10.11</v>
       </c>
       <c r="C4" t="n">
-        <v>1.08</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>11.952</v>
+        <v>9.506</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3940,55 +3940,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.58</v>
+        <v>6.32</v>
       </c>
       <c r="C5" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>9.581</v>
+        <v>10.206</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.47</v>
+        <v>1.91</v>
       </c>
       <c r="C6" t="n">
-        <v>2.926666666666667</v>
+        <v>0.97</v>
       </c>
       <c r="D6" t="n">
-        <v>8.302</v>
+        <v>9.125</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.07</v>
+        <v>0.68</v>
       </c>
       <c r="C7" t="n">
-        <v>0.78</v>
+        <v>1.44</v>
       </c>
       <c r="D7" t="n">
-        <v>19.522</v>
+        <v>0.184</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,17 +3997,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4</v>
+        <v>-2.3</v>
       </c>
       <c r="C8" t="n">
-        <v>1.37</v>
+        <v>0.62</v>
       </c>
       <c r="D8" t="n">
-        <v>0.191</v>
+        <v>1.633</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,39 +4016,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.84</v>
+        <v>-3.446</v>
       </c>
       <c r="C9" t="n">
-        <v>0.61</v>
+        <v>1.142</v>
       </c>
       <c r="D9" t="n">
-        <v>1.684</v>
+        <v>7.52</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.2950000000000004</v>
+        <v>-3.56</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9950000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>21.815</v>
+        <v>1.405</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-6.46</v>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="D11" t="n">
-        <v>18.043</v>
+        <v>17.16</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,112 +4073,112 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.57</v>
+        <v>-6.6775</v>
       </c>
       <c r="C12" t="n">
-        <v>1.02</v>
+        <v>1.0575</v>
       </c>
       <c r="D12" t="n">
-        <v>2.289</v>
+        <v>25.433</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.638</v>
+        <v>-7.7</v>
       </c>
       <c r="C13" t="n">
-        <v>1.108</v>
+        <v>1.23</v>
       </c>
       <c r="D13" t="n">
-        <v>7.327</v>
+        <v>2.294</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.774999999999999</v>
+        <v>-7.81</v>
       </c>
       <c r="C14" t="n">
-        <v>0.735</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.564</v>
+        <v>1.88</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.9225</v>
+        <v>-9.085000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>1.095</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>26.382</v>
+        <v>1.419</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-5.06</v>
+        <v>-9.154999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.369</v>
+        <v>20.829</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-5.17</v>
+        <v>-9.17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="D17" t="n">
-        <v>5.403</v>
+        <v>17.366</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-5.62</v>
+        <v>-10.945</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>13.361</v>
+        <v>86.25300000000001</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -4206,20 +4206,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-6.23</v>
+        <v>-11.27</v>
       </c>
       <c r="C19" t="n">
-        <v>0.865</v>
+        <v>1.42</v>
       </c>
       <c r="D19" t="n">
-        <v>86.84299999999999</v>
+        <v>1.446</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-6.97</v>
+        <v>-11.48</v>
       </c>
       <c r="C20" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-7.79</v>
+        <v>-12.54</v>
       </c>
       <c r="C21" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="D21" t="n">
-        <v>22.045</v>
+        <v>5.249</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-8.119999999999999</v>
+        <v>-13.125</v>
       </c>
       <c r="C22" t="n">
-        <v>0.835</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>3.089</v>
+        <v>12.121</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -4282,20 +4282,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-8.210000000000001</v>
+        <v>-15.195</v>
       </c>
       <c r="C23" t="n">
-        <v>1.27</v>
+        <v>0.91</v>
       </c>
       <c r="D23" t="n">
-        <v>1.473</v>
+        <v>2.722</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-10.835</v>
+        <v>-16.77</v>
       </c>
       <c r="C24" t="n">
-        <v>1.025</v>
+        <v>0.915</v>
       </c>
       <c r="D24" t="n">
-        <v>5.220000000000001</v>
+        <v>4.392</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -4320,74 +4320,74 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-12.64</v>
+        <v>-16.795</v>
       </c>
       <c r="C25" t="n">
-        <v>0.83</v>
+        <v>1.31</v>
       </c>
       <c r="D25" t="n">
-        <v>1.721</v>
+        <v>2.04</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-14.02</v>
+        <v>-20.47</v>
       </c>
       <c r="C26" t="n">
-        <v>1.41</v>
+        <v>0.8</v>
       </c>
       <c r="D26" t="n">
-        <v>2.053</v>
+        <v>20.83</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-15.88</v>
+        <v>-20.61</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>23.022</v>
+        <v>10.041</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-16.51</v>
+        <v>-21.72</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="D28" t="n">
-        <v>14.784</v>
+        <v>0.094</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-17.82</v>
+        <v>-21.75</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="D29" t="n">
-        <v>0.274</v>
+        <v>0.227</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,36 +4415,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-18.06666666666667</v>
+        <v>-29.29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7433333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="D30" t="n">
-        <v>9.809000000000001</v>
+        <v>19.737</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-18.83</v>
+        <v>-29.76</v>
       </c>
       <c r="C31" t="n">
-        <v>1.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.098</v>
+        <v>13.607</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-25.71</v>
+        <v>-32.52</v>
       </c>
       <c r="C32" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="D32" t="n">
-        <v>4.361</v>
+        <v>3.83</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1770</v>
+        <v>1605</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.67</v>
+        <v>-9.32</v>
       </c>
       <c r="F2" t="n">
-        <v>-16.51</v>
+        <v>-29.76</v>
       </c>
       <c r="G2" t="n">
-        <v>36.87</v>
+        <v>32.92</v>
       </c>
       <c r="H2" t="n">
-        <v>-37.5009</v>
+        <v>-50.1919</v>
       </c>
       <c r="I2" t="n">
-        <v>23.1</v>
+        <v>6.1</v>
       </c>
       <c r="J2" t="n">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8.07</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>-27.7</v>
+        <v>21.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1765</v>
+        <v>1665</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-5.67</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-6.46</v>
       </c>
       <c r="G3" t="n">
-        <v>47.62</v>
+        <v>43.48</v>
       </c>
       <c r="H3" t="n">
-        <v>53.0835</v>
+        <v>40.2557</v>
       </c>
       <c r="I3" t="n">
-        <v>34.9</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.45</v>
+        <v>5.13</v>
       </c>
       <c r="L3" t="n">
-        <v>-56.8</v>
+        <v>11.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.7</v>
+        <v>64.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.53</v>
+        <v>4.54</v>
       </c>
       <c r="F4" t="n">
-        <v>5.65</v>
+        <v>0.47</v>
       </c>
       <c r="G4" t="n">
-        <v>40.41</v>
+        <v>47.67</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8545</v>
+        <v>1.5069</v>
       </c>
       <c r="I4" t="n">
-        <v>17.7</v>
+        <v>31.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>24.5</v>
       </c>
       <c r="K4" t="n">
-        <v>8.74</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-56</v>
+        <v>-33.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.09999999999999</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.62</v>
+        <v>-7.96</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.82</v>
+        <v>-21.75</v>
       </c>
       <c r="G5" t="n">
-        <v>48.82</v>
+        <v>44.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7541</v>
+        <v>-1.4551</v>
       </c>
       <c r="I5" t="n">
-        <v>35.4</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>25.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.79</v>
+        <v>6.77</v>
       </c>
       <c r="L5" t="n">
-        <v>-77.59999999999999</v>
+        <v>-48.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>217</v>
+        <v>195.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.46</v>
+        <v>-9.91</v>
       </c>
       <c r="F6" t="n">
-        <v>26.53</v>
+        <v>12.68</v>
       </c>
       <c r="G6" t="n">
-        <v>60.92</v>
+        <v>57.23</v>
       </c>
       <c r="H6" t="n">
-        <v>16.4923</v>
+        <v>14.2477</v>
       </c>
       <c r="I6" t="n">
-        <v>72.40000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="J6" t="n">
-        <v>60.3</v>
+        <v>35.6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.16</v>
+        <v>9.35</v>
       </c>
       <c r="L6" t="n">
-        <v>-77</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>210.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.45</v>
+        <v>-5.61</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.11</v>
+        <v>-6.65</v>
       </c>
       <c r="G7" t="n">
-        <v>52.74</v>
+        <v>46.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4776</v>
+        <v>-0.9557</v>
       </c>
       <c r="I7" t="n">
-        <v>44.7</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>25.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.64</v>
+        <v>4.26</v>
       </c>
       <c r="L7" t="n">
-        <v>-46.3</v>
+        <v>29.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.18</v>
+        <v>9.92</v>
       </c>
       <c r="F2" t="n">
-        <v>319</v>
+        <v>189</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,135 +504,135 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.903</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47.35</v>
+        <v>319</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.68</v>
+        <v>4.93</v>
       </c>
       <c r="F3" t="n">
-        <v>312</v>
+        <v>173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.294</v>
+        <v>6.862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.6</v>
+        <v>90.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.48</v>
+        <v>-1.73</v>
       </c>
       <c r="F4" t="n">
-        <v>304</v>
+        <v>144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.353</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>210.5</v>
+        <v>460</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-4.96</v>
       </c>
       <c r="F5" t="n">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4.25</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>304</v>
+        <v>1220</v>
       </c>
       <c r="E6" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>231</v>
+        <v>138</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.311</v>
+        <v>1.495</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.5</v>
+        <v>185</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.11</v>
+        <v>-3.14</v>
       </c>
       <c r="F7" t="n">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.175</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>87.2</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8</v>
+        <v>2.38</v>
       </c>
       <c r="F8" t="n">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.961</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1810</v>
+        <v>293</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.23</v>
+        <v>7.72</v>
       </c>
       <c r="F9" t="n">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>77.68600000000001</v>
+        <v>5.627</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27.75</v>
+        <v>37.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.117</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1220</v>
+        <v>231</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.58</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>16.25</v>
+        <v>21.568</v>
       </c>
     </row>
     <row r="12">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.78</v>
+        <v>0.39</v>
       </c>
       <c r="F12" t="n">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,135 +844,135 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.202</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1220</v>
+        <v>205.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.06</v>
+        <v>-2.38</v>
       </c>
       <c r="F13" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.446</v>
+        <v>4.314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>484</v>
+        <v>32.6</v>
       </c>
       <c r="E14" t="n">
-        <v>4.54</v>
+        <v>0.31</v>
       </c>
       <c r="F14" t="n">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.88</v>
+        <v>1.203</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37.15</v>
+        <v>1850</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.11</v>
+        <v>2.21</v>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>95</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.184</v>
+        <v>80.249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>3060</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.11</v>
+        <v>2.17</v>
       </c>
       <c r="F16" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>272</v>
+        <v>209.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.39</v>
+        <v>-0.48</v>
       </c>
       <c r="F17" t="n">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,101 +1014,101 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.249</v>
+        <v>14.517</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.71</v>
+        <v>-2.6</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.482</v>
+        <v>3.393</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.25</v>
+        <v>79.2</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.44</v>
+        <v>-2.34</v>
       </c>
       <c r="F19" t="n">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.865</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>210.5</v>
+        <v>46.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.61</v>
+        <v>-1.8</v>
       </c>
       <c r="F20" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,101 +1116,101 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>14.462</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>39.2</v>
+        <v>1290</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.25</v>
+        <v>5.74</v>
       </c>
       <c r="F21" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.875</v>
+        <v>17.095</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>379</v>
+        <v>335.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.07</v>
+        <v>4.84</v>
       </c>
       <c r="F22" t="n">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.405</v>
+        <v>9.648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>144</v>
+        <v>39.05</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.15</v>
+        <v>-0.38</v>
       </c>
       <c r="F23" t="n">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.48</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1605</v>
+        <v>18.35</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.32</v>
+        <v>0.55</v>
       </c>
       <c r="F24" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>13.607</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>127.5</v>
+        <v>105.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3</v>
+        <v>4.46</v>
       </c>
       <c r="F25" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,101 +1286,101 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.59</v>
+        <v>20.573</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2995</v>
+        <v>384.5</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.52</v>
+        <v>1.45</v>
       </c>
       <c r="F26" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.373</v>
+        <v>1.374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="F27" t="n">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.821</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1665</v>
+        <v>282.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.67</v>
+        <v>0.18</v>
       </c>
       <c r="F28" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>17.16</v>
+        <v>5.654</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.5</v>
+        <v>88.3</v>
       </c>
       <c r="E29" t="n">
-        <v>-8.26</v>
+        <v>1.26</v>
       </c>
       <c r="F29" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.674</v>
+        <v>1.996</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>320</v>
+        <v>214.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.43</v>
+        <v>5.93</v>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9.125</v>
+        <v>2.342</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>282</v>
+        <v>1745</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.42</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.569</v>
+        <v>14.595</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>40.05</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.19</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>191</v>
+        <v>40.9</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.74</v>
+        <v>2.12</v>
       </c>
       <c r="F33" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.094</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>101</v>
+        <v>220</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.16</v>
+        <v>3.53</v>
       </c>
       <c r="F34" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>20.83</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>202.5</v>
+        <v>109</v>
       </c>
       <c r="E35" t="n">
-        <v>-10</v>
+        <v>3.32</v>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.365</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>59.7</v>
+        <v>23.1</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.71</v>
+        <v>0.43</v>
       </c>
       <c r="F36" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8.567</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19.15</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.77</v>
+        <v>1.57</v>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.633</v>
+        <v>2.032</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>428.5</v>
+        <v>2245</v>
       </c>
       <c r="E38" t="n">
-        <v>-8.24</v>
+        <v>2.51</v>
       </c>
       <c r="F38" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.048</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="39">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.29</v>
+        <v>4.03</v>
       </c>
       <c r="F39" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.579</v>
+        <v>4.743</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>64.5</v>
+        <v>443</v>
       </c>
       <c r="E40" t="n">
-        <v>4.54</v>
+        <v>3.38</v>
       </c>
       <c r="F40" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.17</v>
+        <v>1.39</v>
       </c>
       <c r="F41" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.83</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>212.5</v>
+        <v>60.4</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.07</v>
+        <v>1.17</v>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.021</v>
+        <v>8.058</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2190</v>
+        <v>111.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.18</v>
+        <v>1.36</v>
       </c>
       <c r="F43" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.748</v>
+        <v>3.748</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>182</v>
+        <v>62.2</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.15</v>
+        <v>4.71</v>
       </c>
       <c r="F44" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.709</v>
+        <v>16.786</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>1705</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.96</v>
+        <v>2.4</v>
       </c>
       <c r="F45" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.227</v>
+        <v>17.186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>59.4</v>
+        <v>62.9</v>
       </c>
       <c r="E46" t="n">
-        <v>-7.62</v>
+        <v>6.61</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>17.366</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2190</v>
+        <v>185</v>
       </c>
       <c r="E47" t="n">
-        <v>-8.369999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="F47" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.944</v>
+        <v>1.556</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>58.4</v>
+        <v>19.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-5.65</v>
+        <v>0.26</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.027</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>210</v>
+        <v>59.8</v>
       </c>
       <c r="E49" t="n">
-        <v>-9.869999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>19.737</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>195.5</v>
+        <v>2260</v>
       </c>
       <c r="E50" t="n">
-        <v>-9.91</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.235</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>92.3</v>
+        <v>272</v>
       </c>
       <c r="E51" t="n">
-        <v>-9.949999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="F51" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,41 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>20.901</v>
+        <v>5.963</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>269</v>
+        <v>201.5</v>
       </c>
       <c r="E52" t="n">
-        <v>-9.880000000000001</v>
+        <v>3.07</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.15</v>
+        <v>3.301</v>
       </c>
     </row>
   </sheetData>
@@ -2261,141 +2261,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12.68</v>
+        <v>18.64</v>
       </c>
       <c r="F2" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="G2" t="n">
-        <v>3.235</v>
+        <v>2.883</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12.41</v>
+        <v>17.84</v>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.353</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.17</v>
+        <v>11.02</v>
       </c>
       <c r="F4" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.944</v>
+        <v>5.963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10.14</v>
+        <v>10.26</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>1.43</v>
       </c>
       <c r="G5" t="n">
-        <v>20.901</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2404,370 +2404,370 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.640000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.25</v>
+        <v>3.393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="F7" t="n">
-        <v>3.03</v>
+        <v>0.93</v>
       </c>
       <c r="G7" t="n">
-        <v>1.903</v>
+        <v>9.648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.26</v>
+        <v>8.16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.33</v>
+        <v>1.82</v>
       </c>
       <c r="G8" t="n">
-        <v>6.15</v>
+        <v>4.314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.02</v>
+        <v>6.59</v>
       </c>
       <c r="F9" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.821</v>
+        <v>1.924</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.91</v>
+        <v>3.88</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
-        <v>9.125</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.68</v>
+        <v>2.79</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.184</v>
+        <v>17.095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.47</v>
+        <v>2.49</v>
       </c>
       <c r="F12" t="n">
-        <v>0.62</v>
+        <v>1.22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9389999999999999</v>
+        <v>80.249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-0.39</v>
+        <v>2.16</v>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>0.89</v>
       </c>
       <c r="G13" t="n">
-        <v>2.202</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.875</v>
+        <v>1.374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
       <c r="F15" t="n">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="G15" t="n">
-        <v>77.68600000000001</v>
+        <v>5.654</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-1.74</v>
+        <v>-0.76</v>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>5.569</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-2.3</v>
+        <v>-1.52</v>
       </c>
       <c r="F17" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G17" t="n">
-        <v>1.633</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2776,137 +2776,137 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-2.95</v>
+        <v>-1.54</v>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.482</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-3.56</v>
+        <v>-2.64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>1.405</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-4.69</v>
+        <v>-3.14</v>
       </c>
       <c r="F20" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>16.25</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-5.2</v>
+        <v>-3.86</v>
       </c>
       <c r="F21" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="G21" t="n">
-        <v>4.59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-5.73</v>
+        <v>-3.93</v>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="G22" t="n">
-        <v>1.961</v>
+        <v>5.627</v>
       </c>
     </row>
     <row r="23">
@@ -2931,75 +2931,75 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-6.46</v>
+        <v>-4.21</v>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="G23" t="n">
-        <v>17.16</v>
+        <v>17.186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-6.65</v>
+        <v>-4.33</v>
       </c>
       <c r="F24" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="G24" t="n">
-        <v>14.462</v>
+        <v>1.996</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-7.65</v>
+        <v>-4.45</v>
       </c>
       <c r="F25" t="n">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>16.786</v>
       </c>
     </row>
     <row r="26">
@@ -3024,478 +3024,478 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-7.7</v>
+        <v>-5.68</v>
       </c>
       <c r="F26" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="G26" t="n">
-        <v>2.294</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-7.81</v>
+        <v>-6.42</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-9.17</v>
+        <v>-6.47</v>
       </c>
       <c r="F28" t="n">
-        <v>0.73</v>
+        <v>1.05</v>
       </c>
       <c r="G28" t="n">
-        <v>17.366</v>
+        <v>14.517</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-10.98</v>
+        <v>-6.94</v>
       </c>
       <c r="F29" t="n">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.027</v>
+        <v>2.032</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-11.13</v>
+        <v>-7.19</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="G30" t="n">
-        <v>5.373</v>
+        <v>4.743</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-11.27</v>
+        <v>-7.25</v>
       </c>
       <c r="F31" t="n">
-        <v>1.42</v>
+        <v>0.65</v>
       </c>
       <c r="G31" t="n">
-        <v>1.446</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-11.48</v>
+        <v>-8.27</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.117</v>
+        <v>1.495</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-12.54</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="G33" t="n">
-        <v>5.249</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-13.12</v>
+        <v>-9.92</v>
       </c>
       <c r="F34" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-13.62</v>
+        <v>-9.98</v>
       </c>
       <c r="F35" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="G35" t="n">
-        <v>4.579</v>
+        <v>1.735</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-14.57</v>
+        <v>-11.39</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="G36" t="n">
-        <v>0.674</v>
+        <v>6.862</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-14.7</v>
+        <v>-11.7</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3</v>
+        <v>0.65</v>
       </c>
       <c r="G37" t="n">
-        <v>1.175</v>
+        <v>8.058</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-15.12</v>
+        <v>-11.75</v>
       </c>
       <c r="F38" t="n">
-        <v>0.76</v>
+        <v>1.03</v>
       </c>
       <c r="G38" t="n">
-        <v>6.748</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-15.17</v>
+        <v>-11.95</v>
       </c>
       <c r="F39" t="n">
-        <v>0.73</v>
+        <v>1.18</v>
       </c>
       <c r="G39" t="n">
-        <v>2.021</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-15.82</v>
+        <v>-12.88</v>
       </c>
       <c r="F40" t="n">
-        <v>1.02</v>
+        <v>0.52</v>
       </c>
       <c r="G40" t="n">
-        <v>2.048</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-17.62</v>
+        <v>-14.1</v>
       </c>
       <c r="F41" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="G41" t="n">
-        <v>6.311</v>
+        <v>1.203</v>
       </c>
     </row>
     <row r="42">
@@ -3520,323 +3520,323 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-18.64</v>
+        <v>-14.87</v>
       </c>
       <c r="F42" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="G42" t="n">
-        <v>0.48</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-18.89</v>
+        <v>-15.06</v>
       </c>
       <c r="F43" t="n">
-        <v>1.32</v>
+        <v>0.73</v>
       </c>
       <c r="G43" t="n">
-        <v>0.865</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-20.47</v>
+        <v>-16.05</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G44" t="n">
-        <v>20.83</v>
+        <v>2.342</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-21.34</v>
+        <v>-16.7</v>
       </c>
       <c r="F45" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="G45" t="n">
-        <v>8.567</v>
+        <v>6.676</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-21.72</v>
+        <v>-17.71</v>
       </c>
       <c r="F46" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="G46" t="n">
-        <v>0.094</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-21.75</v>
+        <v>-18.85</v>
       </c>
       <c r="F47" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="G47" t="n">
-        <v>0.227</v>
+        <v>20.573</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-22.56</v>
+        <v>-22.22</v>
       </c>
       <c r="F48" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="G48" t="n">
-        <v>2.365</v>
+        <v>21.568</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-29.04</v>
+        <v>-24.15</v>
       </c>
       <c r="F49" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="G49" t="n">
-        <v>1.709</v>
+        <v>3.748</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-29.29</v>
+        <v>-24.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="G50" t="n">
-        <v>19.737</v>
+        <v>14.595</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-29.76</v>
+        <v>-24.95</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="G51" t="n">
-        <v>13.607</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-32.52</v>
+        <v>-25.85</v>
       </c>
       <c r="F52" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="G52" t="n">
-        <v>3.83</v>
+        <v>1.556</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.17</v>
+        <v>18.64</v>
       </c>
       <c r="C2" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="D2" t="n">
-        <v>2.944</v>
+        <v>2.883</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,55 +3902,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.14</v>
+        <v>13.04</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>20.901</v>
+        <v>10.136</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.11</v>
+        <v>8.23</v>
       </c>
       <c r="C4" t="n">
-        <v>2.766666666666667</v>
+        <v>0.93</v>
       </c>
       <c r="D4" t="n">
-        <v>9.506</v>
+        <v>9.648</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.32</v>
+        <v>8.146666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9733333333333333</v>
+        <v>2.243333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>10.206</v>
+        <v>9.631</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -3959,17 +3959,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.91</v>
+        <v>3.88</v>
       </c>
       <c r="C6" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
       <c r="D6" t="n">
-        <v>9.125</v>
+        <v>0.191</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,17 +3978,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.184</v>
+        <v>1.374</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,17 +3997,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.3</v>
+        <v>-1.52</v>
       </c>
       <c r="C8" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="D8" t="n">
-        <v>1.633</v>
+        <v>19.89</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,55 +4016,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-3.446</v>
+        <v>-2.2</v>
       </c>
       <c r="C9" t="n">
-        <v>1.142</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>7.52</v>
+        <v>21.838</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.56</v>
+        <v>-3.342</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="D10" t="n">
-        <v>1.405</v>
+        <v>7.612</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-6.46</v>
+        <v>-3.93</v>
       </c>
       <c r="C11" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="D11" t="n">
-        <v>17.16</v>
+        <v>5.627</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,36 +4073,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-6.6775</v>
+        <v>-4.21</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0575</v>
+        <v>0.79</v>
       </c>
       <c r="D12" t="n">
-        <v>25.433</v>
+        <v>17.186</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-7.7</v>
+        <v>-4.45</v>
       </c>
       <c r="C13" t="n">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>2.294</v>
+        <v>16.786</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,96 +4111,96 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-7.81</v>
+        <v>-4.605</v>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>88.30699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-9.085000000000001</v>
+        <v>-4.625</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8</v>
+        <v>0.9825</v>
       </c>
       <c r="D15" t="n">
-        <v>1.419</v>
+        <v>25.561</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-9.154999999999999</v>
+        <v>-5.68</v>
       </c>
       <c r="C16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>20.829</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.17</v>
+        <v>-6.355</v>
       </c>
       <c r="C17" t="n">
-        <v>0.73</v>
+        <v>0.865</v>
       </c>
       <c r="D17" t="n">
-        <v>17.366</v>
+        <v>1.357</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-10.945</v>
+        <v>-7.25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="D18" t="n">
-        <v>86.25300000000001</v>
+        <v>1.422</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-11.27</v>
+        <v>-8.27</v>
       </c>
       <c r="C19" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.446</v>
+        <v>1.495</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,36 +4225,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-11.48</v>
+        <v>-9.955</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="D20" t="n">
-        <v>0.117</v>
+        <v>4.342000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-12.54</v>
+        <v>-9.98</v>
       </c>
       <c r="C21" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="D21" t="n">
-        <v>5.249</v>
+        <v>1.735</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-13.125</v>
+        <v>-10.835</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D22" t="n">
-        <v>12.121</v>
+        <v>2.661</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -4282,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-15.195</v>
+        <v>-11.56</v>
       </c>
       <c r="C23" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="D23" t="n">
-        <v>2.722</v>
+        <v>12.088</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4301,58 +4301,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-16.77</v>
+        <v>-11.95</v>
       </c>
       <c r="C24" t="n">
-        <v>0.915</v>
+        <v>1.18</v>
       </c>
       <c r="D24" t="n">
-        <v>4.392</v>
+        <v>0.116</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-16.795</v>
+        <v>-12.88</v>
       </c>
       <c r="C25" t="n">
-        <v>1.31</v>
+        <v>0.52</v>
       </c>
       <c r="D25" t="n">
-        <v>2.04</v>
+        <v>0.227</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-20.47</v>
+        <v>-15.905</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8</v>
+        <v>1.195</v>
       </c>
       <c r="D26" t="n">
-        <v>20.83</v>
+        <v>2.086</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-20.61</v>
+        <v>-17.43333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>10.041</v>
+        <v>10.298</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -4377,17 +4377,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-21.72</v>
+        <v>-18.85</v>
       </c>
       <c r="C28" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="D28" t="n">
-        <v>0.094</v>
+        <v>20.573</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-21.75</v>
+        <v>-22.22</v>
       </c>
       <c r="C29" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="D29" t="n">
-        <v>0.227</v>
+        <v>21.568</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-29.29</v>
+        <v>-24.15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="D30" t="n">
-        <v>19.737</v>
+        <v>3.748</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-29.76</v>
+        <v>-24.3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="D31" t="n">
-        <v>13.607</v>
+        <v>14.595</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-32.52</v>
+        <v>-24.95</v>
       </c>
       <c r="C32" t="n">
-        <v>0.58</v>
+        <v>0.99</v>
       </c>
       <c r="D32" t="n">
-        <v>3.83</v>
+        <v>0.091</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1605</v>
+        <v>1745</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.32</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-29.76</v>
+        <v>-24.3</v>
       </c>
       <c r="G2" t="n">
-        <v>32.92</v>
+        <v>43.9</v>
       </c>
       <c r="H2" t="n">
-        <v>-50.1919</v>
+        <v>-62.5967</v>
       </c>
       <c r="I2" t="n">
-        <v>6.1</v>
+        <v>26.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="K2" t="n">
-        <v>9.210000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="L2" t="n">
-        <v>21.2</v>
+        <v>-27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1665</v>
+        <v>1705</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.67</v>
+        <v>2.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.46</v>
+        <v>-4.21</v>
       </c>
       <c r="G3" t="n">
-        <v>43.48</v>
+        <v>49.68</v>
       </c>
       <c r="H3" t="n">
-        <v>40.2557</v>
+        <v>29.7305</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>19.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="L3" t="n">
-        <v>11.3</v>
+        <v>-47.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4.54</v>
+        <v>9.92</v>
       </c>
       <c r="F4" t="n">
-        <v>0.47</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>47.67</v>
+        <v>61.28</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5069</v>
+        <v>1.8101</v>
       </c>
       <c r="I4" t="n">
-        <v>31.6</v>
+        <v>63.2</v>
       </c>
       <c r="J4" t="n">
-        <v>24.5</v>
+        <v>69.2</v>
       </c>
       <c r="K4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="L4" t="n">
-        <v>-33.5</v>
+        <v>88.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>62.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.96</v>
+        <v>6.61</v>
       </c>
       <c r="F5" t="n">
-        <v>-21.75</v>
+        <v>-12.88</v>
       </c>
       <c r="G5" t="n">
-        <v>44.39</v>
+        <v>52.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4551</v>
+        <v>-1.6615</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>34.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.77</v>
+        <v>6.45</v>
       </c>
       <c r="L5" t="n">
-        <v>-48.7</v>
+        <v>-48.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>195.5</v>
+        <v>201.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-9.91</v>
+        <v>3.07</v>
       </c>
       <c r="F6" t="n">
-        <v>12.68</v>
+        <v>17.84</v>
       </c>
       <c r="G6" t="n">
-        <v>57.23</v>
+        <v>60.69</v>
       </c>
       <c r="H6" t="n">
-        <v>14.2477</v>
+        <v>11.6491</v>
       </c>
       <c r="I6" t="n">
-        <v>51.5</v>
+        <v>55.9</v>
       </c>
       <c r="J6" t="n">
-        <v>35.6</v>
+        <v>36.3</v>
       </c>
       <c r="K6" t="n">
-        <v>9.35</v>
+        <v>9.15</v>
       </c>
       <c r="L6" t="n">
-        <v>-81.40000000000001</v>
+        <v>-69.59999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210.5</v>
+        <v>209.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.61</v>
+        <v>-0.48</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.65</v>
+        <v>-6.47</v>
       </c>
       <c r="G7" t="n">
-        <v>46.95</v>
+        <v>46.67</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9557</v>
+        <v>-1.9496</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>16.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="L7" t="n">
-        <v>29.7</v>
+        <v>-4.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.92</v>
+        <v>5.64</v>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.889</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>319</v>
+        <v>39.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4.93</v>
+        <v>5.87</v>
       </c>
       <c r="F3" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,101 +538,101 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.862</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90.7</v>
+        <v>137</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.73</v>
+        <v>6.2</v>
       </c>
       <c r="F4" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19.89</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>460</v>
+        <v>350.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.96</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.735</v>
+        <v>7.768</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1220</v>
+        <v>33.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="F6" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.495</v>
+        <v>1.297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.14</v>
+        <v>5.13</v>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.091</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>129</v>
+        <v>229</v>
       </c>
       <c r="E8" t="n">
-        <v>2.38</v>
+        <v>4.09</v>
       </c>
       <c r="F8" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.872</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="9">
@@ -728,47 +728,47 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="E9" t="n">
-        <v>7.72</v>
+        <v>4.44</v>
       </c>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.627</v>
+        <v>5.972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37.5</v>
+        <v>3365</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,101 +776,101 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.191</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>231</v>
+        <v>474</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>3.04</v>
       </c>
       <c r="F11" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>21.568</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51.2</v>
+        <v>1400</v>
       </c>
       <c r="E12" t="n">
-        <v>0.39</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.24</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>205.5</v>
+        <v>133</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.38</v>
+        <v>3.1</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.314</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32.6</v>
+        <v>115.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.31</v>
+        <v>5.96</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.203</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1850</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>2.21</v>
+        <v>3.54</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>80.249</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3060</v>
+        <v>254</v>
       </c>
       <c r="E16" t="n">
-        <v>2.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,67 +980,67 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.412</v>
+        <v>23.246</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>209.5</v>
+        <v>114</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.48</v>
+        <v>8.06</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>14.517</v>
+        <v>21.845</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>388.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6</v>
+        <v>1.04</v>
       </c>
       <c r="F18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,30 +1048,30 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.393</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79.2</v>
+        <v>1890</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.34</v>
+        <v>8.31</v>
       </c>
       <c r="F19" t="n">
         <v>91</v>
@@ -1082,30 +1082,30 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.924</v>
+        <v>15.697</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46.5</v>
+        <v>191</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8</v>
+        <v>3.24</v>
       </c>
       <c r="F20" t="n">
         <v>90</v>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>1.486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1290</v>
+        <v>289</v>
       </c>
       <c r="E21" t="n">
-        <v>5.74</v>
+        <v>2.3</v>
       </c>
       <c r="F21" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17.095</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>335.5</v>
+        <v>1260</v>
       </c>
       <c r="E22" t="n">
-        <v>4.84</v>
+        <v>3.28</v>
       </c>
       <c r="F22" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9.648</v>
+        <v>1.565</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39.05</v>
+        <v>215.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.38</v>
+        <v>0.47</v>
       </c>
       <c r="F23" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,135 +1218,135 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.864</v>
+        <v>2.293</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.35</v>
+        <v>210</v>
       </c>
       <c r="E24" t="n">
-        <v>0.55</v>
+        <v>2.19</v>
       </c>
       <c r="F24" t="n">
         <v>84</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.883</v>
+        <v>4.478</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>105.5</v>
+        <v>1940</v>
       </c>
       <c r="E25" t="n">
-        <v>4.46</v>
+        <v>4.86</v>
       </c>
       <c r="F25" t="n">
         <v>84</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>20.573</v>
+        <v>83.70099999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>384.5</v>
+        <v>219</v>
       </c>
       <c r="E26" t="n">
-        <v>1.45</v>
+        <v>4.53</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.374</v>
+        <v>15.006</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>129</v>
+        <v>192.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1.18</v>
+        <v>4.05</v>
       </c>
       <c r="F27" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>282.5</v>
+        <v>154</v>
       </c>
       <c r="E28" t="n">
-        <v>0.18</v>
+        <v>5.48</v>
       </c>
       <c r="F28" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,67 +1388,67 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.654</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>88.3</v>
+        <v>79.8</v>
       </c>
       <c r="E29" t="n">
-        <v>1.26</v>
+        <v>0.76</v>
       </c>
       <c r="F29" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.996</v>
+        <v>1.974</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>214.5</v>
+        <v>63.2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.93</v>
+        <v>0.48</v>
       </c>
       <c r="F30" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,41 +1456,41 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.342</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1745</v>
+        <v>472</v>
       </c>
       <c r="E31" t="n">
-        <v>8.720000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="F31" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>14.595</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="32">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>28.55</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>1.96</v>
       </c>
       <c r="F32" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>40.9</v>
+        <v>66.3</v>
       </c>
       <c r="E33" t="n">
-        <v>2.12</v>
+        <v>6.59</v>
       </c>
       <c r="F33" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.79</v>
+        <v>16.796</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>220</v>
+        <v>89.2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.53</v>
+        <v>1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.88</v>
+        <v>1.978</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>109</v>
+        <v>99.7</v>
       </c>
       <c r="E35" t="n">
-        <v>3.32</v>
+        <v>9.92</v>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.678</v>
+        <v>20.541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>23.1</v>
+        <v>51.2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.48</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>71.09999999999999</v>
+        <v>39.3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.57</v>
+        <v>0.64</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.032</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2245</v>
+        <v>1765</v>
       </c>
       <c r="E38" t="n">
-        <v>2.51</v>
+        <v>3.52</v>
       </c>
       <c r="F38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,64 +1728,64 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6.676</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>155</v>
+        <v>345.5</v>
       </c>
       <c r="E39" t="n">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="F39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.743</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>443</v>
+        <v>2375</v>
       </c>
       <c r="E40" t="n">
-        <v>3.38</v>
+        <v>5.79</v>
       </c>
       <c r="F40" t="n">
         <v>58</v>
@@ -1796,67 +1796,67 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.983</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>146</v>
+        <v>60.9</v>
       </c>
       <c r="E41" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.468</v>
+        <v>3.498</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60.4</v>
+        <v>19.5</v>
       </c>
       <c r="E42" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="F42" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8.058</v>
+        <v>1.246</v>
       </c>
     </row>
     <row r="43">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>111.5</v>
+        <v>114</v>
       </c>
       <c r="E43" t="n">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="F43" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.748</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>62.2</v>
+        <v>47.15</v>
       </c>
       <c r="E44" t="n">
-        <v>4.71</v>
+        <v>1.4</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>16.786</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1705</v>
+        <v>2485</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>17.186</v>
+        <v>3.068</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>62.9</v>
+        <v>62.2</v>
       </c>
       <c r="E46" t="n">
-        <v>6.61</v>
+        <v>2.98</v>
       </c>
       <c r="F46" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.227</v>
+        <v>7.321</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>185</v>
+        <v>63.4</v>
       </c>
       <c r="E47" t="n">
-        <v>1.65</v>
+        <v>6.02</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.556</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>19.2</v>
+        <v>159</v>
       </c>
       <c r="E48" t="n">
-        <v>0.26</v>
+        <v>2.58</v>
       </c>
       <c r="F48" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,75 +2068,75 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.422</v>
+        <v>4.829</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>59.8</v>
+        <v>23.3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.4</v>
+        <v>0.87</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2260</v>
+        <v>71.8</v>
       </c>
       <c r="E50" t="n">
-        <v>3.2</v>
+        <v>0.98</v>
       </c>
       <c r="F50" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.883</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="51">
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="E51" t="n">
-        <v>1.12</v>
+        <v>9.93</v>
       </c>
       <c r="F51" t="n">
         <v>33</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5.963</v>
+        <v>6.423</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>201.5</v>
+        <v>221.5</v>
       </c>
       <c r="E52" t="n">
-        <v>3.07</v>
+        <v>9.93</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.301</v>
+        <v>3.608</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18.64</v>
+        <v>35.79</v>
       </c>
       <c r="F2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="G2" t="n">
-        <v>2.883</v>
+        <v>3.068</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17.84</v>
+        <v>31.85</v>
       </c>
       <c r="F3" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="G3" t="n">
-        <v>3.301</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="4">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.02</v>
+        <v>27.51</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>5.963</v>
+        <v>6.423</v>
       </c>
     </row>
     <row r="5">
@@ -2373,91 +2373,91 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10.26</v>
+        <v>22.32</v>
       </c>
       <c r="F5" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.872</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9.69</v>
+        <v>16.33</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3.393</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.23</v>
+        <v>14.75</v>
       </c>
       <c r="F7" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="G7" t="n">
-        <v>9.648</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2466,323 +2466,323 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.16</v>
+        <v>14.04</v>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>4.314</v>
+        <v>3.498</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.59</v>
+        <v>12.94</v>
       </c>
       <c r="F9" t="n">
-        <v>2.41</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
-        <v>1.924</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.88</v>
+        <v>12.9</v>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.191</v>
+        <v>4.478</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.79</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>17.095</v>
+        <v>83.70099999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.49</v>
+        <v>8.57</v>
       </c>
       <c r="F12" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>80.249</v>
+        <v>1.974</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.16</v>
+        <v>7.68</v>
       </c>
       <c r="F13" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="G13" t="n">
-        <v>0.889</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.374</v>
+        <v>20.541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-0.18</v>
+        <v>5.32</v>
       </c>
       <c r="F15" t="n">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="G15" t="n">
-        <v>5.654</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-0.76</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G16" t="n">
-        <v>0.864</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1.52</v>
+        <v>3.38</v>
       </c>
       <c r="F17" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="G17" t="n">
-        <v>19.89</v>
+        <v>5.972</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-1.54</v>
+        <v>3.21</v>
       </c>
       <c r="F18" t="n">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="19">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-2.64</v>
+        <v>1.92</v>
       </c>
       <c r="F19" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="G19" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2838,602 +2838,602 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-3.14</v>
+        <v>1.29</v>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="G20" t="n">
-        <v>0.48</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-3.86</v>
+        <v>0.59</v>
       </c>
       <c r="F21" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-3.93</v>
+        <v>0.28</v>
       </c>
       <c r="F22" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="G22" t="n">
-        <v>5.627</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-4.21</v>
+        <v>-0.32</v>
       </c>
       <c r="F23" t="n">
-        <v>0.79</v>
+        <v>1.24</v>
       </c>
       <c r="G23" t="n">
-        <v>17.186</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-4.33</v>
+        <v>-0.32</v>
       </c>
       <c r="F24" t="n">
-        <v>1.32</v>
+        <v>0.63</v>
       </c>
       <c r="G24" t="n">
-        <v>1.996</v>
+        <v>7.321</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-4.45</v>
+        <v>-0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="G25" t="n">
-        <v>16.786</v>
+        <v>15.006</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-5.68</v>
+        <v>-1.06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-6.42</v>
+        <v>-1.83</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="G27" t="n">
-        <v>5.412</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-6.47</v>
+        <v>-1.87</v>
       </c>
       <c r="F28" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="G28" t="n">
-        <v>14.517</v>
+        <v>1.978</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-6.94</v>
+        <v>-1.96</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.032</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-7.19</v>
+        <v>-2.33</v>
       </c>
       <c r="F30" t="n">
-        <v>0.76</v>
+        <v>1.48</v>
       </c>
       <c r="G30" t="n">
-        <v>4.743</v>
+        <v>1.565</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-7.25</v>
+        <v>-3.05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1.422</v>
+        <v>4.829</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-8.27</v>
+        <v>-3.58</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G32" t="n">
-        <v>1.495</v>
+        <v>7.768</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-9.210000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="F33" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="G33" t="n">
-        <v>0.79</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-9.92</v>
+        <v>-4.44</v>
       </c>
       <c r="F34" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.678</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-9.98</v>
+        <v>-4.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="G35" t="n">
-        <v>1.735</v>
+        <v>16.796</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-11.39</v>
+        <v>-4.77</v>
       </c>
       <c r="F36" t="n">
-        <v>1.36</v>
+        <v>0.89</v>
       </c>
       <c r="G36" t="n">
-        <v>6.862</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-11.7</v>
+        <v>-5.03</v>
       </c>
       <c r="F37" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="G37" t="n">
-        <v>8.058</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-11.75</v>
+        <v>-6.02</v>
       </c>
       <c r="F38" t="n">
-        <v>1.03</v>
+        <v>0.62</v>
       </c>
       <c r="G38" t="n">
-        <v>1.983</v>
+        <v>1.246</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-11.95</v>
+        <v>-7.78</v>
       </c>
       <c r="F39" t="n">
-        <v>1.18</v>
+        <v>0.75</v>
       </c>
       <c r="G39" t="n">
-        <v>0.116</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="40">
@@ -3458,168 +3458,168 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-12.88</v>
+        <v>-8.01</v>
       </c>
       <c r="F40" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="G40" t="n">
-        <v>0.227</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-14.1</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>1.203</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-14.87</v>
+        <v>-9.35</v>
       </c>
       <c r="F42" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="G42" t="n">
-        <v>0.468</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-15.06</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.73</v>
+        <v>1.19</v>
       </c>
       <c r="G43" t="n">
-        <v>1.88</v>
+        <v>1.297</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-16.05</v>
+        <v>-11.28</v>
       </c>
       <c r="F44" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G44" t="n">
-        <v>2.342</v>
+        <v>21.845</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-16.7</v>
+        <v>-14.07</v>
       </c>
       <c r="F45" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="G45" t="n">
-        <v>6.676</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="46">
@@ -3644,75 +3644,75 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-17.71</v>
+        <v>-14.41</v>
       </c>
       <c r="F46" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="G46" t="n">
-        <v>0.883</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-18.85</v>
+        <v>-15.16</v>
       </c>
       <c r="F47" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="G47" t="n">
-        <v>20.573</v>
+        <v>2.293</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-22.22</v>
+        <v>-19.46</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G48" t="n">
-        <v>21.568</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="49">
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-24.15</v>
+        <v>-20.56</v>
       </c>
       <c r="F49" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="G49" t="n">
-        <v>3.748</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="50">
@@ -3768,44 +3768,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-24.3</v>
+        <v>-20.59</v>
       </c>
       <c r="F50" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G50" t="n">
-        <v>14.595</v>
+        <v>15.697</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-24.95</v>
+        <v>-22.21</v>
       </c>
       <c r="F51" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="G51" t="n">
-        <v>0.091</v>
+        <v>23.246</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-25.85</v>
+        <v>-24.36</v>
       </c>
       <c r="F52" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="G52" t="n">
-        <v>1.556</v>
+        <v>1.486</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.64</v>
+        <v>35.79</v>
       </c>
       <c r="C2" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="D2" t="n">
-        <v>2.883</v>
+        <v>3.068</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.04</v>
+        <v>27.22666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.64</v>
       </c>
       <c r="D3" t="n">
-        <v>10.136</v>
+        <v>11.015</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.23</v>
+        <v>16.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="D4" t="n">
-        <v>9.648</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,55 +3940,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.146666666666667</v>
+        <v>12.94</v>
       </c>
       <c r="C5" t="n">
-        <v>2.243333333333334</v>
+        <v>1.56</v>
       </c>
       <c r="D5" t="n">
-        <v>9.631</v>
+        <v>0.217</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.88</v>
+        <v>11.83666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>1.41</v>
+        <v>1.486666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.191</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>7.44</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D7" t="n">
-        <v>1.374</v>
+        <v>20.541</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,36 +3997,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.52</v>
+        <v>5.85</v>
       </c>
       <c r="C8" t="n">
-        <v>0.74</v>
+        <v>0.825</v>
       </c>
       <c r="D8" t="n">
-        <v>19.89</v>
+        <v>23.629</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-2.2</v>
+        <v>4.49</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.855</v>
       </c>
       <c r="D9" t="n">
-        <v>21.838</v>
+        <v>91.02199999999999</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -4035,20 +4035,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3.342</v>
+        <v>3.6</v>
       </c>
       <c r="C10" t="n">
-        <v>1.15</v>
+        <v>0.95</v>
       </c>
       <c r="D10" t="n">
-        <v>7.612</v>
+        <v>1.329</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-3.93</v>
+        <v>3.38</v>
       </c>
       <c r="C11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D11" t="n">
-        <v>5.627</v>
+        <v>5.972</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-4.21</v>
+        <v>0.28</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="D12" t="n">
-        <v>17.186</v>
+        <v>17.36</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,112 +4092,112 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-4.45</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="C13" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="D13" t="n">
-        <v>16.786</v>
+        <v>26.397</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-4.605</v>
+        <v>-0.32</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="D14" t="n">
-        <v>88.30699999999999</v>
+        <v>2.17</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-4.625</v>
+        <v>-0.835</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9825</v>
+        <v>0.785</v>
       </c>
       <c r="D15" t="n">
-        <v>25.561</v>
+        <v>12.674</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-5.68</v>
+        <v>-1.164</v>
       </c>
       <c r="C16" t="n">
-        <v>1.28</v>
+        <v>0.944</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>7.46</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-6.355</v>
+        <v>-1.96</v>
       </c>
       <c r="C17" t="n">
-        <v>0.865</v>
+        <v>1.12</v>
       </c>
       <c r="D17" t="n">
-        <v>1.357</v>
+        <v>1.734</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7.25</v>
+        <v>-2.33</v>
       </c>
       <c r="C18" t="n">
-        <v>0.65</v>
+        <v>1.48</v>
       </c>
       <c r="D18" t="n">
-        <v>1.422</v>
+        <v>1.565</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,74 +4206,74 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-8.27</v>
+        <v>-4.390000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>0.825</v>
       </c>
       <c r="D19" t="n">
-        <v>1.495</v>
+        <v>2.761</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.955</v>
+        <v>-4.6</v>
       </c>
       <c r="C20" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="D20" t="n">
-        <v>4.342000000000001</v>
+        <v>16.796</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-9.98</v>
+        <v>-4.805</v>
       </c>
       <c r="C21" t="n">
-        <v>1.09</v>
+        <v>1.145</v>
       </c>
       <c r="D21" t="n">
-        <v>1.735</v>
+        <v>1.384</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-10.835</v>
+        <v>-4.92</v>
       </c>
       <c r="C22" t="n">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
       <c r="D22" t="n">
-        <v>2.661</v>
+        <v>4.362</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -4282,36 +4282,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-11.56</v>
+        <v>-6.02</v>
       </c>
       <c r="C23" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="D23" t="n">
-        <v>12.088</v>
+        <v>1.246</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-11.95</v>
+        <v>-8.01</v>
       </c>
       <c r="C24" t="n">
-        <v>1.18</v>
+        <v>0.51</v>
       </c>
       <c r="D24" t="n">
-        <v>0.116</v>
+        <v>0.219</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-12.88</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="D25" t="n">
-        <v>0.227</v>
+        <v>0.115</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,74 +4339,74 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-15.905</v>
+        <v>-11.28</v>
       </c>
       <c r="C26" t="n">
-        <v>1.195</v>
+        <v>0.83</v>
       </c>
       <c r="D26" t="n">
-        <v>2.086</v>
+        <v>21.845</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-17.43333333333333</v>
+        <v>-11.885</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8866666666666667</v>
+        <v>1.125</v>
       </c>
       <c r="D27" t="n">
-        <v>10.298</v>
+        <v>2.218</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-18.85</v>
+        <v>-14.00333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>20.573</v>
+        <v>11.064</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-22.22</v>
+        <v>-19.46</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="D29" t="n">
-        <v>21.568</v>
+        <v>0.095</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-24.15</v>
+        <v>-20.56</v>
       </c>
       <c r="C30" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="D30" t="n">
-        <v>3.748</v>
+        <v>3.534</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-24.3</v>
+        <v>-20.59</v>
       </c>
       <c r="C31" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="D31" t="n">
-        <v>14.595</v>
+        <v>15.697</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-24.95</v>
+        <v>-22.21</v>
       </c>
       <c r="C32" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="D32" t="n">
-        <v>0.091</v>
+        <v>23.246</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1745</v>
+        <v>1890</v>
       </c>
       <c r="E2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="F2" t="n">
-        <v>-24.3</v>
+        <v>-20.59</v>
       </c>
       <c r="G2" t="n">
-        <v>43.9</v>
+        <v>48.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-62.5967</v>
+        <v>-51.5315</v>
       </c>
       <c r="I2" t="n">
-        <v>26.2</v>
+        <v>50.8</v>
       </c>
       <c r="J2" t="n">
-        <v>30.1</v>
+        <v>61.3</v>
       </c>
       <c r="K2" t="n">
-        <v>8.31</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
-        <v>-27</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1705</v>
+        <v>1765</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4</v>
+        <v>3.52</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.21</v>
+        <v>0.28</v>
       </c>
       <c r="G3" t="n">
-        <v>49.68</v>
+        <v>45.52</v>
       </c>
       <c r="H3" t="n">
-        <v>29.7305</v>
+        <v>27.398</v>
       </c>
       <c r="I3" t="n">
-        <v>19.3</v>
+        <v>40.3</v>
       </c>
       <c r="J3" t="n">
-        <v>14.3</v>
+        <v>35.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.94</v>
+        <v>4.43</v>
       </c>
       <c r="L3" t="n">
-        <v>-47.7</v>
+        <v>-41.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9.92</v>
+        <v>5.64</v>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>-1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>61.28</v>
+        <v>61.19</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8101</v>
+        <v>2.3461</v>
       </c>
       <c r="I4" t="n">
-        <v>63.2</v>
+        <v>84.2</v>
       </c>
       <c r="J4" t="n">
-        <v>69.2</v>
+        <v>97.2</v>
       </c>
       <c r="K4" t="n">
-        <v>8.17</v>
+        <v>7.73</v>
       </c>
       <c r="L4" t="n">
-        <v>88.7</v>
+        <v>262.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.89</v>
+        <v>1.54</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62.9</v>
+        <v>63.2</v>
       </c>
       <c r="E5" t="n">
-        <v>6.61</v>
+        <v>0.48</v>
       </c>
       <c r="F5" t="n">
-        <v>-12.88</v>
+        <v>-8.01</v>
       </c>
       <c r="G5" t="n">
-        <v>52.7</v>
+        <v>50.54</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6615</v>
+        <v>-1.7042</v>
       </c>
       <c r="I5" t="n">
-        <v>34.8</v>
+        <v>38</v>
       </c>
       <c r="J5" t="n">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.45</v>
+        <v>6.39</v>
       </c>
       <c r="L5" t="n">
-        <v>-48.1</v>
+        <v>-28.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>201.5</v>
+        <v>221.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.07</v>
+        <v>9.93</v>
       </c>
       <c r="F6" t="n">
-        <v>17.84</v>
+        <v>31.85</v>
       </c>
       <c r="G6" t="n">
-        <v>60.69</v>
+        <v>63.14</v>
       </c>
       <c r="H6" t="n">
-        <v>11.6491</v>
+        <v>11.9262</v>
       </c>
       <c r="I6" t="n">
-        <v>55.9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>36.3</v>
+        <v>58</v>
       </c>
       <c r="K6" t="n">
-        <v>9.15</v>
+        <v>8.58</v>
       </c>
       <c r="L6" t="n">
-        <v>-69.59999999999999</v>
+        <v>-75.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>209.5</v>
+        <v>219</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.48</v>
+        <v>4.53</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.47</v>
+        <v>-0.68</v>
       </c>
       <c r="G7" t="n">
-        <v>46.67</v>
+        <v>50.28</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9496</v>
+        <v>-2.0656</v>
       </c>
       <c r="I7" t="n">
-        <v>16.1</v>
+        <v>39.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>25.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.5</v>
+        <v>-21.8</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>0.87</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74.90000000000001</v>
+        <v>43.65</v>
       </c>
       <c r="E2" t="n">
-        <v>5.64</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.905</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.87</v>
+        <v>-2</v>
       </c>
       <c r="F3" t="n">
-        <v>206</v>
+        <v>264</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,101 +538,101 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.217</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>137</v>
+        <v>107.5</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2</v>
+        <v>-6.93</v>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.984</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>350.5</v>
+        <v>429</v>
       </c>
       <c r="E5" t="n">
-        <v>9.869999999999999</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.768</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33.9</v>
+        <v>239.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.99</v>
+        <v>-5.71</v>
       </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,67 +640,67 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.297</v>
+        <v>22.552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>348.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5.13</v>
+        <v>-0.57</v>
       </c>
       <c r="F7" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.845</v>
+        <v>8.074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="E8" t="n">
-        <v>4.09</v>
+        <v>-0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,101 +708,101 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.81</v>
+        <v>20.537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>51.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4.44</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.972</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3365</v>
+        <v>38.8</v>
       </c>
       <c r="E10" t="n">
-        <v>9.970000000000001</v>
+        <v>-1.27</v>
       </c>
       <c r="F10" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.94</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>474</v>
+        <v>134.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3.04</v>
+        <v>-1.82</v>
       </c>
       <c r="F11" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,135 +810,135 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.734</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1400</v>
+        <v>46.25</v>
       </c>
       <c r="E12" t="n">
-        <v>8.529999999999999</v>
+        <v>-1.91</v>
       </c>
       <c r="F12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18.8</v>
+        <v>2.126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>133</v>
+        <v>389.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1</v>
+        <v>0.26</v>
       </c>
       <c r="F13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.75</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>115.5</v>
+        <v>204.5</v>
       </c>
       <c r="E14" t="n">
-        <v>5.96</v>
+        <v>-5.1</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.707</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>188.5</v>
       </c>
       <c r="E15" t="n">
-        <v>3.54</v>
+        <v>-1.31</v>
       </c>
       <c r="F15" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.921</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>254</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>9.960000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.246</v>
+        <v>1.979</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>114</v>
+        <v>225.5</v>
       </c>
       <c r="E17" t="n">
-        <v>8.06</v>
+        <v>-1.53</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,101 +1014,101 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>21.845</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>388.5</v>
+        <v>107.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.04</v>
+        <v>-5.7</v>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.329</v>
+        <v>3.288</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1890</v>
+        <v>109</v>
       </c>
       <c r="E19" t="n">
-        <v>8.31</v>
+        <v>-4.39</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15.697</v>
+        <v>20.905</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>191</v>
+        <v>300</v>
       </c>
       <c r="E20" t="n">
-        <v>3.24</v>
+        <v>-1.96</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.486</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>289</v>
+        <v>3315</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3</v>
+        <v>-1.49</v>
       </c>
       <c r="F21" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.796</v>
+        <v>5.794</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1260</v>
+        <v>473</v>
       </c>
       <c r="E22" t="n">
-        <v>3.28</v>
+        <v>-0.21</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.565</v>
+        <v>1.729</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>215.5</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.47</v>
+        <v>-0.53</v>
       </c>
       <c r="F23" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,132 +1218,132 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.293</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>2.19</v>
+        <v>-1.93</v>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4.478</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1940</v>
+        <v>23.1</v>
       </c>
       <c r="E25" t="n">
-        <v>4.86</v>
+        <v>-0.86</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>83.70099999999999</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>219</v>
+        <v>1885</v>
       </c>
       <c r="E26" t="n">
-        <v>4.53</v>
+        <v>-2.84</v>
       </c>
       <c r="F26" t="n">
         <v>78</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15.006</v>
+        <v>81.874</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>192.5</v>
+        <v>1225</v>
       </c>
       <c r="E27" t="n">
-        <v>4.05</v>
+        <v>-2.78</v>
       </c>
       <c r="F27" t="n">
         <v>78</v>
@@ -1354,30 +1354,30 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.095</v>
+        <v>1.525</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>154</v>
+        <v>2290</v>
       </c>
       <c r="E28" t="n">
-        <v>5.48</v>
+        <v>-3.58</v>
       </c>
       <c r="F28" t="n">
         <v>76</v>
@@ -1388,67 +1388,67 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.479</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79.8</v>
+        <v>153.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.76</v>
+        <v>-0.32</v>
       </c>
       <c r="F29" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.974</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>63.2</v>
+        <v>72.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="F30" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.219</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>472</v>
+        <v>288.5</v>
       </c>
       <c r="E31" t="n">
-        <v>6.55</v>
+        <v>-0.17</v>
       </c>
       <c r="F31" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.054</v>
+        <v>5.754</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.55</v>
+        <v>42.95</v>
       </c>
       <c r="E32" t="n">
-        <v>1.96</v>
+        <v>-0.12</v>
       </c>
       <c r="F32" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.115</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>66.3</v>
+        <v>80</v>
       </c>
       <c r="E33" t="n">
-        <v>6.59</v>
+        <v>0.25</v>
       </c>
       <c r="F33" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>16.796</v>
+        <v>2.023</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>89.2</v>
+        <v>63.1</v>
       </c>
       <c r="E34" t="n">
-        <v>1.02</v>
+        <v>-4.83</v>
       </c>
       <c r="F34" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.978</v>
+        <v>15.638</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>99.7</v>
+        <v>33.7</v>
       </c>
       <c r="E35" t="n">
-        <v>9.92</v>
+        <v>-0.59</v>
       </c>
       <c r="F35" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>20.541</v>
+        <v>1.301</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>51.2</v>
+        <v>19.35</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="F36" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.212</v>
+        <v>1.089</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>39.3</v>
+        <v>1810</v>
       </c>
       <c r="E37" t="n">
-        <v>0.64</v>
+        <v>-4.23</v>
       </c>
       <c r="F37" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,101 +1694,101 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.798</v>
+        <v>14.846</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1765</v>
+        <v>62.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.52</v>
+        <v>1.97</v>
       </c>
       <c r="F38" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>17.36</v>
+        <v>3.652</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>345.5</v>
+        <v>1785</v>
       </c>
       <c r="E39" t="n">
-        <v>2.98</v>
+        <v>1.13</v>
       </c>
       <c r="F39" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9.779999999999999</v>
+        <v>17.339</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2375</v>
+        <v>214.5</v>
       </c>
       <c r="E40" t="n">
-        <v>5.79</v>
+        <v>-2.05</v>
       </c>
       <c r="F40" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6.734</v>
+        <v>14.499</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>60.9</v>
+        <v>132.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1.5</v>
+        <v>-0.38</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.498</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.5</v>
+        <v>2470</v>
       </c>
       <c r="E42" t="n">
-        <v>1.56</v>
+        <v>-0.6</v>
       </c>
       <c r="F42" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.246</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>114</v>
+        <v>159.5</v>
       </c>
       <c r="E43" t="n">
-        <v>2.24</v>
+        <v>0.31</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.534</v>
+        <v>4.846</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>47.15</v>
+        <v>60.6</v>
       </c>
       <c r="E44" t="n">
-        <v>1.4</v>
+        <v>-2.57</v>
       </c>
       <c r="F44" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,101 +1932,101 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.17</v>
+        <v>6.745</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2485</v>
+        <v>335</v>
       </c>
       <c r="E45" t="n">
-        <v>9.960000000000001</v>
+        <v>-3.04</v>
       </c>
       <c r="F45" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.068</v>
+        <v>9.532</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>62.2</v>
+        <v>1370</v>
       </c>
       <c r="E46" t="n">
-        <v>2.98</v>
+        <v>-2.14</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7.321</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>63.4</v>
+        <v>211.5</v>
       </c>
       <c r="E47" t="n">
-        <v>6.02</v>
+        <v>0.71</v>
       </c>
       <c r="F47" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.069</v>
+        <v>4.543</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>159</v>
+        <v>63.6</v>
       </c>
       <c r="E48" t="n">
-        <v>2.58</v>
+        <v>0.63</v>
       </c>
       <c r="F48" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4.829</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23.3</v>
+        <v>61.1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.87</v>
+        <v>-3.63</v>
       </c>
       <c r="F49" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.456</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>71.8</v>
+        <v>192.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.016</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>299</v>
+        <v>306.5</v>
       </c>
       <c r="E51" t="n">
-        <v>9.93</v>
+        <v>2.51</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6.423</v>
+        <v>6.383</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>221.5</v>
+        <v>223</v>
       </c>
       <c r="E52" t="n">
-        <v>9.93</v>
+        <v>0.68</v>
       </c>
       <c r="F52" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.608</v>
+        <v>3.583</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35.79</v>
+        <v>45.29</v>
       </c>
       <c r="F2" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="G2" t="n">
-        <v>3.068</v>
+        <v>2.958</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.85</v>
+        <v>42.49</v>
       </c>
       <c r="F3" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="G3" t="n">
-        <v>3.608</v>
+        <v>3.583</v>
       </c>
     </row>
     <row r="4">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27.51</v>
+        <v>38.37</v>
       </c>
       <c r="F4" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="G4" t="n">
-        <v>6.423</v>
+        <v>6.383</v>
       </c>
     </row>
     <row r="5">
@@ -2373,137 +2373,137 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22.32</v>
+        <v>29.95</v>
       </c>
       <c r="F5" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
-        <v>0.984</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.33</v>
+        <v>22.44</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.75</v>
+        <v>18.74</v>
       </c>
       <c r="F7" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="G7" t="n">
-        <v>18.8</v>
+        <v>3.652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.04</v>
+        <v>16.75</v>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
       <c r="G8" t="n">
-        <v>3.498</v>
+        <v>20.537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.94</v>
+        <v>16.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.56</v>
+        <v>0.98</v>
       </c>
       <c r="G9" t="n">
-        <v>0.217</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="10">
@@ -2528,44 +2528,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.9</v>
+        <v>14.95</v>
       </c>
       <c r="F10" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="G10" t="n">
-        <v>4.478</v>
+        <v>4.543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.300000000000001</v>
+        <v>14.73</v>
       </c>
       <c r="F11" t="n">
-        <v>1.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>83.70099999999999</v>
+        <v>9.532</v>
       </c>
     </row>
     <row r="12">
@@ -2590,509 +2590,509 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.57</v>
+        <v>8.84</v>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="G12" t="n">
-        <v>1.974</v>
+        <v>2.023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.68</v>
+        <v>6.8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>5.94</v>
+        <v>81.874</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.44</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="G14" t="n">
-        <v>20.541</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.32</v>
+        <v>5.68</v>
       </c>
       <c r="F15" t="n">
-        <v>0.52</v>
+        <v>0.79</v>
       </c>
       <c r="G15" t="n">
-        <v>2.069</v>
+        <v>5.754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3.6</v>
+        <v>5.57</v>
       </c>
       <c r="F16" t="n">
         <v>0.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1.329</v>
+        <v>5.794</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.38</v>
+        <v>5.53</v>
       </c>
       <c r="F17" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="G17" t="n">
-        <v>5.972</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.21</v>
+        <v>5.29</v>
       </c>
       <c r="F18" t="n">
-        <v>0.84</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>5.796</v>
+        <v>8.074</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.92</v>
+        <v>5.26</v>
       </c>
       <c r="F19" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="G19" t="n">
-        <v>4.75</v>
+        <v>5.858</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.29</v>
+        <v>4.69</v>
       </c>
       <c r="F20" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.798</v>
+        <v>17.339</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.59</v>
+        <v>4.4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.98</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
-        <v>2.212</v>
+        <v>2.126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.28</v>
+        <v>3.52</v>
       </c>
       <c r="F22" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="G22" t="n">
-        <v>17.36</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-0.32</v>
+        <v>0.8</v>
       </c>
       <c r="F23" t="n">
-        <v>1.24</v>
+        <v>0.61</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17</v>
+        <v>15.638</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-0.32</v>
+        <v>0.79</v>
       </c>
       <c r="F24" t="n">
-        <v>0.63</v>
+        <v>1.05</v>
       </c>
       <c r="G24" t="n">
-        <v>7.321</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-0.68</v>
+        <v>0.27</v>
       </c>
       <c r="F25" t="n">
-        <v>0.87</v>
+        <v>2.08</v>
       </c>
       <c r="G25" t="n">
-        <v>15.006</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-1.06</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456</v>
+        <v>14.499</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.905</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-1.87</v>
+        <v>-0.16</v>
       </c>
       <c r="F28" t="n">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="G28" t="n">
-        <v>1.978</v>
+        <v>6.745</v>
       </c>
     </row>
     <row r="29">
@@ -3117,199 +3117,199 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-1.96</v>
+        <v>-0.42</v>
       </c>
       <c r="F29" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G29" t="n">
-        <v>1.734</v>
+        <v>1.729</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-2.33</v>
+        <v>-0.62</v>
       </c>
       <c r="F30" t="n">
-        <v>1.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>1.565</v>
+        <v>4.846</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-3.05</v>
+        <v>-0.78</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="G31" t="n">
-        <v>4.829</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3.58</v>
+        <v>-1.07</v>
       </c>
       <c r="F32" t="n">
-        <v>1.47</v>
+        <v>0.8</v>
       </c>
       <c r="G32" t="n">
-        <v>7.768</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-3.75</v>
+        <v>-1.22</v>
       </c>
       <c r="F33" t="n">
-        <v>0.79</v>
+        <v>1.16</v>
       </c>
       <c r="G33" t="n">
-        <v>0.707</v>
+        <v>1.979</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-4.44</v>
+        <v>-2</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="G34" t="n">
-        <v>0.845</v>
+        <v>1.525</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-4.6</v>
+        <v>-2.05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.63</v>
+        <v>0.83</v>
       </c>
       <c r="G35" t="n">
-        <v>16.796</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="36">
@@ -3334,447 +3334,447 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-4.77</v>
+        <v>-2.42</v>
       </c>
       <c r="F36" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>2.016</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-5.03</v>
+        <v>-4.06</v>
       </c>
       <c r="F37" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="G37" t="n">
-        <v>2.054</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-6.02</v>
+        <v>-4.44</v>
       </c>
       <c r="F38" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>1.246</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-7.78</v>
+        <v>-6.03</v>
       </c>
       <c r="F39" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="G39" t="n">
-        <v>0.479</v>
+        <v>20.905</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-8.01</v>
+        <v>-6.04</v>
       </c>
       <c r="F40" t="n">
-        <v>0.51</v>
+        <v>0.95</v>
       </c>
       <c r="G40" t="n">
-        <v>0.219</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-8.050000000000001</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="G41" t="n">
-        <v>0.115</v>
+        <v>1.089</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-9.35</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="G42" t="n">
-        <v>6.734</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1.19</v>
+        <v>0.86</v>
       </c>
       <c r="G43" t="n">
-        <v>1.297</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-11.28</v>
+        <v>-10.13</v>
       </c>
       <c r="F44" t="n">
-        <v>0.83</v>
+        <v>1.12</v>
       </c>
       <c r="G44" t="n">
-        <v>21.845</v>
+        <v>1.301</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-14.07</v>
+        <v>-13.9</v>
       </c>
       <c r="F45" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G45" t="n">
-        <v>1.81</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-14.41</v>
+        <v>-14.71</v>
       </c>
       <c r="F46" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.921</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-15.16</v>
+        <v>-15.62</v>
       </c>
       <c r="F47" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="G47" t="n">
-        <v>2.293</v>
+        <v>14.846</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-19.46</v>
+        <v>-16.36</v>
       </c>
       <c r="F48" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.095</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-20.56</v>
+        <v>-18.4</v>
       </c>
       <c r="F49" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="G49" t="n">
-        <v>3.534</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-20.59</v>
+        <v>-18.43</v>
       </c>
       <c r="F50" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>15.697</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="51">
@@ -3799,44 +3799,44 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-22.21</v>
+        <v>-18.54</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="G51" t="n">
-        <v>23.246</v>
+        <v>22.552</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-24.36</v>
+        <v>-21.25</v>
       </c>
       <c r="F52" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="G52" t="n">
-        <v>1.486</v>
+        <v>3.288</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.79</v>
+        <v>45.29</v>
       </c>
       <c r="C2" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="D2" t="n">
-        <v>3.068</v>
+        <v>2.958</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.22666666666667</v>
+        <v>36.93666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>0.5566666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>11.015</v>
+        <v>10.965</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.33</v>
+        <v>22.44</v>
       </c>
       <c r="C4" t="n">
-        <v>0.82</v>
+        <v>1.84</v>
       </c>
       <c r="D4" t="n">
-        <v>9.779999999999999</v>
+        <v>0.277</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.94</v>
+        <v>16.75</v>
       </c>
       <c r="C5" t="n">
-        <v>1.56</v>
+        <v>0.89</v>
       </c>
       <c r="D5" t="n">
-        <v>0.217</v>
+        <v>20.537</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,39 +3959,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.83666666666667</v>
+        <v>14.73</v>
       </c>
       <c r="C6" t="n">
-        <v>1.486666666666667</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.532</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.44</v>
+        <v>14.17666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.71</v>
+        <v>1.163333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>20.541</v>
+        <v>10.218</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.85</v>
+        <v>7.990000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.825</v>
+        <v>0.77</v>
       </c>
       <c r="D8" t="n">
-        <v>23.629</v>
+        <v>22.896</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,36 +4016,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.49</v>
+        <v>5.7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.855</v>
+        <v>0.96</v>
       </c>
       <c r="D9" t="n">
-        <v>91.02199999999999</v>
+        <v>1.327</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6</v>
+        <v>5.26</v>
       </c>
       <c r="C10" t="n">
-        <v>0.95</v>
+        <v>1.08</v>
       </c>
       <c r="D10" t="n">
-        <v>1.329</v>
+        <v>5.858</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.38</v>
+        <v>4.69</v>
       </c>
       <c r="C11" t="n">
-        <v>1.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>5.972</v>
+        <v>17.339</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.28</v>
+        <v>4.4</v>
       </c>
       <c r="C12" t="n">
-        <v>0.71</v>
+        <v>1.31</v>
       </c>
       <c r="D12" t="n">
-        <v>17.36</v>
+        <v>2.126</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,93 +4092,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002499999999999947</v>
+        <v>3.32</v>
       </c>
       <c r="C13" t="n">
-        <v>0.86</v>
+        <v>0.825</v>
       </c>
       <c r="D13" t="n">
-        <v>26.397</v>
+        <v>88.619</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.32</v>
+        <v>1.7875</v>
       </c>
       <c r="C14" t="n">
-        <v>1.24</v>
+        <v>0.83</v>
       </c>
       <c r="D14" t="n">
-        <v>2.17</v>
+        <v>25.769</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.835</v>
+        <v>0.8</v>
       </c>
       <c r="C15" t="n">
-        <v>0.785</v>
+        <v>0.61</v>
       </c>
       <c r="D15" t="n">
-        <v>12.674</v>
+        <v>15.638</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.164</v>
+        <v>-0.42</v>
       </c>
       <c r="C16" t="n">
-        <v>0.944</v>
+        <v>1.11</v>
       </c>
       <c r="D16" t="n">
-        <v>7.46</v>
+        <v>1.729</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.96</v>
+        <v>-0.78</v>
       </c>
       <c r="C17" t="n">
-        <v>1.12</v>
+        <v>0.54</v>
       </c>
       <c r="D17" t="n">
-        <v>1.734</v>
+        <v>0.208</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,36 +4187,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-2.33</v>
+        <v>-0.784</v>
       </c>
       <c r="C18" t="n">
-        <v>1.48</v>
+        <v>0.952</v>
       </c>
       <c r="D18" t="n">
-        <v>1.565</v>
+        <v>7.525</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-4.390000000000001</v>
+        <v>-1.895</v>
       </c>
       <c r="C19" t="n">
-        <v>0.825</v>
+        <v>1.43</v>
       </c>
       <c r="D19" t="n">
-        <v>2.761</v>
+        <v>1.262</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -4225,17 +4225,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-4.6</v>
+        <v>-2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.63</v>
+        <v>1.41</v>
       </c>
       <c r="D20" t="n">
-        <v>16.796</v>
+        <v>1.525</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.805</v>
+        <v>-4.57</v>
       </c>
       <c r="C21" t="n">
-        <v>1.145</v>
+        <v>0.82</v>
       </c>
       <c r="D21" t="n">
-        <v>1.384</v>
+        <v>11.944</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-4.92</v>
+        <v>-5.414999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="D22" t="n">
-        <v>4.362</v>
+        <v>4.117</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -4282,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-6.02</v>
+        <v>-6.03</v>
       </c>
       <c r="C23" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="D23" t="n">
-        <v>1.246</v>
+        <v>20.905</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,55 +4301,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-8.01</v>
+        <v>-6.383333333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>0.51</v>
+        <v>1.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.219</v>
+        <v>11.205</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-8.050000000000001</v>
+        <v>-6.870000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="D25" t="n">
-        <v>0.115</v>
+        <v>2.595</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-11.28</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>21.845</v>
+        <v>1.089</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,55 +4358,55 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-11.885</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>1.125</v>
+        <v>0.97</v>
       </c>
       <c r="D27" t="n">
-        <v>2.218</v>
+        <v>0.111</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-14.00333333333333</v>
+        <v>-12.015</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="D28" t="n">
-        <v>11.064</v>
+        <v>2.231</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-19.46</v>
+        <v>-15.62</v>
       </c>
       <c r="C29" t="n">
         <v>0.86</v>
       </c>
       <c r="D29" t="n">
-        <v>0.095</v>
+        <v>14.846</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-20.56</v>
+        <v>-18.43</v>
       </c>
       <c r="C30" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>3.534</v>
+        <v>0.094</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,17 +4434,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-20.59</v>
+        <v>-18.54</v>
       </c>
       <c r="C31" t="n">
-        <v>0.85</v>
+        <v>1.13</v>
       </c>
       <c r="D31" t="n">
-        <v>15.697</v>
+        <v>22.552</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-22.21</v>
+        <v>-21.25</v>
       </c>
       <c r="C32" t="n">
-        <v>0.88</v>
+        <v>0.6</v>
       </c>
       <c r="D32" t="n">
-        <v>23.246</v>
+        <v>3.288</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1890</v>
+        <v>1810</v>
       </c>
       <c r="E2" t="n">
-        <v>8.31</v>
+        <v>-4.23</v>
       </c>
       <c r="F2" t="n">
-        <v>-20.59</v>
+        <v>-15.62</v>
       </c>
       <c r="G2" t="n">
-        <v>48.7</v>
+        <v>49.43</v>
       </c>
       <c r="H2" t="n">
-        <v>-51.5315</v>
+        <v>-48.6567</v>
       </c>
       <c r="I2" t="n">
-        <v>50.8</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>61.3</v>
+        <v>44.1</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>7.99</v>
       </c>
       <c r="L2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1765</v>
+        <v>1785</v>
       </c>
       <c r="E3" t="n">
-        <v>3.52</v>
+        <v>1.13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28</v>
+        <v>4.69</v>
       </c>
       <c r="G3" t="n">
-        <v>45.52</v>
+        <v>45.89</v>
       </c>
       <c r="H3" t="n">
-        <v>27.398</v>
+        <v>26.8538</v>
       </c>
       <c r="I3" t="n">
-        <v>40.3</v>
+        <v>45.7</v>
       </c>
       <c r="J3" t="n">
-        <v>35.7</v>
+        <v>42.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.43</v>
+        <v>4.52</v>
       </c>
       <c r="L3" t="n">
-        <v>-41.2</v>
+        <v>-34.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>5.64</v>
+        <v>-2</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.83</v>
+        <v>0.27</v>
       </c>
       <c r="G4" t="n">
-        <v>61.19</v>
+        <v>60.63</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3461</v>
+        <v>2.6196</v>
       </c>
       <c r="I4" t="n">
-        <v>84.2</v>
+        <v>76.5</v>
       </c>
       <c r="J4" t="n">
-        <v>97.2</v>
+        <v>86.7</v>
       </c>
       <c r="K4" t="n">
-        <v>7.73</v>
+        <v>8.07</v>
       </c>
       <c r="L4" t="n">
-        <v>262.1</v>
+        <v>164.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>💰 STRONG INFLOW</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.01</v>
+        <v>-0.78</v>
       </c>
       <c r="G5" t="n">
-        <v>50.54</v>
+        <v>52.46</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7042</v>
+        <v>-1.6863</v>
       </c>
       <c r="I5" t="n">
-        <v>38</v>
+        <v>40.4</v>
       </c>
       <c r="J5" t="n">
-        <v>28.2</v>
+        <v>30.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.39</v>
+        <v>6.32</v>
       </c>
       <c r="L5" t="n">
-        <v>-28.9</v>
+        <v>-53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>221.5</v>
+        <v>223</v>
       </c>
       <c r="E6" t="n">
-        <v>9.93</v>
+        <v>0.68</v>
       </c>
       <c r="F6" t="n">
-        <v>31.85</v>
+        <v>42.49</v>
       </c>
       <c r="G6" t="n">
-        <v>63.14</v>
+        <v>59.76</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9262</v>
+        <v>12.127</v>
       </c>
       <c r="I6" t="n">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="J6" t="n">
-        <v>58</v>
+        <v>60.1</v>
       </c>
       <c r="K6" t="n">
-        <v>8.58</v>
+        <v>8.33</v>
       </c>
       <c r="L6" t="n">
-        <v>-75.5</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>219</v>
+        <v>214.5</v>
       </c>
       <c r="E7" t="n">
-        <v>4.53</v>
+        <v>-2.05</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>50.28</v>
+        <v>46.41</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0656</v>
+        <v>-2.4919</v>
       </c>
       <c r="I7" t="n">
-        <v>39.4</v>
+        <v>28.5</v>
       </c>
       <c r="J7" t="n">
-        <v>25.7</v>
+        <v>13.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>4.45</v>
       </c>
       <c r="L7" t="n">
-        <v>-21.8</v>
+        <v>-36.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43.65</v>
+        <v>42.75</v>
       </c>
       <c r="E2" t="n">
-        <v>9.949999999999999</v>
+        <v>-2.06</v>
       </c>
       <c r="F2" t="n">
-        <v>335</v>
+        <v>510</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.277</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-2</v>
+        <v>3.13</v>
       </c>
       <c r="F3" t="n">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,101 +538,101 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.797</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>107.5</v>
+        <v>108.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.93</v>
+        <v>9.6</v>
       </c>
       <c r="F4" t="n">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.695</v>
+        <v>21.618</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>429</v>
+        <v>359.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.109999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="F5" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>239.5</v>
+        <v>201</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.71</v>
+        <v>-1.71</v>
       </c>
       <c r="F6" t="n">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,67 +640,67 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22.552</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>348.5</v>
+        <v>38.75</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.57</v>
+        <v>-0.13</v>
       </c>
       <c r="F7" t="n">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8.074</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>2480</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.537</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51.3</v>
+        <v>238</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>-0.63</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.299</v>
+        <v>21.449</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38.8</v>
+        <v>197</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.27</v>
+        <v>4.51</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.796</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>134.5</v>
+        <v>236</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.82</v>
+        <v>4.66</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.999</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.25</v>
+        <v>3190</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.91</v>
+        <v>-3.77</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,101 +844,101 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.126</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>389.5</v>
+        <v>109</v>
       </c>
       <c r="E13" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.327</v>
+        <v>19.408</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>204.5</v>
+        <v>134</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1</v>
+        <v>1.13</v>
       </c>
       <c r="F14" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.154</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>188.5</v>
+        <v>167</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.31</v>
+        <v>4.7</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.411</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="16">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>89.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.22</v>
+        <v>-1.45</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,67 +980,67 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.979</v>
+        <v>1.976</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>225.5</v>
+        <v>192</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.53</v>
+        <v>-0.26</v>
       </c>
       <c r="F17" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>107.5</v>
+        <v>51.3</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.7</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.288</v>
+        <v>2.348</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>109</v>
+        <v>18.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.39</v>
+        <v>-2.12</v>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>20.905</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>300</v>
+        <v>432.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.96</v>
+        <v>0.82</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.858</v>
+        <v>1.877</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3315</v>
+        <v>59.2</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.49</v>
+        <v>-4.67</v>
       </c>
       <c r="F21" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,101 +1150,101 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.794</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>473</v>
+        <v>114</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.21</v>
+        <v>6.05</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.729</v>
+        <v>3.408</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.9</v>
+        <v>136.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.53</v>
+        <v>1.49</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.93</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>1865</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.93</v>
+        <v>-1.06</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.111</v>
+        <v>81.422</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.1</v>
+        <v>33.55</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.86</v>
+        <v>-0.45</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,67 +1286,67 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.447</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1885</v>
+        <v>71.7</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.84</v>
+        <v>-1.1</v>
       </c>
       <c r="F26" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>81.874</v>
+        <v>2.002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1225</v>
+        <v>19.1</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.78</v>
+        <v>-1.29</v>
       </c>
       <c r="F27" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.525</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2290</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.58</v>
+        <v>-0.43</v>
       </c>
       <c r="F28" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.15</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>153.5</v>
+        <v>1720</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.32</v>
+        <v>-3.64</v>
       </c>
       <c r="F29" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.465</v>
+        <v>16.314</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.5</v>
+        <v>295.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.97</v>
+        <v>-1.5</v>
       </c>
       <c r="F30" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.004</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>288.5</v>
+        <v>207.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.17</v>
+        <v>-1.89</v>
       </c>
       <c r="F31" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.754</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="32">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>42.95</v>
+        <v>42.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.12</v>
+        <v>-0.7</v>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,101 +1524,101 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>27.85</v>
       </c>
       <c r="E33" t="n">
-        <v>0.25</v>
+        <v>-0.54</v>
       </c>
       <c r="F33" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.023</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>63.1</v>
+        <v>388</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.83</v>
+        <v>-0.39</v>
       </c>
       <c r="F34" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15.638</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>33.7</v>
+        <v>59.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.59</v>
+        <v>-1.82</v>
       </c>
       <c r="F35" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.301</v>
+        <v>6.267</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19.35</v>
+        <v>1225</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.089</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1810</v>
+        <v>45.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.23</v>
+        <v>-1.62</v>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,101 +1694,101 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14.846</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>62.1</v>
+        <v>1800</v>
       </c>
       <c r="E38" t="n">
-        <v>1.97</v>
+        <v>-0.55</v>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.652</v>
+        <v>13.507</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1785</v>
+        <v>1385</v>
       </c>
       <c r="E39" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="F39" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>17.339</v>
+        <v>18.002</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>214.5</v>
+        <v>64.3</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.05</v>
+        <v>1.9</v>
       </c>
       <c r="F40" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,101 +1796,101 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>14.499</v>
+        <v>15.386</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>132.5</v>
+        <v>2285</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.38</v>
+        <v>-0.22</v>
       </c>
       <c r="F41" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.686</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2470</v>
+        <v>106.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.6</v>
+        <v>-0.93</v>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.958</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>159.5</v>
+        <v>214.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.846</v>
+        <v>14.451</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>60.6</v>
+        <v>289</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.57</v>
+        <v>0.17</v>
       </c>
       <c r="F44" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.745</v>
+        <v>5.709</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>335</v>
+        <v>151.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.04</v>
+        <v>-1.3</v>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,177 +1966,177 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.532</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1370</v>
+        <v>341.5</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.14</v>
+        <v>1.94</v>
       </c>
       <c r="F46" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>18.05</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>211.5</v>
+        <v>470</v>
       </c>
       <c r="E47" t="n">
-        <v>0.71</v>
+        <v>-0.63</v>
       </c>
       <c r="F47" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.543</v>
+        <v>1.678</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>63.6</v>
+        <v>78.7</v>
       </c>
       <c r="E48" t="n">
-        <v>0.63</v>
+        <v>-1.63</v>
       </c>
       <c r="F48" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.208</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61.1</v>
+        <v>62.9</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.63</v>
+        <v>-1.1</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.963</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>192.5</v>
+        <v>237.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="F50" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.094</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>306.5</v>
+        <v>313</v>
       </c>
       <c r="E51" t="n">
-        <v>2.51</v>
+        <v>2.12</v>
       </c>
       <c r="F51" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6.383</v>
+        <v>6.304</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>223</v>
+        <v>60.5</v>
       </c>
       <c r="E52" t="n">
-        <v>0.68</v>
+        <v>-0.98</v>
       </c>
       <c r="F52" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.583</v>
+        <v>1.872</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>45.29</v>
+        <v>46.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.958</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42.49</v>
+        <v>38.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.583</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
@@ -2342,137 +2342,137 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38.37</v>
+        <v>32.35</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="G4" t="n">
-        <v>6.383</v>
+        <v>6.304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29.95</v>
+        <v>28.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="G5" t="n">
-        <v>0.999</v>
+        <v>21.618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22.44</v>
+        <v>26.39</v>
       </c>
       <c r="F6" t="n">
-        <v>1.84</v>
+        <v>1.07</v>
       </c>
       <c r="G6" t="n">
-        <v>0.277</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.74</v>
+        <v>18.42</v>
       </c>
       <c r="F7" t="n">
-        <v>1.18</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>3.652</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.75</v>
+        <v>15.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.89</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>20.537</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2497,91 +2497,91 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16.6</v>
+        <v>13.99</v>
       </c>
       <c r="F9" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G9" t="n">
-        <v>18.05</v>
+        <v>18.002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14.95</v>
+        <v>13.08</v>
       </c>
       <c r="F10" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="G10" t="n">
-        <v>4.543</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.73</v>
+        <v>12.98</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
-        <v>9.532</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2590,742 +2590,742 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.84</v>
+        <v>12.16</v>
       </c>
       <c r="F12" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="G12" t="n">
-        <v>2.023</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.8</v>
+        <v>7.71</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="n">
-        <v>81.874</v>
+        <v>15.386</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>7.46</v>
       </c>
       <c r="F14" t="n">
-        <v>0.96</v>
+        <v>0.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.327</v>
+        <v>1.872</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.68</v>
+        <v>6.93</v>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="G15" t="n">
-        <v>5.754</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.57</v>
+        <v>4.52</v>
       </c>
       <c r="F16" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="G16" t="n">
-        <v>5.794</v>
+        <v>5.709</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.53</v>
+        <v>4.28</v>
       </c>
       <c r="F17" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="G17" t="n">
-        <v>1.963</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.29</v>
+        <v>3.88</v>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>0.95</v>
       </c>
       <c r="G18" t="n">
-        <v>8.074</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.26</v>
+        <v>3.61</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>5.858</v>
+        <v>81.422</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.69</v>
+        <v>3.32</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="G20" t="n">
-        <v>17.339</v>
+        <v>19.408</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="F21" t="n">
-        <v>1.31</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.126</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="F22" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="G22" t="n">
-        <v>4.686</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="F23" t="n">
-        <v>0.61</v>
+        <v>1.26</v>
       </c>
       <c r="G23" t="n">
-        <v>15.638</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="F24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G24" t="n">
-        <v>2.299</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
       <c r="F25" t="n">
-        <v>2.08</v>
+        <v>1.07</v>
       </c>
       <c r="G25" t="n">
-        <v>0.797</v>
+        <v>2.348</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="F26" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="G26" t="n">
-        <v>14.499</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="G27" t="n">
-        <v>0.796</v>
+        <v>14.451</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-0.16</v>
+        <v>-1.56</v>
       </c>
       <c r="F28" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="G28" t="n">
-        <v>6.745</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-0.42</v>
+        <v>-2.05</v>
       </c>
       <c r="F29" t="n">
-        <v>1.11</v>
+        <v>0.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.729</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.62</v>
+        <v>-2.13</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G30" t="n">
-        <v>4.846</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.78</v>
+        <v>-2.14</v>
       </c>
       <c r="F31" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="G31" t="n">
-        <v>0.208</v>
+        <v>6.267</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1.07</v>
+        <v>-3.18</v>
       </c>
       <c r="F32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.8</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.447</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1.22</v>
+        <v>-3.49</v>
       </c>
       <c r="F33" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="G33" t="n">
-        <v>1.979</v>
+        <v>1.678</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2</v>
+        <v>-3.92</v>
       </c>
       <c r="F34" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="G34" t="n">
-        <v>1.525</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-2.05</v>
+        <v>-4.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G35" t="n">
-        <v>0.83</v>
+        <v>2.002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3334,137 +3334,137 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-2.42</v>
+        <v>-4.03</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="G36" t="n">
-        <v>2.004</v>
+        <v>1.976</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-4.06</v>
+        <v>-4.18</v>
       </c>
       <c r="F37" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="G37" t="n">
-        <v>0.465</v>
+        <v>16.314</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-4.44</v>
+        <v>-6.19</v>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>0.79</v>
       </c>
       <c r="G38" t="n">
-        <v>0.695</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-6.03</v>
+        <v>-6.84</v>
       </c>
       <c r="F39" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="G39" t="n">
-        <v>20.905</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-6.04</v>
+        <v>-6.99</v>
       </c>
       <c r="F40" t="n">
-        <v>0.95</v>
+        <v>1.07</v>
       </c>
       <c r="G40" t="n">
-        <v>1.72</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3489,13 +3489,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-8.289999999999999</v>
+        <v>-7.51</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G41" t="n">
-        <v>1.089</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="42">
@@ -3520,13 +3520,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.09</v>
       </c>
       <c r="F42" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="G42" t="n">
-        <v>0.111</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="43">
@@ -3551,292 +3551,292 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G43" t="n">
-        <v>1.9</v>
+        <v>1.877</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-10.13</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="G44" t="n">
-        <v>1.301</v>
+        <v>13.507</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-13.9</v>
+        <v>-11.06</v>
       </c>
       <c r="F45" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="G45" t="n">
-        <v>0.93</v>
+        <v>1.371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-14.71</v>
+        <v>-11.83</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="G46" t="n">
-        <v>6.15</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-15.62</v>
+        <v>-14.23</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>14.846</v>
+        <v>21.449</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-16.36</v>
+        <v>-15.53</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>2.154</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-18.4</v>
+        <v>-15.87</v>
       </c>
       <c r="F49" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="G49" t="n">
-        <v>1.411</v>
+        <v>3.408</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-18.43</v>
+        <v>-17.04</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>0.094</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-18.54</v>
+        <v>-18.12</v>
       </c>
       <c r="F51" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="G51" t="n">
-        <v>22.552</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-21.25</v>
+        <v>-21.79</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="G52" t="n">
-        <v>3.288</v>
+        <v>2.077</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.29</v>
+        <v>46.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="D2" t="n">
-        <v>2.958</v>
+        <v>2.99</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.93666666666667</v>
+        <v>32.27333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5566666666666666</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>10.965</v>
+        <v>11.039</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.44</v>
+        <v>28.4</v>
       </c>
       <c r="C4" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="D4" t="n">
-        <v>0.277</v>
+        <v>21.618</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.75</v>
+        <v>18.42</v>
       </c>
       <c r="C5" t="n">
-        <v>0.89</v>
+        <v>2.14</v>
       </c>
       <c r="D5" t="n">
-        <v>20.537</v>
+        <v>0.354</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.73</v>
+        <v>13.08</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D6" t="n">
-        <v>9.532</v>
+        <v>9.6</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.17666666666667</v>
+        <v>10.69</v>
       </c>
       <c r="C7" t="n">
-        <v>1.163333333333333</v>
+        <v>1.086666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>10.218</v>
+        <v>10.134</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -3997,55 +3997,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.990000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="C8" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="D8" t="n">
-        <v>22.896</v>
+        <v>15.386</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.7</v>
+        <v>5.970000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.96</v>
+        <v>0.79</v>
       </c>
       <c r="D9" t="n">
-        <v>1.327</v>
+        <v>23.119</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.26</v>
+        <v>3.88</v>
       </c>
       <c r="C10" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="D10" t="n">
-        <v>5.858</v>
+        <v>1.323</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.69</v>
+        <v>3.32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="D11" t="n">
-        <v>17.339</v>
+        <v>19.408</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,39 +4073,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4</v>
+        <v>2.046666666666666</v>
       </c>
       <c r="C12" t="n">
-        <v>1.31</v>
+        <v>1.126666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>2.126</v>
+        <v>11.467</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.32</v>
+        <v>1.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0.825</v>
+        <v>1.26</v>
       </c>
       <c r="D13" t="n">
-        <v>88.619</v>
+        <v>2.088</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7875</v>
+        <v>1.175</v>
       </c>
       <c r="C14" t="n">
-        <v>0.83</v>
+        <v>0.8525</v>
       </c>
       <c r="D14" t="n">
-        <v>25.769</v>
+        <v>25.75</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -4130,36 +4130,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8</v>
+        <v>0.7349999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.61</v>
+        <v>0.855</v>
       </c>
       <c r="D15" t="n">
-        <v>15.638</v>
+        <v>87.68899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.42</v>
+        <v>0.68</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.729</v>
+        <v>5.77</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.78</v>
+        <v>-1.56</v>
       </c>
       <c r="C17" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="D17" t="n">
-        <v>0.208</v>
+        <v>0.197</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,55 +4187,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.784</v>
+        <v>-1.875</v>
       </c>
       <c r="C18" t="n">
-        <v>0.952</v>
+        <v>1.525</v>
       </c>
       <c r="D18" t="n">
-        <v>7.525</v>
+        <v>1.371</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.895</v>
+        <v>-2.036</v>
       </c>
       <c r="C19" t="n">
-        <v>1.43</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>1.262</v>
+        <v>7.589</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-2</v>
+        <v>-3.49</v>
       </c>
       <c r="C20" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="D20" t="n">
-        <v>1.525</v>
+        <v>1.678</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,77 +4244,77 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.57</v>
+        <v>-4.18</v>
       </c>
       <c r="C21" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="D21" t="n">
-        <v>11.944</v>
+        <v>16.314</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-5.414999999999999</v>
+        <v>-6.84</v>
       </c>
       <c r="C22" t="n">
-        <v>0.62</v>
+        <v>1.03</v>
       </c>
       <c r="D22" t="n">
-        <v>4.117</v>
+        <v>1.516</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-6.03</v>
+        <v>-7.164999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.83</v>
+        <v>0.655</v>
       </c>
       <c r="D23" t="n">
-        <v>20.905</v>
+        <v>3.949</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-6.383333333333333</v>
+        <v>-7.51</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="D24" t="n">
-        <v>11.205</v>
+        <v>1.014</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-6.870000000000001</v>
+        <v>-7.97</v>
       </c>
       <c r="C25" t="n">
-        <v>0.95</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>2.595</v>
+        <v>2.563</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.09</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="D26" t="n">
-        <v>1.089</v>
+        <v>0.108</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-8.789999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="D27" t="n">
-        <v>0.111</v>
+        <v>13.507</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,17 +4377,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-12.015</v>
+        <v>-9.725</v>
       </c>
       <c r="C28" t="n">
-        <v>1.04</v>
+        <v>0.86</v>
       </c>
       <c r="D28" t="n">
-        <v>2.231</v>
+        <v>11.298</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -4396,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-15.62</v>
+        <v>-14.23</v>
       </c>
       <c r="C29" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="D29" t="n">
-        <v>14.846</v>
+        <v>21.449</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,36 +4415,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-18.43</v>
+        <v>-14.435</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="D30" t="n">
-        <v>0.094</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-18.54</v>
+        <v>-15.87</v>
       </c>
       <c r="C31" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="D31" t="n">
-        <v>22.552</v>
+        <v>3.408</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-21.25</v>
+        <v>-18.12</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="D32" t="n">
-        <v>3.288</v>
+        <v>0.094</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1810</v>
+        <v>1800</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.23</v>
+        <v>-0.55</v>
       </c>
       <c r="F2" t="n">
-        <v>-15.62</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>49.43</v>
+        <v>47.89</v>
       </c>
       <c r="H2" t="n">
-        <v>-48.6567</v>
+        <v>-48.0631</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>44.1</v>
+        <v>41.9</v>
       </c>
       <c r="K2" t="n">
-        <v>7.99</v>
+        <v>7.88</v>
       </c>
       <c r="L2" t="n">
-        <v>-34</v>
+        <v>-43.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1785</v>
+        <v>1720</v>
       </c>
       <c r="E3" t="n">
-        <v>1.13</v>
+        <v>-3.64</v>
       </c>
       <c r="F3" t="n">
-        <v>4.69</v>
+        <v>-4.18</v>
       </c>
       <c r="G3" t="n">
-        <v>45.89</v>
+        <v>41.4</v>
       </c>
       <c r="H3" t="n">
-        <v>26.8538</v>
+        <v>18.2541</v>
       </c>
       <c r="I3" t="n">
-        <v>45.7</v>
+        <v>24.1</v>
       </c>
       <c r="J3" t="n">
-        <v>42.9</v>
+        <v>19.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.52</v>
+        <v>4.67</v>
       </c>
       <c r="L3" t="n">
-        <v>-34.6</v>
+        <v>-31.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-2</v>
+        <v>3.13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.27</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
-        <v>60.63</v>
+        <v>62.01</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6196</v>
+        <v>3.1006</v>
       </c>
       <c r="I4" t="n">
-        <v>76.5</v>
+        <v>86.8</v>
       </c>
       <c r="J4" t="n">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>8.07</v>
+        <v>7.84</v>
       </c>
       <c r="L4" t="n">
-        <v>164.4</v>
+        <v>153</v>
       </c>
       <c r="M4" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>💰 STRONG INFLOW</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.6</v>
+        <v>62.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.63</v>
+        <v>-1.1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.78</v>
+        <v>-1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>52.46</v>
+        <v>51.21</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6863</v>
+        <v>-2.1389</v>
       </c>
       <c r="I5" t="n">
-        <v>40.4</v>
+        <v>36.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.9</v>
+        <v>26.2</v>
       </c>
       <c r="K5" t="n">
-        <v>6.32</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-53</v>
+        <v>-59.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>223</v>
+        <v>237.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.68</v>
+        <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>42.49</v>
+        <v>38.08</v>
       </c>
       <c r="G6" t="n">
-        <v>59.76</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>12.127</v>
+        <v>12.8131</v>
       </c>
       <c r="I6" t="n">
-        <v>72</v>
+        <v>83.2</v>
       </c>
       <c r="J6" t="n">
-        <v>60.1</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
-        <v>8.33</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-67.59999999999999</v>
+        <v>-62</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4835,28 +4835,28 @@
         <v>214.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.05</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="G7" t="n">
-        <v>46.41</v>
+        <v>42.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4919</v>
+        <v>-3.1254</v>
       </c>
       <c r="I7" t="n">
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="J7" t="n">
         <v>13.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="L7" t="n">
-        <v>-36.5</v>
+        <v>-46.7</v>
       </c>
       <c r="M7" t="n">
         <v>0.85</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -4584,7 +4584,7 @@
         <v>47.89</v>
       </c>
       <c r="H2" t="n">
-        <v>-48.0631</v>
+        <v>-55.1742</v>
       </c>
       <c r="I2" t="n">
         <v>37.3</v>
@@ -4636,7 +4636,7 @@
         <v>41.4</v>
       </c>
       <c r="H3" t="n">
-        <v>18.2541</v>
+        <v>17.1312</v>
       </c>
       <c r="I3" t="n">
         <v>24.1</v>
@@ -4688,7 +4688,7 @@
         <v>62.01</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1006</v>
+        <v>3.1306</v>
       </c>
       <c r="I4" t="n">
         <v>86.8</v>
@@ -4740,7 +4740,7 @@
         <v>51.21</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1389</v>
+        <v>-2.1464</v>
       </c>
       <c r="I5" t="n">
         <v>36.8</v>
@@ -4792,7 +4792,7 @@
         <v>66.56999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>12.8131</v>
+        <v>12.6634</v>
       </c>
       <c r="I6" t="n">
         <v>83.2</v>
@@ -4844,7 +4844,7 @@
         <v>42.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1254</v>
+        <v>-3.2003</v>
       </c>
       <c r="I7" t="n">
         <v>28.9</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42.75</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.06</v>
+        <v>-2.64</v>
       </c>
       <c r="F2" t="n">
-        <v>510</v>
+        <v>377</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.354</v>
+        <v>1.289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75.7</v>
+        <v>48.15</v>
       </c>
       <c r="E3" t="n">
-        <v>3.13</v>
+        <v>2.45</v>
       </c>
       <c r="F3" t="n">
-        <v>253</v>
+        <v>354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.912</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>108.5</v>
+        <v>224.5</v>
       </c>
       <c r="E4" t="n">
-        <v>9.6</v>
+        <v>7.67</v>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>270</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>21.618</v>
+        <v>1.742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>359.5</v>
+        <v>285</v>
       </c>
       <c r="E5" t="n">
-        <v>3.16</v>
+        <v>9.83</v>
       </c>
       <c r="F5" t="n">
-        <v>113</v>
+        <v>219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,101 +606,101 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8.380000000000001</v>
+        <v>2.269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>201</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.71</v>
+        <v>6.79</v>
       </c>
       <c r="F6" t="n">
-        <v>112</v>
+        <v>193</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.077</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38.75</v>
+        <v>117.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.13</v>
+        <v>4.91</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2480</v>
+        <v>71.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.99</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>238</v>
+        <v>2810</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.63</v>
+        <v>9.98</v>
       </c>
       <c r="F9" t="n">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21.449</v>
+        <v>3.518</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E10" t="n">
-        <v>4.51</v>
+        <v>-2.08</v>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.371</v>
+        <v>15.081</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>236</v>
+        <v>1945</v>
       </c>
       <c r="E11" t="n">
-        <v>4.66</v>
+        <v>-1.77</v>
       </c>
       <c r="F11" t="n">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,203 +810,203 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.716</v>
+        <v>15.074</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3190</v>
+        <v>271.5</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.77</v>
+        <v>3.82</v>
       </c>
       <c r="F12" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.498</v>
+        <v>24.939</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>109</v>
+        <v>293.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-3.29</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19.408</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="E14" t="n">
-        <v>1.13</v>
+        <v>-5.68</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.79</v>
+        <v>3.292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>167</v>
+        <v>123.5</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7</v>
+        <v>5.56</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.117</v>
+        <v>22.481</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>88.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.45</v>
+        <v>2.09</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.976</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>192</v>
+        <v>89.8</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.26</v>
+        <v>1.13</v>
       </c>
       <c r="F17" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.094</v>
+        <v>2.041</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>51.3</v>
+        <v>202.5</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,67 +1048,67 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.348</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.5</v>
+        <v>134</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.12</v>
+        <v>-0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.914</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>432.5</v>
+        <v>118.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.82</v>
+        <v>2.16</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.877</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>59.2</v>
+        <v>381</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.67</v>
+        <v>0.66</v>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,101 +1150,101 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.594</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>114</v>
+        <v>1440</v>
       </c>
       <c r="E22" t="n">
-        <v>6.05</v>
+        <v>5.88</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.408</v>
+        <v>18.505</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>136.5</v>
+        <v>23.2</v>
       </c>
       <c r="E23" t="n">
-        <v>1.49</v>
+        <v>0.65</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.035</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1865</v>
+        <v>186</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.06</v>
+        <v>-0.8</v>
       </c>
       <c r="F24" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>81.422</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="25">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.55</v>
+        <v>35.7</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.45</v>
+        <v>2.59</v>
       </c>
       <c r="F25" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,67 +1286,67 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.286</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71.7</v>
+        <v>52.9</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1</v>
+        <v>1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.002</v>
+        <v>2.475</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19.1</v>
+        <v>39.35</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.29</v>
+        <v>0.9</v>
       </c>
       <c r="F27" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.014</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.43</v>
+        <v>2.25</v>
       </c>
       <c r="F28" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,101 +1388,101 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.446</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1720</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.64</v>
+        <v>4.04</v>
       </c>
       <c r="F29" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16.314</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>295.5</v>
+        <v>480</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.77</v>
+        <v>1.613</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>207.5</v>
+        <v>289</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.52</v>
+        <v>5.817</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>42.65</v>
+        <v>3190</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7</v>
+        <v>2.08</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8</v>
+        <v>5.108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.85</v>
+        <v>1205</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.54</v>
+        <v>-0.41</v>
       </c>
       <c r="F33" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,67 +1558,67 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.108</v>
+        <v>1.418</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>388</v>
+        <v>73.2</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.39</v>
+        <v>1.1</v>
       </c>
       <c r="F34" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.323</v>
+        <v>2.113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>59.5</v>
+        <v>168</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.82</v>
+        <v>1.82</v>
       </c>
       <c r="F35" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.267</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1225</v>
+        <v>218</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="F36" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.516</v>
+        <v>5.238</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>45.5</v>
+        <v>19</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.62</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.088</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1800</v>
+        <v>2290</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.55</v>
+        <v>1.33</v>
       </c>
       <c r="F38" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,101 +1728,101 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>13.507</v>
+        <v>5.209</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1385</v>
+        <v>294</v>
       </c>
       <c r="E39" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="F39" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>18.002</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>64.3</v>
+        <v>129.5</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9</v>
+        <v>-2.26</v>
       </c>
       <c r="F40" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>15.386</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2285</v>
+        <v>1870</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.22</v>
+        <v>1.69</v>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.8</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>106.5</v>
+        <v>19.25</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.93</v>
+        <v>0.52</v>
       </c>
       <c r="F42" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,101 +1864,101 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>214.5</v>
+        <v>434.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>14.451</v>
+        <v>10.003</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>289</v>
+        <v>46.45</v>
       </c>
       <c r="E44" t="n">
-        <v>0.17</v>
+        <v>-0.85</v>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5.709</v>
+        <v>2.149</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>151.5</v>
+        <v>28</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.3</v>
+        <v>1.08</v>
       </c>
       <c r="F45" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.459</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>341.5</v>
+        <v>1730</v>
       </c>
       <c r="E46" t="n">
-        <v>1.94</v>
+        <v>1.17</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9.6</v>
+        <v>14.828</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>470</v>
+        <v>450.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.63</v>
+        <v>2.27</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,135 +2034,135 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.678</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>78.7</v>
+        <v>60.7</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.63</v>
+        <v>0.33</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.02</v>
+        <v>6.124</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62.9</v>
+        <v>58.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.1</v>
+        <v>-1.35</v>
       </c>
       <c r="F49" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.197</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>237.5</v>
+        <v>342</v>
       </c>
       <c r="E50" t="n">
-        <v>6.5</v>
+        <v>1.33</v>
       </c>
       <c r="F50" t="n">
         <v>38</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.7</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>313</v>
+        <v>130.5</v>
       </c>
       <c r="E51" t="n">
-        <v>2.12</v>
+        <v>9.66</v>
       </c>
       <c r="F51" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6.304</v>
+        <v>23.448</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>60.5</v>
+        <v>79.3</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.98</v>
+        <v>0.51</v>
       </c>
       <c r="F52" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.872</v>
+        <v>2.103</v>
       </c>
     </row>
   </sheetData>
@@ -2280,509 +2280,509 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>46.75</v>
+        <v>56.55</v>
       </c>
       <c r="F2" t="n">
-        <v>0.58</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>2.99</v>
+        <v>3.518</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38.08</v>
+        <v>48.46</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7</v>
+        <v>23.448</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32.35</v>
+        <v>30.28</v>
       </c>
       <c r="F4" t="n">
-        <v>0.29</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>6.304</v>
+        <v>10.003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28.4</v>
+        <v>30.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.99</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>21.618</v>
+        <v>2.269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26.39</v>
+        <v>29.61</v>
       </c>
       <c r="F6" t="n">
-        <v>1.07</v>
+        <v>2.53</v>
       </c>
       <c r="G6" t="n">
-        <v>1.035</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.42</v>
+        <v>26.69</v>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>0.354</v>
+        <v>3.292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15.04</v>
+        <v>25.22</v>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>0.73</v>
       </c>
       <c r="G8" t="n">
-        <v>8.380000000000001</v>
+        <v>18.505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13.99</v>
+        <v>22.29</v>
       </c>
       <c r="F9" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="G9" t="n">
-        <v>18.002</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13.08</v>
+        <v>21.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.71</v>
+        <v>2.39</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>1.289</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.98</v>
+        <v>21.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>0.45</v>
       </c>
       <c r="G11" t="n">
-        <v>3.594</v>
+        <v>2.009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.16</v>
+        <v>20.49</v>
       </c>
       <c r="F12" t="n">
         <v>1.05</v>
       </c>
       <c r="G12" t="n">
-        <v>4.52</v>
+        <v>22.481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.71</v>
+        <v>20.42</v>
       </c>
       <c r="F13" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="G13" t="n">
-        <v>15.386</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.46</v>
+        <v>16.58</v>
       </c>
       <c r="F14" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.872</v>
+        <v>5.238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.93</v>
+        <v>14.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.52</v>
+        <v>11.16</v>
       </c>
       <c r="F16" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="G16" t="n">
-        <v>5.709</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.28</v>
+        <v>10.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.91</v>
+        <v>0.54</v>
       </c>
       <c r="G17" t="n">
-        <v>4.79</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.88</v>
+        <v>6.96</v>
       </c>
       <c r="F18" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.323</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="19">
@@ -2807,137 +2807,137 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.61</v>
+        <v>6.29</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="G19" t="n">
-        <v>81.422</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.32</v>
+        <v>6.02</v>
       </c>
       <c r="F20" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="G20" t="n">
-        <v>19.408</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.44</v>
+        <v>5.86</v>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>0.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0.912</v>
+        <v>5.817</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.16</v>
+        <v>5.54</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>1.716</v>
+        <v>1.273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.22</v>
+        <v>5.1</v>
       </c>
       <c r="F23" t="n">
-        <v>1.26</v>
+        <v>0.93</v>
       </c>
       <c r="G23" t="n">
-        <v>2.088</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="24">
@@ -2962,137 +2962,137 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.68</v>
+        <v>4.81</v>
       </c>
       <c r="F24" t="n">
-        <v>1.06</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="n">
-        <v>5.77</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.39</v>
+        <v>4.41</v>
       </c>
       <c r="F25" t="n">
-        <v>1.07</v>
+        <v>0.78</v>
       </c>
       <c r="G25" t="n">
-        <v>2.348</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.39</v>
+        <v>3.67</v>
       </c>
       <c r="F26" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.92</v>
+        <v>3.07</v>
       </c>
       <c r="F27" t="n">
-        <v>0.85</v>
+        <v>1.26</v>
       </c>
       <c r="G27" t="n">
-        <v>14.451</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-1.56</v>
+        <v>2.32</v>
       </c>
       <c r="F28" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="G28" t="n">
-        <v>0.197</v>
+        <v>2.475</v>
       </c>
     </row>
     <row r="29">
@@ -3117,261 +3117,261 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-2.05</v>
+        <v>1.51</v>
       </c>
       <c r="F29" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.117</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-2.13</v>
+        <v>-0.11</v>
       </c>
       <c r="F30" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G30" t="n">
-        <v>0.446</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-2.14</v>
+        <v>-0.88</v>
       </c>
       <c r="F31" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="G31" t="n">
-        <v>6.267</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3.18</v>
+        <v>-1.1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>1.41</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8</v>
+        <v>1.742</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-3.49</v>
+        <v>-1.27</v>
       </c>
       <c r="F33" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="G33" t="n">
-        <v>1.678</v>
+        <v>24.939</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-3.92</v>
+        <v>-1.3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.03</v>
+        <v>0.57</v>
       </c>
       <c r="G34" t="n">
-        <v>5.498</v>
+        <v>6.124</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-4.02</v>
+        <v>-1.59</v>
       </c>
       <c r="F35" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="G35" t="n">
-        <v>2.002</v>
+        <v>2.149</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-4.03</v>
+        <v>-1.62</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01</v>
+        <v>0.78</v>
       </c>
       <c r="G36" t="n">
-        <v>1.976</v>
+        <v>15.081</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-4.18</v>
+        <v>-1.69</v>
       </c>
       <c r="F37" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G37" t="n">
-        <v>16.314</v>
+        <v>5.108</v>
       </c>
     </row>
     <row r="38">
@@ -3396,168 +3396,168 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-6.19</v>
+        <v>-1.85</v>
       </c>
       <c r="F38" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0.459</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-6.84</v>
+        <v>-2.14</v>
       </c>
       <c r="F39" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>1.516</v>
+        <v>5.209</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-6.99</v>
+        <v>-2.26</v>
       </c>
       <c r="F40" t="n">
-        <v>1.07</v>
+        <v>0.64</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6860000000000001</v>
+        <v>14.828</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-7.51</v>
+        <v>-2.32</v>
       </c>
       <c r="F41" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>1.014</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-8.09</v>
+        <v>-2.91</v>
       </c>
       <c r="F42" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="G42" t="n">
-        <v>0.108</v>
+        <v>1.939</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-8.949999999999999</v>
+        <v>-3.68</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G43" t="n">
-        <v>1.877</v>
+        <v>2.113</v>
       </c>
     </row>
     <row r="44">
@@ -3582,168 +3582,168 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-9.550000000000001</v>
+        <v>-3.71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G44" t="n">
-        <v>13.507</v>
+        <v>15.074</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-11.06</v>
+        <v>-3.96</v>
       </c>
       <c r="F45" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="G45" t="n">
-        <v>1.371</v>
+        <v>2.041</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-11.83</v>
+        <v>-3.98</v>
       </c>
       <c r="F46" t="n">
-        <v>1.12</v>
+        <v>0.71</v>
       </c>
       <c r="G46" t="n">
-        <v>1.286</v>
+        <v>1.418</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-14.23</v>
+        <v>-7.15</v>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="G47" t="n">
-        <v>21.449</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-15.53</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G48" t="n">
-        <v>5.8</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-15.87</v>
+        <v>-9.68</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G49" t="n">
-        <v>3.408</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="50">
@@ -3768,75 +3768,75 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-17.04</v>
+        <v>-16.48</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="G50" t="n">
-        <v>0.914</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-18.12</v>
+        <v>-17.01</v>
       </c>
       <c r="F51" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="G51" t="n">
-        <v>0.094</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-21.79</v>
+        <v>-18.78</v>
       </c>
       <c r="F52" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="G52" t="n">
-        <v>2.077</v>
+        <v>0.093</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.75</v>
+        <v>56.55</v>
       </c>
       <c r="C2" t="n">
-        <v>0.58</v>
+        <v>0.95</v>
       </c>
       <c r="D2" t="n">
-        <v>2.99</v>
+        <v>3.518</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,36 +3902,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.27333333333333</v>
+        <v>48.46</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>11.039</v>
+        <v>23.448</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.4</v>
+        <v>29.61</v>
       </c>
       <c r="C4" t="n">
-        <v>0.99</v>
+        <v>2.53</v>
       </c>
       <c r="D4" t="n">
-        <v>21.618</v>
+        <v>0.518</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.42</v>
+        <v>20.49</v>
       </c>
       <c r="C5" t="n">
-        <v>2.14</v>
+        <v>1.05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.354</v>
+        <v>22.481</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.08</v>
+        <v>20.42</v>
       </c>
       <c r="C6" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="D6" t="n">
-        <v>9.6</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,17 +3978,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.69</v>
+        <v>20.04666666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>1.086666666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>10.134</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -3997,112 +3997,112 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.71</v>
+        <v>19.77333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>0.63</v>
+        <v>1.326666666666666</v>
       </c>
       <c r="D8" t="n">
-        <v>15.386</v>
+        <v>14.014</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.970000000000001</v>
+        <v>14.17</v>
       </c>
       <c r="C9" t="n">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="D9" t="n">
-        <v>23.119</v>
+        <v>17.946</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.88</v>
+        <v>13.365</v>
       </c>
       <c r="C10" t="n">
-        <v>0.95</v>
+        <v>0.665</v>
       </c>
       <c r="D10" t="n">
-        <v>1.323</v>
+        <v>23.465</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.32</v>
+        <v>11.13333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.95</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>19.408</v>
+        <v>11.024</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.046666666666666</v>
+        <v>9.975</v>
       </c>
       <c r="C12" t="n">
-        <v>1.126666666666667</v>
+        <v>1.54</v>
       </c>
       <c r="D12" t="n">
-        <v>11.467</v>
+        <v>1.786</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.22</v>
+        <v>6.96</v>
       </c>
       <c r="C13" t="n">
-        <v>1.26</v>
+        <v>0.78</v>
       </c>
       <c r="D13" t="n">
-        <v>2.088</v>
+        <v>0.22</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,55 +4111,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.175</v>
+        <v>5.54</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8525</v>
+        <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>25.75</v>
+        <v>1.273</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7349999999999999</v>
+        <v>4.81</v>
       </c>
       <c r="C15" t="n">
-        <v>0.855</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>87.68899999999999</v>
+        <v>5.682</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.68</v>
+        <v>4.41</v>
       </c>
       <c r="C16" t="n">
-        <v>1.06</v>
+        <v>0.78</v>
       </c>
       <c r="D16" t="n">
-        <v>5.77</v>
+        <v>3.301</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1.56</v>
+        <v>3.67</v>
       </c>
       <c r="C17" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>0.197</v>
+        <v>1.613</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.875</v>
+        <v>2.495</v>
       </c>
       <c r="C18" t="n">
-        <v>1.525</v>
+        <v>0.645</v>
       </c>
       <c r="D18" t="n">
-        <v>1.371</v>
+        <v>87.934</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -4206,74 +4206,74 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.036</v>
+        <v>2.3075</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.8225</v>
       </c>
       <c r="D19" t="n">
-        <v>7.589</v>
+        <v>26.707</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-3.49</v>
+        <v>2.135</v>
       </c>
       <c r="C20" t="n">
-        <v>1.13</v>
+        <v>0.705</v>
       </c>
       <c r="D20" t="n">
-        <v>1.678</v>
+        <v>4.124000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.18</v>
+        <v>0.07999999999999985</v>
       </c>
       <c r="C21" t="n">
-        <v>0.75</v>
+        <v>1.075</v>
       </c>
       <c r="D21" t="n">
-        <v>16.314</v>
+        <v>2.766</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-6.84</v>
+        <v>-1.27</v>
       </c>
       <c r="C22" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.516</v>
+        <v>24.939</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,55 +4282,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-7.164999999999999</v>
+        <v>-1.59</v>
       </c>
       <c r="C23" t="n">
-        <v>0.655</v>
+        <v>0.67</v>
       </c>
       <c r="D23" t="n">
-        <v>3.949</v>
+        <v>2.149</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.51</v>
+        <v>-1.704</v>
       </c>
       <c r="C24" t="n">
-        <v>0.75</v>
+        <v>0.772</v>
       </c>
       <c r="D24" t="n">
-        <v>1.014</v>
+        <v>7.914</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-7.97</v>
+        <v>-1.915</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9850000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="D25" t="n">
-        <v>2.563</v>
+        <v>10.317</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-8.09</v>
+        <v>-2.26</v>
       </c>
       <c r="C26" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="D26" t="n">
-        <v>0.108</v>
+        <v>14.828</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-9.550000000000001</v>
+        <v>-3.71</v>
       </c>
       <c r="C27" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="D27" t="n">
-        <v>13.507</v>
+        <v>15.074</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,36 +4377,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-9.725</v>
+        <v>-3.98</v>
       </c>
       <c r="C28" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="D28" t="n">
-        <v>11.298</v>
+        <v>1.418</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-14.23</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>1.04</v>
+        <v>0.68</v>
       </c>
       <c r="D29" t="n">
-        <v>21.449</v>
+        <v>0.952</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,39 +4415,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-14.435</v>
+        <v>-9.68</v>
       </c>
       <c r="C30" t="n">
-        <v>1.03</v>
+        <v>0.65</v>
       </c>
       <c r="D30" t="n">
-        <v>2.2</v>
+        <v>0.108</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-15.87</v>
+        <v>-11.815</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7</v>
+        <v>0.835</v>
       </c>
       <c r="D31" t="n">
-        <v>3.408</v>
+        <v>2.369</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-18.12</v>
+        <v>-18.78</v>
       </c>
       <c r="C32" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="D32" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>1945</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.55</v>
+        <v>-1.77</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.550000000000001</v>
+        <v>-3.71</v>
       </c>
       <c r="G2" t="n">
-        <v>47.89</v>
+        <v>45.21</v>
       </c>
       <c r="H2" t="n">
-        <v>-55.1742</v>
+        <v>-33.3725</v>
       </c>
       <c r="I2" t="n">
-        <v>37.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>41.9</v>
+        <v>90.7</v>
       </c>
       <c r="K2" t="n">
-        <v>7.88</v>
+        <v>7.25</v>
       </c>
       <c r="L2" t="n">
-        <v>-43.3</v>
+        <v>45.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1720</v>
+        <v>1730</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.64</v>
+        <v>1.17</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.18</v>
+        <v>-2.26</v>
       </c>
       <c r="G3" t="n">
-        <v>41.4</v>
+        <v>43.45</v>
       </c>
       <c r="H3" t="n">
-        <v>17.1312</v>
+        <v>10.3475</v>
       </c>
       <c r="I3" t="n">
-        <v>24.1</v>
+        <v>30.9</v>
       </c>
       <c r="J3" t="n">
-        <v>19.6</v>
+        <v>23.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-31.8</v>
+        <v>-50.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75.7</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>3.13</v>
+        <v>-2.64</v>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>21.8</v>
       </c>
       <c r="G4" t="n">
-        <v>62.01</v>
+        <v>56.35</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1306</v>
+        <v>4.3357</v>
       </c>
       <c r="I4" t="n">
-        <v>86.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>7.84</v>
+        <v>7.96</v>
       </c>
       <c r="L4" t="n">
-        <v>153</v>
+        <v>277</v>
       </c>
       <c r="M4" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>💰 STRONG INFLOW</t>
         </is>
       </c>
     </row>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1</v>
+        <v>6.79</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.56</v>
+        <v>6.96</v>
       </c>
       <c r="G5" t="n">
-        <v>51.21</v>
+        <v>40.85</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1464</v>
+        <v>-1.929</v>
       </c>
       <c r="I5" t="n">
-        <v>36.8</v>
+        <v>62.3</v>
       </c>
       <c r="J5" t="n">
-        <v>26.2</v>
+        <v>57.7</v>
       </c>
       <c r="K5" t="n">
-        <v>6.5</v>
+        <v>5.48</v>
       </c>
       <c r="L5" t="n">
-        <v>-59.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>237.5</v>
+        <v>216</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
+        <v>-5.68</v>
       </c>
       <c r="F6" t="n">
-        <v>38.08</v>
+        <v>26.69</v>
       </c>
       <c r="G6" t="n">
-        <v>66.56999999999999</v>
+        <v>54.57</v>
       </c>
       <c r="H6" t="n">
-        <v>12.6634</v>
+        <v>11.8976</v>
       </c>
       <c r="I6" t="n">
-        <v>83.2</v>
+        <v>57.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>36.6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.050000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-62</v>
+        <v>31.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>214.5</v>
+        <v>212</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.92</v>
+        <v>-1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>42.6</v>
+        <v>38.37</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2003</v>
+        <v>-3.2095</v>
       </c>
       <c r="I7" t="n">
-        <v>28.9</v>
+        <v>24.2</v>
       </c>
       <c r="J7" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="L7" t="n">
-        <v>-46.7</v>
+        <v>49.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.64</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.289</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48.15</v>
+        <v>313.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.45</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.518</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>224.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>7.67</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.742</v>
+        <v>1.561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>285</v>
+        <v>246.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.269</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67.59999999999999</v>
+        <v>323</v>
       </c>
       <c r="E6" t="n">
-        <v>6.79</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.22</v>
+        <v>6.295</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>117.5</v>
+        <v>2725</v>
       </c>
       <c r="E7" t="n">
-        <v>4.91</v>
+        <v>-3.02</v>
       </c>
       <c r="F7" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.827</v>
+        <v>3.353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71.7</v>
+        <v>211</v>
       </c>
       <c r="E8" t="n">
-        <v>9.970000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17.946</v>
+        <v>2.267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2810</v>
+        <v>66.8</v>
       </c>
       <c r="E9" t="n">
-        <v>9.98</v>
+        <v>-1.18</v>
       </c>
       <c r="F9" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3.518</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>47.2</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.08</v>
+        <v>-1.97</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>15.081</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1945</v>
+        <v>128</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.77</v>
+        <v>3.64</v>
       </c>
       <c r="F11" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>15.074</v>
+        <v>23.702</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>271.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.82</v>
+        <v>0.28</v>
       </c>
       <c r="F12" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24.939</v>
+        <v>18.221</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>293.5</v>
+        <v>227.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.29</v>
+        <v>5.32</v>
       </c>
       <c r="F13" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.612</v>
+        <v>3.596</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>216</v>
+        <v>143.5</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.68</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.292</v>
+        <v>25.826</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>123.5</v>
+        <v>481</v>
       </c>
       <c r="E15" t="n">
-        <v>5.56</v>
+        <v>6.77</v>
       </c>
       <c r="F15" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22.481</v>
+        <v>2.119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>2515</v>
       </c>
       <c r="E16" t="n">
-        <v>2.09</v>
+        <v>9.83</v>
       </c>
       <c r="F16" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,67 +980,67 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.839</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>89.8</v>
+        <v>164</v>
       </c>
       <c r="E17" t="n">
-        <v>1.13</v>
+        <v>3.14</v>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.041</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>202.5</v>
+        <v>187</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.74</v>
+        <v>0.54</v>
       </c>
       <c r="F18" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.115</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>134</v>
+        <v>322.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.74</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,271 +1082,271 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4.97</v>
+        <v>6.156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>118.5</v>
+        <v>3300</v>
       </c>
       <c r="E20" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.301</v>
+        <v>5.248</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>381</v>
+        <v>130.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.66</v>
+        <v>-2.61</v>
       </c>
       <c r="F21" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.273</v>
+        <v>4.941</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1440</v>
+        <v>1975</v>
       </c>
       <c r="E22" t="n">
-        <v>5.88</v>
+        <v>1.54</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>18.505</v>
+        <v>14.597</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.2</v>
+        <v>276</v>
       </c>
       <c r="E23" t="n">
-        <v>0.65</v>
+        <v>1.66</v>
       </c>
       <c r="F23" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.457</v>
+        <v>24.924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>186</v>
+        <v>382.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8</v>
+        <v>0.39</v>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.093</v>
+        <v>1.277</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35.7</v>
+        <v>357.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.59</v>
+        <v>4.53</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.415</v>
+        <v>9.115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52.9</v>
+        <v>44.35</v>
       </c>
       <c r="E26" t="n">
-        <v>1.93</v>
+        <v>0.8</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.475</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.35</v>
+        <v>210</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,101 +1354,101 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.828</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>159</v>
+        <v>293</v>
       </c>
       <c r="E28" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="F28" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.497</v>
+        <v>5.899</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64.40000000000001</v>
+        <v>39.3</v>
       </c>
       <c r="E29" t="n">
-        <v>4.04</v>
+        <v>-0.13</v>
       </c>
       <c r="F29" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.009</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>480</v>
+        <v>1250</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="F30" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.613</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>289</v>
+        <v>1465</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="F31" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.817</v>
+        <v>18.858</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3190</v>
+        <v>18.95</v>
       </c>
       <c r="E32" t="n">
-        <v>2.08</v>
+        <v>-0.26</v>
       </c>
       <c r="F32" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.108</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1205</v>
+        <v>19.3</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.41</v>
+        <v>0.26</v>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.418</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>73.2</v>
+        <v>28.1</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1</v>
+        <v>0.36</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.113</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>168</v>
+        <v>482</v>
       </c>
       <c r="E35" t="n">
-        <v>1.82</v>
+        <v>0.42</v>
       </c>
       <c r="F35" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.96</v>
+        <v>1.588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.23</v>
+        <v>1.19</v>
       </c>
       <c r="F36" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.238</v>
+        <v>5.113</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>23.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.954</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2290</v>
+        <v>1730</v>
       </c>
       <c r="E38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,101 +1728,101 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.209</v>
+        <v>14.415</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>294</v>
+        <v>134.5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.08</v>
+        <v>3.86</v>
       </c>
       <c r="F39" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.682</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>129.5</v>
+        <v>35.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.26</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.989</v>
+        <v>1.413</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1870</v>
+        <v>121</v>
       </c>
       <c r="E41" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>81.81</v>
+        <v>3.132</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.25</v>
+        <v>61.1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,67 +1864,67 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.952</v>
+        <v>5.996</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>434.5</v>
+        <v>47.3</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>1.83</v>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10.003</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>46.45</v>
+        <v>89.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.85</v>
+        <v>-0.33</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.149</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>1.08</v>
+        <v>0.27</v>
       </c>
       <c r="F45" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,109 +1966,109 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.108</v>
+        <v>2.111</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1730</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>1.17</v>
+        <v>0.31</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>14.828</v>
+        <v>2.013</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>450.5</v>
+        <v>1905</v>
       </c>
       <c r="E47" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="F47" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.939</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>60.7</v>
+        <v>53.3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.124</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="49">
@@ -2088,81 +2088,81 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.35</v>
+        <v>-0.34</v>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.683</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>342</v>
+        <v>218</v>
       </c>
       <c r="E50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.119999999999999</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>130.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>9.66</v>
+        <v>0.76</v>
       </c>
       <c r="F51" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>23.448</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>79.3</v>
+        <v>477.5</v>
       </c>
       <c r="E52" t="n">
-        <v>0.51</v>
+        <v>9.9</v>
       </c>
       <c r="F52" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.103</v>
+        <v>10.422</v>
       </c>
     </row>
   </sheetData>
@@ -2261,1071 +2261,1071 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56.55</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="G2" t="n">
-        <v>3.518</v>
+        <v>25.826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.46</v>
+        <v>55.79</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="G3" t="n">
-        <v>23.448</v>
+        <v>10.422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30.28</v>
+        <v>47.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="G4" t="n">
-        <v>10.003</v>
+        <v>3.353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30.14</v>
+        <v>46.92</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>0.71</v>
       </c>
       <c r="G5" t="n">
-        <v>2.269</v>
+        <v>6.156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>29.61</v>
+        <v>46.07</v>
       </c>
       <c r="F6" t="n">
-        <v>2.53</v>
+        <v>2.11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.518</v>
+        <v>1.561</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26.69</v>
+        <v>41.86</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>1.59</v>
       </c>
       <c r="G7" t="n">
-        <v>3.292</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25.22</v>
+        <v>38.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>18.505</v>
+        <v>3.596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22.29</v>
+        <v>32.58</v>
       </c>
       <c r="F9" t="n">
-        <v>0.54</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.612</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21.8</v>
+        <v>30.88</v>
       </c>
       <c r="F10" t="n">
-        <v>2.39</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>1.289</v>
+        <v>23.702</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.28</v>
+        <v>26.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="G11" t="n">
-        <v>2.009</v>
+        <v>18.858</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20.49</v>
+        <v>24.23</v>
       </c>
       <c r="F12" t="n">
-        <v>1.05</v>
+        <v>0.46</v>
       </c>
       <c r="G12" t="n">
-        <v>22.481</v>
+        <v>2.013</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.42</v>
+        <v>20.63</v>
       </c>
       <c r="F13" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="G13" t="n">
-        <v>9.119999999999999</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>16.58</v>
+        <v>17.41</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="G14" t="n">
-        <v>5.238</v>
+        <v>9.115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14.17</v>
+        <v>17.1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.89</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>17.946</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.16</v>
+        <v>16.27</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="G16" t="n">
-        <v>0.989</v>
+        <v>5.313</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10.8</v>
+        <v>13.93</v>
       </c>
       <c r="F17" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
       </c>
       <c r="G17" t="n">
-        <v>3.683</v>
+        <v>6.295</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.96</v>
+        <v>13.23</v>
       </c>
       <c r="F18" t="n">
-        <v>0.78</v>
+        <v>1.07</v>
       </c>
       <c r="G18" t="n">
-        <v>0.22</v>
+        <v>18.221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.29</v>
+        <v>11.69</v>
       </c>
       <c r="F19" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="G19" t="n">
-        <v>81.81</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.02</v>
+        <v>10.73</v>
       </c>
       <c r="F20" t="n">
-        <v>0.54</v>
+        <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>2.103</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.86</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="G21" t="n">
-        <v>5.817</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.54</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>0.47</v>
       </c>
       <c r="G22" t="n">
-        <v>1.273</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.1</v>
+        <v>7.37</v>
       </c>
       <c r="F23" t="n">
-        <v>0.93</v>
+        <v>0.66</v>
       </c>
       <c r="G23" t="n">
-        <v>4.97</v>
+        <v>82.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.81</v>
+        <v>5.94</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G24" t="n">
-        <v>5.682</v>
+        <v>5.248</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.41</v>
+        <v>5.89</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>3.301</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.67</v>
+        <v>4.83</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.613</v>
+        <v>5.899</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.07</v>
+        <v>4.79</v>
       </c>
       <c r="F27" t="n">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.827</v>
+        <v>1.277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.32</v>
+        <v>4.55</v>
       </c>
       <c r="F28" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.475</v>
+        <v>24.924</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.51</v>
+        <v>4.22</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="G29" t="n">
-        <v>4.96</v>
+        <v>14.597</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.11</v>
+        <v>3.39</v>
       </c>
       <c r="F30" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="G30" t="n">
-        <v>0.839</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.88</v>
+        <v>3.34</v>
       </c>
       <c r="F31" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G31" t="n">
-        <v>0.828</v>
+        <v>5.113</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1.1</v>
+        <v>3.29</v>
       </c>
       <c r="F32" t="n">
-        <v>1.41</v>
+        <v>0.82</v>
       </c>
       <c r="G32" t="n">
-        <v>1.742</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1.27</v>
+        <v>3.22</v>
       </c>
       <c r="F33" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="G33" t="n">
-        <v>24.939</v>
+        <v>2.119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.57</v>
+        <v>0.76</v>
       </c>
       <c r="G34" t="n">
-        <v>6.124</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-1.59</v>
+        <v>2.01</v>
       </c>
       <c r="F35" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G35" t="n">
-        <v>2.149</v>
+        <v>1.588</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3334,153 +3334,153 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-1.62</v>
+        <v>1.26</v>
       </c>
       <c r="F36" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="G36" t="n">
-        <v>15.081</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.69</v>
+        <v>1.21</v>
       </c>
       <c r="F37" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="G37" t="n">
-        <v>5.108</v>
+        <v>1.471</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.85</v>
+        <v>1.17</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="G38" t="n">
-        <v>0.497</v>
+        <v>14.415</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-2.14</v>
+        <v>1.16</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="G39" t="n">
-        <v>5.209</v>
+        <v>4.941</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-2.26</v>
+        <v>0.83</v>
       </c>
       <c r="F40" t="n">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="G40" t="n">
-        <v>14.828</v>
+        <v>3.132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3489,60 +3489,60 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.32</v>
+        <v>-1.26</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G41" t="n">
-        <v>0.457</v>
+        <v>0.836</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.91</v>
+        <v>-1.29</v>
       </c>
       <c r="F42" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="G42" t="n">
-        <v>1.939</v>
+        <v>5.996</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3551,60 +3551,60 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.68</v>
+        <v>-1.9</v>
       </c>
       <c r="F43" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="G43" t="n">
-        <v>2.113</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.71</v>
+        <v>-2.33</v>
       </c>
       <c r="F44" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="G44" t="n">
-        <v>15.074</v>
+        <v>15.125</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3613,106 +3613,106 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.96</v>
+        <v>-3.04</v>
       </c>
       <c r="F45" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="G45" t="n">
-        <v>2.041</v>
+        <v>2.111</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.98</v>
+        <v>-3.14</v>
       </c>
       <c r="F46" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>1.418</v>
+        <v>2.042</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-7.15</v>
+        <v>-5.39</v>
       </c>
       <c r="F47" t="n">
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
       <c r="G47" t="n">
-        <v>1.415</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-8.109999999999999</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="G48" t="n">
-        <v>0.952</v>
+        <v>1.413</v>
       </c>
     </row>
     <row r="49">
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-9.68</v>
+        <v>-8.77</v>
       </c>
       <c r="F49" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G49" t="n">
         <v>0.108</v>
@@ -3749,94 +3749,94 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-16.48</v>
+        <v>-11.9</v>
       </c>
       <c r="F50" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.954</v>
+        <v>2.267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-17.01</v>
+        <v>-15</v>
       </c>
       <c r="F51" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>2.115</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-18.78</v>
+        <v>-16.34</v>
       </c>
       <c r="F52" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="G52" t="n">
-        <v>0.093</v>
+        <v>0.969</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.55</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="D2" t="n">
-        <v>3.518</v>
+        <v>25.826</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48.46</v>
+        <v>47.3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="D3" t="n">
-        <v>23.448</v>
+        <v>3.353</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,55 +3921,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.61</v>
+        <v>38.25</v>
       </c>
       <c r="C4" t="n">
-        <v>2.53</v>
+        <v>1.366666666666666</v>
       </c>
       <c r="D4" t="n">
-        <v>0.518</v>
+        <v>14.931</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.49</v>
+        <v>35.28333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>1.05</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>22.481</v>
+        <v>10.797</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.42</v>
+        <v>32.58</v>
       </c>
       <c r="C6" t="n">
-        <v>0.51</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
-        <v>9.119999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,55 +3978,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.04666666666667</v>
+        <v>30.88</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7166666666666667</v>
+        <v>1.15</v>
       </c>
       <c r="D7" t="n">
-        <v>9.893000000000001</v>
+        <v>23.702</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.77333333333333</v>
+        <v>24.285</v>
       </c>
       <c r="C8" t="n">
-        <v>1.326666666666666</v>
+        <v>1.435</v>
       </c>
       <c r="D8" t="n">
-        <v>14.014</v>
+        <v>2.092</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.17</v>
+        <v>17.41</v>
       </c>
       <c r="C9" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="D9" t="n">
-        <v>17.946</v>
+        <v>9.115</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.365</v>
+        <v>14.815</v>
       </c>
       <c r="C10" t="n">
-        <v>0.665</v>
+        <v>0.675</v>
       </c>
       <c r="D10" t="n">
-        <v>23.465</v>
+        <v>23.971</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -4054,74 +4054,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.13333333333333</v>
+        <v>13.93</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.91</v>
       </c>
       <c r="D11" t="n">
-        <v>11.024</v>
+        <v>6.295</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.975</v>
+        <v>13.23</v>
       </c>
       <c r="C12" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="D12" t="n">
-        <v>1.786</v>
+        <v>18.221</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.96</v>
+        <v>12.02666666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>0.78</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>0.22</v>
+        <v>11.184</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.54</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="D14" t="n">
-        <v>1.273</v>
+        <v>0.228</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,169 +4130,169 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.81</v>
+        <v>6.975000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="D15" t="n">
-        <v>5.682</v>
+        <v>3.179</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.41</v>
+        <v>6.165</v>
       </c>
       <c r="C16" t="n">
         <v>0.78</v>
       </c>
       <c r="D16" t="n">
-        <v>3.301</v>
+        <v>4.279999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.67</v>
+        <v>5.915</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8</v>
+        <v>0.855</v>
       </c>
       <c r="D17" t="n">
-        <v>1.613</v>
+        <v>10.868</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.495</v>
+        <v>4.79</v>
       </c>
       <c r="C18" t="n">
-        <v>0.645</v>
+        <v>0.9</v>
       </c>
       <c r="D18" t="n">
-        <v>87.934</v>
+        <v>1.277</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.3075</v>
+        <v>4.55</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8225</v>
+        <v>1.26</v>
       </c>
       <c r="D19" t="n">
-        <v>26.707</v>
+        <v>24.924</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.135</v>
+        <v>4.22</v>
       </c>
       <c r="C20" t="n">
-        <v>0.705</v>
+        <v>1.03</v>
       </c>
       <c r="D20" t="n">
-        <v>4.124000000000001</v>
+        <v>14.597</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07999999999999985</v>
+        <v>3.39</v>
       </c>
       <c r="C21" t="n">
-        <v>1.075</v>
+        <v>0.71</v>
       </c>
       <c r="D21" t="n">
-        <v>2.766</v>
+        <v>2.172</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.27</v>
+        <v>3.04</v>
       </c>
       <c r="C22" t="n">
-        <v>1.21</v>
+        <v>0.635</v>
       </c>
       <c r="D22" t="n">
-        <v>24.939</v>
+        <v>88.366</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.59</v>
+        <v>2.01</v>
       </c>
       <c r="C23" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="D23" t="n">
-        <v>2.149</v>
+        <v>1.588</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,39 +4301,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.704</v>
+        <v>1.23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.772</v>
+        <v>0.825</v>
       </c>
       <c r="D24" t="n">
-        <v>7.914</v>
+        <v>26.782</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.915</v>
+        <v>1.21</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D25" t="n">
-        <v>10.317</v>
+        <v>1.471</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.26</v>
+        <v>1.17</v>
       </c>
       <c r="C26" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="D26" t="n">
-        <v>14.828</v>
+        <v>14.415</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-3.71</v>
+        <v>0.83</v>
       </c>
       <c r="C27" t="n">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="D27" t="n">
-        <v>15.074</v>
+        <v>3.132</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,20 +4377,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-3.98</v>
+        <v>-1.21</v>
       </c>
       <c r="C28" t="n">
-        <v>0.71</v>
+        <v>0.8019999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>1.418</v>
+        <v>7.948</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-8.109999999999999</v>
+        <v>-5.39</v>
       </c>
       <c r="C29" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="D29" t="n">
-        <v>0.952</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-9.68</v>
+        <v>-8.77</v>
       </c>
       <c r="C30" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="D30" t="n">
         <v>0.108</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-11.815</v>
+        <v>-12.185</v>
       </c>
       <c r="C31" t="n">
-        <v>0.835</v>
+        <v>0.75</v>
       </c>
       <c r="D31" t="n">
-        <v>2.369</v>
+        <v>2.382</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-18.78</v>
+        <v>-15</v>
       </c>
       <c r="C32" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.093</v>
+        <v>0.095</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1945</v>
+        <v>1975</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.77</v>
+        <v>1.54</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.71</v>
+        <v>4.22</v>
       </c>
       <c r="G2" t="n">
-        <v>45.21</v>
+        <v>52.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-33.3725</v>
+        <v>-21.6059</v>
       </c>
       <c r="I2" t="n">
-        <v>71.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="J2" t="n">
-        <v>90.7</v>
+        <v>98.7</v>
       </c>
       <c r="K2" t="n">
-        <v>7.25</v>
+        <v>7.03</v>
       </c>
       <c r="L2" t="n">
-        <v>45.7</v>
+        <v>16.6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4627,31 +4627,31 @@
         <v>1730</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>1.17</v>
       </c>
-      <c r="F3" t="n">
-        <v>-2.26</v>
-      </c>
       <c r="G3" t="n">
-        <v>43.45</v>
+        <v>39.71</v>
       </c>
       <c r="H3" t="n">
-        <v>10.3475</v>
+        <v>7.9758</v>
       </c>
       <c r="I3" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="J3" t="n">
         <v>23.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="L3" t="n">
-        <v>-50.3</v>
+        <v>-27.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.64</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>21.8</v>
+        <v>46.07</v>
       </c>
       <c r="G4" t="n">
-        <v>56.35</v>
+        <v>63.98</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3357</v>
+        <v>5.2811</v>
       </c>
       <c r="I4" t="n">
-        <v>93.09999999999999</v>
+        <v>109.6</v>
       </c>
       <c r="J4" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>7.96</v>
+        <v>7.45</v>
       </c>
       <c r="L4" t="n">
-        <v>277</v>
+        <v>118.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.39</v>
+        <v>2.11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>💰 STRONG INFLOW</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="E5" t="n">
-        <v>6.79</v>
+        <v>-1.18</v>
       </c>
       <c r="F5" t="n">
-        <v>6.96</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>40.85</v>
+        <v>39.62</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.929</v>
+        <v>-1.6282</v>
       </c>
       <c r="I5" t="n">
-        <v>62.3</v>
+        <v>56.3</v>
       </c>
       <c r="J5" t="n">
-        <v>57.7</v>
+        <v>52.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.48</v>
+        <v>5.59</v>
       </c>
       <c r="L5" t="n">
-        <v>93.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>216</v>
+        <v>227.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.68</v>
+        <v>5.32</v>
       </c>
       <c r="F6" t="n">
-        <v>26.69</v>
+        <v>38.3</v>
       </c>
       <c r="G6" t="n">
-        <v>54.57</v>
+        <v>57.99</v>
       </c>
       <c r="H6" t="n">
-        <v>11.8976</v>
+        <v>11.826</v>
       </c>
       <c r="I6" t="n">
-        <v>57.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>36.6</v>
+        <v>57.1</v>
       </c>
       <c r="K6" t="n">
-        <v>9.359999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="L6" t="n">
-        <v>31.1</v>
+        <v>39.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.08</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.62</v>
+        <v>-2.33</v>
       </c>
       <c r="G7" t="n">
-        <v>38.37</v>
+        <v>25.17</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.2095</v>
+        <v>-3.6175</v>
       </c>
       <c r="I7" t="n">
-        <v>24.2</v>
+        <v>20.8</v>
       </c>
       <c r="J7" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.46</v>
+        <v>4.12</v>
       </c>
       <c r="L7" t="n">
-        <v>49.6</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="E2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="F2" t="n">
-        <v>388</v>
+        <v>350</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,67 +504,67 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>2.508</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>313.5</v>
+        <v>174</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>-6.95</v>
       </c>
       <c r="F3" t="n">
-        <v>227</v>
+        <v>298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.539</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89.09999999999999</v>
+        <v>124</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>-3.88</v>
       </c>
       <c r="F4" t="n">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.561</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>246.5</v>
+        <v>309</v>
       </c>
       <c r="E5" t="n">
-        <v>9.800000000000001</v>
+        <v>-1.44</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.97</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>323</v>
+        <v>86.3</v>
       </c>
       <c r="E6" t="n">
-        <v>9.859999999999999</v>
+        <v>-3.14</v>
       </c>
       <c r="F6" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.295</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2725</v>
+        <v>354.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.02</v>
+        <v>9.92</v>
       </c>
       <c r="F7" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,101 +674,101 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.353</v>
+        <v>7.213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>211</v>
+        <v>48.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="F8" t="n">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.267</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66.8</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.18</v>
+        <v>-2.59</v>
       </c>
       <c r="F9" t="n">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.228</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.2</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.97</v>
+        <v>4.31</v>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.543</v>
+        <v>19.825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>2610</v>
       </c>
       <c r="E11" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="F11" t="n">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23.702</v>
+        <v>6.106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71.90000000000001</v>
+        <v>227</v>
       </c>
       <c r="E12" t="n">
-        <v>0.28</v>
+        <v>-0.22</v>
       </c>
       <c r="F12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18.221</v>
+        <v>3.773</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>227.5</v>
+        <v>48.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.32</v>
+        <v>2.75</v>
       </c>
       <c r="F13" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3.596</v>
+        <v>2.327</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>143.5</v>
+        <v>373.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9.960000000000001</v>
+        <v>-2.35</v>
       </c>
       <c r="F14" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>25.826</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>481</v>
+        <v>2775</v>
       </c>
       <c r="E15" t="n">
-        <v>6.77</v>
+        <v>1.83</v>
       </c>
       <c r="F15" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.119</v>
+        <v>3.392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2515</v>
+        <v>316</v>
       </c>
       <c r="E16" t="n">
-        <v>9.83</v>
+        <v>-2.17</v>
       </c>
       <c r="F16" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.62</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>164</v>
+        <v>135.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.14</v>
+        <v>0.74</v>
       </c>
       <c r="F17" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.531</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E18" t="n">
-        <v>0.54</v>
+        <v>-2.38</v>
       </c>
       <c r="F18" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,41 +1048,41 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.095</v>
+        <v>15.309</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>322.5</v>
+        <v>88.2</v>
       </c>
       <c r="E19" t="n">
-        <v>9.880000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="F19" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6.156</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="20">
@@ -1102,47 +1102,47 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3300</v>
+        <v>3220</v>
       </c>
       <c r="E20" t="n">
-        <v>3.45</v>
+        <v>-2.42</v>
       </c>
       <c r="F20" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.248</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>130.5</v>
+        <v>34.65</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.61</v>
+        <v>-2.39</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.941</v>
+        <v>1.408</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1975</v>
+        <v>122</v>
       </c>
       <c r="E22" t="n">
-        <v>1.54</v>
+        <v>-4.69</v>
       </c>
       <c r="F22" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,169 +1184,169 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.597</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>276</v>
+        <v>472</v>
       </c>
       <c r="E23" t="n">
-        <v>1.66</v>
+        <v>-1.87</v>
       </c>
       <c r="F23" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>24.924</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>382.5</v>
+        <v>508</v>
       </c>
       <c r="E24" t="n">
-        <v>0.39</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.277</v>
+        <v>11.169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>357.5</v>
+        <v>38.95</v>
       </c>
       <c r="E25" t="n">
-        <v>4.53</v>
+        <v>-0.89</v>
       </c>
       <c r="F25" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9.115</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.35</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8</v>
+        <v>-2.45</v>
       </c>
       <c r="F26" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8169999999999999</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-5.8</v>
       </c>
       <c r="F27" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>15.125</v>
+        <v>23.404</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>293</v>
+        <v>127.5</v>
       </c>
       <c r="E28" t="n">
-        <v>1.38</v>
+        <v>-2.3</v>
       </c>
       <c r="F28" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.899</v>
+        <v>4.869</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.3</v>
+        <v>51.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.13</v>
+        <v>-3.19</v>
       </c>
       <c r="F29" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.836</v>
+        <v>2.471</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1250</v>
+        <v>58.7</v>
       </c>
       <c r="E30" t="n">
-        <v>3.73</v>
+        <v>-3.93</v>
       </c>
       <c r="F30" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.471</v>
+        <v>5.599</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1465</v>
+        <v>476.5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.74</v>
+        <v>-1.14</v>
       </c>
       <c r="F31" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.858</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18.95</v>
+        <v>22.95</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.26</v>
+        <v>-1.08</v>
       </c>
       <c r="F32" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.969</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19.3</v>
+        <v>1680</v>
       </c>
       <c r="E33" t="n">
-        <v>0.26</v>
+        <v>-2.89</v>
       </c>
       <c r="F33" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9419999999999999</v>
+        <v>13.591</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>28.1</v>
+        <v>205.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.36</v>
+        <v>-2.61</v>
       </c>
       <c r="F34" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.108</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>482</v>
+        <v>1960</v>
       </c>
       <c r="E35" t="n">
-        <v>0.42</v>
+        <v>-0.76</v>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.588</v>
+        <v>14.311</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>170</v>
+        <v>27.55</v>
       </c>
       <c r="E36" t="n">
-        <v>1.19</v>
+        <v>-1.96</v>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.113</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23.2</v>
+        <v>1850</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-2.89</v>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,30 +1694,30 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.459</v>
+        <v>79.48399999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1730</v>
+        <v>347</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-2.94</v>
       </c>
       <c r="F38" t="n">
         <v>72</v>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>14.415</v>
+        <v>8.545999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>134.5</v>
+        <v>43.45</v>
       </c>
       <c r="E39" t="n">
-        <v>3.86</v>
+        <v>-2.03</v>
       </c>
       <c r="F39" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.045</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>35.5</v>
+        <v>160.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-5.59</v>
       </c>
       <c r="F40" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,67 +1796,67 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.413</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>121</v>
+        <v>1455</v>
       </c>
       <c r="E41" t="n">
-        <v>2.11</v>
+        <v>-0.68</v>
       </c>
       <c r="F41" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.132</v>
+        <v>18.672</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>61.1</v>
+        <v>18.7</v>
       </c>
       <c r="E42" t="n">
-        <v>0.66</v>
+        <v>-1.32</v>
       </c>
       <c r="F42" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5.996</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>47.3</v>
+        <v>1205</v>
       </c>
       <c r="E43" t="n">
-        <v>1.83</v>
+        <v>-3.6</v>
       </c>
       <c r="F43" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.172</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>89.5</v>
+        <v>117.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.33</v>
+        <v>-2.89</v>
       </c>
       <c r="F44" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,101 +1932,101 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.042</v>
+        <v>2.747</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>73.40000000000001</v>
+        <v>160.5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.27</v>
+        <v>-2.13</v>
       </c>
       <c r="F45" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.111</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>64.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="E46" t="n">
-        <v>0.31</v>
+        <v>-2.4</v>
       </c>
       <c r="F46" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2.013</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1905</v>
+        <v>217.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1.87</v>
+        <v>-0.23</v>
       </c>
       <c r="F47" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,41 +2034,41 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>82.37</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>53.3</v>
+        <v>286.5</v>
       </c>
       <c r="E48" t="n">
-        <v>0.76</v>
+        <v>-2.22</v>
       </c>
       <c r="F48" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.5</v>
+        <v>5.736</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>58.3</v>
+        <v>56.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.34</v>
+        <v>-3.09</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,30 +2102,30 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.73</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>9.41</v>
       </c>
       <c r="F50" t="n">
         <v>46</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5.313</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="51">
@@ -2156,47 +2156,47 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>79.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="E51" t="n">
-        <v>0.76</v>
+        <v>-1.75</v>
       </c>
       <c r="F51" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.141</v>
+        <v>2.135</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>477.5</v>
+        <v>63.4</v>
       </c>
       <c r="E52" t="n">
-        <v>9.9</v>
+        <v>-1.86</v>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10.422</v>
+        <v>1.942</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="G2" t="n">
-        <v>25.826</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="3">
@@ -2311,230 +2311,230 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.79</v>
+        <v>69.08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>10.422</v>
+        <v>11.169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47.3</v>
+        <v>49.89</v>
       </c>
       <c r="F4" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>3.353</v>
+        <v>7.213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.92</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>0.71</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
-        <v>6.156</v>
+        <v>3.392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>46.07</v>
+        <v>38.26</v>
       </c>
       <c r="F6" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.561</v>
+        <v>2.702</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>41.86</v>
+        <v>35.85</v>
       </c>
       <c r="F7" t="n">
-        <v>1.59</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.539</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38.3</v>
+        <v>32.57</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.596</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32.58</v>
+        <v>31.21</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>1.16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.543</v>
+        <v>3.773</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30.88</v>
+        <v>29.36</v>
       </c>
       <c r="F10" t="n">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>23.702</v>
+        <v>2.508</v>
       </c>
     </row>
     <row r="11">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.29</v>
+        <v>23.31</v>
       </c>
       <c r="F11" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>18.858</v>
+        <v>18.672</v>
       </c>
     </row>
     <row r="12">
@@ -2590,137 +2590,137 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>24.23</v>
+        <v>18.28</v>
       </c>
       <c r="F12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G12" t="n">
-        <v>2.013</v>
+        <v>1.942</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.63</v>
+        <v>17.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.73</v>
+        <v>1.28</v>
       </c>
       <c r="G13" t="n">
-        <v>1.045</v>
+        <v>19.825</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.41</v>
+        <v>17.32</v>
       </c>
       <c r="F14" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="G14" t="n">
-        <v>9.115</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>17.1</v>
+        <v>16.62</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1.97</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>16.27</v>
+        <v>13.49</v>
       </c>
       <c r="F16" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
-        <v>5.313</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="17">
@@ -2745,587 +2745,587 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.93</v>
+        <v>8.4</v>
       </c>
       <c r="F17" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G17" t="n">
-        <v>6.295</v>
+        <v>6.207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13.23</v>
+        <v>8.24</v>
       </c>
       <c r="F18" t="n">
-        <v>1.07</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>18.221</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.69</v>
+        <v>6.75</v>
       </c>
       <c r="F19" t="n">
-        <v>0.54</v>
+        <v>0.98</v>
       </c>
       <c r="G19" t="n">
-        <v>3.73</v>
+        <v>6.106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.73</v>
+        <v>6.37</v>
       </c>
       <c r="F20" t="n">
-        <v>1.71</v>
+        <v>0.41</v>
       </c>
       <c r="G20" t="n">
-        <v>1.06</v>
+        <v>2.135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.869999999999999</v>
+        <v>6.12</v>
       </c>
       <c r="F21" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="G21" t="n">
-        <v>0.228</v>
+        <v>8.545999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.119999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="F22" t="n">
-        <v>0.47</v>
+        <v>1.85</v>
       </c>
       <c r="G22" t="n">
-        <v>2.141</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.37</v>
+        <v>4.18</v>
       </c>
       <c r="F23" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="G23" t="n">
-        <v>82.37</v>
+        <v>2.327</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.94</v>
+        <v>3.82</v>
       </c>
       <c r="F24" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G24" t="n">
-        <v>5.248</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.89</v>
+        <v>2.26</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="G25" t="n">
-        <v>5.62</v>
+        <v>79.48399999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.83</v>
+        <v>2.23</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="G26" t="n">
-        <v>5.899</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.79</v>
+        <v>1.82</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9</v>
+        <v>1.06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.277</v>
+        <v>14.311</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.55</v>
+        <v>1.28</v>
       </c>
       <c r="F28" t="n">
-        <v>1.26</v>
+        <v>0.71</v>
       </c>
       <c r="G28" t="n">
-        <v>24.924</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.22</v>
+        <v>0.88</v>
       </c>
       <c r="F29" t="n">
-        <v>1.03</v>
+        <v>0.67</v>
       </c>
       <c r="G29" t="n">
-        <v>14.597</v>
+        <v>5.736</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.39</v>
+        <v>0.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="G30" t="n">
-        <v>2.172</v>
+        <v>1.266</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.34</v>
+        <v>-0.77</v>
       </c>
       <c r="F31" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G31" t="n">
-        <v>5.113</v>
+        <v>2.471</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.29</v>
+        <v>-1.26</v>
       </c>
       <c r="F32" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.22</v>
+        <v>-1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>2.119</v>
+        <v>5.117</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.5</v>
+        <v>-2.03</v>
       </c>
       <c r="F34" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="G34" t="n">
-        <v>0.531</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.01</v>
+        <v>-2.14</v>
       </c>
       <c r="F35" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="G35" t="n">
-        <v>1.588</v>
+        <v>0.837</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3334,153 +3334,153 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.26</v>
+        <v>-2.67</v>
       </c>
       <c r="F36" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8169999999999999</v>
+        <v>4.869</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.21</v>
+        <v>-3.01</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="G37" t="n">
-        <v>1.471</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.17</v>
+        <v>-3.37</v>
       </c>
       <c r="F38" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="G38" t="n">
-        <v>14.415</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.16</v>
+        <v>-5.28</v>
       </c>
       <c r="F39" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="G39" t="n">
-        <v>4.941</v>
+        <v>23.404</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.83</v>
+        <v>-5.93</v>
       </c>
       <c r="F40" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="G40" t="n">
-        <v>3.132</v>
+        <v>5.599</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3489,261 +3489,261 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.26</v>
+        <v>-5.97</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="G41" t="n">
-        <v>0.836</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.29</v>
+        <v>-6.18</v>
       </c>
       <c r="F42" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="G42" t="n">
-        <v>5.996</v>
+        <v>15.309</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1.9</v>
+        <v>-6.75</v>
       </c>
       <c r="F43" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="G43" t="n">
-        <v>0.459</v>
+        <v>2.747</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.33</v>
+        <v>-7.25</v>
       </c>
       <c r="F44" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="G44" t="n">
-        <v>15.125</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.04</v>
+        <v>-7.49</v>
       </c>
       <c r="F45" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>2.111</v>
+        <v>4.784</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.14</v>
+        <v>-7.62</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="G46" t="n">
-        <v>2.042</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.39</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9419999999999999</v>
+        <v>13.591</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-8.029999999999999</v>
+        <v>-10.11</v>
       </c>
       <c r="F48" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="G48" t="n">
-        <v>1.413</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-8.77</v>
+        <v>-10.7</v>
       </c>
       <c r="F49" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="G49" t="n">
-        <v>0.108</v>
+        <v>1.408</v>
       </c>
     </row>
     <row r="50">
@@ -3768,75 +3768,75 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-11.9</v>
+        <v>-15.43</v>
       </c>
       <c r="F50" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G50" t="n">
-        <v>2.267</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-15</v>
+        <v>-17.98</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="G51" t="n">
-        <v>0.095</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-16.34</v>
+        <v>-22.49</v>
       </c>
       <c r="F52" t="n">
-        <v>0.72</v>
+        <v>1.23</v>
       </c>
       <c r="G52" t="n">
-        <v>0.969</v>
+        <v>0.102</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="D2" t="n">
-        <v>25.826</v>
+        <v>27.93</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="D3" t="n">
-        <v>3.353</v>
+        <v>3.392</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25</v>
+        <v>45.56666666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>1.366666666666666</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="n">
-        <v>14.931</v>
+        <v>16.379</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3940,55 +3940,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.28333333333333</v>
+        <v>35.85</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7933333333333333</v>
+        <v>2.34</v>
       </c>
       <c r="D5" t="n">
-        <v>10.797</v>
+        <v>0.615</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.58</v>
+        <v>32.80666666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>0.9733333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.543</v>
+        <v>12.084</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.88</v>
+        <v>17.55</v>
       </c>
       <c r="C7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="D7" t="n">
-        <v>23.702</v>
+        <v>19.825</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.285</v>
+        <v>17.4</v>
       </c>
       <c r="C8" t="n">
-        <v>1.435</v>
+        <v>1.405</v>
       </c>
       <c r="D8" t="n">
-        <v>2.092</v>
+        <v>2.196</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,17 +4016,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.41</v>
+        <v>13.49</v>
       </c>
       <c r="C9" t="n">
-        <v>0.62</v>
+        <v>1.17</v>
       </c>
       <c r="D9" t="n">
-        <v>9.115</v>
+        <v>22.85</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4035,20 +4035,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.815</v>
+        <v>10.41</v>
       </c>
       <c r="C10" t="n">
-        <v>0.675</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.971</v>
+        <v>11.218</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.93</v>
+        <v>8.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="D11" t="n">
-        <v>6.295</v>
+        <v>6.207</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,55 +4073,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.23</v>
+        <v>7.909999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1.07</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>18.221</v>
+        <v>23.456</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.02666666666667</v>
+        <v>6.12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.65</v>
       </c>
       <c r="D13" t="n">
-        <v>11.184</v>
+        <v>8.545999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.869999999999999</v>
+        <v>4.18</v>
       </c>
       <c r="C14" t="n">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="D14" t="n">
-        <v>0.228</v>
+        <v>2.327</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,36 +4130,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.975000000000001</v>
+        <v>3.82</v>
       </c>
       <c r="C15" t="n">
-        <v>1.35</v>
+        <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>3.179</v>
+        <v>0.223</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.165</v>
+        <v>2.385</v>
       </c>
       <c r="C16" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="D16" t="n">
-        <v>4.279999999999999</v>
+        <v>11.223</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -4168,74 +4168,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.915</v>
+        <v>1.82</v>
       </c>
       <c r="C17" t="n">
-        <v>0.855</v>
+        <v>1.06</v>
       </c>
       <c r="D17" t="n">
-        <v>10.868</v>
+        <v>14.311</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.79</v>
+        <v>1.69</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>1.355</v>
       </c>
       <c r="D18" t="n">
-        <v>1.277</v>
+        <v>3.225</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.55</v>
+        <v>1.425000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1.26</v>
+        <v>0.76</v>
       </c>
       <c r="D19" t="n">
-        <v>24.924</v>
+        <v>4.141</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.22</v>
+        <v>1.28</v>
       </c>
       <c r="C20" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="D20" t="n">
-        <v>14.597</v>
+        <v>1.568</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.39</v>
+        <v>0.4</v>
       </c>
       <c r="C21" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="D21" t="n">
-        <v>2.172</v>
+        <v>1.266</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.04</v>
+        <v>-1.835</v>
       </c>
       <c r="C22" t="n">
-        <v>0.635</v>
+        <v>0.66</v>
       </c>
       <c r="D22" t="n">
-        <v>88.366</v>
+        <v>85.083</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -4282,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.01</v>
+        <v>-2.03</v>
       </c>
       <c r="C23" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="D23" t="n">
-        <v>1.588</v>
+        <v>1.42</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.23</v>
+        <v>-2.745</v>
       </c>
       <c r="C24" t="n">
-        <v>0.825</v>
+        <v>0.85</v>
       </c>
       <c r="D24" t="n">
-        <v>26.782</v>
+        <v>26.707</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -4320,36 +4320,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.21</v>
+        <v>-3.9</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>0.7859999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>1.471</v>
+        <v>7.895</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.17</v>
+        <v>-5.28</v>
       </c>
       <c r="C26" t="n">
-        <v>0.66</v>
+        <v>1.11</v>
       </c>
       <c r="D26" t="n">
-        <v>14.415</v>
+        <v>23.404</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.83</v>
+        <v>-6.75</v>
       </c>
       <c r="C27" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D27" t="n">
-        <v>3.132</v>
+        <v>2.747</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,36 +4377,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.21</v>
+        <v>-7.62</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8019999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="D28" t="n">
-        <v>7.948</v>
+        <v>0.982</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-5.39</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9419999999999999</v>
+        <v>13.591</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-8.77</v>
+        <v>-10.11</v>
       </c>
       <c r="C30" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="D30" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-12.185</v>
+        <v>-14.34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="D31" t="n">
-        <v>2.382</v>
+        <v>2.369</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-15</v>
+        <v>-22.49</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="D32" t="n">
-        <v>0.095</v>
+        <v>0.102</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1975</v>
+        <v>1960</v>
       </c>
       <c r="E2" t="n">
-        <v>1.54</v>
+        <v>-0.76</v>
       </c>
       <c r="F2" t="n">
-        <v>4.22</v>
+        <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>52.1</v>
+        <v>52.99</v>
       </c>
       <c r="H2" t="n">
-        <v>-21.6059</v>
+        <v>-13.3374</v>
       </c>
       <c r="I2" t="n">
-        <v>77.2</v>
+        <v>73</v>
       </c>
       <c r="J2" t="n">
-        <v>98.7</v>
+        <v>94.7</v>
       </c>
       <c r="K2" t="n">
-        <v>7.03</v>
+        <v>6.98</v>
       </c>
       <c r="L2" t="n">
-        <v>16.6</v>
+        <v>-20.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1730</v>
+        <v>1680</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-2.89</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>39.71</v>
+        <v>29.77</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9758</v>
+        <v>2.0381</v>
       </c>
       <c r="I3" t="n">
-        <v>30.3</v>
+        <v>17.1</v>
       </c>
       <c r="J3" t="n">
-        <v>23.2</v>
+        <v>6.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
       <c r="L3" t="n">
-        <v>-27.9</v>
+        <v>-16.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>-3.14</v>
       </c>
       <c r="F4" t="n">
-        <v>46.07</v>
+        <v>32.57</v>
       </c>
       <c r="G4" t="n">
-        <v>63.98</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2811</v>
+        <v>5.7382</v>
       </c>
       <c r="I4" t="n">
-        <v>109.6</v>
+        <v>93.5</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>7.45</v>
+        <v>7.65</v>
       </c>
       <c r="L4" t="n">
-        <v>118.6</v>
+        <v>124.4</v>
       </c>
       <c r="M4" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>💰 STRONG INFLOW</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.8</v>
+        <v>65.2</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.18</v>
+        <v>-2.4</v>
       </c>
       <c r="F5" t="n">
-        <v>9.869999999999999</v>
+        <v>3.82</v>
       </c>
       <c r="G5" t="n">
-        <v>39.62</v>
+        <v>36.53</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6282</v>
+        <v>-1.5017</v>
       </c>
       <c r="I5" t="n">
-        <v>56.3</v>
+        <v>46.4</v>
       </c>
       <c r="J5" t="n">
-        <v>52.3</v>
+        <v>48.8</v>
       </c>
       <c r="K5" t="n">
-        <v>5.59</v>
+        <v>5.55</v>
       </c>
       <c r="L5" t="n">
-        <v>67.2</v>
+        <v>-42.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>227.5</v>
+        <v>227</v>
       </c>
       <c r="E6" t="n">
-        <v>5.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>38.3</v>
+        <v>31.21</v>
       </c>
       <c r="G6" t="n">
-        <v>57.99</v>
+        <v>52.87</v>
       </c>
       <c r="H6" t="n">
-        <v>11.826</v>
+        <v>11.5953</v>
       </c>
       <c r="I6" t="n">
-        <v>67.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>57.1</v>
+        <v>56.2</v>
       </c>
       <c r="K6" t="n">
-        <v>8.81</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>39.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.38</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.33</v>
+        <v>-6.18</v>
       </c>
       <c r="G7" t="n">
-        <v>25.17</v>
+        <v>24.67</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6175</v>
+        <v>-4.2948</v>
       </c>
       <c r="I7" t="n">
-        <v>20.8</v>
+        <v>13.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.12</v>
+        <v>3.97</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>11.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>271</v>
+        <v>385</v>
       </c>
       <c r="E2" t="n">
-        <v>9.94</v>
+        <v>3.08</v>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>441</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,67 +504,67 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.508</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>174</v>
+        <v>479.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.95</v>
+        <v>0.63</v>
       </c>
       <c r="F3" t="n">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.102</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>124</v>
+        <v>261.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.88</v>
+        <v>-3.51</v>
       </c>
       <c r="F4" t="n">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>309</v>
+        <v>344</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.44</v>
+        <v>-2.96</v>
       </c>
       <c r="F5" t="n">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.702</v>
+        <v>7.363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86.3</v>
+        <v>302</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.14</v>
+        <v>-2.27</v>
       </c>
       <c r="F6" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.685</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>354.5</v>
+        <v>308</v>
       </c>
       <c r="E7" t="n">
-        <v>9.92</v>
+        <v>-2.53</v>
       </c>
       <c r="F7" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,75 +674,75 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7.213</v>
+        <v>6.387</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.5</v>
+        <v>191</v>
       </c>
       <c r="E8" t="n">
-        <v>2.75</v>
+        <v>9.77</v>
       </c>
       <c r="F8" t="n">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.615</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>3375</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.59</v>
+        <v>4.81</v>
       </c>
       <c r="F9" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="10">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4.31</v>
+        <v>0.67</v>
       </c>
       <c r="F10" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.825</v>
+        <v>21.222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2610</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.78</v>
+        <v>0.93</v>
       </c>
       <c r="F11" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,101 +810,101 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6.106</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>227</v>
+        <v>19.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.22</v>
+        <v>3.46</v>
       </c>
       <c r="F12" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.773</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48.6</v>
+        <v>110</v>
       </c>
       <c r="E13" t="n">
-        <v>2.75</v>
+        <v>-9.84</v>
       </c>
       <c r="F13" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.327</v>
+        <v>21.351</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>373.5</v>
+        <v>234</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.35</v>
+        <v>-10</v>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,67 +912,67 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.266</v>
+        <v>21.754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2775</v>
+        <v>130</v>
       </c>
       <c r="E15" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3.392</v>
+        <v>5.235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>316</v>
+        <v>48.1</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.17</v>
+        <v>-0.82</v>
       </c>
       <c r="F16" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.207</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>135.5</v>
+        <v>230</v>
       </c>
       <c r="E17" t="n">
-        <v>0.74</v>
+        <v>1.32</v>
       </c>
       <c r="F17" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,41 +1014,41 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.098</v>
+        <v>3.786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>205</v>
+        <v>1915</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.38</v>
+        <v>-2.3</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.309</v>
+        <v>14.199</v>
       </c>
     </row>
     <row r="19">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.45</v>
+        <v>0.45</v>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,237 +1082,237 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.063</v>
+        <v>2.165</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3220</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.42</v>
+        <v>0.64</v>
       </c>
       <c r="F20" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.117</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34.65</v>
+        <v>2645</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.39</v>
+        <v>1.34</v>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.408</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>122</v>
+        <v>38.75</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.69</v>
+        <v>-0.51</v>
       </c>
       <c r="F22" t="n">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>22.85</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>472</v>
+        <v>203</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.87</v>
+        <v>-0.98</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.125</v>
+        <v>15.595</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>508</v>
+        <v>1475</v>
       </c>
       <c r="E24" t="n">
-        <v>9.949999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>11.169</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38.95</v>
+        <v>125</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.837</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71.59999999999999</v>
+        <v>1840</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.45</v>
+        <v>-0.54</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.064</v>
+        <v>79.464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>260</v>
+        <v>1700</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.8</v>
+        <v>1.19</v>
       </c>
       <c r="F27" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>23.404</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>127.5</v>
+        <v>201.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.3</v>
+        <v>-1.95</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.869</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>51.6</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.19</v>
+        <v>1.63</v>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,75 +1422,75 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.471</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>58.7</v>
+        <v>214</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.93</v>
+        <v>-1.61</v>
       </c>
       <c r="F30" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.599</v>
+        <v>5.502</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>476.5</v>
+        <v>344</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.14</v>
+        <v>-0.86</v>
       </c>
       <c r="F31" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.568</v>
+        <v>8.303000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1513,10 +1513,10 @@
         <v>22.95</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.08</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1680</v>
+        <v>47.6</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.89</v>
+        <v>-2.06</v>
       </c>
       <c r="F33" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>13.591</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>205.5</v>
+        <v>34.8</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.61</v>
+        <v>0.43</v>
       </c>
       <c r="F34" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.199</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1960</v>
+        <v>42.8</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.76</v>
+        <v>-1.5</v>
       </c>
       <c r="F35" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>14.311</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27.55</v>
+        <v>72</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.106</v>
+        <v>2.101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1850</v>
+        <v>57.8</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.89</v>
+        <v>-1.53</v>
       </c>
       <c r="F37" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>79.48399999999999</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>347</v>
+        <v>1200</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.94</v>
+        <v>-0.41</v>
       </c>
       <c r="F38" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.545999999999999</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>43.45</v>
+        <v>457.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.03</v>
+        <v>-9.94</v>
       </c>
       <c r="F39" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,101 +1762,101 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.793</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>160.5</v>
+        <v>2700</v>
       </c>
       <c r="E40" t="n">
-        <v>-5.59</v>
+        <v>-2.7</v>
       </c>
       <c r="F40" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4.784</v>
+        <v>3.238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1455</v>
+        <v>52.1</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.68</v>
+        <v>0.97</v>
       </c>
       <c r="F41" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>18.672</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>18.7</v>
+        <v>116</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.32</v>
+        <v>-1.28</v>
       </c>
       <c r="F42" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.961</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1205</v>
+        <v>56.1</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.6</v>
+        <v>-0.71</v>
       </c>
       <c r="F43" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.42</v>
+        <v>3.777</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>117.5</v>
+        <v>157.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.89</v>
+        <v>-1.87</v>
       </c>
       <c r="F44" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.747</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>160.5</v>
+        <v>132.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.13</v>
+        <v>-2.21</v>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.511</v>
+        <v>1.079</v>
       </c>
     </row>
     <row r="46">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>65.2</v>
+        <v>63.1</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.4</v>
+        <v>-3.22</v>
       </c>
       <c r="F46" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,169 +2000,169 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.223</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>217.5</v>
+        <v>283.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.23</v>
+        <v>-1.05</v>
       </c>
       <c r="F47" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.4</v>
+        <v>5.647</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>286.5</v>
+        <v>469</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.22</v>
+        <v>-0.64</v>
       </c>
       <c r="F48" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.736</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>56.5</v>
+        <v>62.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.09</v>
+        <v>-1.42</v>
       </c>
       <c r="F49" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.683</v>
+        <v>1.919</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>157</v>
+        <v>18.85</v>
       </c>
       <c r="E50" t="n">
-        <v>9.41</v>
+        <v>0.8</v>
       </c>
       <c r="F50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>27.93</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>78.5</v>
+        <v>160</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.75</v>
+        <v>-0.31</v>
       </c>
       <c r="F51" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.135</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ChipMOS</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="F52" t="n">
-        <v>30</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Accumulation (Up)</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1.942</v>
+        <v>4.464</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,156 +2227,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.8</v>
+        <v>59.2</v>
       </c>
       <c r="F2" t="n">
         <v>0.73</v>
       </c>
       <c r="G2" t="n">
-        <v>27.93</v>
+        <v>10.193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69.08</v>
+        <v>49.58</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>11.169</v>
+        <v>3.238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.89</v>
+        <v>41.78</v>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>7.213</v>
+        <v>2.889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>36.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>3.392</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38.26</v>
+        <v>34.64</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.702</v>
+        <v>7.363</v>
       </c>
     </row>
     <row r="7">
@@ -2435,199 +2401,199 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35.85</v>
+        <v>32.87</v>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>0.615</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>32.57</v>
+        <v>30.1</v>
       </c>
       <c r="F8" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="G8" t="n">
-        <v>1.685</v>
+        <v>2.814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31.21</v>
+        <v>24.47</v>
       </c>
       <c r="F9" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
       <c r="G9" t="n">
-        <v>3.773</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29.36</v>
+        <v>21.05</v>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
-        <v>2.508</v>
+        <v>3.786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.31</v>
+        <v>17.92</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="G11" t="n">
-        <v>18.672</v>
+        <v>1.919</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18.28</v>
+        <v>17.42</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43</v>
+        <v>1.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.942</v>
+        <v>21.222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17.55</v>
+        <v>15.05</v>
       </c>
       <c r="F13" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="G13" t="n">
-        <v>19.825</v>
+        <v>5.502</v>
       </c>
     </row>
     <row r="14">
@@ -2652,292 +2618,292 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.32</v>
+        <v>14.22</v>
       </c>
       <c r="F14" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.098</v>
+        <v>1.079</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16.62</v>
+        <v>6.28</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>21.351</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.49</v>
+        <v>6.25</v>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>22.85</v>
+        <v>3.777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.4</v>
+        <v>6.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.97</v>
+        <v>0.59</v>
       </c>
       <c r="G17" t="n">
-        <v>6.207</v>
+        <v>2.297</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.24</v>
+        <v>5.59</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="G18" t="n">
-        <v>3.683</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.75</v>
+        <v>4.93</v>
       </c>
       <c r="F19" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="G19" t="n">
-        <v>6.106</v>
+        <v>14.199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.37</v>
+        <v>4.85</v>
       </c>
       <c r="F20" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="G20" t="n">
-        <v>2.135</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.12</v>
+        <v>2.88</v>
       </c>
       <c r="F21" t="n">
-        <v>0.65</v>
+        <v>1.99</v>
       </c>
       <c r="G21" t="n">
-        <v>8.545999999999999</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.64</v>
+        <v>2.27</v>
       </c>
       <c r="F22" t="n">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.18</v>
+        <v>2.12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.77</v>
+        <v>1.55</v>
       </c>
       <c r="G23" t="n">
-        <v>2.327</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="24">
@@ -2962,106 +2928,106 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.82</v>
+        <v>2.1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>0.223</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="F25" t="n">
-        <v>0.65</v>
+        <v>1.26</v>
       </c>
       <c r="G25" t="n">
-        <v>79.48399999999999</v>
+        <v>6.387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.23</v>
+        <v>0.77</v>
       </c>
       <c r="F26" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G26" t="n">
-        <v>0.511</v>
+        <v>2.518</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.82</v>
+        <v>0.39</v>
       </c>
       <c r="F27" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="G27" t="n">
-        <v>14.311</v>
+        <v>5.235</v>
       </c>
     </row>
     <row r="28">
@@ -3086,354 +3052,354 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.28</v>
+        <v>0.21</v>
       </c>
       <c r="F28" t="n">
-        <v>0.71</v>
+        <v>1.24</v>
       </c>
       <c r="G28" t="n">
-        <v>1.568</v>
+        <v>1.879</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="G29" t="n">
-        <v>5.736</v>
+        <v>8.303000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4</v>
+        <v>-0.53</v>
       </c>
       <c r="F30" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.266</v>
+        <v>5.647</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.77</v>
+        <v>-1.81</v>
       </c>
       <c r="F31" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="G31" t="n">
-        <v>2.471</v>
+        <v>79.464</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1.26</v>
+        <v>-2.64</v>
       </c>
       <c r="F32" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G32" t="n">
-        <v>2.125</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1.98</v>
+        <v>-3.97</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>5.117</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2.03</v>
+        <v>-4.58</v>
       </c>
       <c r="F34" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="G34" t="n">
-        <v>1.42</v>
+        <v>2.069</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-2.14</v>
+        <v>-4.99</v>
       </c>
       <c r="F35" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G35" t="n">
-        <v>0.837</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-2.67</v>
+        <v>-5.12</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="G36" t="n">
-        <v>4.869</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-3.01</v>
+        <v>-6.24</v>
       </c>
       <c r="F37" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="G37" t="n">
-        <v>0.793</v>
+        <v>2.165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-3.37</v>
+        <v>-6.8</v>
       </c>
       <c r="F38" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G38" t="n">
-        <v>0.46</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-5.28</v>
+        <v>-6.83</v>
       </c>
       <c r="F39" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="G39" t="n">
-        <v>23.404</v>
+        <v>2.562</v>
       </c>
     </row>
     <row r="40">
@@ -3458,29 +3424,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-5.93</v>
+        <v>-7.37</v>
       </c>
       <c r="F40" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G40" t="n">
-        <v>5.599</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3489,292 +3455,292 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-5.97</v>
+        <v>-7.57</v>
       </c>
       <c r="F41" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G41" t="n">
-        <v>2.063</v>
+        <v>2.101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-6.18</v>
+        <v>-7.69</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G42" t="n">
-        <v>15.309</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-6.75</v>
+        <v>-7.86</v>
       </c>
       <c r="F43" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="G43" t="n">
-        <v>2.747</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-7.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="G44" t="n">
-        <v>2.064</v>
+        <v>15.595</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-7.49</v>
+        <v>-8.94</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G45" t="n">
-        <v>4.784</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-7.62</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="G46" t="n">
-        <v>0.982</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-8.199999999999999</v>
+        <v>-10.77</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="G47" t="n">
-        <v>13.591</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-10.11</v>
+        <v>-13.65</v>
       </c>
       <c r="F48" t="n">
-        <v>0.64</v>
+        <v>1.2</v>
       </c>
       <c r="G48" t="n">
-        <v>0.106</v>
+        <v>21.754</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-10.7</v>
+        <v>-16.04</v>
       </c>
       <c r="F49" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>1.408</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-15.43</v>
+        <v>-16.41</v>
       </c>
       <c r="F50" t="n">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="G50" t="n">
-        <v>2.199</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="51">
@@ -3799,44 +3765,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-17.98</v>
+        <v>-17.86</v>
       </c>
       <c r="F51" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="G51" t="n">
-        <v>0.961</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Andes Tech</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>IP Core (RISC-V)</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-22.49</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.102</v>
+        <v>0.952</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3883,17 +3818,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.8</v>
+        <v>49.58</v>
       </c>
       <c r="C2" t="n">
-        <v>0.73</v>
+        <v>1.33</v>
       </c>
       <c r="D2" t="n">
-        <v>27.93</v>
+        <v>3.238</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,169 +3837,169 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>43.69333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>1.35</v>
+        <v>1.626666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>3.392</v>
+        <v>15.896</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.56666666666666</v>
+        <v>32.87</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="D4" t="n">
-        <v>16.379</v>
+        <v>0.659</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.85</v>
+        <v>23.30333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>2.34</v>
+        <v>1.22</v>
       </c>
       <c r="D5" t="n">
-        <v>0.615</v>
+        <v>12.228</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.80666666666666</v>
+        <v>17.42</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9733333333333333</v>
+        <v>1.48</v>
       </c>
       <c r="D6" t="n">
-        <v>12.084</v>
+        <v>21.222</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.55</v>
+        <v>14.645</v>
       </c>
       <c r="C7" t="n">
-        <v>1.28</v>
+        <v>1.405</v>
       </c>
       <c r="D7" t="n">
-        <v>19.825</v>
+        <v>2.341</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.4</v>
+        <v>9.113333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>1.405</v>
+        <v>0.63</v>
       </c>
       <c r="D8" t="n">
-        <v>2.196</v>
+        <v>11.576</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.49</v>
+        <v>7.305</v>
       </c>
       <c r="C9" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="D9" t="n">
-        <v>22.85</v>
+        <v>23.924</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.41</v>
+        <v>6.28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5533333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="D10" t="n">
-        <v>11.218</v>
+        <v>21.351</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.4</v>
+        <v>4.93</v>
       </c>
       <c r="C11" t="n">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="D11" t="n">
-        <v>6.207</v>
+        <v>14.199</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,55 +4008,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.909999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D12" t="n">
-        <v>23.456</v>
+        <v>2.328</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.12</v>
+        <v>3.93</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65</v>
+        <v>1.105</v>
       </c>
       <c r="D13" t="n">
-        <v>8.545999999999999</v>
+        <v>12.177</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.18</v>
+        <v>2.12</v>
       </c>
       <c r="C14" t="n">
-        <v>0.77</v>
+        <v>1.55</v>
       </c>
       <c r="D14" t="n">
-        <v>2.327</v>
+        <v>1.602</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4134,13 +4069,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.82</v>
+        <v>2.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="D15" t="n">
-        <v>0.223</v>
+        <v>0.218</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,207 +4084,207 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.385</v>
+        <v>1.99</v>
       </c>
       <c r="C16" t="n">
-        <v>0.96</v>
+        <v>1.26</v>
       </c>
       <c r="D16" t="n">
-        <v>11.223</v>
+        <v>6.387</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.82</v>
+        <v>0.9400000000000013</v>
       </c>
       <c r="C17" t="n">
-        <v>1.06</v>
+        <v>0.765</v>
       </c>
       <c r="D17" t="n">
-        <v>14.311</v>
+        <v>4.108000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.69</v>
+        <v>0.21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.355</v>
+        <v>1.24</v>
       </c>
       <c r="D18" t="n">
-        <v>3.225</v>
+        <v>1.879</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.425000000000001</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="D19" t="n">
-        <v>4.141</v>
+        <v>8.303000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.28</v>
+        <v>-0.8500000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.71</v>
+        <v>1.415</v>
       </c>
       <c r="D20" t="n">
-        <v>1.568</v>
+        <v>3.18</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4</v>
+        <v>-3.3175</v>
       </c>
       <c r="C21" t="n">
-        <v>0.95</v>
+        <v>0.9225</v>
       </c>
       <c r="D21" t="n">
-        <v>1.266</v>
+        <v>27.264</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.835</v>
+        <v>-3.930000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.66</v>
+        <v>0.8280000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>85.083</v>
+        <v>8.103</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.03</v>
+        <v>-4.59</v>
       </c>
       <c r="C23" t="n">
-        <v>0.65</v>
+        <v>0.715</v>
       </c>
       <c r="D23" t="n">
-        <v>1.42</v>
+        <v>84.947</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-2.745</v>
+        <v>-5.12</v>
       </c>
       <c r="C24" t="n">
-        <v>0.85</v>
+        <v>1.09</v>
       </c>
       <c r="D24" t="n">
-        <v>26.707</v>
+        <v>1.093</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-3.9</v>
+        <v>-6.83</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7859999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="D25" t="n">
-        <v>7.895</v>
+        <v>2.562</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-5.28</v>
+        <v>-7.69</v>
       </c>
       <c r="C26" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="D26" t="n">
-        <v>23.404</v>
+        <v>1.405</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4293,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-6.75</v>
+        <v>-7.86</v>
       </c>
       <c r="C27" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="D27" t="n">
-        <v>2.747</v>
+        <v>13.503</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,17 +4312,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-7.62</v>
+        <v>-8.94</v>
       </c>
       <c r="C28" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="D28" t="n">
-        <v>0.982</v>
+        <v>0.108</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,17 +4331,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-8.199999999999999</v>
+        <v>-13.65</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="D29" t="n">
-        <v>13.591</v>
+        <v>21.754</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,57 +4350,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-10.11</v>
+        <v>-14.315</v>
       </c>
       <c r="C30" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="D30" t="n">
-        <v>0.106</v>
+        <v>2.372</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-14.34</v>
+        <v>-16.41</v>
       </c>
       <c r="C31" t="n">
-        <v>0.765</v>
+        <v>1.43</v>
       </c>
       <c r="D31" t="n">
-        <v>2.369</v>
+        <v>0.124</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>IP Core (RISC-V)</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>-22.49</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4572,34 +4488,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1960</v>
+        <v>1915</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.76</v>
+        <v>-2.3</v>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>4.93</v>
       </c>
       <c r="G2" t="n">
-        <v>52.99</v>
+        <v>49.79</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.3374</v>
+        <v>-15.7716</v>
       </c>
       <c r="I2" t="n">
-        <v>73</v>
+        <v>61.9</v>
       </c>
       <c r="J2" t="n">
-        <v>94.7</v>
+        <v>82.7</v>
       </c>
       <c r="K2" t="n">
-        <v>6.98</v>
+        <v>7.37</v>
       </c>
       <c r="L2" t="n">
-        <v>-20.4</v>
+        <v>47.1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4540,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1680</v>
+        <v>1700</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.89</v>
+        <v>1.19</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.86</v>
       </c>
       <c r="G3" t="n">
-        <v>29.77</v>
+        <v>34.13</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0381</v>
+        <v>-1.1394</v>
       </c>
       <c r="I3" t="n">
-        <v>17.1</v>
+        <v>26.2</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4</v>
+        <v>23.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-16.4</v>
+        <v>-0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4592,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.14</v>
+        <v>0.93</v>
       </c>
       <c r="F4" t="n">
-        <v>32.57</v>
+        <v>36.09</v>
       </c>
       <c r="G4" t="n">
-        <v>64.34999999999999</v>
+        <v>65.77</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7382</v>
+        <v>6.2575</v>
       </c>
       <c r="I4" t="n">
-        <v>93.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>7.65</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>124.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>💰 STRONG INFLOW</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4644,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.2</v>
+        <v>63.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4</v>
+        <v>-3.22</v>
       </c>
       <c r="F5" t="n">
-        <v>3.82</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>36.53</v>
+        <v>36.65</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5017</v>
+        <v>-1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>46.4</v>
+        <v>33.7</v>
       </c>
       <c r="J5" t="n">
-        <v>48.8</v>
+        <v>45.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.55</v>
+        <v>5.77</v>
       </c>
       <c r="L5" t="n">
-        <v>-42.5</v>
+        <v>-26.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4696,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.22</v>
+        <v>1.32</v>
       </c>
       <c r="F6" t="n">
-        <v>31.21</v>
+        <v>21.05</v>
       </c>
       <c r="G6" t="n">
-        <v>52.87</v>
+        <v>46.94</v>
       </c>
       <c r="H6" t="n">
-        <v>11.5953</v>
+        <v>10.9771</v>
       </c>
       <c r="I6" t="n">
-        <v>65.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="J6" t="n">
-        <v>56.2</v>
+        <v>61.6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>68.90000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,19 +4748,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.38</v>
+        <v>-0.98</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.18</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>24.67</v>
+        <v>25.34</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.2948</v>
+        <v>-4.5969</v>
       </c>
       <c r="I7" t="n">
         <v>13.2</v>
@@ -4853,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>385</v>
+        <v>198.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3.08</v>
+        <v>3.93</v>
       </c>
       <c r="F2" t="n">
-        <v>441</v>
+        <v>362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.602</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>479.5</v>
+        <v>256</v>
       </c>
       <c r="E3" t="n">
-        <v>0.63</v>
+        <v>-2.1</v>
       </c>
       <c r="F3" t="n">
-        <v>364</v>
+        <v>195</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.879</v>
+        <v>2.983</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>261.5</v>
+        <v>221.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.51</v>
+        <v>-3.7</v>
       </c>
       <c r="F4" t="n">
-        <v>338</v>
+        <v>170</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.814</v>
+        <v>3.541</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>344</v>
+        <v>19.05</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.96</v>
+        <v>-2.06</v>
       </c>
       <c r="F5" t="n">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.363</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.27</v>
+        <v>-8.43</v>
       </c>
       <c r="F6" t="n">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.889</v>
+        <v>6.683</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>308</v>
+        <v>86.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.53</v>
+        <v>-0.34</v>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6.387</v>
+        <v>1.971</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>191</v>
+        <v>51.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9.77</v>
+        <v>-1.15</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>122</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,135 +708,135 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.124</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3375</v>
+        <v>22.55</v>
       </c>
       <c r="E9" t="n">
-        <v>4.81</v>
+        <v>-1.74</v>
       </c>
       <c r="F9" t="n">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.805</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75.5</v>
+        <v>34.85</v>
       </c>
       <c r="E10" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21.222</v>
+        <v>1.449</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>87.09999999999999</v>
+        <v>286</v>
       </c>
       <c r="E11" t="n">
-        <v>0.93</v>
+        <v>-7.14</v>
       </c>
       <c r="F11" t="n">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.865</v>
+        <v>5.925</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.45</v>
+        <v>372</v>
       </c>
       <c r="E12" t="n">
-        <v>3.46</v>
+        <v>-3.38</v>
       </c>
       <c r="F12" t="n">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.093</v>
+        <v>1.586</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>71.7</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.84</v>
+        <v>-0.42</v>
       </c>
       <c r="F13" t="n">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21.351</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>234</v>
+        <v>86.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-10</v>
+        <v>-2.03</v>
       </c>
       <c r="F14" t="n">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.754</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>130</v>
+        <v>38.35</v>
       </c>
       <c r="E15" t="n">
-        <v>1.96</v>
+        <v>-1.03</v>
       </c>
       <c r="F15" t="n">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,237 +946,237 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.235</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48.1</v>
+        <v>1410</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.82</v>
+        <v>-4.41</v>
       </c>
       <c r="F16" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.659</v>
+        <v>18.494</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="E17" t="n">
-        <v>1.32</v>
+        <v>-3.45</v>
       </c>
       <c r="F17" t="n">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.786</v>
+        <v>15.127</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1915</v>
+        <v>44.75</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3</v>
+        <v>-5.99</v>
       </c>
       <c r="F18" t="n">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14.199</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>88.59999999999999</v>
+        <v>116.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.45</v>
+        <v>-6.8</v>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.165</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.64</v>
+        <v>-8.48</v>
       </c>
       <c r="F20" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.297</v>
+        <v>19.521</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2645</v>
+        <v>2600</v>
       </c>
       <c r="E21" t="n">
-        <v>1.34</v>
+        <v>-3.7</v>
       </c>
       <c r="F21" t="n">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.372</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.75</v>
+        <v>3190</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.51</v>
+        <v>-5.48</v>
       </c>
       <c r="F22" t="n">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.858</v>
+        <v>5.441</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>203</v>
+        <v>469.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.98</v>
+        <v>-2.09</v>
       </c>
       <c r="F23" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,75 +1218,75 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>15.595</v>
+        <v>1.861</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1475</v>
+        <v>223</v>
       </c>
       <c r="E24" t="n">
-        <v>1.37</v>
+        <v>-4.7</v>
       </c>
       <c r="F24" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19.46</v>
+        <v>20.575</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.71</v>
       </c>
       <c r="F25" t="n">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.111</v>
+        <v>2.118</v>
       </c>
     </row>
     <row r="26">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1840</v>
+        <v>1810</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.54</v>
+        <v>-1.63</v>
       </c>
       <c r="F26" t="n">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>79.464</v>
+        <v>77.663</v>
       </c>
     </row>
     <row r="27">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1700</v>
+        <v>1625</v>
       </c>
       <c r="E27" t="n">
-        <v>1.19</v>
+        <v>-4.41</v>
       </c>
       <c r="F27" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.503</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>201.5</v>
+        <v>125.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.95</v>
+        <v>-3.46</v>
       </c>
       <c r="F28" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.189</v>
+        <v>5.069</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>280</v>
       </c>
       <c r="E29" t="n">
-        <v>1.63</v>
+        <v>-1.23</v>
       </c>
       <c r="F29" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,101 +1422,101 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.108</v>
+        <v>5.564</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>214</v>
+        <v>107.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.61</v>
+        <v>-2.27</v>
       </c>
       <c r="F30" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.502</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>344</v>
+        <v>46.8</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.86</v>
+        <v>-2.7</v>
       </c>
       <c r="F31" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8.303000000000001</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22.95</v>
+        <v>204</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-4.67</v>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.461</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>47.6</v>
+        <v>56.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.06</v>
+        <v>-1.9</v>
       </c>
       <c r="F33" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,41 +1558,41 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.328</v>
+        <v>5.309</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34.8</v>
+        <v>2590</v>
       </c>
       <c r="E34" t="n">
-        <v>0.43</v>
+        <v>-2.08</v>
       </c>
       <c r="F34" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.42</v>
+        <v>6.286</v>
       </c>
     </row>
     <row r="35">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>42.8</v>
+        <v>41.95</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.5</v>
+        <v>-1.99</v>
       </c>
       <c r="F35" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.787</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>72</v>
+        <v>1160</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.33</v>
       </c>
       <c r="F36" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.101</v>
+        <v>1.373</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>57.8</v>
+        <v>27.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.53</v>
+        <v>-2.86</v>
       </c>
       <c r="F37" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.483</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1200</v>
+        <v>329.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.41</v>
+        <v>-4.22</v>
       </c>
       <c r="F38" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,101 +1728,101 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.405</v>
+        <v>7.858</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>457.5</v>
+        <v>1800</v>
       </c>
       <c r="E39" t="n">
-        <v>-9.94</v>
+        <v>-6.01</v>
       </c>
       <c r="F39" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.193</v>
+        <v>13.255</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2700</v>
+        <v>121.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.238</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>52.1</v>
+        <v>151</v>
       </c>
       <c r="E41" t="n">
-        <v>0.97</v>
+        <v>-4.13</v>
       </c>
       <c r="F41" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.518</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>116</v>
+        <v>74.8</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.28</v>
+        <v>-5.32</v>
       </c>
       <c r="F42" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.562</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>56.1</v>
+        <v>18.55</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.71</v>
+        <v>-1.59</v>
       </c>
       <c r="F43" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.777</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>157.5</v>
+        <v>441.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.87</v>
+        <v>-5.86</v>
       </c>
       <c r="F44" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,41 +1932,41 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.476</v>
+        <v>1.822</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>132.5</v>
+        <v>113</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.21</v>
+        <v>-2.59</v>
       </c>
       <c r="F45" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.079</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="46">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>63.1</v>
+        <v>60.8</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.22</v>
+        <v>-3.65</v>
       </c>
       <c r="F46" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.218</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>283.5</v>
+        <v>272</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.05</v>
+        <v>-9.93</v>
       </c>
       <c r="F47" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.647</v>
+        <v>2.582</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>469</v>
+        <v>412</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.64</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.069</v>
+        <v>9.143000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62.5</v>
+        <v>52.8</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.42</v>
+        <v>-5.88</v>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.919</v>
+        <v>3.602</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>18.85</v>
+        <v>154</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8</v>
+        <v>-3.75</v>
       </c>
       <c r="F50" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,41 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.952</v>
+        <v>4.121</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>160</v>
+        <v>148.5</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.31</v>
+        <v>-7.19</v>
       </c>
       <c r="F51" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Accumulation (Up)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>22.659</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>南茂</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ChipMOS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-6.72</v>
+      </c>
+      <c r="F52" t="n">
+        <v>23</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>4.464</v>
+      <c r="H52" t="n">
+        <v>1.768</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,249 +2261,249 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59.2</v>
+        <v>50.76</v>
       </c>
       <c r="F2" t="n">
-        <v>0.73</v>
+        <v>0.65</v>
       </c>
       <c r="G2" t="n">
-        <v>10.193</v>
+        <v>22.659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.58</v>
+        <v>44.83</v>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="n">
-        <v>3.238</v>
+        <v>9.143000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41.78</v>
+        <v>34.16</v>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="G4" t="n">
-        <v>2.889</v>
+        <v>1.971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.09</v>
+        <v>31.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.865</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>34.64</v>
+        <v>30.98</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.363</v>
+        <v>2.977</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.87</v>
+        <v>28.32</v>
       </c>
       <c r="F7" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>0.659</v>
+        <v>2.983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30.1</v>
+        <v>28.05</v>
       </c>
       <c r="F8" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.814</v>
+        <v>6.683</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.47</v>
+        <v>24.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>1.77</v>
       </c>
       <c r="G9" t="n">
-        <v>19.46</v>
+        <v>2.582</v>
       </c>
     </row>
     <row r="10">
@@ -2494,106 +2528,106 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21.05</v>
+        <v>23.06</v>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>3.786</v>
+        <v>3.541</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.92</v>
+        <v>11.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>1.919</v>
+        <v>18.494</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.42</v>
+        <v>9.68</v>
       </c>
       <c r="F12" t="n">
-        <v>1.48</v>
+        <v>0.62</v>
       </c>
       <c r="G12" t="n">
-        <v>21.222</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.05</v>
+        <v>9.51</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
+        <v>1.47</v>
       </c>
       <c r="G13" t="n">
-        <v>5.502</v>
+        <v>19.521</v>
       </c>
     </row>
     <row r="14">
@@ -2618,215 +2652,215 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.22</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.079</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.28</v>
+        <v>9.18</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>0.47</v>
       </c>
       <c r="G15" t="n">
-        <v>21.351</v>
+        <v>1.768</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.25</v>
+        <v>4.65</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="G16" t="n">
-        <v>3.777</v>
+        <v>6.286</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.04</v>
+        <v>2.64</v>
       </c>
       <c r="F17" t="n">
-        <v>0.59</v>
+        <v>2.03</v>
       </c>
       <c r="G17" t="n">
-        <v>2.297</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.59</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>6.372</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.93</v>
+        <v>-0.27</v>
       </c>
       <c r="F19" t="n">
-        <v>1.22</v>
+        <v>0.57</v>
       </c>
       <c r="G19" t="n">
-        <v>14.199</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.85</v>
+        <v>-0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.82</v>
+        <v>1.59</v>
       </c>
       <c r="G20" t="n">
-        <v>2.328</v>
+        <v>1.586</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2835,277 +2869,277 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.88</v>
+        <v>-0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>1.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1.111</v>
+        <v>1.822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.27</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="G22" t="n">
-        <v>5.805</v>
+        <v>3.602</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.12</v>
+        <v>-1.34</v>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>1.602</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.1</v>
+        <v>-1.37</v>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.218</v>
+        <v>1.861</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.99</v>
+        <v>-1.94</v>
       </c>
       <c r="F25" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="G25" t="n">
-        <v>6.387</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.77</v>
+        <v>-2.1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G26" t="n">
-        <v>2.518</v>
+        <v>5.564</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.39</v>
+        <v>-2.96</v>
       </c>
       <c r="F27" t="n">
         <v>1.12</v>
       </c>
       <c r="G27" t="n">
-        <v>5.235</v>
+        <v>13.255</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.21</v>
+        <v>-3.76</v>
       </c>
       <c r="F28" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="G28" t="n">
-        <v>1.879</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-4.24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="G29" t="n">
-        <v>8.303000000000001</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3114,13 +3148,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.53</v>
+        <v>-4.56</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>1.06</v>
       </c>
       <c r="G30" t="n">
-        <v>5.647</v>
+        <v>5.069</v>
       </c>
     </row>
     <row r="31">
@@ -3145,44 +3179,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1.81</v>
+        <v>-5.17</v>
       </c>
       <c r="F31" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="G31" t="n">
-        <v>79.464</v>
+        <v>77.663</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-2.64</v>
+        <v>-5.62</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="G32" t="n">
-        <v>0.858</v>
+        <v>5.441</v>
       </c>
     </row>
     <row r="33">
@@ -3207,230 +3241,230 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-3.97</v>
+        <v>-5.65</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="G33" t="n">
-        <v>0.461</v>
+        <v>0.454</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-4.58</v>
+        <v>-6.79</v>
       </c>
       <c r="F34" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="G34" t="n">
-        <v>2.069</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-4.99</v>
+        <v>-7.05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G35" t="n">
-        <v>0.787</v>
+        <v>7.858</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-5.12</v>
+        <v>-7.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="G36" t="n">
-        <v>1.093</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-6.24</v>
+        <v>-8.66</v>
       </c>
       <c r="F37" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="G37" t="n">
-        <v>2.165</v>
+        <v>1.373</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-6.8</v>
+        <v>-8.77</v>
       </c>
       <c r="F38" t="n">
-        <v>0.85</v>
+        <v>1.33</v>
       </c>
       <c r="G38" t="n">
-        <v>0.476</v>
+        <v>5.925</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-6.83</v>
+        <v>-8.82</v>
       </c>
       <c r="F39" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.562</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-7.37</v>
+        <v>-8.85</v>
       </c>
       <c r="F40" t="n">
-        <v>0.71</v>
+        <v>1.23</v>
       </c>
       <c r="G40" t="n">
-        <v>5.483</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="41">
@@ -3455,323 +3489,354 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-7.57</v>
+        <v>-9.01</v>
       </c>
       <c r="F41" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G41" t="n">
-        <v>2.101</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-7.69</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G42" t="n">
-        <v>1.405</v>
+        <v>5.309</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-7.86</v>
+        <v>-10.3</v>
       </c>
       <c r="F43" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="G43" t="n">
-        <v>13.503</v>
+        <v>1.449</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-8.140000000000001</v>
+        <v>-10.32</v>
       </c>
       <c r="F44" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="G44" t="n">
-        <v>15.595</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-8.94</v>
+        <v>-10.99</v>
       </c>
       <c r="F45" t="n">
-        <v>0.71</v>
+        <v>1.83</v>
       </c>
       <c r="G45" t="n">
-        <v>0.108</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-9.859999999999999</v>
+        <v>-11.26</v>
       </c>
       <c r="F46" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="G46" t="n">
-        <v>4.464</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-10.77</v>
+        <v>-12.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G47" t="n">
-        <v>1.42</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-13.65</v>
+        <v>-13.66</v>
       </c>
       <c r="F48" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G48" t="n">
-        <v>21.754</v>
+        <v>15.127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-16.04</v>
+        <v>-14.21</v>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="G49" t="n">
-        <v>2.189</v>
+        <v>4.121</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-16.41</v>
+        <v>-18.28</v>
       </c>
       <c r="F50" t="n">
-        <v>1.43</v>
+        <v>0.61</v>
       </c>
       <c r="G50" t="n">
-        <v>0.124</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-17.86</v>
+        <v>-19.78</v>
       </c>
       <c r="F51" t="n">
-        <v>0.64</v>
+        <v>1.18</v>
       </c>
       <c r="G51" t="n">
-        <v>0.952</v>
+        <v>20.575</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PTI (Powertech)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Memory - Packaging</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-20.99</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.118</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3818,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.58</v>
+        <v>50.76</v>
       </c>
       <c r="C2" t="n">
-        <v>1.33</v>
+        <v>0.65</v>
       </c>
       <c r="D2" t="n">
-        <v>3.238</v>
+        <v>22.659</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3841,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.69333333333334</v>
+        <v>32.45</v>
       </c>
       <c r="C3" t="n">
-        <v>1.626666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="n">
-        <v>15.896</v>
+        <v>14.708</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -3860,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32.87</v>
+        <v>31.09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="D4" t="n">
-        <v>0.659</v>
+        <v>0.658</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3875,39 +3940,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.30333333333333</v>
+        <v>30.98</v>
       </c>
       <c r="C5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="n">
-        <v>12.228</v>
+        <v>2.977</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.42</v>
+        <v>20.19</v>
       </c>
       <c r="C6" t="n">
-        <v>1.48</v>
+        <v>1.323333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>21.222</v>
+        <v>11.224</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3917,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.645</v>
+        <v>13.685</v>
       </c>
       <c r="C7" t="n">
-        <v>1.405</v>
+        <v>1.36</v>
       </c>
       <c r="D7" t="n">
-        <v>2.341</v>
+        <v>2.393</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3932,39 +3997,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.113333333333333</v>
+        <v>9.51</v>
       </c>
       <c r="C8" t="n">
-        <v>0.63</v>
+        <v>1.47</v>
       </c>
       <c r="D8" t="n">
-        <v>11.576</v>
+        <v>19.521</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.305</v>
+        <v>2.823333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.71</v>
+        <v>0.5566666666666666</v>
       </c>
       <c r="D9" t="n">
-        <v>23.924</v>
+        <v>11.194</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3974,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.28</v>
+        <v>1.9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="D10" t="n">
-        <v>21.351</v>
+        <v>20.57</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3989,93 +4054,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.93</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="D11" t="n">
-        <v>14.199</v>
+        <v>2.824</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.85</v>
+        <v>-0.4849999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.82</v>
+        <v>1.135</v>
       </c>
       <c r="D12" t="n">
-        <v>2.328</v>
+        <v>11.727</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.93</v>
+        <v>-0.8</v>
       </c>
       <c r="C13" t="n">
-        <v>1.105</v>
+        <v>1.59</v>
       </c>
       <c r="D13" t="n">
-        <v>12.177</v>
+        <v>1.586</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.12</v>
+        <v>-1.155</v>
       </c>
       <c r="C14" t="n">
-        <v>1.55</v>
+        <v>0.77</v>
       </c>
       <c r="D14" t="n">
-        <v>1.602</v>
+        <v>22.615</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1</v>
+        <v>-1.37</v>
       </c>
       <c r="C15" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="D15" t="n">
-        <v>0.218</v>
+        <v>1.861</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4084,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.99</v>
+        <v>-1.94</v>
       </c>
       <c r="C16" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="D16" t="n">
-        <v>6.387</v>
+        <v>0.207</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4103,36 +4168,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9400000000000013</v>
+        <v>-2.96</v>
       </c>
       <c r="C17" t="n">
-        <v>0.765</v>
+        <v>1.12</v>
       </c>
       <c r="D17" t="n">
-        <v>4.108000000000001</v>
+        <v>13.255</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.21</v>
+        <v>-3.76</v>
       </c>
       <c r="C18" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="D18" t="n">
-        <v>1.879</v>
+        <v>2.244</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4141,36 +4206,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-5.812</v>
       </c>
       <c r="C19" t="n">
-        <v>0.73</v>
+        <v>0.8960000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>8.303000000000001</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.8500000000000001</v>
+        <v>-5.904999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1.415</v>
+        <v>0.755</v>
       </c>
       <c r="D20" t="n">
-        <v>3.18</v>
+        <v>3.886</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -4183,13 +4248,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.3175</v>
+        <v>-6.955</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9225</v>
+        <v>0.9425</v>
       </c>
       <c r="D21" t="n">
-        <v>27.264</v>
+        <v>26.519</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -4198,20 +4263,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-3.930000000000001</v>
+        <v>-7.05</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8280000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="D22" t="n">
-        <v>8.103</v>
+        <v>7.858</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4221,13 +4286,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-4.59</v>
+        <v>-7.44</v>
       </c>
       <c r="C23" t="n">
-        <v>0.715</v>
+        <v>0.735</v>
       </c>
       <c r="D23" t="n">
-        <v>84.947</v>
+        <v>82.97199999999999</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4236,17 +4301,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-5.12</v>
+        <v>-8.66</v>
       </c>
       <c r="C24" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="D24" t="n">
-        <v>1.093</v>
+        <v>1.373</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4255,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-6.83</v>
+        <v>-8.77</v>
       </c>
       <c r="C25" t="n">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
       <c r="D25" t="n">
-        <v>2.562</v>
+        <v>5.925</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4274,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-7.69</v>
+        <v>-8.85</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>1.23</v>
       </c>
       <c r="D26" t="n">
-        <v>1.405</v>
+        <v>1.09</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4293,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-7.86</v>
+        <v>-10.32</v>
       </c>
       <c r="C27" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="D27" t="n">
-        <v>13.503</v>
+        <v>2.48</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4312,17 +4377,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-8.94</v>
+        <v>-10.99</v>
       </c>
       <c r="C28" t="n">
-        <v>0.71</v>
+        <v>1.83</v>
       </c>
       <c r="D28" t="n">
-        <v>0.108</v>
+        <v>0.152</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4331,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-13.65</v>
+        <v>-11.26</v>
       </c>
       <c r="C29" t="n">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="D29" t="n">
-        <v>21.754</v>
+        <v>0.104</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4350,38 +4415,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-14.315</v>
+        <v>-12.4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>2.372</v>
+        <v>12.756</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-16.41</v>
+        <v>-14.29</v>
       </c>
       <c r="C31" t="n">
-        <v>1.43</v>
+        <v>0.75</v>
       </c>
       <c r="D31" t="n">
-        <v>0.124</v>
+        <v>2.373</v>
       </c>
       <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Memory - DRAM</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D32" t="n">
+        <v>20.575</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4488,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1915</v>
+        <v>1800</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.3</v>
+        <v>-6.01</v>
       </c>
       <c r="F2" t="n">
-        <v>4.93</v>
+        <v>-2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>49.79</v>
+        <v>51.98</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.7716</v>
+        <v>-18.2334</v>
       </c>
       <c r="I2" t="n">
-        <v>61.9</v>
+        <v>36.8</v>
       </c>
       <c r="J2" t="n">
-        <v>82.7</v>
+        <v>52</v>
       </c>
       <c r="K2" t="n">
-        <v>7.37</v>
+        <v>7.6</v>
       </c>
       <c r="L2" t="n">
-        <v>47.1</v>
+        <v>-37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4540,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1700</v>
+        <v>1625</v>
       </c>
       <c r="E3" t="n">
-        <v>1.19</v>
+        <v>-4.41</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.86</v>
+        <v>-12.4</v>
       </c>
       <c r="G3" t="n">
-        <v>34.13</v>
+        <v>34.68</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1394</v>
+        <v>-19.6135</v>
       </c>
       <c r="I3" t="n">
-        <v>26.2</v>
+        <v>7.7</v>
       </c>
       <c r="J3" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9</v>
+        <v>-18.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4592,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>87.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.93</v>
+        <v>-0.34</v>
       </c>
       <c r="F4" t="n">
-        <v>36.09</v>
+        <v>34.16</v>
       </c>
       <c r="G4" t="n">
-        <v>65.77</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2575</v>
+        <v>6.5051</v>
       </c>
       <c r="I4" t="n">
-        <v>90.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="J4" t="n">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
-        <v>86.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4644,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.1</v>
+        <v>60.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.22</v>
+        <v>-3.65</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>-1.94</v>
       </c>
       <c r="G5" t="n">
-        <v>36.65</v>
+        <v>38.19</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.51</v>
+        <v>-1.5868</v>
       </c>
       <c r="I5" t="n">
-        <v>33.7</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>45.1</v>
+        <v>20.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.77</v>
+        <v>5.69</v>
       </c>
       <c r="L5" t="n">
-        <v>-26.9</v>
+        <v>-55.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4696,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>230</v>
+        <v>221.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.32</v>
+        <v>-3.7</v>
       </c>
       <c r="F6" t="n">
-        <v>21.05</v>
+        <v>23.06</v>
       </c>
       <c r="G6" t="n">
-        <v>46.94</v>
+        <v>39.51</v>
       </c>
       <c r="H6" t="n">
-        <v>10.9771</v>
+        <v>10.671</v>
       </c>
       <c r="I6" t="n">
-        <v>67.5</v>
+        <v>53.5</v>
       </c>
       <c r="J6" t="n">
-        <v>61.6</v>
+        <v>61.9</v>
       </c>
       <c r="K6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="L6" t="n">
-        <v>55.5</v>
+        <v>70.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4748,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.98</v>
+        <v>-3.45</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.140000000000001</v>
+        <v>-13.66</v>
       </c>
       <c r="G7" t="n">
-        <v>25.34</v>
+        <v>26.43</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.5969</v>
+        <v>-5.4863</v>
       </c>
       <c r="I7" t="n">
-        <v>13.2</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>-5.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198.5</v>
+        <v>251</v>
       </c>
       <c r="E2" t="n">
-        <v>3.93</v>
+        <v>-1.95</v>
       </c>
       <c r="F2" t="n">
-        <v>362</v>
+        <v>262</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.152</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>256</v>
+        <v>242.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.1</v>
+        <v>9.48</v>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.983</v>
+        <v>4.024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>221.5</v>
+        <v>313.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.7</v>
+        <v>-0.48</v>
       </c>
       <c r="F4" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.541</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.05</v>
+        <v>216.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.06</v>
+        <v>-2.91</v>
       </c>
       <c r="F5" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,135 +606,135 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>20.587</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>315</v>
+        <v>187</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.43</v>
+        <v>-5.79</v>
       </c>
       <c r="F6" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.683</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86.8</v>
+        <v>1685</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.34</v>
+        <v>-6.39</v>
       </c>
       <c r="F7" t="n">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.971</v>
+        <v>12.809</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51.5</v>
+        <v>85.7</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.15</v>
+        <v>-1.27</v>
       </c>
       <c r="F8" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.559</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.55</v>
+        <v>62.7</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.74</v>
+        <v>-9.26</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.454</v>
+        <v>18.061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34.85</v>
+        <v>2535</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>-2.5</v>
       </c>
       <c r="F10" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.449</v>
+        <v>3.004</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>99.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.14</v>
+        <v>-7.44</v>
       </c>
       <c r="F11" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.925</v>
+        <v>19.284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>372</v>
+        <v>1415</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.38</v>
+        <v>0.35</v>
       </c>
       <c r="F12" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.586</v>
+        <v>17.944</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71.7</v>
+        <v>38.85</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.42</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.093</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>86.8</v>
+        <v>2505</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.03</v>
+        <v>-3.28</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.155</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38.35</v>
+        <v>129</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.03</v>
+        <v>2.79</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.843</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1410</v>
+        <v>70.8</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.41</v>
+        <v>-1.26</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18.494</v>
+        <v>1.989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>196</v>
+        <v>35.3</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.45</v>
+        <v>1.29</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.127</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44.75</v>
+        <v>22.9</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.99</v>
+        <v>1.55</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,101 +1048,101 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.244</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>116.5</v>
+        <v>278.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.8</v>
+        <v>-2.62</v>
       </c>
       <c r="F19" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.002</v>
+        <v>5.613</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>69.09999999999999</v>
+        <v>3110</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.48</v>
+        <v>-2.51</v>
       </c>
       <c r="F20" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19.521</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2600</v>
+        <v>46.65</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7</v>
+        <v>-0.32</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.977</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3190</v>
+        <v>1620</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.48</v>
+        <v>-0.31</v>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.441</v>
+        <v>11.856</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>469.5</v>
+        <v>195</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.09</v>
+        <v>-0.51</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.861</v>
+        <v>14.785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>223</v>
+        <v>1810</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>20.575</v>
+        <v>73.788</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>192</v>
+        <v>18.75</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.71</v>
+        <v>1.08</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.118</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1810</v>
+        <v>148</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.63</v>
+        <v>-1.99</v>
       </c>
       <c r="F26" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,67 +1320,67 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>77.663</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1625</v>
+        <v>253</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.41</v>
+        <v>-6.99</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>12.756</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>125.5</v>
+        <v>56.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.46</v>
+        <v>-0.35</v>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.069</v>
+        <v>5.042</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.23</v>
+        <v>-1.29</v>
       </c>
       <c r="F29" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.564</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>107.5</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.27</v>
+        <v>0.97</v>
       </c>
       <c r="F30" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>20.57</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46.8</v>
+        <v>19.2</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.7</v>
+        <v>0.79</v>
       </c>
       <c r="F31" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.658</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>204</v>
+        <v>386.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.67</v>
+        <v>-6.19</v>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5.376</v>
+        <v>8.271000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>56.7</v>
+        <v>281.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.9</v>
+        <v>0.54</v>
       </c>
       <c r="F33" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,67 +1558,67 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.309</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2590</v>
+        <v>431.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.08</v>
+        <v>-2.27</v>
       </c>
       <c r="F34" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.286</v>
+        <v>1.677</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>41.95</v>
+        <v>370</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.99</v>
+        <v>-0.54</v>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.759</v>
+        <v>1.555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1160</v>
+        <v>121</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.33</v>
+        <v>-0.41</v>
       </c>
       <c r="F36" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.373</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>27.2</v>
+        <v>42.25</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.86</v>
+        <v>0.72</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.104</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>329.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.22</v>
+        <v>0.35</v>
       </c>
       <c r="F38" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.858</v>
+        <v>2.056</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1800</v>
+        <v>1155</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.01</v>
+        <v>-0.43</v>
       </c>
       <c r="F39" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,67 +1762,67 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>13.255</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>121.5</v>
+        <v>480.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-8.300000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>1.819</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.13</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.422</v>
+        <v>2.351</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74.8</v>
+        <v>332.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-5.32</v>
+        <v>0.91</v>
       </c>
       <c r="F42" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.216</v>
+        <v>7.452</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.55</v>
+        <v>192</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.59</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.924</v>
+        <v>2.029</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>441.5</v>
+        <v>60.4</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.86</v>
+        <v>-0.66</v>
       </c>
       <c r="F44" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.822</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.59</v>
+        <v>-0.65</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.48</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>60.8</v>
+        <v>203</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.65</v>
+        <v>-0.49</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,75 +2000,75 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.207</v>
+        <v>5.252</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>272</v>
+        <v>45.05</v>
       </c>
       <c r="E47" t="n">
-        <v>-9.93</v>
+        <v>0.67</v>
       </c>
       <c r="F47" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.582</v>
+        <v>2.235</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>412</v>
+        <v>57.1</v>
       </c>
       <c r="E48" t="n">
-        <v>-9.949999999999999</v>
+        <v>-2.06</v>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.143000000000001</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>52.8</v>
+        <v>52.4</v>
       </c>
       <c r="E49" t="n">
-        <v>-5.88</v>
+        <v>-0.76</v>
       </c>
       <c r="F49" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,109 +2102,75 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.602</v>
+        <v>3.536</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>154</v>
+        <v>136.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.75</v>
+        <v>-8.08</v>
       </c>
       <c r="F50" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.121</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>148.5</v>
+        <v>74</v>
       </c>
       <c r="E51" t="n">
-        <v>-7.19</v>
+        <v>-1.07</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>22.659</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>南茂</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ChipMOS</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="F52" t="n">
-        <v>23</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1.768</v>
+        <v>2.189</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,94 +2227,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.76</v>
+        <v>32.92</v>
       </c>
       <c r="F2" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="G2" t="n">
-        <v>22.659</v>
+        <v>8.271000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44.83</v>
+        <v>31.88</v>
       </c>
       <c r="F3" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="G3" t="n">
-        <v>9.143000000000001</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.16</v>
+        <v>29.68</v>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.971</v>
+        <v>4.024</v>
       </c>
     </row>
     <row r="5">
@@ -2373,44 +2339,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31.09</v>
+        <v>26.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.658</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.98</v>
+        <v>20.87</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="G6" t="n">
-        <v>2.977</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="7">
@@ -2435,106 +2401,106 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28.32</v>
+        <v>20.67</v>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="G7" t="n">
-        <v>2.983</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28.05</v>
+        <v>16.28</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>6.683</v>
+        <v>3.004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.2</v>
+        <v>15.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.582</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>23.06</v>
+        <v>15.53</v>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G10" t="n">
-        <v>3.541</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="11">
@@ -2559,13 +2525,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.9</v>
+        <v>8.43</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G11" t="n">
-        <v>18.494</v>
+        <v>17.944</v>
       </c>
     </row>
     <row r="12">
@@ -2590,44 +2556,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9.68</v>
+        <v>7.69</v>
       </c>
       <c r="F12" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="n">
-        <v>5.376</v>
+        <v>5.252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.51</v>
+        <v>5.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>19.521</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="14">
@@ -2652,13 +2618,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.460000000000001</v>
+        <v>5.68</v>
       </c>
       <c r="F14" t="n">
         <v>0.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="15">
@@ -2683,44 +2649,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.18</v>
+        <v>3.07</v>
       </c>
       <c r="F15" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="G15" t="n">
-        <v>1.768</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.65</v>
+        <v>1.53</v>
       </c>
       <c r="F16" t="n">
-        <v>1.12</v>
+        <v>0.86</v>
       </c>
       <c r="G16" t="n">
-        <v>6.286</v>
+        <v>1.677</v>
       </c>
     </row>
     <row r="17">
@@ -2745,153 +2711,153 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.64</v>
+        <v>1.32</v>
       </c>
       <c r="F17" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1.002</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.9</v>
+        <v>0.95</v>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>20.57</v>
+        <v>1.819</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="F19" t="n">
-        <v>0.57</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.216</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.8</v>
+        <v>-0.71</v>
       </c>
       <c r="F20" t="n">
-        <v>1.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1.586</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-0.9</v>
+        <v>-2.12</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>1.822</v>
+        <v>1.555</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2900,13 +2866,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.01</v>
       </c>
       <c r="F22" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>3.602</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="23">
@@ -2931,184 +2897,184 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-1.34</v>
+        <v>-3.53</v>
       </c>
       <c r="F23" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>2.559</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-1.37</v>
+        <v>-4.15</v>
       </c>
       <c r="F24" t="n">
-        <v>1.28</v>
+        <v>0.71</v>
       </c>
       <c r="G24" t="n">
-        <v>1.861</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-1.94</v>
+        <v>-4.25</v>
       </c>
       <c r="F25" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="G25" t="n">
-        <v>0.207</v>
+        <v>2.235</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-2.1</v>
+        <v>-4.43</v>
       </c>
       <c r="F26" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>5.564</v>
+        <v>73.788</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-2.96</v>
+        <v>-4.73</v>
       </c>
       <c r="F27" t="n">
-        <v>1.12</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>13.255</v>
+        <v>7.452</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-3.76</v>
+        <v>-5.13</v>
       </c>
       <c r="F28" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="G28" t="n">
-        <v>2.244</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3117,385 +3083,385 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-4.24</v>
+        <v>-5.57</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.843</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-4.56</v>
+        <v>-5.59</v>
       </c>
       <c r="F30" t="n">
-        <v>1.06</v>
+        <v>0.46</v>
       </c>
       <c r="G30" t="n">
-        <v>5.069</v>
+        <v>3.536</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-5.17</v>
+        <v>-5.8</v>
       </c>
       <c r="F31" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="G31" t="n">
-        <v>77.663</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-5.62</v>
+        <v>-6.11</v>
       </c>
       <c r="F32" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="G32" t="n">
-        <v>5.441</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-5.65</v>
+        <v>-6.42</v>
       </c>
       <c r="F33" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="G33" t="n">
-        <v>0.454</v>
+        <v>18.061</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-6.79</v>
+        <v>-6.61</v>
       </c>
       <c r="F34" t="n">
-        <v>0.87</v>
+        <v>1.19</v>
       </c>
       <c r="G34" t="n">
-        <v>0.422</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-7.05</v>
+        <v>-7.11</v>
       </c>
       <c r="F35" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="G35" t="n">
-        <v>7.858</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-7.5</v>
+        <v>-8.99</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.759</v>
+        <v>2.056</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-8.66</v>
+        <v>-9.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="G37" t="n">
-        <v>1.373</v>
+        <v>2.351</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-8.77</v>
+        <v>-9.75</v>
       </c>
       <c r="F38" t="n">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="G38" t="n">
-        <v>5.925</v>
+        <v>11.856</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-8.82</v>
+        <v>-10.12</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="G39" t="n">
-        <v>2.155</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-8.85</v>
+        <v>-11.06</v>
       </c>
       <c r="F40" t="n">
-        <v>1.23</v>
+        <v>0.85</v>
       </c>
       <c r="G40" t="n">
-        <v>1.09</v>
+        <v>1.989</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9.01</v>
+        <v>-11.11</v>
       </c>
       <c r="F41" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="G41" t="n">
-        <v>2.093</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="42">
@@ -3520,261 +3486,261 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-9.710000000000001</v>
+        <v>-11.58</v>
       </c>
       <c r="F42" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="G42" t="n">
-        <v>5.309</v>
+        <v>5.042</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-10.3</v>
+        <v>-12.01</v>
       </c>
       <c r="F43" t="n">
-        <v>0.89</v>
+        <v>1.42</v>
       </c>
       <c r="G43" t="n">
-        <v>1.449</v>
+        <v>5.613</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-10.32</v>
+        <v>-12.47</v>
       </c>
       <c r="F44" t="n">
-        <v>0.79</v>
+        <v>1.09</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48</v>
+        <v>12.809</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-10.99</v>
+        <v>-13.48</v>
       </c>
       <c r="F45" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="G45" t="n">
-        <v>0.152</v>
+        <v>19.284</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-11.26</v>
+        <v>-14.58</v>
       </c>
       <c r="F46" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="G46" t="n">
-        <v>0.104</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-12.4</v>
+        <v>-14.66</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="G47" t="n">
-        <v>12.756</v>
+        <v>14.785</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-13.66</v>
+        <v>-17.07</v>
       </c>
       <c r="F48" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="G48" t="n">
-        <v>15.127</v>
+        <v>3.864</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-14.21</v>
+        <v>-17.44</v>
       </c>
       <c r="F49" t="n">
-        <v>0.64</v>
+        <v>1.94</v>
       </c>
       <c r="G49" t="n">
-        <v>4.121</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-18.28</v>
+        <v>-22.89</v>
       </c>
       <c r="F50" t="n">
-        <v>0.61</v>
+        <v>0.96</v>
       </c>
       <c r="G50" t="n">
-        <v>0.924</v>
+        <v>2.029</v>
       </c>
     </row>
     <row r="51">
@@ -3799,44 +3765,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-19.78</v>
+        <v>-25.09</v>
       </c>
       <c r="F51" t="n">
         <v>1.18</v>
       </c>
       <c r="G51" t="n">
-        <v>20.575</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>PTI (Powertech)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Memory - Packaging</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-20.99</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2.118</v>
+        <v>20.587</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3887,13 +3822,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.76</v>
+        <v>31.88</v>
       </c>
       <c r="C2" t="n">
         <v>0.65</v>
       </c>
       <c r="D2" t="n">
-        <v>22.659</v>
+        <v>19.79</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,77 +3837,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.45</v>
+        <v>26.08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="D3" t="n">
-        <v>14.708</v>
+        <v>0.669</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.09</v>
+        <v>23.04</v>
       </c>
       <c r="C4" t="n">
-        <v>1.64</v>
+        <v>1.413333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.658</v>
+        <v>13.956</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.98</v>
+        <v>17.08666666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>2.977</v>
+        <v>11.687</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.19</v>
+        <v>16.28</v>
       </c>
       <c r="C6" t="n">
-        <v>1.323333333333333</v>
+        <v>1.17</v>
       </c>
       <c r="D6" t="n">
-        <v>11.224</v>
+        <v>3.004</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3982,13 +3917,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.685</v>
+        <v>4.880000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="D7" t="n">
-        <v>2.393</v>
+        <v>2.457</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3997,74 +3932,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.51</v>
+        <v>1.425</v>
       </c>
       <c r="C8" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="D8" t="n">
-        <v>19.521</v>
+        <v>2.658</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.823333333333333</v>
+        <v>0.95</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5566666666666666</v>
+        <v>1.31</v>
       </c>
       <c r="D9" t="n">
-        <v>11.194</v>
+        <v>1.819</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9</v>
+        <v>-0.3033333333333331</v>
       </c>
       <c r="C10" t="n">
-        <v>1.26</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>20.57</v>
+        <v>10.977</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8700000000000001</v>
+        <v>-0.4550000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1.42</v>
+        <v>1.195</v>
       </c>
       <c r="D11" t="n">
-        <v>2.824</v>
+        <v>11.132</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -4073,36 +4008,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.4849999999999999</v>
+        <v>-2.12</v>
       </c>
       <c r="C12" t="n">
-        <v>1.135</v>
+        <v>1.56</v>
       </c>
       <c r="D12" t="n">
-        <v>11.727</v>
+        <v>1.555</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.8</v>
+        <v>-4.15</v>
       </c>
       <c r="C13" t="n">
-        <v>1.59</v>
+        <v>0.71</v>
       </c>
       <c r="D13" t="n">
-        <v>1.586</v>
+        <v>1.327</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,55 +4046,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.155</v>
+        <v>-4.25</v>
       </c>
       <c r="C14" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="D14" t="n">
-        <v>22.615</v>
+        <v>2.235</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.37</v>
+        <v>-4.32</v>
       </c>
       <c r="C15" t="n">
-        <v>1.28</v>
+        <v>0.765</v>
       </c>
       <c r="D15" t="n">
-        <v>1.861</v>
+        <v>21.808</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.94</v>
+        <v>-4.73</v>
       </c>
       <c r="C16" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.207</v>
+        <v>7.452</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,36 +4103,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-2.96</v>
+        <v>-5.39</v>
       </c>
       <c r="C17" t="n">
-        <v>1.12</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>13.255</v>
+        <v>26.114</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-3.76</v>
+        <v>-6.11</v>
       </c>
       <c r="C18" t="n">
-        <v>0.84</v>
+        <v>1.28</v>
       </c>
       <c r="D18" t="n">
-        <v>2.244</v>
+        <v>1.07</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,74 +4141,74 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-5.812</v>
+        <v>-6.42</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8960000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="D19" t="n">
-        <v>8.103999999999999</v>
+        <v>18.061</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-5.904999999999999</v>
+        <v>-6.856</v>
       </c>
       <c r="C20" t="n">
-        <v>0.755</v>
+        <v>0.9179999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>3.886</v>
+        <v>7.755</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-6.955</v>
+        <v>-8.004999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9425</v>
+        <v>0.79</v>
       </c>
       <c r="D21" t="n">
-        <v>26.519</v>
+        <v>78.83</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-7.05</v>
+        <v>-9.6</v>
       </c>
       <c r="C22" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="D22" t="n">
-        <v>7.858</v>
+        <v>2.351</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,55 +4217,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-7.44</v>
+        <v>-9.75</v>
       </c>
       <c r="C23" t="n">
-        <v>0.735</v>
+        <v>0.88</v>
       </c>
       <c r="D23" t="n">
-        <v>82.97199999999999</v>
+        <v>11.856</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-8.66</v>
+        <v>-9.91</v>
       </c>
       <c r="C24" t="n">
-        <v>0.72</v>
+        <v>0.675</v>
       </c>
       <c r="D24" t="n">
-        <v>1.373</v>
+        <v>3.733</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-8.77</v>
+        <v>-10.12</v>
       </c>
       <c r="C25" t="n">
-        <v>1.33</v>
+        <v>0.82</v>
       </c>
       <c r="D25" t="n">
-        <v>5.925</v>
+        <v>0.191</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,36 +4274,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-8.85</v>
+        <v>-10.845</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23</v>
+        <v>0.765</v>
       </c>
       <c r="D26" t="n">
-        <v>1.09</v>
+        <v>2.349</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-10.32</v>
+        <v>-12.01</v>
       </c>
       <c r="C27" t="n">
-        <v>0.79</v>
+        <v>1.42</v>
       </c>
       <c r="D27" t="n">
-        <v>2.48</v>
+        <v>5.613</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,17 +4312,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-10.99</v>
+        <v>-12.47</v>
       </c>
       <c r="C28" t="n">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="D28" t="n">
-        <v>0.152</v>
+        <v>12.809</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,17 +4331,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-11.26</v>
+        <v>-13.48</v>
       </c>
       <c r="C29" t="n">
-        <v>0.72</v>
+        <v>1.23</v>
       </c>
       <c r="D29" t="n">
-        <v>0.104</v>
+        <v>19.284</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,17 +4350,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-12.4</v>
+        <v>-17.44</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>1.94</v>
       </c>
       <c r="D30" t="n">
-        <v>12.756</v>
+        <v>0.151</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,38 +4369,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-14.29</v>
+        <v>-25.09</v>
       </c>
       <c r="C31" t="n">
-        <v>0.75</v>
+        <v>1.18</v>
       </c>
       <c r="D31" t="n">
-        <v>2.373</v>
+        <v>20.587</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Memory - DRAM</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>-19.78</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D32" t="n">
-        <v>20.575</v>
-      </c>
-      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4572,38 +4488,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>1685</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.01</v>
+        <v>-6.39</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.96</v>
+        <v>-12.47</v>
       </c>
       <c r="G2" t="n">
-        <v>51.98</v>
+        <v>49.17</v>
       </c>
       <c r="H2" t="n">
-        <v>-18.2334</v>
+        <v>-37.576</v>
       </c>
       <c r="I2" t="n">
-        <v>36.8</v>
+        <v>15.6</v>
       </c>
       <c r="J2" t="n">
-        <v>52</v>
+        <v>21.3</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6</v>
+        <v>8.41</v>
       </c>
       <c r="L2" t="n">
-        <v>-37</v>
+        <v>50.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4624,34 +4540,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.41</v>
+        <v>-0.31</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.4</v>
+        <v>-9.75</v>
       </c>
       <c r="G3" t="n">
-        <v>34.68</v>
+        <v>40.57</v>
       </c>
       <c r="H3" t="n">
-        <v>-19.6135</v>
+        <v>-35.5075</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="L3" t="n">
-        <v>-18.8</v>
+        <v>-27.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4592,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.8</v>
+        <v>85.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.34</v>
+        <v>-1.27</v>
       </c>
       <c r="F4" t="n">
-        <v>34.16</v>
+        <v>20.87</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5051</v>
+        <v>6.1449</v>
       </c>
       <c r="I4" t="n">
-        <v>85.2</v>
+        <v>79</v>
       </c>
       <c r="J4" t="n">
-        <v>91.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6</v>
+        <v>7.78</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>29.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4644,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60.8</v>
+        <v>60.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.65</v>
+        <v>-0.66</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.94</v>
+        <v>-10.12</v>
       </c>
       <c r="G5" t="n">
-        <v>38.19</v>
+        <v>46.83</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5868</v>
+        <v>-1.9115</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="J5" t="n">
-        <v>20.9</v>
+        <v>16.3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.69</v>
+        <v>5.37</v>
       </c>
       <c r="L5" t="n">
-        <v>-55.5</v>
+        <v>-61.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4696,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>221.5</v>
+        <v>242.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.7</v>
+        <v>9.48</v>
       </c>
       <c r="F6" t="n">
-        <v>23.06</v>
+        <v>29.68</v>
       </c>
       <c r="G6" t="n">
-        <v>39.51</v>
+        <v>55.76</v>
       </c>
       <c r="H6" t="n">
-        <v>10.671</v>
+        <v>11.6842</v>
       </c>
       <c r="I6" t="n">
-        <v>53.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>8.77</v>
+        <v>8.01</v>
       </c>
       <c r="L6" t="n">
-        <v>70.3</v>
+        <v>129.1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4748,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.45</v>
+        <v>-0.51</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.66</v>
+        <v>-14.66</v>
       </c>
       <c r="G7" t="n">
-        <v>26.43</v>
+        <v>31.36</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.4863</v>
+        <v>-6.4918</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>10.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.79</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.4</v>
+        <v>-28.9</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>251</v>
+        <v>254.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.95</v>
+        <v>1.39</v>
       </c>
       <c r="F2" t="n">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.274</v>
+        <v>3.491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>242.5</v>
+        <v>2475</v>
       </c>
       <c r="E3" t="n">
-        <v>9.48</v>
+        <v>-1.2</v>
       </c>
       <c r="F3" t="n">
-        <v>229</v>
+        <v>120</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.024</v>
+        <v>5.931</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>313.5</v>
+        <v>1550</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.654</v>
+        <v>19.798</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>216.5</v>
+        <v>48.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.91</v>
+        <v>4.18</v>
       </c>
       <c r="F5" t="n">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20.587</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>39.15</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.79</v>
+        <v>0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.151</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1685</v>
+        <v>98.2</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.39</v>
+        <v>-1.31</v>
       </c>
       <c r="F7" t="n">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12.809</v>
+        <v>18.788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85.7</v>
+        <v>226.5</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.27</v>
+        <v>4.62</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.058</v>
+        <v>21.578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62.7</v>
+        <v>1845</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.26</v>
+        <v>1.93</v>
       </c>
       <c r="F9" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,101 +742,101 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>18.061</v>
+        <v>75.215</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2535</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5</v>
+        <v>3.67</v>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3.004</v>
+        <v>18.538</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>99.5</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.44</v>
+        <v>3.85</v>
       </c>
       <c r="F11" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19.284</v>
+        <v>2.218</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1415</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
-        <v>0.35</v>
+        <v>9.73</v>
       </c>
       <c r="F12" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,101 +844,101 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17.944</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>38.85</v>
+        <v>23.35</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>1.97</v>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.819</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2505</v>
+        <v>128</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.28</v>
+        <v>-0.78</v>
       </c>
       <c r="F14" t="n">
         <v>85</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.93</v>
+        <v>5.164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>129</v>
+        <v>1620</v>
       </c>
       <c r="E15" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.15</v>
+        <v>11.783</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70.8</v>
+        <v>489</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.26</v>
+        <v>1.77</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.989</v>
+        <v>1.847</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>35.3</v>
+        <v>352</v>
       </c>
       <c r="E17" t="n">
-        <v>1.29</v>
+        <v>5.86</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.454</v>
+        <v>7.582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>22.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.55</v>
+        <v>0.85</v>
       </c>
       <c r="F18" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.431</v>
+        <v>1.991</v>
       </c>
     </row>
     <row r="19">
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>278.5</v>
+        <v>288.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.62</v>
+        <v>3.59</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.613</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3110</v>
+        <v>188.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.51</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,67 +1116,67 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.202</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.65</v>
+        <v>203.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.32</v>
+        <v>5.99</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.669</v>
+        <v>2.089</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1620</v>
+        <v>59.1</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.31</v>
+        <v>4.6</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,101 +1184,101 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.856</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>195</v>
+        <v>2785</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14.785</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1810</v>
+        <v>52.8</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>73.788</v>
+        <v>2.481</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.75</v>
+        <v>19.3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="F25" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.895</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>148</v>
+        <v>1725</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.99</v>
+        <v>2.37</v>
       </c>
       <c r="F26" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,67 +1320,67 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.399</v>
+        <v>13.053</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>253</v>
+        <v>3150</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.99</v>
+        <v>1.29</v>
       </c>
       <c r="F27" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.411</v>
+        <v>5.107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56.5</v>
+        <v>157.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.35</v>
+        <v>2.94</v>
       </c>
       <c r="F28" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,30 +1388,30 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5.042</v>
+        <v>3.796</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>115</v>
+        <v>88.8</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.29</v>
+        <v>1.95</v>
       </c>
       <c r="F29" t="n">
         <v>58</v>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.981</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>42.9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.97</v>
+        <v>1.54</v>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.46</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.2</v>
+        <v>200</v>
       </c>
       <c r="E31" t="n">
-        <v>0.79</v>
+        <v>2.56</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,101 +1490,101 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.07</v>
+        <v>14.906</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>386.5</v>
+        <v>126.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.19</v>
+        <v>4.55</v>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8.271000000000001</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>281.5</v>
+        <v>35.65</v>
       </c>
       <c r="E33" t="n">
-        <v>0.54</v>
+        <v>0.99</v>
       </c>
       <c r="F33" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.445</v>
+        <v>1.444</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>431.5</v>
+        <v>18.95</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.27</v>
+        <v>1.07</v>
       </c>
       <c r="F34" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.677</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>370</v>
+        <v>285</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.54</v>
+        <v>1.24</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.555</v>
+        <v>5.453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>121</v>
+        <v>61.5</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.41</v>
+        <v>1.82</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.009</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>42.25</v>
+        <v>266.5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.72</v>
+        <v>9.9</v>
       </c>
       <c r="F37" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.734</v>
+        <v>3.965</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>87.09999999999999</v>
+        <v>27.75</v>
       </c>
       <c r="E38" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="F38" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,169 +1728,169 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.056</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1155</v>
+        <v>118</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.43</v>
+        <v>2.61</v>
       </c>
       <c r="F39" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.327</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>480.5</v>
+        <v>1175</v>
       </c>
       <c r="E40" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.819</v>
+        <v>1.314</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>113</v>
+        <v>405</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="F41" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.351</v>
+        <v>8.561</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>332.5</v>
+        <v>255</v>
       </c>
       <c r="E42" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="F42" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7.452</v>
+        <v>2.413</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="F43" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.029</v>
+        <v>5.321</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>60.4</v>
+        <v>45.65</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.66</v>
+        <v>1.33</v>
       </c>
       <c r="F44" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.191</v>
+        <v>2.226</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>153</v>
+        <v>151.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.65</v>
+        <v>2.36</v>
       </c>
       <c r="F45" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,30 +1966,30 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.864</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>203</v>
+        <v>450</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.49</v>
+        <v>4.29</v>
       </c>
       <c r="F46" t="n">
         <v>31</v>
@@ -2000,30 +2000,30 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5.252</v>
+        <v>1.668</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>45.05</v>
+        <v>377.5</v>
       </c>
       <c r="E47" t="n">
-        <v>0.67</v>
+        <v>2.03</v>
       </c>
       <c r="F47" t="n">
         <v>31</v>
@@ -2034,67 +2034,67 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.235</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>57.1</v>
+        <v>344.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.704</v>
+        <v>7.141</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>52.4</v>
+        <v>59.1</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.76</v>
+        <v>3.5</v>
       </c>
       <c r="F49" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,75 +2102,109 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.536</v>
+        <v>1.699</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>136.5</v>
+        <v>53.7</v>
       </c>
       <c r="E50" t="n">
-        <v>-8.08</v>
+        <v>2.48</v>
       </c>
       <c r="F50" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>19.79</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Macronix (MXIC)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>142</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F51" t="n">
+        <v>17</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Accumulation (Up)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>19.893</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2615</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>萬海</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Wan Hai Lines</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>74</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="F51" t="n">
-        <v>21</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="D52" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>2.189</v>
+      <c r="H52" t="n">
+        <v>2.229</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2246,168 +2280,168 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>32.92</v>
+        <v>33.72</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="G2" t="n">
-        <v>8.271000000000001</v>
+        <v>8.561</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.88</v>
+        <v>33.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.65</v>
+        <v>1.68</v>
       </c>
       <c r="G3" t="n">
-        <v>19.79</v>
+        <v>3.965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29.68</v>
+        <v>26.56</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>4.024</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26.08</v>
+        <v>25.11</v>
       </c>
       <c r="F5" t="n">
-        <v>1.23</v>
+        <v>0.37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.669</v>
+        <v>19.893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>20.87</v>
+        <v>18.93</v>
       </c>
       <c r="F6" t="n">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.058</v>
+        <v>3.491</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.67</v>
+        <v>18.19</v>
       </c>
       <c r="F7" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>3.274</v>
+        <v>2.218</v>
       </c>
     </row>
     <row r="8">
@@ -2432,13 +2466,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.28</v>
+        <v>16.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.004</v>
+        <v>2.853</v>
       </c>
     </row>
     <row r="9">
@@ -2463,13 +2497,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>6.654</v>
+        <v>7.141</v>
       </c>
     </row>
     <row r="10">
@@ -2494,13 +2528,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15.53</v>
+        <v>12.09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="G10" t="n">
-        <v>2.411</v>
+        <v>2.413</v>
       </c>
     </row>
     <row r="11">
@@ -2525,13 +2559,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.43</v>
+        <v>11.91</v>
       </c>
       <c r="F11" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>17.944</v>
+        <v>19.798</v>
       </c>
     </row>
     <row r="12">
@@ -2556,44 +2590,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.69</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>5.252</v>
+        <v>5.321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>2.95</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>5.93</v>
+        <v>1.847</v>
       </c>
     </row>
     <row r="14">
@@ -2618,60 +2652,60 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.68</v>
+        <v>2.43</v>
       </c>
       <c r="F14" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.009</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3.07</v>
+        <v>1.12</v>
       </c>
       <c r="F15" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
       <c r="G15" t="n">
-        <v>1.704</v>
+        <v>1.668</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2680,370 +2714,370 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.53</v>
+        <v>0.85</v>
       </c>
       <c r="F16" t="n">
-        <v>0.86</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>1.677</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.32</v>
+        <v>0.35</v>
       </c>
       <c r="F17" t="n">
-        <v>1.88</v>
+        <v>0.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.981</v>
+        <v>5.453</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.31</v>
+        <v>0.33</v>
       </c>
       <c r="G18" t="n">
-        <v>1.819</v>
+        <v>1.699</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.39</v>
+        <v>-0.26</v>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>5.15</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.71</v>
+        <v>-1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>5.445</v>
+        <v>5.931</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-2.12</v>
+        <v>-1.86</v>
       </c>
       <c r="F21" t="n">
-        <v>1.56</v>
+        <v>0.84</v>
       </c>
       <c r="G21" t="n">
-        <v>1.555</v>
+        <v>2.481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-3.01</v>
+        <v>-1.95</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="G22" t="n">
-        <v>2.189</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-3.53</v>
+        <v>-2.29</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="G23" t="n">
-        <v>2.46</v>
+        <v>5.164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-4.15</v>
+        <v>-2.91</v>
       </c>
       <c r="F24" t="n">
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="G24" t="n">
-        <v>1.327</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-4.25</v>
+        <v>-3.94</v>
       </c>
       <c r="F25" t="n">
-        <v>0.82</v>
+        <v>0.41</v>
       </c>
       <c r="G25" t="n">
-        <v>2.235</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-4.43</v>
+        <v>-4.04</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="G26" t="n">
-        <v>73.788</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-4.73</v>
+        <v>-4.56</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="G27" t="n">
-        <v>7.452</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3052,106 +3086,106 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-5.13</v>
+        <v>-5.63</v>
       </c>
       <c r="F28" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="G28" t="n">
-        <v>0.819</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-5.57</v>
+        <v>-5.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="G29" t="n">
-        <v>0.431</v>
+        <v>75.215</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-5.59</v>
+        <v>-6.07</v>
       </c>
       <c r="F30" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="G30" t="n">
-        <v>3.536</v>
+        <v>2.226</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-5.8</v>
+        <v>-6.18</v>
       </c>
       <c r="F31" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="G31" t="n">
-        <v>0.734</v>
+        <v>1.444</v>
       </c>
     </row>
     <row r="32">
@@ -3176,602 +3210,633 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-6.11</v>
+        <v>-6.76</v>
       </c>
       <c r="F32" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G32" t="n">
-        <v>1.07</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-6.42</v>
+        <v>-7.11</v>
       </c>
       <c r="F33" t="n">
-        <v>1.42</v>
+        <v>0.62</v>
       </c>
       <c r="G33" t="n">
-        <v>18.061</v>
+        <v>1.314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-6.61</v>
+        <v>-7.73</v>
       </c>
       <c r="F34" t="n">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="G34" t="n">
-        <v>5.202</v>
+        <v>7.582</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-7.11</v>
+        <v>-8.16</v>
       </c>
       <c r="F35" t="n">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>1.454</v>
+        <v>5.107</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-8.99</v>
+        <v>-8.42</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="G36" t="n">
-        <v>2.056</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-9.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="G37" t="n">
-        <v>2.351</v>
+        <v>1.991</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9.75</v>
+        <v>-9.01</v>
       </c>
       <c r="F38" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="G38" t="n">
-        <v>11.856</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-10.12</v>
+        <v>-9.82</v>
       </c>
       <c r="F39" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.191</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-11.06</v>
+        <v>-11.03</v>
       </c>
       <c r="F40" t="n">
-        <v>0.85</v>
+        <v>0.59</v>
       </c>
       <c r="G40" t="n">
-        <v>1.989</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-11.11</v>
+        <v>-11.23</v>
       </c>
       <c r="F41" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="G41" t="n">
-        <v>0.399</v>
+        <v>11.783</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-11.58</v>
+        <v>-11.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.78</v>
+        <v>1.23</v>
       </c>
       <c r="G42" t="n">
-        <v>5.042</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-12.01</v>
+        <v>-11.8</v>
       </c>
       <c r="F43" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="G43" t="n">
-        <v>5.613</v>
+        <v>18.538</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-12.47</v>
+        <v>-12.44</v>
       </c>
       <c r="F44" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>12.809</v>
+        <v>4.895</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-13.48</v>
+        <v>-13.79</v>
       </c>
       <c r="F45" t="n">
-        <v>1.23</v>
+        <v>0.91</v>
       </c>
       <c r="G45" t="n">
-        <v>19.284</v>
+        <v>14.906</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-14.58</v>
+        <v>-15.98</v>
       </c>
       <c r="F46" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G46" t="n">
-        <v>0.895</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-14.66</v>
+        <v>-16.41</v>
       </c>
       <c r="F47" t="n">
-        <v>0.98</v>
+        <v>1.89</v>
       </c>
       <c r="G47" t="n">
-        <v>14.785</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-17.07</v>
+        <v>-16.67</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="G48" t="n">
-        <v>3.864</v>
+        <v>13.053</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-17.44</v>
+        <v>-18.6</v>
       </c>
       <c r="F49" t="n">
-        <v>1.94</v>
+        <v>0.55</v>
       </c>
       <c r="G49" t="n">
-        <v>0.151</v>
+        <v>3.796</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-22.89</v>
+        <v>-19.51</v>
       </c>
       <c r="F50" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="G50" t="n">
-        <v>2.029</v>
+        <v>18.788</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PTI (Powertech)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Memory - Packaging</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-20.97</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.089</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2408</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>南亞科</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Nanya Technology</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Memory - DRAM</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>-25.09</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G51" t="n">
-        <v>20.587</v>
+      <c r="E52" t="n">
+        <v>-23.99</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G52" t="n">
+        <v>21.578</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3818,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.88</v>
+        <v>26.56</v>
       </c>
       <c r="C2" t="n">
-        <v>0.65</v>
+        <v>1.17</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79</v>
+        <v>0.717</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3837,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.08</v>
+        <v>25.11</v>
       </c>
       <c r="C3" t="n">
-        <v>1.23</v>
+        <v>0.37</v>
       </c>
       <c r="D3" t="n">
-        <v>0.669</v>
+        <v>19.893</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3860,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.04</v>
+        <v>21.58</v>
       </c>
       <c r="C4" t="n">
-        <v>1.413333333333333</v>
+        <v>1.32</v>
       </c>
       <c r="D4" t="n">
-        <v>13.956</v>
+        <v>14.465</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3879,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.08666666666667</v>
+        <v>17.16</v>
       </c>
       <c r="C5" t="n">
-        <v>1.416666666666667</v>
+        <v>1.36</v>
       </c>
       <c r="D5" t="n">
-        <v>11.687</v>
+        <v>12.148</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -3898,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.28</v>
+        <v>16.77</v>
       </c>
       <c r="C6" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="D6" t="n">
-        <v>3.004</v>
+        <v>2.853</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3917,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.880000000000001</v>
+        <v>4.590000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1.18</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>2.457</v>
+        <v>2.611</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3932,169 +3997,169 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.425</v>
+        <v>2.95</v>
       </c>
       <c r="C8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="D8" t="n">
-        <v>2.658</v>
+        <v>1.847</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.95</v>
+        <v>1.313333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1.31</v>
+        <v>0.4966666666666666</v>
       </c>
       <c r="D9" t="n">
-        <v>1.819</v>
+        <v>11.17</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3033333333333331</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>10.977</v>
+        <v>2.667</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4550000000000001</v>
+        <v>-1.95</v>
       </c>
       <c r="C11" t="n">
-        <v>1.195</v>
+        <v>1.49</v>
       </c>
       <c r="D11" t="n">
-        <v>11.132</v>
+        <v>1.549</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.12</v>
+        <v>-3.345000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>1.56</v>
+        <v>0.775</v>
       </c>
       <c r="D12" t="n">
-        <v>1.555</v>
+        <v>23.594</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-4.15</v>
+        <v>-4.58</v>
       </c>
       <c r="C13" t="n">
-        <v>0.71</v>
+        <v>1.155</v>
       </c>
       <c r="D13" t="n">
-        <v>1.327</v>
+        <v>11.038</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-4.25</v>
+        <v>-4.628</v>
       </c>
       <c r="C14" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>2.235</v>
+        <v>7.791</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-4.32</v>
+        <v>-5.0725</v>
       </c>
       <c r="C15" t="n">
-        <v>0.765</v>
+        <v>0.7925</v>
       </c>
       <c r="D15" t="n">
-        <v>21.808</v>
+        <v>26.262</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-4.73</v>
+        <v>-6.07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="D16" t="n">
-        <v>7.452</v>
+        <v>2.226</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4103,36 +4168,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-5.39</v>
+        <v>-6.76</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="D17" t="n">
-        <v>26.114</v>
+        <v>1.051</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-6.11</v>
+        <v>-7.11</v>
       </c>
       <c r="C18" t="n">
-        <v>1.28</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>1.07</v>
+        <v>1.314</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4141,17 +4206,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-6.42</v>
+        <v>-7.73</v>
       </c>
       <c r="C19" t="n">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
-        <v>18.061</v>
+        <v>7.582</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4160,36 +4225,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-6.856</v>
+        <v>-8.42</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9179999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="D20" t="n">
-        <v>7.755</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-8.004999999999999</v>
+        <v>-8.605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79</v>
+        <v>0.735</v>
       </c>
       <c r="D21" t="n">
-        <v>78.83</v>
+        <v>2.302</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4198,36 +4263,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-9.6</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.66</v>
+        <v>0.845</v>
       </c>
       <c r="D22" t="n">
-        <v>2.351</v>
+        <v>80.11</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-9.75</v>
+        <v>-9.82</v>
       </c>
       <c r="C23" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D23" t="n">
-        <v>11.856</v>
+        <v>2.41</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4240,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-9.91</v>
+        <v>-10.485</v>
       </c>
       <c r="C24" t="n">
-        <v>0.675</v>
+        <v>0.55</v>
       </c>
       <c r="D24" t="n">
-        <v>3.733</v>
+        <v>3.788</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -4255,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-10.12</v>
+        <v>-11.23</v>
       </c>
       <c r="C25" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="D25" t="n">
-        <v>0.191</v>
+        <v>11.783</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4274,36 +4339,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-10.845</v>
+        <v>-11.5</v>
       </c>
       <c r="C26" t="n">
-        <v>0.765</v>
+        <v>1.23</v>
       </c>
       <c r="D26" t="n">
-        <v>2.349</v>
+        <v>5.74</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-12.01</v>
+        <v>-11.8</v>
       </c>
       <c r="C27" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="D27" t="n">
-        <v>5.613</v>
+        <v>18.538</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4312,17 +4377,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-12.47</v>
+        <v>-15.98</v>
       </c>
       <c r="C28" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="D28" t="n">
-        <v>12.809</v>
+        <v>0.166</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4331,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-13.48</v>
+        <v>-16.41</v>
       </c>
       <c r="C29" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="D29" t="n">
-        <v>19.284</v>
+        <v>0.155</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4350,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-17.44</v>
+        <v>-16.67</v>
       </c>
       <c r="C30" t="n">
-        <v>1.94</v>
+        <v>0.99</v>
       </c>
       <c r="D30" t="n">
-        <v>0.151</v>
+        <v>13.053</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4369,19 +4434,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Memory - Flash/DRAM</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-19.51</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18.788</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Memory - DRAM</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>-25.09</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="D31" t="n">
-        <v>20.587</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="B32" t="n">
+        <v>-23.99</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D32" t="n">
+        <v>21.578</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4488,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1685</v>
+        <v>1725</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.39</v>
+        <v>2.37</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.47</v>
+        <v>-16.67</v>
       </c>
       <c r="G2" t="n">
-        <v>49.17</v>
+        <v>46.72</v>
       </c>
       <c r="H2" t="n">
-        <v>-37.576</v>
+        <v>-44.7129</v>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>25.8</v>
       </c>
       <c r="J2" t="n">
-        <v>21.3</v>
+        <v>32</v>
       </c>
       <c r="K2" t="n">
-        <v>8.41</v>
+        <v>7.95</v>
       </c>
       <c r="L2" t="n">
-        <v>50.8</v>
+        <v>-39.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4543,28 +4627,28 @@
         <v>1620</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.75</v>
+        <v>-11.23</v>
       </c>
       <c r="G3" t="n">
-        <v>40.57</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
-        <v>-35.5075</v>
+        <v>-39.345</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>15.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.17</v>
+        <v>4.01</v>
       </c>
       <c r="L3" t="n">
-        <v>-27.3</v>
+        <v>-19.7</v>
       </c>
       <c r="M3" t="n">
         <v>0.88</v>
@@ -4592,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>85.7</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.27</v>
+        <v>3.85</v>
       </c>
       <c r="F4" t="n">
-        <v>20.87</v>
+        <v>18.19</v>
       </c>
       <c r="G4" t="n">
-        <v>78.26000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1449</v>
+        <v>6.3345</v>
       </c>
       <c r="I4" t="n">
-        <v>79</v>
+        <v>84.2</v>
       </c>
       <c r="J4" t="n">
-        <v>87.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>7.78</v>
+        <v>7.4</v>
       </c>
       <c r="L4" t="n">
-        <v>29.4</v>
+        <v>-5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4644,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60.4</v>
+        <v>61.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.66</v>
+        <v>1.82</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.12</v>
+        <v>-15.98</v>
       </c>
       <c r="G5" t="n">
-        <v>46.83</v>
+        <v>43.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9115</v>
+        <v>-1.9391</v>
       </c>
       <c r="I5" t="n">
-        <v>21.6</v>
+        <v>29.6</v>
       </c>
       <c r="J5" t="n">
-        <v>16.3</v>
+        <v>29.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.37</v>
+        <v>5.11</v>
       </c>
       <c r="L5" t="n">
-        <v>-61.6</v>
+        <v>-54.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4696,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>242.5</v>
+        <v>266.5</v>
       </c>
       <c r="E6" t="n">
-        <v>9.48</v>
+        <v>9.9</v>
       </c>
       <c r="F6" t="n">
-        <v>29.68</v>
+        <v>33.25</v>
       </c>
       <c r="G6" t="n">
-        <v>55.76</v>
+        <v>65.7</v>
       </c>
       <c r="H6" t="n">
-        <v>11.6842</v>
+        <v>14.1421</v>
       </c>
       <c r="I6" t="n">
-        <v>84.09999999999999</v>
+        <v>110.1</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>8.01</v>
+        <v>6.98</v>
       </c>
       <c r="L6" t="n">
-        <v>129.1</v>
+        <v>-56.9</v>
       </c>
       <c r="M6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4748,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.51</v>
+        <v>2.56</v>
       </c>
       <c r="F7" t="n">
-        <v>-14.66</v>
+        <v>-13.79</v>
       </c>
       <c r="G7" t="n">
-        <v>31.36</v>
+        <v>28.95</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.4918</v>
+        <v>-6.6601</v>
       </c>
       <c r="I7" t="n">
-        <v>10.1</v>
+        <v>21.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="L7" t="n">
-        <v>-28.9</v>
+        <v>-45.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>254.5</v>
+        <v>272</v>
       </c>
       <c r="E2" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>355</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.491</v>
+        <v>4.544</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2475</v>
+        <v>358.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2</v>
+        <v>4.06</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>222</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.931</v>
+        <v>7.557</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1550</v>
+        <v>50.1</v>
       </c>
       <c r="E4" t="n">
-        <v>9.539999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,169 +572,169 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19.798</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>48.6</v>
+        <v>225.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4.18</v>
+        <v>-0.44</v>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>22.774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39.15</v>
+        <v>2925</v>
       </c>
       <c r="E6" t="n">
-        <v>0.77</v>
+        <v>5.03</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.829</v>
+        <v>2.941</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.2</v>
+        <v>392</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.31</v>
+        <v>3.84</v>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18.788</v>
+        <v>1.687</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>226.5</v>
+        <v>19.75</v>
       </c>
       <c r="E8" t="n">
-        <v>4.62</v>
+        <v>2.33</v>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.578</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1845</v>
+        <v>117</v>
       </c>
       <c r="E9" t="n">
-        <v>1.93</v>
+        <v>-5.65</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,169 +742,169 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>75.215</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>65</v>
+        <v>229.5</v>
       </c>
       <c r="E10" t="n">
-        <v>3.67</v>
+        <v>-9.82</v>
       </c>
       <c r="F10" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18.538</v>
+        <v>3.255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>3065</v>
       </c>
       <c r="E11" t="n">
-        <v>3.85</v>
+        <v>-2.7</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.218</v>
+        <v>5.046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>28.55</v>
       </c>
       <c r="E12" t="n">
-        <v>9.73</v>
+        <v>2.88</v>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.41</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.35</v>
+        <v>2540</v>
       </c>
       <c r="E13" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="F13" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.433</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>62.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.78</v>
+        <v>-3.38</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.164</v>
+        <v>17.291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1620</v>
+        <v>95.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.783</v>
+        <v>18.362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>489</v>
+        <v>1590</v>
       </c>
       <c r="E16" t="n">
-        <v>1.77</v>
+        <v>-1.85</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.847</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>352</v>
+        <v>1515</v>
       </c>
       <c r="E17" t="n">
-        <v>5.86</v>
+        <v>-2.26</v>
       </c>
       <c r="F17" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,67 +1014,67 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7.582</v>
+        <v>19.232</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.85</v>
+        <v>-1.01</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.991</v>
+        <v>2.282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>288.5</v>
+        <v>198.5</v>
       </c>
       <c r="E19" t="n">
-        <v>3.59</v>
+        <v>-2.46</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.74</v>
+        <v>2.007</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>188.5</v>
+        <v>39.1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>-0.13</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,67 +1116,67 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.155</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>203.5</v>
+        <v>359</v>
       </c>
       <c r="E21" t="n">
-        <v>5.99</v>
+        <v>1.99</v>
       </c>
       <c r="F21" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.089</v>
+        <v>7.564</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59.1</v>
+        <v>47.45</v>
       </c>
       <c r="E22" t="n">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="F22" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4.895</v>
+        <v>2.158</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2785</v>
+        <v>118.5</v>
       </c>
       <c r="E23" t="n">
-        <v>9.859999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="F23" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,67 +1218,67 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.853</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>52.8</v>
+        <v>151</v>
       </c>
       <c r="E24" t="n">
-        <v>1.54</v>
+        <v>-0.33</v>
       </c>
       <c r="F24" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.481</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19.3</v>
+        <v>288</v>
       </c>
       <c r="E25" t="n">
-        <v>0.52</v>
+        <v>-0.17</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.051</v>
+        <v>5.695</v>
       </c>
     </row>
     <row r="26">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1725</v>
+        <v>1650</v>
       </c>
       <c r="E26" t="n">
-        <v>2.37</v>
+        <v>-4.35</v>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,67 +1320,67 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.053</v>
+        <v>12.025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3150</v>
+        <v>454.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.107</v>
+        <v>1.686</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>157.5</v>
+        <v>125</v>
       </c>
       <c r="E28" t="n">
-        <v>2.94</v>
+        <v>-1.19</v>
       </c>
       <c r="F28" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,67 +1388,67 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3.796</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>88.8</v>
+        <v>23.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.95</v>
+        <v>0.64</v>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.057</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42.9</v>
+        <v>287</v>
       </c>
       <c r="E30" t="n">
-        <v>1.54</v>
+        <v>0.7</v>
       </c>
       <c r="F30" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,67 +1456,67 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.739</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>200</v>
+        <v>42.95</v>
       </c>
       <c r="E31" t="n">
-        <v>2.56</v>
+        <v>0.12</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>14.906</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>126.5</v>
+        <v>127</v>
       </c>
       <c r="E32" t="n">
-        <v>4.55</v>
+        <v>-0.78</v>
       </c>
       <c r="F32" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.042</v>
+        <v>4.727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>35.65</v>
+        <v>154</v>
       </c>
       <c r="E33" t="n">
-        <v>0.99</v>
+        <v>-2.22</v>
       </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.444</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18.95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.07</v>
+        <v>-0.23</v>
       </c>
       <c r="F34" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.858</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>285</v>
+        <v>200.5</v>
       </c>
       <c r="E35" t="n">
-        <v>1.24</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.453</v>
+        <v>13.725</v>
       </c>
     </row>
     <row r="36">
@@ -1646,13 +1646,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>61.5</v>
+        <v>61.1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.82</v>
+        <v>-0.65</v>
       </c>
       <c r="F36" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.166</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>266.5</v>
+        <v>184</v>
       </c>
       <c r="E37" t="n">
-        <v>9.9</v>
+        <v>-2.39</v>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.965</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27.75</v>
+        <v>1840</v>
       </c>
       <c r="E38" t="n">
-        <v>0.73</v>
+        <v>-0.27</v>
       </c>
       <c r="F38" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.1</v>
+        <v>73.18300000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>118</v>
+        <v>489</v>
       </c>
       <c r="E39" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.999</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1175</v>
+        <v>70.8</v>
       </c>
       <c r="E40" t="n">
-        <v>1.73</v>
+        <v>-0.84</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,203 +1796,203 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.314</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>405</v>
+        <v>1180</v>
       </c>
       <c r="E41" t="n">
-        <v>4.79</v>
+        <v>0.43</v>
       </c>
       <c r="F41" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8.561</v>
+        <v>1.257</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>255</v>
+        <v>58.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.79</v>
+        <v>-1.52</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.413</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>206</v>
+        <v>371</v>
       </c>
       <c r="E43" t="n">
-        <v>1.48</v>
+        <v>-8.4</v>
       </c>
       <c r="F43" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5.321</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>45.65</v>
+        <v>35.35</v>
       </c>
       <c r="E44" t="n">
-        <v>1.33</v>
+        <v>-0.84</v>
       </c>
       <c r="F44" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.226</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>151.5</v>
+        <v>53</v>
       </c>
       <c r="E45" t="n">
-        <v>2.36</v>
+        <v>0.38</v>
       </c>
       <c r="F45" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.393</v>
+        <v>2.422</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>450</v>
+        <v>242</v>
       </c>
       <c r="E46" t="n">
-        <v>4.29</v>
+        <v>-5.1</v>
       </c>
       <c r="F46" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.668</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>377.5</v>
+        <v>18.75</v>
       </c>
       <c r="E47" t="n">
-        <v>2.03</v>
+        <v>-1.06</v>
       </c>
       <c r="F47" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,101 +2034,101 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.549</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>344.5</v>
+        <v>58.5</v>
       </c>
       <c r="E48" t="n">
-        <v>9.890000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="F48" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7.141</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>59.1</v>
+        <v>128</v>
       </c>
       <c r="E49" t="n">
-        <v>3.5</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.699</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>53.7</v>
+        <v>203</v>
       </c>
       <c r="E50" t="n">
-        <v>2.48</v>
+        <v>-1.46</v>
       </c>
       <c r="F50" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,41 +2136,41 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.62</v>
+        <v>5.161</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>142</v>
+        <v>52.6</v>
       </c>
       <c r="E51" t="n">
-        <v>4.03</v>
+        <v>-2.05</v>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>19.893</v>
+        <v>3.539</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>75.5</v>
+        <v>74.5</v>
       </c>
       <c r="E52" t="n">
-        <v>2.03</v>
+        <v>-1.32</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.229</v>
+        <v>2.186</v>
       </c>
     </row>
   </sheetData>
@@ -2261,94 +2261,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33.72</v>
+        <v>37.37</v>
       </c>
       <c r="F2" t="n">
-        <v>0.64</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="n">
-        <v>8.561</v>
+        <v>4.544</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33.25</v>
+        <v>31.15</v>
       </c>
       <c r="F3" t="n">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
-        <v>3.965</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26.56</v>
+        <v>28.66</v>
       </c>
       <c r="F4" t="n">
-        <v>1.17</v>
+        <v>0.54</v>
       </c>
       <c r="G4" t="n">
-        <v>0.717</v>
+        <v>7.641</v>
       </c>
     </row>
     <row r="5">
@@ -2373,106 +2373,106 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25.11</v>
+        <v>18.52</v>
       </c>
       <c r="F5" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="G5" t="n">
-        <v>19.893</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.93</v>
+        <v>18.26</v>
       </c>
       <c r="F6" t="n">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="G6" t="n">
-        <v>3.491</v>
+        <v>2.282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.19</v>
+        <v>17.71</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.218</v>
+        <v>2.941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.77</v>
+        <v>12.56</v>
       </c>
       <c r="F8" t="n">
-        <v>1.07</v>
+        <v>0.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2.853</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="9">
@@ -2497,44 +2497,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.8</v>
+        <v>11.34</v>
       </c>
       <c r="F9" t="n">
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>7.141</v>
+        <v>7.557</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.09</v>
+        <v>5.73</v>
       </c>
       <c r="F10" t="n">
-        <v>1.21</v>
+        <v>0.51</v>
       </c>
       <c r="G10" t="n">
-        <v>2.413</v>
+        <v>5.161</v>
       </c>
     </row>
     <row r="11">
@@ -2559,137 +2559,137 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.91</v>
+        <v>5.57</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="G11" t="n">
-        <v>19.798</v>
+        <v>19.232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.140000000000001</v>
+        <v>4.79</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="G12" t="n">
-        <v>5.321</v>
+        <v>3.255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.95</v>
+        <v>3.73</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>1.847</v>
+        <v>1.045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.43</v>
+        <v>3.06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.71</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.042</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="F15" t="n">
-        <v>0.65</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.668</v>
+        <v>1.687</v>
       </c>
     </row>
     <row r="16">
@@ -2717,243 +2717,243 @@
         <v>0.85</v>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>0.76</v>
       </c>
       <c r="G16" t="n">
-        <v>0.999</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>5.453</v>
+        <v>1.686</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="F18" t="n">
-        <v>0.33</v>
+        <v>0.77</v>
       </c>
       <c r="G18" t="n">
-        <v>1.699</v>
+        <v>2.422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.26</v>
+        <v>-1.36</v>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>2.229</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-1</v>
+        <v>-1.88</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>5.931</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-1.86</v>
+        <v>-2.49</v>
       </c>
       <c r="F21" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.481</v>
+        <v>2.186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1.95</v>
+        <v>-3.53</v>
       </c>
       <c r="F22" t="n">
-        <v>1.49</v>
+        <v>0.68</v>
       </c>
       <c r="G22" t="n">
-        <v>1.549</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-2.29</v>
+        <v>-3.58</v>
       </c>
       <c r="F23" t="n">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="n">
-        <v>5.164</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2962,13 +2962,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-2.91</v>
+        <v>-4.63</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>0.433</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="25">
@@ -2993,633 +2993,633 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-3.94</v>
+        <v>-6.57</v>
       </c>
       <c r="F25" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="G25" t="n">
-        <v>3.62</v>
+        <v>3.539</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-4.04</v>
+        <v>-6.85</v>
       </c>
       <c r="F26" t="n">
-        <v>1.09</v>
+        <v>0.76</v>
       </c>
       <c r="G26" t="n">
-        <v>0.829</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-4.56</v>
+        <v>-7.06</v>
       </c>
       <c r="F27" t="n">
-        <v>0.68</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0.739</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-5.63</v>
+        <v>-7.31</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>2.057</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-5.8</v>
+        <v>-7.44</v>
       </c>
       <c r="F29" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>75.215</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-6.07</v>
+        <v>-7.71</v>
       </c>
       <c r="F30" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G30" t="n">
-        <v>2.226</v>
+        <v>7.564</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-6.18</v>
+        <v>-7.93</v>
       </c>
       <c r="F31" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G31" t="n">
-        <v>1.444</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-6.76</v>
+        <v>-7.97</v>
       </c>
       <c r="F32" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="G32" t="n">
-        <v>1.051</v>
+        <v>4.727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-7.11</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="G33" t="n">
-        <v>1.314</v>
+        <v>73.18300000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-7.73</v>
+        <v>-9.85</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="G34" t="n">
-        <v>7.582</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-8.16</v>
+        <v>-10</v>
       </c>
       <c r="F35" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="G35" t="n">
-        <v>5.107</v>
+        <v>5.695</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-8.42</v>
+        <v>-10</v>
       </c>
       <c r="F36" t="n">
-        <v>0.74</v>
+        <v>0.37</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-8.699999999999999</v>
+        <v>-10.27</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="G37" t="n">
-        <v>1.991</v>
+        <v>1.257</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9.01</v>
+        <v>-11.14</v>
       </c>
       <c r="F38" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="G38" t="n">
-        <v>0.393</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-9.82</v>
+        <v>-11.14</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G39" t="n">
-        <v>2.41</v>
+        <v>2.158</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-11.03</v>
+        <v>-11.15</v>
       </c>
       <c r="F40" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
       <c r="G40" t="n">
-        <v>0.858</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-11.23</v>
+        <v>-11.93</v>
       </c>
       <c r="F41" t="n">
-        <v>0.88</v>
+        <v>1.14</v>
       </c>
       <c r="G41" t="n">
-        <v>11.783</v>
+        <v>5.046</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-11.5</v>
+        <v>-13.33</v>
       </c>
       <c r="F42" t="n">
-        <v>1.23</v>
+        <v>0.84</v>
       </c>
       <c r="G42" t="n">
-        <v>5.74</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-11.8</v>
+        <v>-14.29</v>
       </c>
       <c r="F43" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="G43" t="n">
-        <v>18.538</v>
+        <v>12.025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-12.44</v>
+        <v>-14.97</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G44" t="n">
-        <v>4.895</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-13.79</v>
+        <v>-15.4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.91</v>
+        <v>1.62</v>
       </c>
       <c r="G45" t="n">
-        <v>14.906</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="46">
@@ -3644,199 +3644,199 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-15.98</v>
+        <v>-16.64</v>
       </c>
       <c r="F46" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G46" t="n">
-        <v>0.166</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-16.41</v>
+        <v>-18.23</v>
       </c>
       <c r="F47" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="G47" t="n">
-        <v>0.155</v>
+        <v>17.291</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-16.67</v>
+        <v>-18.64</v>
       </c>
       <c r="F48" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="G48" t="n">
-        <v>13.053</v>
+        <v>18.362</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-18.6</v>
+        <v>-18.66</v>
       </c>
       <c r="F49" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="G49" t="n">
-        <v>3.796</v>
+        <v>13.725</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-19.51</v>
+        <v>-19.79</v>
       </c>
       <c r="F50" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="G50" t="n">
-        <v>18.788</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-20.97</v>
+        <v>-21.7</v>
       </c>
       <c r="F51" t="n">
-        <v>0.77</v>
+        <v>1.3</v>
       </c>
       <c r="G51" t="n">
-        <v>2.089</v>
+        <v>22.774</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-23.99</v>
+        <v>-23.06</v>
       </c>
       <c r="F52" t="n">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
       <c r="G52" t="n">
-        <v>21.578</v>
+        <v>2.007</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.56</v>
+        <v>31.15</v>
       </c>
       <c r="C2" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.717</v>
+        <v>0.806</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.11</v>
+        <v>18.52</v>
       </c>
       <c r="C3" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="D3" t="n">
-        <v>19.893</v>
+        <v>16.73</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,20 +3921,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.58</v>
+        <v>17.71</v>
       </c>
       <c r="C4" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="D4" t="n">
-        <v>14.465</v>
+        <v>2.941</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.16</v>
+        <v>17.48</v>
       </c>
       <c r="C5" t="n">
-        <v>1.36</v>
+        <v>1.393333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>12.148</v>
+        <v>13.146</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -3959,20 +3959,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.77</v>
+        <v>15.33666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.853</v>
+        <v>13.134</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.590000000000001</v>
+        <v>4.205000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9850000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>2.611</v>
+        <v>2.669</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="C8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.847</v>
+        <v>1.827</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,20 +4016,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.313333333333333</v>
+        <v>1.29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4966666666666666</v>
+        <v>1.54</v>
       </c>
       <c r="D9" t="n">
-        <v>11.17</v>
+        <v>1.687</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9850000000000001</v>
+        <v>0.645</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D10" t="n">
-        <v>2.667</v>
+        <v>2.711</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -4054,39 +4054,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.95</v>
+        <v>-1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>1.49</v>
+        <v>0.45</v>
       </c>
       <c r="D11" t="n">
-        <v>1.549</v>
+        <v>10.886</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3.345000000000001</v>
+        <v>-3.79</v>
       </c>
       <c r="C12" t="n">
-        <v>0.775</v>
+        <v>0.9039999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>23.594</v>
+        <v>7.57</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-4.58</v>
+        <v>-6.645</v>
       </c>
       <c r="C13" t="n">
-        <v>1.155</v>
+        <v>1.085</v>
       </c>
       <c r="D13" t="n">
-        <v>11.038</v>
+        <v>11.186</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -4111,55 +4111,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-4.628</v>
+        <v>-7.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="D14" t="n">
-        <v>7.791</v>
+        <v>1.048</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-5.0725</v>
+        <v>-7.109999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7925</v>
+        <v>0.795</v>
       </c>
       <c r="D15" t="n">
-        <v>26.262</v>
+        <v>22.826</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-6.07</v>
+        <v>-7.31</v>
       </c>
       <c r="C16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2.226</v>
+        <v>0.102</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-6.76</v>
+        <v>-7.71</v>
       </c>
       <c r="C17" t="n">
-        <v>1.29</v>
+        <v>0.79</v>
       </c>
       <c r="D17" t="n">
-        <v>1.051</v>
+        <v>7.564</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,112 +4187,112 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7.11</v>
+        <v>-8.995000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="D18" t="n">
-        <v>1.314</v>
+        <v>2.225</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-7.73</v>
+        <v>-9.4</v>
       </c>
       <c r="C19" t="n">
-        <v>0.75</v>
+        <v>0.8150000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>7.582</v>
+        <v>24.107</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-8.42</v>
+        <v>-9.77</v>
       </c>
       <c r="C20" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>77.673</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-8.605</v>
+        <v>-10</v>
       </c>
       <c r="C21" t="n">
-        <v>0.735</v>
+        <v>1.16</v>
       </c>
       <c r="D21" t="n">
-        <v>2.302</v>
+        <v>5.695</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-9.119999999999999</v>
+        <v>-10.27</v>
       </c>
       <c r="C22" t="n">
-        <v>0.845</v>
+        <v>0.62</v>
       </c>
       <c r="D22" t="n">
-        <v>80.11</v>
+        <v>1.257</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-9.82</v>
+        <v>-11.14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="D23" t="n">
-        <v>2.41</v>
+        <v>2.158</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,36 +4301,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-10.485</v>
+        <v>-13.33</v>
       </c>
       <c r="C24" t="n">
-        <v>0.55</v>
+        <v>0.84</v>
       </c>
       <c r="D24" t="n">
-        <v>3.788</v>
+        <v>2.21</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-11.23</v>
+        <v>-14.29</v>
       </c>
       <c r="C25" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
       <c r="D25" t="n">
-        <v>11.783</v>
+        <v>12.025</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-11.5</v>
+        <v>-14.97</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23</v>
+        <v>0.9</v>
       </c>
       <c r="D26" t="n">
-        <v>5.74</v>
+        <v>11.5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-11.8</v>
+        <v>-15.4</v>
       </c>
       <c r="C27" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="D27" t="n">
-        <v>18.538</v>
+        <v>0.147</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,36 +4377,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-15.98</v>
+        <v>-16.53</v>
       </c>
       <c r="C28" t="n">
-        <v>0.63</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.166</v>
+        <v>3.477</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-16.41</v>
+        <v>-16.64</v>
       </c>
       <c r="C29" t="n">
-        <v>1.89</v>
+        <v>0.64</v>
       </c>
       <c r="D29" t="n">
-        <v>0.155</v>
+        <v>0.149</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-16.67</v>
+        <v>-18.23</v>
       </c>
       <c r="C30" t="n">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
       <c r="D30" t="n">
-        <v>13.053</v>
+        <v>17.291</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-19.51</v>
+        <v>-18.64</v>
       </c>
       <c r="C31" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="D31" t="n">
-        <v>18.788</v>
+        <v>18.362</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-23.99</v>
+        <v>-21.7</v>
       </c>
       <c r="C32" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="D32" t="n">
-        <v>21.578</v>
+        <v>22.774</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1725</v>
+        <v>1650</v>
       </c>
       <c r="E2" t="n">
-        <v>2.37</v>
+        <v>-4.35</v>
       </c>
       <c r="F2" t="n">
-        <v>-16.67</v>
+        <v>-14.29</v>
       </c>
       <c r="G2" t="n">
-        <v>46.72</v>
+        <v>44.96</v>
       </c>
       <c r="H2" t="n">
-        <v>-44.7129</v>
+        <v>-55.7779</v>
       </c>
       <c r="I2" t="n">
-        <v>25.8</v>
+        <v>13.2</v>
       </c>
       <c r="J2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>7.95</v>
+        <v>8.27</v>
       </c>
       <c r="L2" t="n">
-        <v>-39.9</v>
+        <v>-23.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-1.85</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.23</v>
+        <v>-14.97</v>
       </c>
       <c r="G3" t="n">
-        <v>33.68</v>
+        <v>32.32</v>
       </c>
       <c r="H3" t="n">
-        <v>-39.345</v>
+        <v>-44.2963</v>
       </c>
       <c r="I3" t="n">
-        <v>15.7</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="L3" t="n">
-        <v>-19.7</v>
+        <v>-2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.85</v>
+        <v>-1.01</v>
       </c>
       <c r="F4" t="n">
-        <v>18.19</v>
+        <v>18.26</v>
       </c>
       <c r="G4" t="n">
-        <v>78.75</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3345</v>
+        <v>6.339</v>
       </c>
       <c r="I4" t="n">
-        <v>84.2</v>
+        <v>79</v>
       </c>
       <c r="J4" t="n">
-        <v>99.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>7.4</v>
+        <v>7.73</v>
       </c>
       <c r="L4" t="n">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61.5</v>
+        <v>61.1</v>
       </c>
       <c r="E5" t="n">
-        <v>1.82</v>
+        <v>-0.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.98</v>
+        <v>-16.64</v>
       </c>
       <c r="G5" t="n">
         <v>43.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9391</v>
+        <v>-1.9705</v>
       </c>
       <c r="I5" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="J5" t="n">
-        <v>29.1</v>
+        <v>24.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5.11</v>
+        <v>5.18</v>
       </c>
       <c r="L5" t="n">
-        <v>-54.4</v>
+        <v>-44.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>266.5</v>
+        <v>272</v>
       </c>
       <c r="E6" t="n">
-        <v>9.9</v>
+        <v>2.06</v>
       </c>
       <c r="F6" t="n">
-        <v>33.25</v>
+        <v>37.37</v>
       </c>
       <c r="G6" t="n">
-        <v>65.7</v>
+        <v>67.3</v>
       </c>
       <c r="H6" t="n">
-        <v>14.1421</v>
+        <v>16.3454</v>
       </c>
       <c r="I6" t="n">
-        <v>110.1</v>
+        <v>107.1</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>6.98</v>
+        <v>7.23</v>
       </c>
       <c r="L6" t="n">
-        <v>-56.9</v>
+        <v>255.1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200</v>
+        <v>200.5</v>
       </c>
       <c r="E7" t="n">
-        <v>2.56</v>
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.79</v>
+        <v>-18.66</v>
       </c>
       <c r="G7" t="n">
-        <v>28.95</v>
+        <v>30.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.6601</v>
+        <v>-6.6762</v>
       </c>
       <c r="I7" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>17.9</v>
+        <v>22.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="L7" t="n">
-        <v>-45.1</v>
+        <v>-40.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>272</v>
+        <v>382.5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.06</v>
+        <v>6.69</v>
       </c>
       <c r="F2" t="n">
-        <v>355</v>
+        <v>274</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.544</v>
+        <v>8.393000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>358.5</v>
+        <v>399</v>
       </c>
       <c r="E3" t="n">
-        <v>4.06</v>
+        <v>1.79</v>
       </c>
       <c r="F3" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.557</v>
+        <v>1.782</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50.1</v>
+        <v>270.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3.09</v>
+        <v>-0.55</v>
       </c>
       <c r="F4" t="n">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.806</v>
+        <v>4.682</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>225.5</v>
+        <v>1565</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.44</v>
+        <v>-5.15</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,101 +606,101 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>22.774</v>
+        <v>11.621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2925</v>
+        <v>39.1</v>
       </c>
       <c r="E6" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.941</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>392</v>
+        <v>219.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.84</v>
+        <v>-2.66</v>
       </c>
       <c r="F7" t="n">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.687</v>
+        <v>22.898</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.75</v>
+        <v>2825</v>
       </c>
       <c r="E8" t="n">
-        <v>2.33</v>
+        <v>-3.42</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.048</v>
+        <v>2.849</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>117</v>
+        <v>43.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.65</v>
+        <v>0.35</v>
       </c>
       <c r="F9" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.21</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>229.5</v>
+        <v>120.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.82</v>
+        <v>2.99</v>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3.255</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3065</v>
+        <v>1585</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7</v>
+        <v>-0.31</v>
       </c>
       <c r="F11" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,101 +810,101 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.046</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>28.55</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.88</v>
+        <v>-0.28</v>
       </c>
       <c r="F12" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.102</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2540</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.14</v>
+        <v>2.425</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62.8</v>
+        <v>278.5</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.38</v>
+        <v>-3.3</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.291</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>95.5</v>
+        <v>114.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.24</v>
+        <v>-3.38</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>18.362</v>
+        <v>1.011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1590</v>
+        <v>3040</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.85</v>
+        <v>-0.82</v>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>11.5</v>
+        <v>5.008</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1515</v>
+        <v>353.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.26</v>
+        <v>-1.53</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,101 +1014,101 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19.232</v>
+        <v>7.078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>88.09999999999999</v>
+        <v>150.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.01</v>
+        <v>-0.33</v>
       </c>
       <c r="F18" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.282</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>198.5</v>
+        <v>228.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.46</v>
+        <v>-0.44</v>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.007</v>
+        <v>3.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.13</v>
+        <v>-3.25</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,101 +1116,101 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.828</v>
+        <v>17.662</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>359</v>
+        <v>59.2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.99</v>
+        <v>-5.73</v>
       </c>
       <c r="F21" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.564</v>
+        <v>16.004</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47.45</v>
+        <v>1510</v>
       </c>
       <c r="E22" t="n">
-        <v>3.94</v>
+        <v>-0.33</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.158</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>118.5</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,101 +1218,101 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.025</v>
+        <v>2.247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>151</v>
+        <v>494.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.33</v>
+        <v>1.12</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.387</v>
+        <v>1.801</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.17</v>
+        <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.695</v>
+        <v>4.828</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1650</v>
+        <v>1820</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.35</v>
+        <v>-1.09</v>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,101 +1320,101 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12.025</v>
+        <v>69.69499999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>454.5</v>
+        <v>152</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>-1.3</v>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.686</v>
+        <v>2.918</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>125</v>
+        <v>23.4</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.19</v>
+        <v>-0.43</v>
       </c>
       <c r="F28" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.045</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>23.5</v>
+        <v>2460</v>
       </c>
       <c r="E29" t="n">
-        <v>0.64</v>
+        <v>-3.15</v>
       </c>
       <c r="F29" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.428</v>
+        <v>5.546</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>287</v>
+        <v>87.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7</v>
+        <v>-1.02</v>
       </c>
       <c r="F30" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,67 +1456,67 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.96</v>
+        <v>1.874</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>42.95</v>
+        <v>195</v>
       </c>
       <c r="E31" t="n">
-        <v>0.12</v>
+        <v>-1.76</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.695</v>
+        <v>1.917</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>127</v>
+        <v>27.95</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.78</v>
+        <v>-2.1</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.727</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>154</v>
+        <v>57.8</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.22</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,67 +1558,67 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3.594</v>
+        <v>4.073</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>88.59999999999999</v>
+        <v>35.45</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.23</v>
+        <v>0.28</v>
       </c>
       <c r="F34" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.988</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>200.5</v>
+        <v>18.65</v>
       </c>
       <c r="E35" t="n">
-        <v>0.25</v>
+        <v>-0.53</v>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,41 +1626,41 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>13.725</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>61.1</v>
+        <v>390.5</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.65</v>
+        <v>5.26</v>
       </c>
       <c r="F36" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.149</v>
+        <v>7.913</v>
       </c>
     </row>
     <row r="37">
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>184</v>
+        <v>178.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.39</v>
+        <v>-2.99</v>
       </c>
       <c r="F37" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,67 +1694,67 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.147</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1840</v>
+        <v>48.7</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.27</v>
+        <v>-2.79</v>
       </c>
       <c r="F38" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>73.18300000000001</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>489</v>
+        <v>19.6</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.76</v>
       </c>
       <c r="F39" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.827</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>70.8</v>
+        <v>129.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.84</v>
+        <v>3.6</v>
       </c>
       <c r="F40" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.904</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1180</v>
+        <v>127</v>
       </c>
       <c r="E41" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.257</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58.2</v>
+        <v>447.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.52</v>
+        <v>-1.54</v>
       </c>
       <c r="F42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,132 +1864,132 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>4.49</v>
+        <v>1.614</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>371</v>
+        <v>46.9</v>
       </c>
       <c r="E43" t="n">
-        <v>-8.4</v>
+        <v>-1.16</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7.641</v>
+        <v>2.018</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>35.35</v>
+        <v>199.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.84</v>
+        <v>-0.5</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.411</v>
+        <v>12.765</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>53</v>
+        <v>61.7</v>
       </c>
       <c r="E45" t="n">
-        <v>0.38</v>
+        <v>0.98</v>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.422</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>242</v>
+        <v>56.3</v>
       </c>
       <c r="E46" t="n">
-        <v>-5.1</v>
+        <v>-3.76</v>
       </c>
       <c r="F46" t="n">
         <v>40</v>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2.238</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.75</v>
+        <v>1165</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.06</v>
+        <v>-1.27</v>
       </c>
       <c r="F47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.192</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>58.5</v>
+        <v>201</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.02</v>
+        <v>-0.99</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.47</v>
+        <v>4.955</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E49" t="n">
-        <v>-9.859999999999999</v>
+        <v>-2.34</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>16.73</v>
+        <v>15.734</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.46</v>
+        <v>-2.48</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5.161</v>
+        <v>2.163</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>52.6</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3.539</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>74.5</v>
+        <v>52.4</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.32</v>
+        <v>-0.38</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.186</v>
+        <v>3.479</v>
       </c>
     </row>
   </sheetData>
@@ -2261,187 +2261,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37.37</v>
+        <v>41.35</v>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>0.48</v>
       </c>
       <c r="G2" t="n">
-        <v>4.544</v>
+        <v>7.913</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.15</v>
+        <v>28.01</v>
       </c>
       <c r="F3" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.806</v>
+        <v>2.425</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28.66</v>
+        <v>27.82</v>
       </c>
       <c r="F4" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>7.641</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18.52</v>
+        <v>24.37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>16.73</v>
+        <v>4.682</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18.26</v>
+        <v>13.64</v>
       </c>
       <c r="F6" t="n">
-        <v>1.14</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.282</v>
+        <v>15.734</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.71</v>
+        <v>13.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>2.941</v>
+        <v>8.393000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2466,75 +2466,75 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.56</v>
+        <v>12.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="G8" t="n">
-        <v>2.238</v>
+        <v>2.163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.34</v>
+        <v>11.74</v>
       </c>
       <c r="F9" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="G9" t="n">
-        <v>7.557</v>
+        <v>3.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.73</v>
+        <v>11.66</v>
       </c>
       <c r="F10" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="G10" t="n">
-        <v>5.161</v>
+        <v>2.849</v>
       </c>
     </row>
     <row r="11">
@@ -2559,106 +2559,106 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.57</v>
+        <v>5.59</v>
       </c>
       <c r="F11" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>19.232</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.79</v>
+        <v>5.28</v>
       </c>
       <c r="F12" t="n">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="G12" t="n">
-        <v>3.255</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3.73</v>
+        <v>2.7</v>
       </c>
       <c r="F13" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1.045</v>
+        <v>1.801</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3.06</v>
+        <v>2.03</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>0.41</v>
       </c>
       <c r="G14" t="n">
-        <v>1.827</v>
+        <v>4.955</v>
       </c>
     </row>
     <row r="15">
@@ -2683,44 +2683,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.687</v>
+        <v>1.782</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.025</v>
+        <v>4.828</v>
       </c>
     </row>
     <row r="17">
@@ -2745,385 +2745,385 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.44</v>
+        <v>-1.65</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="G17" t="n">
-        <v>1.686</v>
+        <v>1.614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-0.93</v>
+        <v>-1.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.77</v>
+        <v>0.25</v>
       </c>
       <c r="G18" t="n">
-        <v>2.422</v>
+        <v>2.191</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-1.36</v>
+        <v>-2.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>6.14</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-1.88</v>
+        <v>-2.97</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.428</v>
+        <v>1.011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-2.49</v>
+        <v>-3.58</v>
       </c>
       <c r="F21" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.186</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-3.53</v>
+        <v>-5.19</v>
       </c>
       <c r="F22" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>4.96</v>
+        <v>2.247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-3.58</v>
+        <v>-5.54</v>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="G23" t="n">
-        <v>0.828</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-4.63</v>
+        <v>-6.62</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="G24" t="n">
-        <v>1.988</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-6.57</v>
+        <v>-6.71</v>
       </c>
       <c r="F25" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="G25" t="n">
-        <v>3.539</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-6.85</v>
+        <v>-6.81</v>
       </c>
       <c r="F26" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="G26" t="n">
-        <v>1.411</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-7.06</v>
+        <v>-6.9</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="G27" t="n">
-        <v>1.048</v>
+        <v>1.874</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-7.31</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="F28" t="n">
         <v>0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.102</v>
+        <v>69.69499999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-7.44</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7</v>
+        <v>0.26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.695</v>
+        <v>3.479</v>
       </c>
     </row>
     <row r="30">
@@ -3148,106 +3148,106 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-7.71</v>
+        <v>-8.77</v>
       </c>
       <c r="F30" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G30" t="n">
-        <v>7.564</v>
+        <v>7.078</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-7.93</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G31" t="n">
-        <v>1.904</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-7.97</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>1.01</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="n">
-        <v>4.727</v>
+        <v>2.018</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-8.390000000000001</v>
+        <v>-9.74</v>
       </c>
       <c r="F33" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="G33" t="n">
-        <v>73.18300000000001</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="34">
@@ -3272,75 +3272,75 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-9.85</v>
+        <v>-10.42</v>
       </c>
       <c r="F34" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.387</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-10</v>
+        <v>-11.19</v>
       </c>
       <c r="F35" t="n">
-        <v>1.16</v>
+        <v>0.55</v>
       </c>
       <c r="G35" t="n">
-        <v>5.695</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-10</v>
+        <v>-11.19</v>
       </c>
       <c r="F36" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="G36" t="n">
-        <v>1.47</v>
+        <v>5.546</v>
       </c>
     </row>
     <row r="37">
@@ -3365,106 +3365,106 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-10.27</v>
+        <v>-11.41</v>
       </c>
       <c r="F37" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G37" t="n">
-        <v>1.257</v>
+        <v>1.192</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-11.14</v>
+        <v>-11.42</v>
       </c>
       <c r="F38" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.746</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-11.14</v>
+        <v>-11.62</v>
       </c>
       <c r="F39" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
-        <v>2.158</v>
+        <v>4.073</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-11.15</v>
+        <v>-12.14</v>
       </c>
       <c r="F40" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="G40" t="n">
-        <v>4.49</v>
+        <v>2.918</v>
       </c>
     </row>
     <row r="41">
@@ -3489,323 +3489,323 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-11.93</v>
+        <v>-12.89</v>
       </c>
       <c r="F41" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="G41" t="n">
-        <v>5.046</v>
+        <v>5.008</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-13.33</v>
+        <v>-14.83</v>
       </c>
       <c r="F42" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="G42" t="n">
-        <v>2.21</v>
+        <v>5.498</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-14.29</v>
+        <v>-16.51</v>
       </c>
       <c r="F43" t="n">
-        <v>1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>12.025</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-14.97</v>
+        <v>-17.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="G44" t="n">
-        <v>11.5</v>
+        <v>11.621</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-15.4</v>
+        <v>-17.9</v>
       </c>
       <c r="F45" t="n">
-        <v>1.62</v>
+        <v>0.74</v>
       </c>
       <c r="G45" t="n">
-        <v>0.147</v>
+        <v>12.765</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-16.64</v>
+        <v>-18.49</v>
       </c>
       <c r="F46" t="n">
-        <v>0.64</v>
+        <v>1.46</v>
       </c>
       <c r="G46" t="n">
-        <v>0.149</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-18.23</v>
+        <v>-18.51</v>
       </c>
       <c r="F47" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="G47" t="n">
-        <v>17.291</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-18.64</v>
+        <v>-21.26</v>
       </c>
       <c r="F48" t="n">
-        <v>1.13</v>
+        <v>0.39</v>
       </c>
       <c r="G48" t="n">
-        <v>18.362</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-18.66</v>
+        <v>-22.82</v>
       </c>
       <c r="F49" t="n">
-        <v>0.87</v>
+        <v>1.03</v>
       </c>
       <c r="G49" t="n">
-        <v>13.725</v>
+        <v>16.004</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-19.79</v>
+        <v>-23.12</v>
       </c>
       <c r="F50" t="n">
-        <v>0.52</v>
+        <v>1.22</v>
       </c>
       <c r="G50" t="n">
-        <v>3.594</v>
+        <v>22.898</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-21.7</v>
+        <v>-24.18</v>
       </c>
       <c r="F51" t="n">
-        <v>1.3</v>
+        <v>0.95</v>
       </c>
       <c r="G51" t="n">
-        <v>22.774</v>
+        <v>17.662</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-23.06</v>
+        <v>-24.42</v>
       </c>
       <c r="F52" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="G52" t="n">
-        <v>2.007</v>
+        <v>1.917</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.15</v>
+        <v>27.82</v>
       </c>
       <c r="C2" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.806</v>
+        <v>0.797</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,77 +3902,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.52</v>
+        <v>21.82333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.32</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73</v>
+        <v>13.304</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.71</v>
+        <v>14.27333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>1.12</v>
+        <v>1.346666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>2.941</v>
+        <v>14.131</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.48</v>
+        <v>13.64</v>
       </c>
       <c r="C5" t="n">
-        <v>1.393333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>13.146</v>
+        <v>15.734</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.33666666666667</v>
+        <v>11.66</v>
       </c>
       <c r="C6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="D6" t="n">
-        <v>13.134</v>
+        <v>2.849</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.205000000000001</v>
+        <v>8.795000000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="D7" t="n">
-        <v>2.669</v>
+        <v>2.781</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3</v>
+        <v>0.71</v>
       </c>
       <c r="D8" t="n">
-        <v>1.827</v>
+        <v>1.801</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="C9" t="n">
-        <v>1.54</v>
+        <v>1.09</v>
       </c>
       <c r="D9" t="n">
-        <v>1.687</v>
+        <v>1.782</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.645</v>
+        <v>-2.31</v>
       </c>
       <c r="C10" t="n">
-        <v>0.66</v>
+        <v>0.625</v>
       </c>
       <c r="D10" t="n">
-        <v>2.711</v>
+        <v>2.625</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.11</v>
+        <v>-2.793333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.45</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="D11" t="n">
-        <v>10.886</v>
+        <v>10.625</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -4073,93 +4073,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3.79</v>
+        <v>-3.275</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9039999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="D12" t="n">
-        <v>7.57</v>
+        <v>21.588</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-6.645</v>
+        <v>-5.54</v>
       </c>
       <c r="C13" t="n">
-        <v>1.085</v>
+        <v>0.96</v>
       </c>
       <c r="D13" t="n">
-        <v>11.186</v>
+        <v>0.988</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-7.06</v>
+        <v>-5.918</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2</v>
+        <v>0.884</v>
       </c>
       <c r="D14" t="n">
-        <v>1.048</v>
+        <v>7.086</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-7.109999999999999</v>
+        <v>-8.047499999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.795</v>
+        <v>0.74</v>
       </c>
       <c r="D15" t="n">
-        <v>22.826</v>
+        <v>22.775</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-7.31</v>
+        <v>-8.77</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D16" t="n">
-        <v>0.102</v>
+        <v>7.078</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,96 +4168,96 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-7.71</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79</v>
+        <v>0.635</v>
       </c>
       <c r="D17" t="n">
-        <v>7.564</v>
+        <v>2.149</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-8.995000000000001</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="D18" t="n">
-        <v>2.225</v>
+        <v>2.018</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-9.4</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8150000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="D19" t="n">
-        <v>24.107</v>
+        <v>0.098</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.77</v>
+        <v>-9.74</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="D20" t="n">
-        <v>77.673</v>
+        <v>2.306</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-10</v>
+        <v>-10.045</v>
       </c>
       <c r="C21" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="D21" t="n">
-        <v>5.695</v>
+        <v>73.768</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-10.27</v>
+        <v>-11.41</v>
       </c>
       <c r="C22" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="D22" t="n">
-        <v>1.257</v>
+        <v>1.192</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,36 +4282,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-11.14</v>
+        <v>-12.04</v>
       </c>
       <c r="C23" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="D23" t="n">
-        <v>2.158</v>
+        <v>10.554</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-13.33</v>
+        <v>-14.83</v>
       </c>
       <c r="C24" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="D24" t="n">
-        <v>2.21</v>
+        <v>5.498</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-14.29</v>
+        <v>-16.51</v>
       </c>
       <c r="C25" t="n">
-        <v>1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>12.025</v>
+        <v>0.139</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-14.97</v>
+        <v>-17.2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="D26" t="n">
-        <v>11.5</v>
+        <v>11.621</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-15.4</v>
+        <v>-18.49</v>
       </c>
       <c r="C27" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="D27" t="n">
-        <v>0.147</v>
+        <v>0.132</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,36 +4377,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-16.53</v>
+        <v>-18.51</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D28" t="n">
-        <v>3.477</v>
+        <v>10.92</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-16.64</v>
+        <v>-22.82</v>
       </c>
       <c r="C29" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="D29" t="n">
-        <v>0.149</v>
+        <v>16.004</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,36 +4415,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-18.23</v>
+        <v>-22.84</v>
       </c>
       <c r="C30" t="n">
-        <v>1.24</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>17.291</v>
+        <v>3.014</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-18.64</v>
+        <v>-23.12</v>
       </c>
       <c r="C31" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="D31" t="n">
-        <v>18.362</v>
+        <v>22.898</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-21.7</v>
+        <v>-24.18</v>
       </c>
       <c r="C32" t="n">
-        <v>1.3</v>
+        <v>0.95</v>
       </c>
       <c r="D32" t="n">
-        <v>22.774</v>
+        <v>17.662</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1650</v>
+        <v>1565</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.35</v>
+        <v>-5.15</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.29</v>
+        <v>-17.2</v>
       </c>
       <c r="G2" t="n">
-        <v>44.96</v>
+        <v>48.2</v>
       </c>
       <c r="H2" t="n">
-        <v>-55.7779</v>
+        <v>-85.3758</v>
       </c>
       <c r="I2" t="n">
-        <v>13.2</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
       <c r="L2" t="n">
-        <v>-23.5</v>
+        <v>36.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.85</v>
+        <v>-0.31</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.97</v>
+        <v>-18.51</v>
       </c>
       <c r="G3" t="n">
-        <v>32.32</v>
+        <v>40</v>
       </c>
       <c r="H3" t="n">
-        <v>-44.2963</v>
+        <v>-48.6943</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.07</v>
+        <v>3.58</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.01</v>
+        <v>3.75</v>
       </c>
       <c r="F4" t="n">
-        <v>18.26</v>
+        <v>28.01</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>80.22</v>
       </c>
       <c r="H4" t="n">
-        <v>6.339</v>
+        <v>5.477</v>
       </c>
       <c r="I4" t="n">
-        <v>79</v>
+        <v>83.2</v>
       </c>
       <c r="J4" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>7.73</v>
+        <v>7.23</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61.1</v>
+        <v>61.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.65</v>
+        <v>0.98</v>
       </c>
       <c r="F5" t="n">
-        <v>-16.64</v>
+        <v>-16.51</v>
       </c>
       <c r="G5" t="n">
-        <v>43.7</v>
+        <v>56.99</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9705</v>
+        <v>-1.5878</v>
       </c>
       <c r="I5" t="n">
-        <v>28.7</v>
+        <v>33.6</v>
       </c>
       <c r="J5" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5.18</v>
+        <v>4.63</v>
       </c>
       <c r="L5" t="n">
-        <v>-44.3</v>
+        <v>-59.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>272</v>
+        <v>270.5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.06</v>
+        <v>-0.55</v>
       </c>
       <c r="F6" t="n">
-        <v>37.37</v>
+        <v>24.37</v>
       </c>
       <c r="G6" t="n">
-        <v>67.3</v>
+        <v>76.98</v>
       </c>
       <c r="H6" t="n">
-        <v>16.3454</v>
+        <v>17.5996</v>
       </c>
       <c r="I6" t="n">
-        <v>107.1</v>
+        <v>96.8</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="L6" t="n">
-        <v>255.1</v>
+        <v>61.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>200.5</v>
+        <v>199.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-18.66</v>
+        <v>-17.9</v>
       </c>
       <c r="G7" t="n">
-        <v>30.09</v>
+        <v>37.78</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.6762</v>
+        <v>-6.6783</v>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="J7" t="n">
-        <v>22.9</v>
+        <v>18.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.31</v>
+        <v>2.86</v>
       </c>
       <c r="L7" t="n">
-        <v>-40.6</v>
+        <v>-55.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>382.5</v>
+        <v>390.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6.69</v>
+        <v>2.09</v>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,237 +504,237 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.393000000000001</v>
+        <v>8.866</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>399</v>
+        <v>2750</v>
       </c>
       <c r="E3" t="n">
-        <v>1.79</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.782</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>270.5</v>
+        <v>38.65</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.55</v>
+        <v>-1.15</v>
       </c>
       <c r="F4" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.682</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1565</v>
+        <v>23.2</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.15</v>
+        <v>-0.85</v>
       </c>
       <c r="F5" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11.621</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39.1</v>
+        <v>391</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="F6" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.82</v>
+        <v>1.801</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>219.5</v>
+        <v>48.25</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.66</v>
+        <v>2.88</v>
       </c>
       <c r="F7" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22.898</v>
+        <v>2.008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2825</v>
+        <v>19.15</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.42</v>
+        <v>-2.3</v>
       </c>
       <c r="F8" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.849</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43.1</v>
+        <v>92.7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.35</v>
+        <v>1.42</v>
       </c>
       <c r="F9" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.694</v>
+        <v>2.541</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120.5</v>
+        <v>220.5</v>
       </c>
       <c r="E10" t="n">
-        <v>2.99</v>
+        <v>0.46</v>
       </c>
       <c r="F10" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.306</v>
+        <v>23.799</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1585</v>
+        <v>281</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.31</v>
+        <v>-2.77</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.92</v>
+        <v>4.319</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.28</v>
+        <v>-2.08</v>
       </c>
       <c r="F12" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.746</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>91.40000000000001</v>
+        <v>273.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3.75</v>
+        <v>1.11</v>
       </c>
       <c r="F13" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.425</v>
+        <v>4.823</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>278.5</v>
+        <v>179</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.3</v>
+        <v>0.28</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.498</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>114.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.38</v>
+        <v>-0.28</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.011</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3040</v>
+        <v>220.5</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.82</v>
+        <v>-3.5</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.008</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>353.5</v>
+        <v>1510</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.53</v>
+        <v>-4.73</v>
       </c>
       <c r="F17" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7.078</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150.5</v>
+        <v>1780</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.33</v>
+        <v>-2.2</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,67 +1048,67 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.356</v>
+        <v>67.363</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>228.5</v>
+        <v>2310</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.44</v>
+        <v>-6.1</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.228</v>
+        <v>5.176</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>92.40000000000001</v>
+        <v>146.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.25</v>
+        <v>-2.66</v>
       </c>
       <c r="F20" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17.662</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>59.2</v>
+        <v>41.4</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.73</v>
+        <v>-3.94</v>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,101 +1150,101 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>16.004</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1510</v>
+        <v>1110</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.33</v>
+        <v>-4.72</v>
       </c>
       <c r="F22" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>18.67</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>53</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-1.48</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.247</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>494.5</v>
+        <v>1485</v>
       </c>
       <c r="E24" t="n">
-        <v>1.12</v>
+        <v>-1.66</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,101 +1252,101 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.801</v>
+        <v>18.137</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>289</v>
+        <v>1605</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7</v>
+        <v>2.56</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.828</v>
+        <v>12.151</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1820</v>
+        <v>117</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.09</v>
+        <v>-2.9</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>69.69499999999999</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3</v>
+        <v>-1.38</v>
       </c>
       <c r="F27" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,101 +1354,101 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.918</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>23.4</v>
+        <v>111.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.43</v>
+        <v>-2.62</v>
       </c>
       <c r="F28" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.399</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2460</v>
+        <v>272</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.15</v>
+        <v>-2.33</v>
       </c>
       <c r="F29" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.546</v>
+        <v>5.422</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>87.7</v>
+        <v>93</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.02</v>
+        <v>0.65</v>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.874</v>
+        <v>17.761</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>195</v>
+        <v>353.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.917</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.95</v>
+        <v>488</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.1</v>
+        <v>-1.31</v>
       </c>
       <c r="F32" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.098</v>
+        <v>1.771</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>57.8</v>
+        <v>58.1</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.86</v>
       </c>
       <c r="F33" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,135 +1558,135 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.073</v>
+        <v>15.586</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>35.45</v>
+        <v>125.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.28</v>
+        <v>-3.09</v>
       </c>
       <c r="F34" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.363</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.65</v>
+        <v>2685</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.53</v>
+        <v>-4.96</v>
       </c>
       <c r="F35" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.786</v>
+        <v>2.724</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>390.5</v>
+        <v>194</v>
       </c>
       <c r="E36" t="n">
-        <v>5.26</v>
+        <v>-2.76</v>
       </c>
       <c r="F36" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7.913</v>
+        <v>12.135</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>178.5</v>
+        <v>78.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.99</v>
+        <v>4.13</v>
       </c>
       <c r="F37" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,67 +1694,67 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.132</v>
+        <v>2.209</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>48.7</v>
+        <v>61.1</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.79</v>
+        <v>-0.97</v>
       </c>
       <c r="F38" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.797</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>19.6</v>
+        <v>34.65</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.76</v>
+        <v>-2.26</v>
       </c>
       <c r="F39" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.988</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>129.5</v>
+        <v>196</v>
       </c>
       <c r="E40" t="n">
-        <v>3.6</v>
+        <v>0.51</v>
       </c>
       <c r="F40" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.056</v>
+        <v>1.906</v>
       </c>
     </row>
     <row r="41">
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="F41" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.488</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>447.5</v>
+        <v>18.35</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.54</v>
+        <v>-1.61</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.614</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>46.9</v>
+        <v>56.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.16</v>
+        <v>0.36</v>
       </c>
       <c r="F43" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.018</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>199.5</v>
+        <v>47.75</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5</v>
+        <v>-1.95</v>
       </c>
       <c r="F44" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>12.765</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>61.7</v>
+        <v>149.5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.98</v>
+        <v>-1.64</v>
       </c>
       <c r="F45" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.139</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>56.3</v>
+        <v>437</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.76</v>
+        <v>-2.35</v>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,41 +2000,41 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.097</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1165</v>
+        <v>370</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.27</v>
+        <v>-5.25</v>
       </c>
       <c r="F47" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.192</v>
+        <v>7.371</v>
       </c>
     </row>
     <row r="48">
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>201</v>
+        <v>203.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.99</v>
+        <v>1.24</v>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4.955</v>
+        <v>4.613</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>125</v>
+        <v>27.75</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.34</v>
+        <v>-0.72</v>
       </c>
       <c r="F49" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>15.734</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>236</v>
+        <v>53</v>
       </c>
       <c r="E50" t="n">
-        <v>-2.48</v>
+        <v>1.15</v>
       </c>
       <c r="F50" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.163</v>
+        <v>3.354</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>75.09999999999999</v>
+        <v>228</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.39</v>
       </c>
       <c r="F51" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,41 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.191</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>52.4</v>
+        <v>128</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.38</v>
+        <v>2.4</v>
       </c>
       <c r="F52" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.479</v>
+        <v>15.104</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41.35</v>
+        <v>31.18</v>
       </c>
       <c r="F2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="G2" t="n">
-        <v>7.913</v>
+        <v>7.371</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28.01</v>
+        <v>31.12</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.425</v>
+        <v>2.541</v>
       </c>
     </row>
     <row r="4">
@@ -2342,29 +2342,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27.82</v>
+        <v>23.23</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="G4" t="n">
-        <v>0.797</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2373,91 +2373,91 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24.37</v>
+        <v>17.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>4.682</v>
+        <v>8.866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13.64</v>
+        <v>14.44</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>15.734</v>
+        <v>4.823</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.17</v>
+        <v>10.34</v>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>0.28</v>
       </c>
       <c r="G7" t="n">
-        <v>8.393000000000001</v>
+        <v>15.104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2466,75 +2466,75 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.38</v>
+        <v>7.82</v>
       </c>
       <c r="F8" t="n">
-        <v>0.43</v>
+        <v>1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.163</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11.74</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.228</v>
+        <v>2.724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11.66</v>
+        <v>4.35</v>
       </c>
       <c r="F10" t="n">
-        <v>1.15</v>
+        <v>0.39</v>
       </c>
       <c r="G10" t="n">
-        <v>2.849</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="11">
@@ -2559,72 +2559,72 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.59</v>
+        <v>4.21</v>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>18.67</v>
+        <v>18.137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.28</v>
+        <v>2.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="G12" t="n">
-        <v>1.056</v>
+        <v>1.771</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2.7</v>
+        <v>1.16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="G13" t="n">
         <v>1.801</v>
@@ -2633,172 +2633,172 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.03</v>
+        <v>-0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.41</v>
+        <v>0.62</v>
       </c>
       <c r="G14" t="n">
-        <v>4.955</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.53</v>
+        <v>-0.68</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.782</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-0.86</v>
+        <v>-2.13</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="G16" t="n">
-        <v>4.828</v>
+        <v>2.209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1.65</v>
+        <v>-3.1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="G17" t="n">
-        <v>1.614</v>
+        <v>4.613</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-1.7</v>
+        <v>-3.13</v>
       </c>
       <c r="F18" t="n">
-        <v>0.25</v>
+        <v>0.93</v>
       </c>
       <c r="G18" t="n">
-        <v>2.191</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,215 +2807,215 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-2.5</v>
+        <v>-3.53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="G19" t="n">
-        <v>0.399</v>
+        <v>2.137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-2.97</v>
+        <v>-3.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.71</v>
+        <v>1.17</v>
       </c>
       <c r="G20" t="n">
-        <v>1.011</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-3.58</v>
+        <v>-3.88</v>
       </c>
       <c r="F21" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="G21" t="n">
-        <v>0.82</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-5.19</v>
+        <v>-4.55</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="G22" t="n">
-        <v>2.247</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-5.54</v>
+        <v>-4.59</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.988</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-6.62</v>
+        <v>-4.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="G24" t="n">
-        <v>4.488</v>
+        <v>2.008</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-6.71</v>
+        <v>-5.43</v>
       </c>
       <c r="F25" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="G25" t="n">
-        <v>1.363</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3024,137 +3024,137 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-6.81</v>
+        <v>-6.64</v>
       </c>
       <c r="F26" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="G26" t="n">
-        <v>0.694</v>
+        <v>4.319</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-6.9</v>
+        <v>-7.04</v>
       </c>
       <c r="F27" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="G27" t="n">
-        <v>1.874</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-8.470000000000001</v>
+        <v>-7.1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="G28" t="n">
-        <v>69.69499999999999</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-8.710000000000001</v>
+        <v>-7.49</v>
       </c>
       <c r="F29" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="G29" t="n">
-        <v>3.479</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-8.77</v>
+        <v>-7.56</v>
       </c>
       <c r="F30" t="n">
-        <v>0.78</v>
+        <v>0.58</v>
       </c>
       <c r="G30" t="n">
-        <v>7.078</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="31">
@@ -3179,385 +3179,385 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.42</v>
       </c>
       <c r="F31" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.098</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.58</v>
       </c>
       <c r="F32" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="G32" t="n">
-        <v>2.018</v>
+        <v>67.363</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-9.74</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>2.306</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-10.42</v>
+        <v>-9.65</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="G34" t="n">
-        <v>0.356</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-11.19</v>
+        <v>-11.54</v>
       </c>
       <c r="F35" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="G35" t="n">
-        <v>0.786</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-11.19</v>
+        <v>-11.63</v>
       </c>
       <c r="F36" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="G36" t="n">
-        <v>5.546</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-11.41</v>
+        <v>-11.67</v>
       </c>
       <c r="F37" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="G37" t="n">
-        <v>1.192</v>
+        <v>3.354</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-11.42</v>
+        <v>-12.01</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>1.746</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-11.62</v>
+        <v>-12.67</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>4.073</v>
+        <v>5.176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-12.14</v>
+        <v>-13.62</v>
       </c>
       <c r="F40" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="G40" t="n">
-        <v>2.918</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-12.89</v>
+        <v>-13.92</v>
       </c>
       <c r="F41" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>5.008</v>
+        <v>5.422</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-14.83</v>
+        <v>-14.78</v>
       </c>
       <c r="F42" t="n">
-        <v>0.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>5.498</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-16.51</v>
+        <v>-15.76</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="G43" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="44">
@@ -3582,137 +3582,137 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-17.2</v>
+        <v>-16.41</v>
       </c>
       <c r="F44" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="G44" t="n">
-        <v>11.621</v>
+        <v>12.151</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-17.9</v>
+        <v>-16.79</v>
       </c>
       <c r="F45" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="G45" t="n">
-        <v>12.765</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-18.49</v>
+        <v>-18.83</v>
       </c>
       <c r="F46" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="G46" t="n">
-        <v>0.132</v>
+        <v>12.135</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-18.51</v>
+        <v>-20.06</v>
       </c>
       <c r="F47" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="G47" t="n">
-        <v>10.92</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-21.26</v>
+        <v>-20.53</v>
       </c>
       <c r="F48" t="n">
-        <v>0.39</v>
+        <v>0.95</v>
       </c>
       <c r="G48" t="n">
-        <v>1.097</v>
+        <v>10.284</v>
       </c>
     </row>
     <row r="49">
@@ -3737,106 +3737,106 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-22.82</v>
+        <v>-22.33</v>
       </c>
       <c r="F49" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G49" t="n">
-        <v>16.004</v>
+        <v>15.586</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-23.12</v>
+        <v>-22.53</v>
       </c>
       <c r="F50" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
       <c r="G50" t="n">
-        <v>22.898</v>
+        <v>1.906</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-24.18</v>
+        <v>-22.63</v>
       </c>
       <c r="F51" t="n">
-        <v>0.95</v>
+        <v>1.26</v>
       </c>
       <c r="G51" t="n">
-        <v>17.662</v>
+        <v>23.799</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-24.42</v>
+        <v>-24.91</v>
       </c>
       <c r="F52" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="G52" t="n">
-        <v>1.917</v>
+        <v>17.761</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.82</v>
+        <v>23.23</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="D2" t="n">
-        <v>0.797</v>
+        <v>0.788</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.82333333333333</v>
+        <v>14.45</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.7433333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>13.304</v>
+        <v>12.65</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.27333333333333</v>
+        <v>10.61333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>1.346666666666667</v>
+        <v>1.373333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>14.131</v>
+        <v>14.714</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.64</v>
+        <v>10.34</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="D5" t="n">
-        <v>15.734</v>
+        <v>15.104</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,39 +3959,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.66</v>
+        <v>9.555</v>
       </c>
       <c r="C6" t="n">
-        <v>1.15</v>
+        <v>0.885</v>
       </c>
       <c r="D6" t="n">
-        <v>2.849</v>
+        <v>2.889</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.795000000000002</v>
+        <v>5.5</v>
       </c>
       <c r="C7" t="n">
-        <v>0.845</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.781</v>
+        <v>2.724</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D8" t="n">
-        <v>1.801</v>
+        <v>1.771</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="C9" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.782</v>
+        <v>1.801</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.31</v>
+        <v>-2.28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="D10" t="n">
-        <v>2.625</v>
+        <v>2.54</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -4054,55 +4054,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2.793333333333333</v>
+        <v>-3.665</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3066666666666666</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>10.625</v>
+        <v>20.832</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3.275</v>
+        <v>-4.59</v>
       </c>
       <c r="C12" t="n">
-        <v>0.825</v>
+        <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>21.588</v>
+        <v>6.903</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-5.54</v>
+        <v>-4.83</v>
       </c>
       <c r="C13" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="D13" t="n">
-        <v>0.988</v>
+        <v>2.008</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,58 +4111,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-5.918</v>
+        <v>-5.43</v>
       </c>
       <c r="C14" t="n">
-        <v>0.884</v>
+        <v>0.9</v>
       </c>
       <c r="D14" t="n">
-        <v>7.086</v>
+        <v>0.971</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-8.047499999999999</v>
+        <v>-5.45</v>
       </c>
       <c r="C15" t="n">
-        <v>0.74</v>
+        <v>0.884</v>
       </c>
       <c r="D15" t="n">
-        <v>22.775</v>
+        <v>6.966</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-8.77</v>
+        <v>-5.633333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.78</v>
+        <v>0.2933333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>7.078</v>
+        <v>10.176</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-8.949999999999999</v>
+        <v>-6.055</v>
       </c>
       <c r="C17" t="n">
-        <v>0.635</v>
+        <v>0.605</v>
       </c>
       <c r="D17" t="n">
-        <v>2.149</v>
+        <v>1.965</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.42</v>
       </c>
       <c r="C18" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>2.018</v>
+        <v>0.095</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,17 +4206,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.65</v>
       </c>
       <c r="C19" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="D19" t="n">
-        <v>0.098</v>
+        <v>2.204</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,20 +4225,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-9.74</v>
+        <v>-10</v>
       </c>
       <c r="C20" t="n">
-        <v>0.87</v>
+        <v>0.745</v>
       </c>
       <c r="D20" t="n">
-        <v>2.306</v>
+        <v>21.491</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-10.045</v>
+        <v>-10.605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="D21" t="n">
-        <v>73.768</v>
+        <v>71.277</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-11.41</v>
+        <v>-13.62</v>
       </c>
       <c r="C22" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="D22" t="n">
-        <v>1.192</v>
+        <v>1.149</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,36 +4282,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-12.04</v>
+        <v>-13.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D23" t="n">
-        <v>10.554</v>
+        <v>5.422</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-14.83</v>
+        <v>-14.78</v>
       </c>
       <c r="C24" t="n">
-        <v>0.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>5.498</v>
+        <v>0.134</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-16.51</v>
+        <v>-15.76</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D25" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,36 +4339,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-17.2</v>
+        <v>-16.365</v>
       </c>
       <c r="C26" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="D26" t="n">
-        <v>11.621</v>
+        <v>10.003</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-18.49</v>
+        <v>-16.41</v>
       </c>
       <c r="C27" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="D27" t="n">
-        <v>0.132</v>
+        <v>12.151</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,36 +4377,36 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-18.51</v>
+        <v>-19.66</v>
       </c>
       <c r="C28" t="n">
-        <v>0.91</v>
+        <v>0.585</v>
       </c>
       <c r="D28" t="n">
-        <v>10.92</v>
+        <v>2.802</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-22.82</v>
+        <v>-20.53</v>
       </c>
       <c r="C29" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="D29" t="n">
-        <v>16.004</v>
+        <v>10.284</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4415,20 +4415,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-22.84</v>
+        <v>-22.33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="D30" t="n">
-        <v>3.014</v>
+        <v>15.586</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-23.12</v>
+        <v>-22.63</v>
       </c>
       <c r="C31" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="D31" t="n">
-        <v>22.898</v>
+        <v>23.799</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-24.18</v>
+        <v>-24.91</v>
       </c>
       <c r="C32" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="D32" t="n">
-        <v>17.662</v>
+        <v>17.761</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1565</v>
+        <v>1605</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.15</v>
+        <v>2.56</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.2</v>
+        <v>-16.41</v>
       </c>
       <c r="G2" t="n">
-        <v>48.2</v>
+        <v>43.07</v>
       </c>
       <c r="H2" t="n">
-        <v>-85.3758</v>
+        <v>-97.1664</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>15.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="K2" t="n">
-        <v>8.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>36.9</v>
+        <v>-11.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1585</v>
+        <v>1510</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.31</v>
+        <v>-4.73</v>
       </c>
       <c r="F3" t="n">
-        <v>-18.51</v>
+        <v>-20.53</v>
       </c>
       <c r="G3" t="n">
-        <v>40</v>
+        <v>27.59</v>
       </c>
       <c r="H3" t="n">
-        <v>-48.6943</v>
+        <v>-55.6489</v>
       </c>
       <c r="I3" t="n">
-        <v>10.7</v>
+        <v>-7.6</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8</v>
+        <v>6.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3.75</v>
+        <v>1.42</v>
       </c>
       <c r="F4" t="n">
-        <v>28.01</v>
+        <v>31.12</v>
       </c>
       <c r="G4" t="n">
-        <v>80.22</v>
+        <v>77.66</v>
       </c>
       <c r="H4" t="n">
-        <v>5.477</v>
+        <v>5.2527</v>
       </c>
       <c r="I4" t="n">
-        <v>83.2</v>
+        <v>82.5</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.1</v>
+        <v>25.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,31 +4728,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61.7</v>
+        <v>61.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="F5" t="n">
-        <v>-16.51</v>
+        <v>-14.78</v>
       </c>
       <c r="G5" t="n">
-        <v>56.99</v>
+        <v>44.37</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5878</v>
+        <v>-1.3578</v>
       </c>
       <c r="I5" t="n">
-        <v>33.6</v>
+        <v>28.7</v>
       </c>
       <c r="J5" t="n">
-        <v>18.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>4.63</v>
+        <v>4.54</v>
       </c>
       <c r="L5" t="n">
-        <v>-59.1</v>
+        <v>-34.6</v>
       </c>
       <c r="M5" t="n">
         <v>0.5600000000000001</v>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>270.5</v>
+        <v>273.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.55</v>
+        <v>1.11</v>
       </c>
       <c r="F6" t="n">
-        <v>24.37</v>
+        <v>14.44</v>
       </c>
       <c r="G6" t="n">
-        <v>76.98</v>
+        <v>76.47</v>
       </c>
       <c r="H6" t="n">
-        <v>17.5996</v>
+        <v>18.97</v>
       </c>
       <c r="I6" t="n">
-        <v>96.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>7.14</v>
+        <v>7.34</v>
       </c>
       <c r="L6" t="n">
-        <v>61.4</v>
+        <v>11.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199.5</v>
+        <v>194</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5</v>
+        <v>-2.76</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.9</v>
+        <v>-18.83</v>
       </c>
       <c r="G7" t="n">
-        <v>37.78</v>
+        <v>34.34</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.6783</v>
+        <v>-6.8107</v>
       </c>
       <c r="I7" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="J7" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="L7" t="n">
-        <v>-55.4</v>
+        <v>-29.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,95 +476,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>390.5</v>
+        <v>2485</v>
       </c>
       <c r="E2" t="n">
-        <v>2.09</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.866</v>
+        <v>4.713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2750</v>
+        <v>351.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.99</v>
       </c>
       <c r="F3" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.827</v>
+        <v>8.632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.65</v>
+        <v>40.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.15</v>
+        <v>-3.26</v>
       </c>
       <c r="F4" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,203 +572,203 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.845</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.2</v>
+        <v>1490</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.85</v>
+        <v>-1.32</v>
       </c>
       <c r="F5" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.397</v>
+        <v>10.192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>391</v>
+        <v>38.45</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.01</v>
+        <v>-0.52</v>
       </c>
       <c r="F6" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.801</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>48.25</v>
+        <v>1380</v>
       </c>
       <c r="E7" t="n">
-        <v>2.88</v>
+        <v>-7.07</v>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.008</v>
+        <v>16.986</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.15</v>
+        <v>2630</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3</v>
+        <v>-2.05</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.971</v>
+        <v>2.759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.7</v>
+        <v>187.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1.42</v>
+        <v>-3.35</v>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.541</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>220.5</v>
+        <v>140.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.46</v>
+        <v>-6.02</v>
       </c>
       <c r="F10" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>23.799</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>281</v>
+        <v>1500</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.77</v>
+        <v>-6.54</v>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.319</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51.9</v>
+        <v>198.5</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.08</v>
+        <v>-9.98</v>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.137</v>
+        <v>21.993</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>273.5</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1.11</v>
+        <v>-1.31</v>
       </c>
       <c r="F13" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.823</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>179</v>
+        <v>1760</v>
       </c>
       <c r="E14" t="n">
-        <v>0.28</v>
+        <v>-1.12</v>
       </c>
       <c r="F14" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.136</v>
+        <v>67.145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.28</v>
+        <v>-3.01</v>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.749</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>220.5</v>
+        <v>328.5</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.5</v>
+        <v>-7.07</v>
       </c>
       <c r="F16" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.222</v>
+        <v>6.302</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1510</v>
+        <v>246.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.73</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10.284</v>
+        <v>4.432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1780</v>
+        <v>141</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2</v>
+        <v>-3.75</v>
       </c>
       <c r="F18" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>67.363</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2310</v>
+        <v>70.3</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.1</v>
+        <v>-0.14</v>
       </c>
       <c r="F19" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.176</v>
+        <v>1.769</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>146.5</v>
+        <v>2165</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.66</v>
+        <v>-6.28</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.348</v>
+        <v>4.839</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41.4</v>
+        <v>278.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.94</v>
+        <v>-0.89</v>
       </c>
       <c r="F21" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.663</v>
+        <v>4.212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1110</v>
+        <v>23.45</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.72</v>
+        <v>1.08</v>
       </c>
       <c r="F22" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.149</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>86.40000000000001</v>
+        <v>45.9</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.48</v>
+        <v>-4.87</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,135 +1218,135 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.838</v>
+        <v>1.928</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1485</v>
+        <v>56.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.66</v>
+        <v>-0.88</v>
       </c>
       <c r="F24" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>18.137</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1605</v>
+        <v>478</v>
       </c>
       <c r="E25" t="n">
-        <v>2.56</v>
+        <v>-2.05</v>
       </c>
       <c r="F25" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>12.151</v>
+        <v>1.751</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>117</v>
+        <v>122.5</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9</v>
+        <v>-2.39</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.204</v>
+        <v>4.262</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>107.5</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.38</v>
+        <v>-3.59</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3.914</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>111.5</v>
+        <v>17.9</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.62</v>
+        <v>-2.45</v>
       </c>
       <c r="F28" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.007</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>272</v>
+        <v>379.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.33</v>
+        <v>-2.94</v>
       </c>
       <c r="F29" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5.422</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>93</v>
+        <v>51.3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.65</v>
+        <v>-1.16</v>
       </c>
       <c r="F30" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.761</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>353.5</v>
+        <v>261</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-4.04</v>
       </c>
       <c r="F31" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6.903</v>
+        <v>5.299</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>488</v>
+        <v>116</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.31</v>
+        <v>-0.85</v>
       </c>
       <c r="F32" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.771</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>58.1</v>
+        <v>27.2</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.86</v>
+        <v>-1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>15.586</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>125.5</v>
+        <v>187</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.09</v>
+        <v>-4.59</v>
       </c>
       <c r="F34" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.025</v>
+        <v>1.741</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2685</v>
+        <v>199</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.96</v>
+        <v>-9.75</v>
       </c>
       <c r="F35" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.724</v>
+        <v>2.934</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>194</v>
+        <v>53.1</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.76</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>12.135</v>
+        <v>13.807</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>78.2</v>
+        <v>86</v>
       </c>
       <c r="E37" t="n">
-        <v>4.13</v>
+        <v>-0.46</v>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.209</v>
+        <v>1.845</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>61.1</v>
+        <v>33.95</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.97</v>
+        <v>-2.02</v>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.134</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>34.65</v>
+        <v>86.2</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.26</v>
+        <v>-7.01</v>
       </c>
       <c r="F39" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.25</v>
+        <v>2.391</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>196</v>
+        <v>420.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.51</v>
+        <v>-3.78</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.906</v>
+        <v>1.443</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>125.5</v>
+        <v>1065</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.18</v>
+        <v>-4.05</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.374</v>
